--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,31 +56,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-知名度要求
-1.知名度要求：填写要求的下限
-2.需要道具的ID_需要的道具数量；填0表示不需要道具
-3.两个条件需要同时满足</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="H1" authorId="0">
       <text>
         <r>
@@ -99,14 +74,14 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-空：表示该游客不支持道具解锁，仅靠知名度解锁
-填写道具ID后 (如 1970000_1)：表示该游客可以通过使用该道具进行解锁
-2.需要道具的ID_需要的道具数量|......
-3.要完成解锁需要知名度和道具两个条件同时满足</t>
+知名度影响各种品质游客（已解锁）出现在赌场的权重
+知名度参数设置为为0时，与基础刷新权重一样；
+公式：（个人知名度*设置的知名度/参数100+1）*基础刷新权重
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -156,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -170,22 +145,25 @@
     <t>名称备注</t>
   </si>
   <si>
-    <t>基础停留时长</t>
+    <t>无奖励的服务能力</t>
+  </si>
+  <si>
+    <t>服务能力</t>
   </si>
   <si>
     <t>行为模式</t>
   </si>
   <si>
-    <t>知名度要求</t>
-  </si>
-  <si>
-    <t>解锁道具</t>
+    <t>知名度</t>
   </si>
   <si>
     <t>基础刷新权重</t>
   </si>
   <si>
-    <t>曝光时的刷新权重</t>
+    <t>知名度刷新权重</t>
+  </si>
+  <si>
+    <t>概率</t>
   </si>
   <si>
     <t>建筑交互权重</t>
@@ -200,10 +178,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>Map&lt;int{_}int&gt;{|}</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
+    <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>list&lt;int&gt;{_}</t>
@@ -218,21 +193,18 @@
     <t>Tourist</t>
   </si>
   <si>
-    <t>BaseDwellTime</t>
+    <t>BaseServiceCapacity</t>
+  </si>
+  <si>
+    <t>ServiceCapacity</t>
   </si>
   <si>
     <t>awareness</t>
   </si>
   <si>
-    <t>unlockitems</t>
-  </si>
-  <si>
     <t>BaseWeight</t>
   </si>
   <si>
-    <t>RefreshWeights</t>
-  </si>
-  <si>
     <t>InteractionWeight</t>
   </si>
   <si>
@@ -245,10 +217,13 @@
     <t>随机</t>
   </si>
   <si>
-    <t>1990000_1</t>
-  </si>
-  <si>
-    <t>10101_5000|10201_4000|10301_3000|10401_2000|11101_2000|11201_2000|20101_2000|20201_2000|20301_2000|20401_2000|20501_2000|20601_2000|20701_2000|20801_2000|21001_2000</t>
+    <t>1101_5000|1102_4000|1103_3000|1104_2000|1105_2000|1106_2000|1107_2000|1108_2000|1109_2000|1110_2000|1111_2000|1201_2000|1202_2000|1301_2000|1302_2000|1303_2000|1304_2000</t>
+  </si>
+  <si>
+    <t>1401_1402_1403_1404_1405</t>
+  </si>
+  <si>
+    <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
   </si>
   <si>
     <t>普通路人2</t>
@@ -260,9 +235,6 @@
     <t>固定</t>
   </si>
   <si>
-    <t>10301_10201_10901_11101</t>
-  </si>
-  <si>
     <t>精英白领1</t>
   </si>
   <si>
@@ -297,6 +269,51 @@
   </si>
   <si>
     <t>达官显贵3</t>
+  </si>
+  <si>
+    <t>普通路人4</t>
+  </si>
+  <si>
+    <t>普通路人5</t>
+  </si>
+  <si>
+    <t>普通路人6</t>
+  </si>
+  <si>
+    <t>精英白领4</t>
+  </si>
+  <si>
+    <t>精英白领5</t>
+  </si>
+  <si>
+    <t>精英白领6</t>
+  </si>
+  <si>
+    <t>社交名流4</t>
+  </si>
+  <si>
+    <t>社交名流5</t>
+  </si>
+  <si>
+    <t>社交名流6</t>
+  </si>
+  <si>
+    <t>富豪商人4</t>
+  </si>
+  <si>
+    <t>富豪商人5</t>
+  </si>
+  <si>
+    <t>富豪商人6</t>
+  </si>
+  <si>
+    <t>达官显贵4</t>
+  </si>
+  <si>
+    <t>达官显贵5</t>
+  </si>
+  <si>
+    <t>达官显贵6</t>
   </si>
 </sst>
 </file>
@@ -979,7 +996,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1004,11 +1021,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1335,22 +1361,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="4" width="11.75" customWidth="1"/>
-    <col min="5" max="6" width="15.75" customWidth="1"/>
-    <col min="7" max="12" width="18.625" customWidth="1"/>
-    <col min="13" max="13" width="14.75" customWidth="1"/>
-    <col min="15" max="15" width="13.125" customWidth="1"/>
-    <col min="16" max="16" width="17.25" customWidth="1"/>
-    <col min="17" max="17" width="17.625" customWidth="1"/>
-    <col min="18" max="18" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="7" width="15.75" customWidth="1"/>
+    <col min="8" max="9" width="18.625" customWidth="1"/>
+    <col min="10" max="10" width="14.75" customWidth="1"/>
+    <col min="11" max="11" width="10.75" customWidth="1"/>
+    <col min="12" max="13" width="18.625" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="16" max="16" width="13.125" customWidth="1"/>
+    <col min="17" max="17" width="17.25" customWidth="1"/>
+    <col min="18" max="18" width="17.625" customWidth="1"/>
+    <col min="19" max="19" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:18">
+    <row r="1" ht="15.75" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1363,74 +1393,79 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="N1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1">
+        <v>100</v>
+      </c>
+      <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" spans="1:18">
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+    </row>
+    <row r="2" ht="21" customHeight="1" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="9"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:18">
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" ht="15.75" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1441,36 +1476,35 @@
         <v>19</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="9"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:18">
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:19">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -1478,11 +1512,13 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="9"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:18">
+      <c r="M4" s="2"/>
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:19">
       <c r="A5" s="1">
-        <v>101</v>
+        <f>B5*1000+C5</f>
+        <v>1001</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -1491,37 +1527,45 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1">
+        <v>100</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="1">
-        <v>100</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>500</v>
+      </c>
+      <c r="J5" s="1">
+        <f>IF(H5=0,I5,($O$1*H5/100+1)*I5)</f>
+        <v>500</v>
+      </c>
+      <c r="K5" s="11">
+        <f>J5/SUM($J$5:$J$34)</f>
+        <v>0.00330425588157547</v>
+      </c>
+      <c r="L5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="M5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="1">
-        <v>50</v>
-      </c>
-      <c r="J5" s="1">
-        <v>40</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="N5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:18">
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:19">
       <c r="A6" s="1">
-        <v>102</v>
+        <f t="shared" ref="A6:A34" si="0">B6*1000+C6</f>
+        <v>1002</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -1532,35 +1576,41 @@
       <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
         <v>100</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>500</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" ref="J6:J34" si="1">IF(H6=0,I6,($O$1*H6/100+1)*I6)</f>
+        <v>500</v>
+      </c>
+      <c r="K6" s="11">
+        <f t="shared" ref="K6:K34" si="2">J6/SUM($J$5:$J$34)</f>
+        <v>0.00330425588157547</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="M6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="1">
-        <v>50</v>
-      </c>
-      <c r="J6" s="1">
-        <v>40</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8"/>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="N6" s="12"/>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1">
-        <v>103</v>
+        <f t="shared" si="0"/>
+        <v>1003</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -1571,33 +1621,41 @@
       <c r="D7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="3">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1">
         <v>100</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1">
+        <v>500</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K7" s="11">
+        <f t="shared" si="2"/>
+        <v>0.00330425588157547</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="1">
-        <v>50</v>
-      </c>
-      <c r="J7" s="1">
-        <v>40</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="N7" s="12"/>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1">
-        <v>201</v>
+        <f t="shared" si="0"/>
+        <v>2001</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -1606,37 +1664,43 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="1">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1">
         <v>120</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>300</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="K8" s="11">
+        <f t="shared" si="2"/>
+        <v>0.00198255352894528</v>
+      </c>
+      <c r="L8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="M8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="1">
-        <v>50</v>
-      </c>
-      <c r="J8" s="1">
-        <v>40</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1">
-        <v>202</v>
+        <f t="shared" si="0"/>
+        <v>2002</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -1645,37 +1709,43 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="1">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1">
         <v>120</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>300</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="K9" s="11">
+        <f t="shared" si="2"/>
+        <v>0.00198255352894528</v>
+      </c>
+      <c r="L9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="M9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="1">
-        <v>50</v>
-      </c>
-      <c r="J9" s="1">
-        <v>40</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1">
-        <v>203</v>
+        <f t="shared" si="0"/>
+        <v>2003</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -1684,35 +1754,43 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1">
+        <v>36</v>
+      </c>
+      <c r="E10" s="3">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1">
         <v>120</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1">
+        <v>300</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="K10" s="11">
+        <f t="shared" si="2"/>
+        <v>0.00198255352894528</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="1">
-        <v>50</v>
-      </c>
-      <c r="J10" s="1">
-        <v>40</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="N10" s="12"/>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1">
-        <v>301</v>
+        <f t="shared" si="0"/>
+        <v>3001</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -1721,37 +1799,43 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="1">
+        <v>37</v>
+      </c>
+      <c r="E11" s="3">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
         <v>150</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>100</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="K11" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000660851176315094</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="M11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="1">
-        <v>50</v>
-      </c>
-      <c r="J11" s="1">
-        <v>40</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="N11" s="12"/>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1">
-        <v>302</v>
+        <f t="shared" si="0"/>
+        <v>3002</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -1760,37 +1844,43 @@
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="1">
+        <v>38</v>
+      </c>
+      <c r="E12" s="3">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1">
         <v>150</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K12" s="11">
+        <f t="shared" si="2"/>
+        <v>6.60851176315094e-5</v>
+      </c>
+      <c r="L12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="M12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="1">
-        <v>50</v>
-      </c>
-      <c r="J12" s="1">
-        <v>40</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1">
-        <v>303</v>
+        <f t="shared" si="0"/>
+        <v>3003</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -1799,35 +1889,43 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="1">
+        <v>39</v>
+      </c>
+      <c r="E13" s="3">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1">
         <v>150</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1">
+        <v>100</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="K13" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000660851176315094</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="1">
-        <v>50</v>
-      </c>
-      <c r="J13" s="1">
-        <v>40</v>
-      </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1">
-        <v>401</v>
+        <f t="shared" si="0"/>
+        <v>4001</v>
       </c>
       <c r="B14" s="1">
         <v>4</v>
@@ -1836,37 +1934,43 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="1">
+        <v>40</v>
+      </c>
+      <c r="E14" s="3">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1">
         <v>180</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>50</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K14" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000330425588157547</v>
+      </c>
+      <c r="L14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="M14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="1">
-        <v>50</v>
-      </c>
-      <c r="J14" s="1">
-        <v>40</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="1">
-        <v>402</v>
+        <f t="shared" si="0"/>
+        <v>4002</v>
       </c>
       <c r="B15" s="1">
         <v>4</v>
@@ -1875,37 +1979,43 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="1">
+        <v>41</v>
+      </c>
+      <c r="E15" s="3">
+        <v>20</v>
+      </c>
+      <c r="F15" s="1">
         <v>180</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>50</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K15" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000330425588157547</v>
+      </c>
+      <c r="L15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="M15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="1">
-        <v>50</v>
-      </c>
-      <c r="J15" s="1">
-        <v>40</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="N15" s="12"/>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1">
-        <v>403</v>
+        <f t="shared" si="0"/>
+        <v>4003</v>
       </c>
       <c r="B16" s="1">
         <v>4</v>
@@ -1914,35 +2024,43 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="1">
+        <v>42</v>
+      </c>
+      <c r="E16" s="3">
+        <v>20</v>
+      </c>
+      <c r="F16" s="1">
         <v>180</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1">
+        <v>50</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K16" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000330425588157547</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="1">
-        <v>50</v>
-      </c>
-      <c r="J16" s="1">
-        <v>40</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="12"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1">
-        <v>501</v>
+        <f t="shared" si="0"/>
+        <v>5001</v>
       </c>
       <c r="B17" s="1">
         <v>5</v>
@@ -1951,37 +2069,43 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="1">
+        <v>43</v>
+      </c>
+      <c r="E17" s="3">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
         <v>200</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>50</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K17" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000330425588157547</v>
+      </c>
+      <c r="L17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="M17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="1">
-        <v>50</v>
-      </c>
-      <c r="J17" s="1">
-        <v>40</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1">
-        <v>502</v>
+        <f t="shared" si="0"/>
+        <v>5002</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
@@ -1990,37 +2114,43 @@
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="1">
+        <v>44</v>
+      </c>
+      <c r="E18" s="3">
+        <v>20</v>
+      </c>
+      <c r="F18" s="1">
         <v>200</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>50</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K18" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000330425588157547</v>
+      </c>
+      <c r="L18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="M18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="1">
-        <v>50</v>
-      </c>
-      <c r="J18" s="1">
-        <v>40</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="8"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="1">
-        <v>503</v>
+        <f t="shared" si="0"/>
+        <v>5003</v>
       </c>
       <c r="B19" s="1">
         <v>5</v>
@@ -2029,719 +2159,828 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="1">
+        <v>45</v>
+      </c>
+      <c r="E19" s="3">
+        <v>20</v>
+      </c>
+      <c r="F19" s="1">
         <v>200</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1">
+        <v>50</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K19" s="11">
+        <f t="shared" si="2"/>
+        <v>0.000330425588157547</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="1">
-        <v>50</v>
-      </c>
-      <c r="J19" s="1">
-        <v>40</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M19" s="8"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1">
-        <v>1001</v>
+        <f t="shared" si="0"/>
+        <v>1004</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="3">
+        <v>20</v>
+      </c>
+      <c r="F20" s="1">
+        <v>100</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="1">
-        <v>100</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="H20" s="1">
+        <v>50</v>
+      </c>
+      <c r="I20" s="1">
+        <v>500</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="1"/>
+        <v>25500</v>
+      </c>
+      <c r="K20" s="11">
+        <f t="shared" si="2"/>
+        <v>0.168517049960349</v>
+      </c>
+      <c r="L20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="1">
-        <v>50</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="M20" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="1">
-        <v>50</v>
-      </c>
-      <c r="J20" s="1">
-        <v>40</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="8"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1">
-        <v>1002</v>
+        <f t="shared" si="0"/>
+        <v>1005</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
       <c r="C21" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="1">
+        <v>47</v>
+      </c>
+      <c r="E21" s="3">
+        <v>20</v>
+      </c>
+      <c r="F21" s="1">
         <v>100</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="1">
+        <v>50</v>
+      </c>
+      <c r="I21" s="1">
+        <v>500</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="1"/>
+        <v>25500</v>
+      </c>
+      <c r="K21" s="11">
+        <f t="shared" si="2"/>
+        <v>0.168517049960349</v>
+      </c>
+      <c r="L21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="1">
-        <v>50</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="M21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I21" s="1">
-        <v>50</v>
-      </c>
-      <c r="J21" s="1">
-        <v>40</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="1">
-        <v>1003</v>
+        <f t="shared" si="0"/>
+        <v>1006</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="1">
+        <v>48</v>
+      </c>
+      <c r="E22" s="3">
+        <v>20</v>
+      </c>
+      <c r="F22" s="1">
         <v>100</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="1">
-        <v>50</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="1">
+        <v>50</v>
+      </c>
+      <c r="I22" s="1">
+        <v>500</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="1"/>
+        <v>25500</v>
+      </c>
+      <c r="K22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.168517049960349</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="1">
-        <v>50</v>
-      </c>
-      <c r="J22" s="1">
-        <v>40</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="1">
-        <v>2001</v>
+        <f t="shared" si="0"/>
+        <v>2004</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="1">
+        <v>49</v>
+      </c>
+      <c r="E23" s="3">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1">
         <v>120</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="1">
+        <v>50</v>
+      </c>
+      <c r="I23" s="1">
+        <v>300</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="1"/>
+        <v>15300</v>
+      </c>
+      <c r="K23" s="11">
+        <f t="shared" si="2"/>
+        <v>0.101110229976209</v>
+      </c>
+      <c r="L23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="1">
-        <v>50</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="M23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="1">
-        <v>50</v>
-      </c>
-      <c r="J23" s="1">
-        <v>40</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="8"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="1">
-        <v>2002</v>
+        <f t="shared" si="0"/>
+        <v>2005</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="1">
+        <v>50</v>
+      </c>
+      <c r="E24" s="3">
+        <v>20</v>
+      </c>
+      <c r="F24" s="1">
         <v>120</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="1">
+        <v>50</v>
+      </c>
+      <c r="I24" s="1">
+        <v>300</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="1"/>
+        <v>15300</v>
+      </c>
+      <c r="K24" s="11">
+        <f t="shared" si="2"/>
+        <v>0.101110229976209</v>
+      </c>
+      <c r="L24" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="1">
-        <v>50</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="M24" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="1">
-        <v>50</v>
-      </c>
-      <c r="J24" s="1">
-        <v>40</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="8"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="1">
-        <v>2003</v>
+        <f t="shared" si="0"/>
+        <v>2006</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="1">
+        <v>51</v>
+      </c>
+      <c r="E25" s="3">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1">
         <v>120</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="1">
-        <v>50</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="1">
+        <v>50</v>
+      </c>
+      <c r="I25" s="1">
+        <v>300</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="1"/>
+        <v>15300</v>
+      </c>
+      <c r="K25" s="11">
+        <f t="shared" si="2"/>
+        <v>0.101110229976209</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M25" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="1">
-        <v>50</v>
-      </c>
-      <c r="J25" s="1">
-        <v>40</v>
-      </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="8"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="1">
-        <v>3001</v>
+        <f t="shared" si="0"/>
+        <v>3004</v>
       </c>
       <c r="B26" s="1">
         <v>3</v>
       </c>
       <c r="C26" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="1">
+        <v>52</v>
+      </c>
+      <c r="E26" s="3">
+        <v>20</v>
+      </c>
+      <c r="F26" s="1">
         <v>150</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="1">
+        <v>50</v>
+      </c>
+      <c r="I26" s="1">
+        <v>100</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="1"/>
+        <v>5100</v>
+      </c>
+      <c r="K26" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0337034099920698</v>
+      </c>
+      <c r="L26" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="1">
-        <v>50</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="M26" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="1">
-        <v>50</v>
-      </c>
-      <c r="J26" s="1">
-        <v>40</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="8"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="1">
-        <v>3002</v>
+        <f t="shared" si="0"/>
+        <v>3005</v>
       </c>
       <c r="B27" s="1">
         <v>3</v>
       </c>
       <c r="C27" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="1">
+        <v>53</v>
+      </c>
+      <c r="E27" s="3">
+        <v>20</v>
+      </c>
+      <c r="F27" s="1">
         <v>150</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="1">
+        <v>50</v>
+      </c>
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K27" s="11">
+        <f t="shared" si="2"/>
+        <v>0.00337034099920698</v>
+      </c>
+      <c r="L27" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="1">
-        <v>50</v>
-      </c>
-      <c r="H27" s="1" t="s">
+      <c r="M27" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="1">
-        <v>50</v>
-      </c>
-      <c r="J27" s="1">
-        <v>40</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="8"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="1">
-        <v>3003</v>
+        <f t="shared" si="0"/>
+        <v>3006</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
       <c r="C28" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="1">
+        <v>54</v>
+      </c>
+      <c r="E28" s="3">
+        <v>20</v>
+      </c>
+      <c r="F28" s="1">
         <v>150</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="1">
-        <v>50</v>
-      </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="1">
+        <v>50</v>
+      </c>
+      <c r="I28" s="1">
+        <v>100</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="1"/>
+        <v>5100</v>
+      </c>
+      <c r="K28" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0337034099920698</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="1">
-        <v>50</v>
-      </c>
-      <c r="J28" s="1">
-        <v>40</v>
-      </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="8"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="1">
-        <v>4001</v>
+        <f t="shared" si="0"/>
+        <v>4004</v>
       </c>
       <c r="B29" s="1">
         <v>4</v>
       </c>
       <c r="C29" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="1">
+        <v>55</v>
+      </c>
+      <c r="E29" s="3">
+        <v>20</v>
+      </c>
+      <c r="F29" s="1">
         <v>180</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="1">
+        <v>50</v>
+      </c>
+      <c r="I29" s="1">
+        <v>50</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="K29" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0168517049960349</v>
+      </c>
+      <c r="L29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="1">
-        <v>50</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="M29" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="1">
-        <v>50</v>
-      </c>
-      <c r="J29" s="1">
-        <v>40</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="8"/>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="1">
-        <v>4002</v>
+        <f t="shared" si="0"/>
+        <v>4005</v>
       </c>
       <c r="B30" s="1">
         <v>4</v>
       </c>
       <c r="C30" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="1">
+        <v>56</v>
+      </c>
+      <c r="E30" s="3">
+        <v>20</v>
+      </c>
+      <c r="F30" s="1">
         <v>180</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="1">
+        <v>50</v>
+      </c>
+      <c r="I30" s="1">
+        <v>50</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="K30" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0168517049960349</v>
+      </c>
+      <c r="L30" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="1">
-        <v>50</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="M30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I30" s="1">
-        <v>50</v>
-      </c>
-      <c r="J30" s="1">
-        <v>40</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="8"/>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="12"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="1">
-        <v>4003</v>
+        <f t="shared" si="0"/>
+        <v>4006</v>
       </c>
       <c r="B31" s="1">
         <v>4</v>
       </c>
       <c r="C31" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="1">
+        <v>57</v>
+      </c>
+      <c r="E31" s="3">
+        <v>20</v>
+      </c>
+      <c r="F31" s="1">
         <v>180</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="1">
-        <v>50</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="1">
+        <v>50</v>
+      </c>
+      <c r="I31" s="1">
+        <v>50</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="K31" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0168517049960349</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M31" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I31" s="1">
-        <v>50</v>
-      </c>
-      <c r="J31" s="1">
-        <v>40</v>
-      </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M31" s="8"/>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="1">
-        <v>5001</v>
+        <f t="shared" si="0"/>
+        <v>5004</v>
       </c>
       <c r="B32" s="1">
         <v>5</v>
       </c>
       <c r="C32" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="1">
+        <v>58</v>
+      </c>
+      <c r="E32" s="3">
+        <v>20</v>
+      </c>
+      <c r="F32" s="1">
         <v>200</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="1">
+        <v>50</v>
+      </c>
+      <c r="I32" s="1">
+        <v>50</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="K32" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0168517049960349</v>
+      </c>
+      <c r="L32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G32" s="1">
-        <v>50</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="M32" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I32" s="1">
-        <v>50</v>
-      </c>
-      <c r="J32" s="1">
-        <v>40</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="8"/>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" s="12"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="1">
-        <v>5002</v>
+        <f t="shared" si="0"/>
+        <v>5005</v>
       </c>
       <c r="B33" s="1">
         <v>5</v>
       </c>
       <c r="C33" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="1">
+        <v>59</v>
+      </c>
+      <c r="E33" s="3">
+        <v>20</v>
+      </c>
+      <c r="F33" s="1">
         <v>200</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="1">
+        <v>50</v>
+      </c>
+      <c r="I33" s="1">
+        <v>50</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="K33" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0168517049960349</v>
+      </c>
+      <c r="L33" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="1">
-        <v>50</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="M33" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="1">
-        <v>50</v>
-      </c>
-      <c r="J33" s="1">
-        <v>40</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="8"/>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="12"/>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="1">
-        <v>5003</v>
+        <f t="shared" si="0"/>
+        <v>5006</v>
       </c>
       <c r="B34" s="1">
         <v>5</v>
       </c>
       <c r="C34" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="1">
+        <v>60</v>
+      </c>
+      <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="1">
         <v>200</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G34" s="1">
-        <v>50</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="1">
+        <v>50</v>
+      </c>
+      <c r="I34" s="1">
+        <v>50</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="K34" s="11">
+        <f t="shared" si="2"/>
+        <v>0.0168517049960349</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I34" s="1">
-        <v>50</v>
-      </c>
-      <c r="J34" s="1">
-        <v>40</v>
-      </c>
-      <c r="K34" s="1"/>
-      <c r="L34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M34" s="8"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-    </row>
-    <row r="39" ht="17.25" spans="1:13">
-      <c r="D39" s="11"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-    </row>
-    <row r="49" spans="4:6">
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-    </row>
-    <row r="50" spans="4:6">
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-    </row>
-    <row r="51" spans="4:6">
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-    </row>
-    <row r="52" spans="4:6">
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-    </row>
-    <row r="53" ht="14.25" spans="4:6">
-      <c r="D53" s="12"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-    </row>
-    <row r="54" spans="4:6">
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-    </row>
-    <row r="55" spans="4:6">
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-    </row>
-    <row r="56" spans="4:6">
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-    </row>
-    <row r="57" spans="4:6">
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-    </row>
-    <row r="58" spans="4:6">
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-    </row>
-    <row r="59" spans="4:6">
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-    </row>
-    <row r="60" spans="4:6">
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
+      <c r="N34" s="12"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+    </row>
+    <row r="39" ht="17.25" spans="1:14">
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+    </row>
+    <row r="49" spans="4:7">
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+    </row>
+    <row r="50" spans="4:7">
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+    </row>
+    <row r="51" spans="4:7">
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+    </row>
+    <row r="52" spans="4:7">
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+    </row>
+    <row r="53" ht="14.25" spans="4:7">
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+    </row>
+    <row r="54" spans="4:7">
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+    </row>
+    <row r="55" spans="4:7">
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+    </row>
+    <row r="56" spans="4:7">
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+    </row>
+    <row r="57" spans="4:7">
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+    </row>
+    <row r="58" spans="4:7">
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+    </row>
+    <row r="59" spans="4:7">
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+    </row>
+    <row r="60" spans="4:7">
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="F17:F18 F14:F15 F11:F12 A8:A19 C8:C19 F4:F9 A4:D4 F1 A1:B1 D1:D3 L1:M1 L61:M63 M35:M60 M5:M19 M2:M3 L4:M4" formula="1"/>
+    <ignoredError sqref="M1:N1 M4:N4 G17:G18 G14:G15 G11:G12 C8:C19 G4:G9 A4:D4 G1 A1:B1 D1:D3 M61:N63 N35:N60 N6 N8:N19 N2:N3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -217,7 +217,7 @@
     <t>随机</t>
   </si>
   <si>
-    <t>1101_5000|1102_4000|1103_3000|1104_2000|1105_2000|1106_2000|1107_2000|1108_2000|1109_2000|1110_2000|1111_2000|1201_2000|1202_2000|1301_2000|1302_2000|1303_2000|1304_2000</t>
+    <t>1101_5000|1102_4000|1103_0|1104_0|1105_0|1106_0|1107_0|1108_0|1109_0|1110_0|1111_0|1201_0|1202_0|1301_0|1302_0|1303_0|1304_0</t>
   </si>
   <si>
     <t>1401_1402_1403_1404_1405</t>
@@ -2980,7 +2980,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="M1:N1 M4:N4 G17:G18 G14:G15 G11:G12 C8:C19 G4:G9 A4:D4 G1 A1:B1 D1:D3 M61:N63 N35:N60 N6 N8:N19 N2:N3" formula="1"/>
+    <ignoredError sqref="N2:N3 N8:N19 N6 N35:N60 M61:N63 D1:D3 A1:B1 G1 A4:D4 G4:G9 C8:C19 G11:G12 G14:G15 G17:G18 M4:N4 M1:N1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-读取交互区域表中的ID；该区域中的具体设备随机选择</t>
+读取交互区域表中的ID；该区域中的具体设备随机选择
+注： 先不配置 前端是随机行走观光点的  。服务器在使用~~  </t>
         </r>
       </text>
     </comment>
@@ -131,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -217,10 +218,7 @@
     <t>随机</t>
   </si>
   <si>
-    <t>1101_5000|1102_4000|1103_0|1104_0|1105_0|1106_0|1107_0|1108_0|1109_0|1110_0|1111_0|1201_0|1202_0|1301_0|1302_0|1303_0|1304_0</t>
-  </si>
-  <si>
-    <t>1401_1402_1403_1404_1405</t>
+    <t>1101_5000|1102_4000|1103_0|1104_0|1105_0|1106_0|1107_0|1108_0|1109_0|1110_0|1111_0|1201_0|1202_0</t>
   </si>
   <si>
     <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
@@ -1372,7 +1370,8 @@
     <col min="8" max="9" width="18.625" customWidth="1"/>
     <col min="10" max="10" width="14.75" customWidth="1"/>
     <col min="11" max="11" width="10.75" customWidth="1"/>
-    <col min="12" max="13" width="18.625" customWidth="1"/>
+    <col min="12" max="12" width="23.625" customWidth="1"/>
+    <col min="13" max="13" width="31.875" customWidth="1"/>
     <col min="14" max="14" width="14.75" customWidth="1"/>
     <col min="16" max="16" width="13.125" customWidth="1"/>
     <col min="17" max="17" width="17.25" customWidth="1"/>
@@ -1555,11 +1554,9 @@
       <c r="L5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:19">
@@ -1574,7 +1571,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3">
         <v>20</v>
@@ -1602,9 +1599,7 @@
       <c r="L6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M6" s="12"/>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:19">
@@ -1619,7 +1614,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3">
         <v>20</v>
@@ -1628,7 +1623,7 @@
         <v>100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1647,9 +1642,7 @@
       <c r="L7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M7" s="12"/>
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:19">
@@ -1664,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3">
         <v>20</v>
@@ -1692,9 +1685,7 @@
       <c r="L8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M8" s="12"/>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:19">
@@ -1709,7 +1700,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="3">
         <v>20</v>
@@ -1737,9 +1728,7 @@
       <c r="L9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M9" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M9" s="12"/>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:19">
@@ -1754,7 +1743,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3">
         <v>20</v>
@@ -1763,7 +1752,7 @@
         <v>120</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -1782,9 +1771,7 @@
       <c r="L10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M10" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M10" s="12"/>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:19">
@@ -1799,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3">
         <v>20</v>
@@ -1827,9 +1814,7 @@
       <c r="L11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M11" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M11" s="12"/>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:19">
@@ -1844,7 +1829,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" s="3">
         <v>20</v>
@@ -1872,9 +1857,7 @@
       <c r="L12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M12" s="12"/>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:19">
@@ -1889,7 +1872,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" s="3">
         <v>20</v>
@@ -1898,7 +1881,7 @@
         <v>150</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -1917,9 +1900,7 @@
       <c r="L13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M13" s="12"/>
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:19">
@@ -1934,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="3">
         <v>20</v>
@@ -1962,9 +1943,7 @@
       <c r="L14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M14" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M14" s="12"/>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:19">
@@ -1979,7 +1958,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3">
         <v>20</v>
@@ -2007,9 +1986,7 @@
       <c r="L15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M15" s="12"/>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:19">
@@ -2024,7 +2001,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" s="3">
         <v>20</v>
@@ -2033,7 +2010,7 @@
         <v>180</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -2052,9 +2029,7 @@
       <c r="L16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M16" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M16" s="12"/>
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14">
@@ -2069,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3">
         <v>20</v>
@@ -2097,9 +2072,7 @@
       <c r="L17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M17" s="12"/>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14">
@@ -2114,7 +2087,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="3">
         <v>20</v>
@@ -2142,9 +2115,7 @@
       <c r="L18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M18" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M18" s="12"/>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14">
@@ -2159,7 +2130,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3">
         <v>20</v>
@@ -2168,7 +2139,7 @@
         <v>200</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -2187,9 +2158,7 @@
       <c r="L19" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M19" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M19" s="12"/>
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14">
@@ -2204,7 +2173,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="3">
         <v>20</v>
@@ -2232,9 +2201,7 @@
       <c r="L20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M20" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M20" s="12"/>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14">
@@ -2249,7 +2216,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" s="3">
         <v>20</v>
@@ -2277,9 +2244,7 @@
       <c r="L21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M21" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M21" s="12"/>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14">
@@ -2294,7 +2259,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" s="3">
         <v>20</v>
@@ -2303,7 +2268,7 @@
         <v>100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H22" s="1">
         <v>50</v>
@@ -2322,9 +2287,7 @@
       <c r="L22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M22" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M22" s="12"/>
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14">
@@ -2339,7 +2302,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" s="3">
         <v>20</v>
@@ -2367,9 +2330,7 @@
       <c r="L23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M23" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M23" s="12"/>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14">
@@ -2384,7 +2345,7 @@
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3">
         <v>20</v>
@@ -2412,9 +2373,7 @@
       <c r="L24" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M24" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M24" s="12"/>
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14">
@@ -2429,7 +2388,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3">
         <v>20</v>
@@ -2438,7 +2397,7 @@
         <v>120</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25" s="1">
         <v>50</v>
@@ -2457,9 +2416,7 @@
       <c r="L25" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M25" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M25" s="12"/>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14">
@@ -2474,7 +2431,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" s="3">
         <v>20</v>
@@ -2502,9 +2459,7 @@
       <c r="L26" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M26" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M26" s="12"/>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14">
@@ -2519,7 +2474,7 @@
         <v>5</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" s="3">
         <v>20</v>
@@ -2547,9 +2502,7 @@
       <c r="L27" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M27" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M27" s="12"/>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14">
@@ -2564,7 +2517,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3">
         <v>20</v>
@@ -2573,7 +2526,7 @@
         <v>150</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H28" s="1">
         <v>50</v>
@@ -2592,9 +2545,7 @@
       <c r="L28" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M28" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M28" s="12"/>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14">
@@ -2609,7 +2560,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="3">
         <v>20</v>
@@ -2637,9 +2588,7 @@
       <c r="L29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M29" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M29" s="12"/>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14">
@@ -2654,7 +2603,7 @@
         <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" s="3">
         <v>20</v>
@@ -2682,9 +2631,7 @@
       <c r="L30" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M30" s="12"/>
       <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14">
@@ -2699,7 +2646,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" s="3">
         <v>20</v>
@@ -2708,7 +2655,7 @@
         <v>180</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H31" s="1">
         <v>50</v>
@@ -2727,9 +2674,7 @@
       <c r="L31" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M31" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M31" s="12"/>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14">
@@ -2744,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E32" s="3">
         <v>20</v>
@@ -2772,9 +2717,7 @@
       <c r="L32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M32" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M32" s="12"/>
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14">
@@ -2789,7 +2732,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="3">
         <v>20</v>
@@ -2817,9 +2760,7 @@
       <c r="L33" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M33" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M33" s="12"/>
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14">
@@ -2834,7 +2775,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" s="3">
         <v>20</v>
@@ -2843,7 +2784,7 @@
         <v>200</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H34" s="1">
         <v>50</v>
@@ -2862,9 +2803,7 @@
       <c r="L34" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M34" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="M34" s="12"/>
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14">
@@ -2980,7 +2919,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="N2:N3 N8:N19 N6 N35:N60 M61:N63 D1:D3 A1:B1 G1 A4:D4 G4:G9 C8:C19 G11:G12 G14:G15 G17:G18 M4:N4 M1:N1" formula="1"/>
+    <ignoredError sqref="M1:N1 M4:N4 G17:G18 G14:G15 G11:G12 C8:C19 G4:G9 A4:D4 G1 A1:B1 D1:D3 M61:N63 N35:N60 N6 N8:N19 N2:N3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -33,6 +33,28 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+影响交互次数 = 服务能力 / 繁荣度 </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G1" authorId="0">
       <text>
         <r>
@@ -222,7 +244,7 @@
     <t>随机</t>
   </si>
   <si>
-    <t>1101_3000|1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_2000|1108_2000|1109_2000|1110_1000|1111_1000|1112_1000|1201_0|1202_0</t>
+    <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_2000|1108_2000|1109_2000|1110_1000|1111_1000|1112_1000|1201_0|1202_0</t>
   </si>
   <si>
     <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
@@ -427,7 +449,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,6 +464,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF212529"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF212529"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.5"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
@@ -450,11 +514,12 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FF212529"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FF212529"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -967,173 +1032,200 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1143,10 +1235,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1468,1537 +1560,1537 @@
   <dimension ref="A1:S60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="11.625" customWidth="1"/>
-    <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="11.75" customWidth="1"/>
-    <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="7" width="15.75" customWidth="1"/>
-    <col min="8" max="9" width="18.625" customWidth="1"/>
-    <col min="10" max="10" width="14.75" customWidth="1"/>
-    <col min="11" max="11" width="10.75" customWidth="1"/>
-    <col min="12" max="12" width="23.625" customWidth="1"/>
-    <col min="13" max="13" width="31.875" customWidth="1"/>
-    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="1" max="1" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="22.125" customWidth="1"/>
+    <col min="4" max="4" width="8.375" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
+    <col min="7" max="7" width="8.375" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="12.875" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="6.375" customWidth="1"/>
+    <col min="12" max="12" width="113.816666666667" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="48.375" customWidth="1"/>
     <col min="16" max="16" width="13.125" customWidth="1"/>
     <col min="17" max="17" width="17.25" customWidth="1"/>
     <col min="18" max="18" width="17.625" customWidth="1"/>
     <col min="19" max="19" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:19">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="2" customFormat="1" ht="15.75" spans="1:19">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1">
-        <v>100</v>
-      </c>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" spans="1:19">
-      <c r="A2" s="2" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+    </row>
+    <row r="2" s="3" customFormat="1" ht="21" customHeight="1" spans="1:19">
+      <c r="A2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="14"/>
+      <c r="H2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="11"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:19">
-      <c r="A3" s="2" t="s">
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="15.75" spans="1:19">
+      <c r="A3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="14"/>
+      <c r="H3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3" t="s">
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="11"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="4" ht="15.75" spans="1:19">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="11"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:19">
-      <c r="A5" s="2">
+      <c r="A5" s="17">
         <v>1001</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="19">
         <v>20</v>
       </c>
-      <c r="F5" s="2">
-        <v>100</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="17">
+        <v>450</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="17">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="17">
         <v>500</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="17">
         <f>IF(H5=0,I5,($O$1*H5/100+1)*I5)</f>
         <v>500</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="21">
         <f>J5/SUM($J$5:$J$34)</f>
-        <v>0.00330425588157547</v>
-      </c>
-      <c r="L5" s="13" t="s">
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13" t="s">
+      <c r="M5" s="22"/>
+      <c r="N5" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:19">
-      <c r="A6" s="2">
+      <c r="A6" s="17">
         <v>1002</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="17">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="19">
         <v>20</v>
       </c>
-      <c r="F6" s="2">
-        <v>100</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="17">
+        <v>450</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="17">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="17">
         <v>500</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="17">
         <f t="shared" ref="J6:J34" si="0">IF(H6=0,I6,($O$1*H6/100+1)*I6)</f>
         <v>500</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="21">
         <f t="shared" ref="K6:K34" si="1">J6/SUM($J$5:$J$34)</f>
-        <v>0.00330425588157547</v>
-      </c>
-      <c r="L6" s="13" t="s">
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="2">
+      <c r="A7" s="17">
         <v>1003</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="17">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="19">
         <v>20</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="17">
+        <v>450</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="17">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17">
+        <v>500</v>
+      </c>
+      <c r="J7" s="17">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="K7" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="17">
+        <v>2001</v>
+      </c>
+      <c r="B8" s="17">
+        <v>2</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="19">
+        <v>20</v>
+      </c>
+      <c r="F8" s="17">
+        <v>450</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="17">
+        <v>0</v>
+      </c>
+      <c r="I8" s="17">
+        <v>300</v>
+      </c>
+      <c r="J8" s="17">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="K8" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0515463917525773</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="17">
+        <v>2002</v>
+      </c>
+      <c r="B9" s="17">
+        <v>2</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="19">
+        <v>20</v>
+      </c>
+      <c r="F9" s="17">
+        <v>450</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="17">
+        <v>0</v>
+      </c>
+      <c r="I9" s="17">
+        <v>300</v>
+      </c>
+      <c r="J9" s="17">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="K9" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0515463917525773</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="17">
+        <v>2003</v>
+      </c>
+      <c r="B10" s="17">
+        <v>2</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="19">
+        <v>20</v>
+      </c>
+      <c r="F10" s="17">
+        <v>450</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="17">
+        <v>0</v>
+      </c>
+      <c r="I10" s="17">
+        <v>300</v>
+      </c>
+      <c r="J10" s="17">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="K10" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0515463917525773</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="17">
+        <v>3001</v>
+      </c>
+      <c r="B11" s="17">
+        <v>3</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="19">
+        <v>20</v>
+      </c>
+      <c r="F11" s="17">
+        <v>450</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="17">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17">
         <v>100</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="J11" s="17">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K11" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0171821305841924</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="17">
+        <v>3002</v>
+      </c>
+      <c r="B12" s="17">
+        <v>3</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="19">
+        <v>20</v>
+      </c>
+      <c r="F12" s="17">
+        <v>450</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="17">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17">
+        <v>10</v>
+      </c>
+      <c r="J12" s="17">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="K12" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00171821305841924</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="17">
+        <v>3003</v>
+      </c>
+      <c r="B13" s="17">
+        <v>3</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="19">
+        <v>20</v>
+      </c>
+      <c r="F13" s="17">
+        <v>450</v>
+      </c>
+      <c r="G13" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H13" s="17">
         <v>0</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I13" s="17">
+        <v>100</v>
+      </c>
+      <c r="J13" s="17">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K13" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0171821305841924</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="17">
+        <v>4001</v>
+      </c>
+      <c r="B14" s="17">
+        <v>4</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="19">
+        <v>20</v>
+      </c>
+      <c r="F14" s="17">
+        <v>450</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17">
+        <v>50</v>
+      </c>
+      <c r="J14" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K14" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="17">
+        <v>4002</v>
+      </c>
+      <c r="B15" s="17">
+        <v>4</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="19">
+        <v>20</v>
+      </c>
+      <c r="F15" s="17">
+        <v>450</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17">
+        <v>50</v>
+      </c>
+      <c r="J15" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K15" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="17">
+        <v>4003</v>
+      </c>
+      <c r="B16" s="17">
+        <v>4</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="19">
+        <v>20</v>
+      </c>
+      <c r="F16" s="17">
+        <v>450</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>50</v>
+      </c>
+      <c r="J16" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K16" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="17">
+        <v>5001</v>
+      </c>
+      <c r="B17" s="17">
+        <v>5</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="19">
+        <v>20</v>
+      </c>
+      <c r="F17" s="17">
+        <v>450</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="17">
+        <v>50</v>
+      </c>
+      <c r="J17" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K17" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="17">
+        <v>5002</v>
+      </c>
+      <c r="B18" s="17">
+        <v>5</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="19">
+        <v>20</v>
+      </c>
+      <c r="F18" s="17">
+        <v>450</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0</v>
+      </c>
+      <c r="I18" s="17">
+        <v>50</v>
+      </c>
+      <c r="J18" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K18" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="17">
+        <v>5003</v>
+      </c>
+      <c r="B19" s="17">
+        <v>5</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="19">
+        <v>20</v>
+      </c>
+      <c r="F19" s="17">
+        <v>450</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0</v>
+      </c>
+      <c r="I19" s="17">
+        <v>50</v>
+      </c>
+      <c r="J19" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K19" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="17">
+        <v>1004</v>
+      </c>
+      <c r="B20" s="17">
+        <v>1</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="19">
+        <v>20</v>
+      </c>
+      <c r="F20" s="17">
+        <v>450</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="17">
+        <v>50</v>
+      </c>
+      <c r="I20" s="17">
         <v>500</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J20" s="17">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K7" s="12">
-        <f t="shared" si="1"/>
-        <v>0.00330425588157547</v>
-      </c>
-      <c r="L7" s="13" t="s">
+      <c r="K20" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="L20" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="17">
+        <v>1005</v>
+      </c>
+      <c r="B21" s="17">
+        <v>1</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="19">
+        <v>20</v>
+      </c>
+      <c r="F21" s="17">
+        <v>450</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="17">
+        <v>50</v>
+      </c>
+      <c r="I21" s="17">
+        <v>500</v>
+      </c>
+      <c r="J21" s="17">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="K21" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="17">
+        <v>1006</v>
+      </c>
+      <c r="B22" s="17">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="19">
+        <v>20</v>
+      </c>
+      <c r="F22" s="17">
+        <v>450</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="17">
+        <v>50</v>
+      </c>
+      <c r="I22" s="17">
+        <v>500</v>
+      </c>
+      <c r="J22" s="17">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="K22" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="17">
+        <v>2004</v>
+      </c>
+      <c r="B23" s="17">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="C23" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="19">
         <v>20</v>
       </c>
-      <c r="F8" s="2">
-        <v>120</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="F23" s="17">
+        <v>450</v>
+      </c>
+      <c r="G23" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="H23" s="17">
+        <v>50</v>
+      </c>
+      <c r="I23" s="17">
         <v>300</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J23" s="17">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K8" s="12">
-        <f t="shared" si="1"/>
-        <v>0.00198255352894528</v>
-      </c>
-      <c r="L8" s="13" t="s">
+      <c r="K23" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0515463917525773</v>
+      </c>
+      <c r="L23" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="17">
+        <v>2005</v>
+      </c>
+      <c r="B24" s="17">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="C24" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="19">
         <v>20</v>
       </c>
-      <c r="F9" s="2">
-        <v>120</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="F24" s="17">
+        <v>450</v>
+      </c>
+      <c r="G24" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="H24" s="17">
+        <v>50</v>
+      </c>
+      <c r="I24" s="17">
         <v>300</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J24" s="17">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K9" s="12">
-        <f t="shared" si="1"/>
-        <v>0.00198255352894528</v>
-      </c>
-      <c r="L9" s="13" t="s">
+      <c r="K24" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0515463917525773</v>
+      </c>
+      <c r="L24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="17">
+        <v>2006</v>
+      </c>
+      <c r="B25" s="17">
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="C25" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="19">
         <v>20</v>
       </c>
-      <c r="F10" s="2">
-        <v>120</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F25" s="17">
+        <v>450</v>
+      </c>
+      <c r="G25" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="H25" s="17">
+        <v>50</v>
+      </c>
+      <c r="I25" s="17">
         <v>300</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J25" s="17">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K10" s="12">
-        <f t="shared" si="1"/>
-        <v>0.00198255352894528</v>
-      </c>
-      <c r="L10" s="13" t="s">
+      <c r="K25" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0515463917525773</v>
+      </c>
+      <c r="L25" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="2">
-        <v>3001</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="17">
+        <v>3004</v>
+      </c>
+      <c r="B26" s="17">
         <v>3</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="C26" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="19">
         <v>20</v>
       </c>
-      <c r="F11" s="2">
-        <v>150</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="F26" s="17">
+        <v>450</v>
+      </c>
+      <c r="G26" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="H26" s="17">
+        <v>50</v>
+      </c>
+      <c r="I26" s="17">
         <v>100</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J26" s="17">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K11" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000660851176315094</v>
-      </c>
-      <c r="L11" s="13" t="s">
+      <c r="K26" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0171821305841924</v>
+      </c>
+      <c r="L26" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-    </row>
-    <row r="12" spans="1:19">
-      <c r="A12" s="2">
-        <v>3002</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="17">
+        <v>3005</v>
+      </c>
+      <c r="B27" s="17">
         <v>3</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="C27" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="19">
         <v>20</v>
       </c>
-      <c r="F12" s="2">
-        <v>150</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="F27" s="17">
+        <v>450</v>
+      </c>
+      <c r="G27" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="H27" s="17">
+        <v>50</v>
+      </c>
+      <c r="I27" s="17">
         <v>10</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J27" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K12" s="12">
-        <f t="shared" si="1"/>
-        <v>6.60851176315094e-5</v>
-      </c>
-      <c r="L12" s="13" t="s">
+      <c r="K27" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00171821305841924</v>
+      </c>
+      <c r="L27" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-    </row>
-    <row r="13" spans="1:19">
-      <c r="A13" s="2">
-        <v>3003</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="17">
+        <v>3006</v>
+      </c>
+      <c r="B28" s="17">
         <v>3</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="C28" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="19">
         <v>20</v>
       </c>
-      <c r="F13" s="2">
-        <v>150</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="F28" s="17">
+        <v>450</v>
+      </c>
+      <c r="G28" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="H28" s="17">
+        <v>50</v>
+      </c>
+      <c r="I28" s="17">
         <v>100</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J28" s="17">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K13" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000660851176315094</v>
-      </c>
-      <c r="L13" s="13" t="s">
+      <c r="K28" s="21">
+        <f t="shared" si="1"/>
+        <v>0.0171821305841924</v>
+      </c>
+      <c r="L28" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" s="2">
-        <v>4001</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="17">
+        <v>4004</v>
+      </c>
+      <c r="B29" s="17">
         <v>4</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="C29" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="19">
         <v>20</v>
       </c>
-      <c r="F14" s="2">
-        <v>180</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="F29" s="17">
+        <v>450</v>
+      </c>
+      <c r="G29" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>50</v>
-      </c>
-      <c r="J14" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K14" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000330425588157547</v>
-      </c>
-      <c r="L14" s="13" t="s">
+      <c r="H29" s="17">
+        <v>50</v>
+      </c>
+      <c r="I29" s="17">
+        <v>50</v>
+      </c>
+      <c r="J29" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K29" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L29" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-    </row>
-    <row r="15" spans="1:19">
-      <c r="A15" s="2">
-        <v>4002</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="17">
+        <v>4005</v>
+      </c>
+      <c r="B30" s="17">
         <v>4</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="C30" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" s="19">
         <v>20</v>
       </c>
-      <c r="F15" s="2">
-        <v>180</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="F30" s="17">
+        <v>450</v>
+      </c>
+      <c r="G30" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>50</v>
-      </c>
-      <c r="J15" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K15" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000330425588157547</v>
-      </c>
-      <c r="L15" s="13" t="s">
+      <c r="H30" s="17">
+        <v>50</v>
+      </c>
+      <c r="I30" s="17">
+        <v>50</v>
+      </c>
+      <c r="J30" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K30" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L30" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="2">
-        <v>4003</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="17">
+        <v>4006</v>
+      </c>
+      <c r="B31" s="17">
         <v>4</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="C31" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="19">
         <v>20</v>
       </c>
-      <c r="F16" s="2">
-        <v>180</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="F31" s="17">
+        <v>450</v>
+      </c>
+      <c r="G31" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>50</v>
-      </c>
-      <c r="J16" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K16" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000330425588157547</v>
-      </c>
-      <c r="L16" s="13" t="s">
+      <c r="H31" s="17">
+        <v>50</v>
+      </c>
+      <c r="I31" s="17">
+        <v>50</v>
+      </c>
+      <c r="J31" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K31" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L31" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="2">
-        <v>5001</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="17">
+        <v>5004</v>
+      </c>
+      <c r="B32" s="17">
         <v>5</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="C32" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="19">
         <v>20</v>
       </c>
-      <c r="F17" s="2">
-        <v>200</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="F32" s="17">
+        <v>450</v>
+      </c>
+      <c r="G32" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>50</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K17" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000330425588157547</v>
-      </c>
-      <c r="L17" s="13" t="s">
+      <c r="H32" s="17">
+        <v>50</v>
+      </c>
+      <c r="I32" s="17">
+        <v>50</v>
+      </c>
+      <c r="J32" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K32" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L32" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="2">
-        <v>5002</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="17">
+        <v>5005</v>
+      </c>
+      <c r="B33" s="17">
         <v>5</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="C33" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="19">
         <v>20</v>
       </c>
-      <c r="F18" s="2">
-        <v>200</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="F33" s="17">
+        <v>450</v>
+      </c>
+      <c r="G33" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>50</v>
-      </c>
-      <c r="J18" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K18" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000330425588157547</v>
-      </c>
-      <c r="L18" s="13" t="s">
+      <c r="H33" s="17">
+        <v>50</v>
+      </c>
+      <c r="I33" s="17">
+        <v>50</v>
+      </c>
+      <c r="J33" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K33" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L33" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="2">
-        <v>5003</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="17">
+        <v>5006</v>
+      </c>
+      <c r="B34" s="17">
         <v>5</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="C34" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="19">
         <v>20</v>
       </c>
-      <c r="F19" s="2">
-        <v>200</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="F34" s="17">
+        <v>450</v>
+      </c>
+      <c r="G34" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>50</v>
-      </c>
-      <c r="J19" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K19" s="12">
-        <f t="shared" si="1"/>
-        <v>0.000330425588157547</v>
-      </c>
-      <c r="L19" s="13" t="s">
+      <c r="H34" s="17">
+        <v>50</v>
+      </c>
+      <c r="I34" s="17">
+        <v>50</v>
+      </c>
+      <c r="J34" s="17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K34" s="21">
+        <f t="shared" si="1"/>
+        <v>0.00859106529209622</v>
+      </c>
+      <c r="L34" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="2">
-        <v>1004</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="4">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2">
-        <v>100</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="2">
-        <v>50</v>
-      </c>
-      <c r="I20" s="2">
-        <v>500</v>
-      </c>
-      <c r="J20" s="2">
-        <f t="shared" si="0"/>
-        <v>25500</v>
-      </c>
-      <c r="K20" s="12">
-        <f t="shared" si="1"/>
-        <v>0.168517049960349</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="2">
-        <v>1005</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="4">
-        <v>20</v>
-      </c>
-      <c r="F21" s="2">
-        <v>100</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="2">
-        <v>50</v>
-      </c>
-      <c r="I21" s="2">
-        <v>500</v>
-      </c>
-      <c r="J21" s="2">
-        <f t="shared" si="0"/>
-        <v>25500</v>
-      </c>
-      <c r="K21" s="12">
-        <f t="shared" si="1"/>
-        <v>0.168517049960349</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="4">
-        <v>20</v>
-      </c>
-      <c r="F22" s="2">
-        <v>100</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="2">
-        <v>50</v>
-      </c>
-      <c r="I22" s="2">
-        <v>500</v>
-      </c>
-      <c r="J22" s="2">
-        <f t="shared" si="0"/>
-        <v>25500</v>
-      </c>
-      <c r="K22" s="12">
-        <f t="shared" si="1"/>
-        <v>0.168517049960349</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B23" s="2">
-        <v>2</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="4">
-        <v>20</v>
-      </c>
-      <c r="F23" s="2">
-        <v>120</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="2">
-        <v>50</v>
-      </c>
-      <c r="I23" s="2">
-        <v>300</v>
-      </c>
-      <c r="J23" s="2">
-        <f t="shared" si="0"/>
-        <v>15300</v>
-      </c>
-      <c r="K23" s="12">
-        <f t="shared" si="1"/>
-        <v>0.101110229976209</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="2">
-        <v>2005</v>
-      </c>
-      <c r="B24" s="2">
-        <v>2</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="4">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2">
-        <v>120</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="2">
-        <v>50</v>
-      </c>
-      <c r="I24" s="2">
-        <v>300</v>
-      </c>
-      <c r="J24" s="2">
-        <f t="shared" si="0"/>
-        <v>15300</v>
-      </c>
-      <c r="K24" s="12">
-        <f t="shared" si="1"/>
-        <v>0.101110229976209</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="2">
-        <v>2006</v>
-      </c>
-      <c r="B25" s="2">
-        <v>2</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="4">
-        <v>20</v>
-      </c>
-      <c r="F25" s="2">
-        <v>120</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="2">
-        <v>50</v>
-      </c>
-      <c r="I25" s="2">
-        <v>300</v>
-      </c>
-      <c r="J25" s="2">
-        <f t="shared" si="0"/>
-        <v>15300</v>
-      </c>
-      <c r="K25" s="12">
-        <f t="shared" si="1"/>
-        <v>0.101110229976209</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="2">
-        <v>3004</v>
-      </c>
-      <c r="B26" s="2">
-        <v>3</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E26" s="4">
-        <v>20</v>
-      </c>
-      <c r="F26" s="2">
-        <v>150</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="2">
-        <v>50</v>
-      </c>
-      <c r="I26" s="2">
-        <v>100</v>
-      </c>
-      <c r="J26" s="2">
-        <f t="shared" si="0"/>
-        <v>5100</v>
-      </c>
-      <c r="K26" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0337034099920698</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="2">
-        <v>3005</v>
-      </c>
-      <c r="B27" s="2">
-        <v>3</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" s="4">
-        <v>20</v>
-      </c>
-      <c r="F27" s="2">
-        <v>150</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="2">
-        <v>50</v>
-      </c>
-      <c r="I27" s="2">
-        <v>10</v>
-      </c>
-      <c r="J27" s="2">
-        <f t="shared" si="0"/>
-        <v>510</v>
-      </c>
-      <c r="K27" s="12">
-        <f t="shared" si="1"/>
-        <v>0.00337034099920698</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="2">
-        <v>3006</v>
-      </c>
-      <c r="B28" s="2">
-        <v>3</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="4">
-        <v>20</v>
-      </c>
-      <c r="F28" s="2">
-        <v>150</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" s="2">
-        <v>50</v>
-      </c>
-      <c r="I28" s="2">
-        <v>100</v>
-      </c>
-      <c r="J28" s="2">
-        <f t="shared" si="0"/>
-        <v>5100</v>
-      </c>
-      <c r="K28" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0337034099920698</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="2">
-        <v>4004</v>
-      </c>
-      <c r="B29" s="2">
-        <v>4</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E29" s="4">
-        <v>20</v>
-      </c>
-      <c r="F29" s="2">
-        <v>180</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="2">
-        <v>50</v>
-      </c>
-      <c r="I29" s="2">
-        <v>50</v>
-      </c>
-      <c r="J29" s="2">
-        <f t="shared" si="0"/>
-        <v>2550</v>
-      </c>
-      <c r="K29" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0168517049960349</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="2">
-        <v>4005</v>
-      </c>
-      <c r="B30" s="2">
-        <v>4</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="4">
-        <v>20</v>
-      </c>
-      <c r="F30" s="2">
-        <v>180</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="2">
-        <v>50</v>
-      </c>
-      <c r="I30" s="2">
-        <v>50</v>
-      </c>
-      <c r="J30" s="2">
-        <f t="shared" si="0"/>
-        <v>2550</v>
-      </c>
-      <c r="K30" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0168517049960349</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="2">
-        <v>4006</v>
-      </c>
-      <c r="B31" s="2">
-        <v>4</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" s="4">
-        <v>20</v>
-      </c>
-      <c r="F31" s="2">
-        <v>180</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H31" s="2">
-        <v>50</v>
-      </c>
-      <c r="I31" s="2">
-        <v>50</v>
-      </c>
-      <c r="J31" s="2">
-        <f t="shared" si="0"/>
-        <v>2550</v>
-      </c>
-      <c r="K31" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0168517049960349</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="2">
-        <v>5004</v>
-      </c>
-      <c r="B32" s="2">
-        <v>5</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" s="4">
-        <v>20</v>
-      </c>
-      <c r="F32" s="2">
-        <v>200</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" s="2">
-        <v>50</v>
-      </c>
-      <c r="I32" s="2">
-        <v>50</v>
-      </c>
-      <c r="J32" s="2">
-        <f t="shared" si="0"/>
-        <v>2550</v>
-      </c>
-      <c r="K32" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0168517049960349</v>
-      </c>
-      <c r="L32" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="2">
-        <v>5005</v>
-      </c>
-      <c r="B33" s="2">
-        <v>5</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="4">
-        <v>20</v>
-      </c>
-      <c r="F33" s="2">
-        <v>200</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" s="2">
-        <v>50</v>
-      </c>
-      <c r="I33" s="2">
-        <v>50</v>
-      </c>
-      <c r="J33" s="2">
-        <f t="shared" si="0"/>
-        <v>2550</v>
-      </c>
-      <c r="K33" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0168517049960349</v>
-      </c>
-      <c r="L33" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="2">
-        <v>5006</v>
-      </c>
-      <c r="B34" s="2">
-        <v>5</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E34" s="4">
-        <v>20</v>
-      </c>
-      <c r="F34" s="2">
-        <v>200</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="2">
-        <v>50</v>
-      </c>
-      <c r="I34" s="2">
-        <v>50</v>
-      </c>
-      <c r="J34" s="2">
-        <f t="shared" si="0"/>
-        <v>2550</v>
-      </c>
-      <c r="K34" s="12">
-        <f t="shared" si="1"/>
-        <v>0.0168517049960349</v>
-      </c>
-      <c r="L34" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
     </row>
     <row r="39" ht="17.25" spans="1:14">
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
     </row>
     <row r="47" spans="1:14">
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
     </row>
     <row r="49" spans="3:7">
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
     </row>
     <row r="50" spans="3:7">
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
     </row>
     <row r="51" spans="3:7">
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
     </row>
     <row r="52" spans="3:7">
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
     </row>
     <row r="53" ht="14.25" spans="3:7">
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
     </row>
     <row r="54" spans="3:7">
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
     </row>
     <row r="55" spans="3:7">
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="56" spans="3:7">
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
     </row>
     <row r="57" spans="3:7">
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
     </row>
     <row r="58" spans="3:7">
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
     </row>
     <row r="59" spans="3:7">
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
     </row>
     <row r="60" spans="3:7">
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="N2:N3 N8:N19 N6 N35:N60 M61:N63 A1:B1 G1 A4:B4 G4:G9 G11:G12 G14:G15 G17:G18 M4:N4 M1:N1" formula="1"/>
+    <ignoredError sqref="M1:N1 M4:N4 G17:G18 G14:G15 G11:G12 G4:G9 A4:B4 G1 A1:B1 M61:N63 N35:N60 N6 N8:N19 N2:N3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -680,12 +680,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1162,7 +1162,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1210,9 +1210,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1687,8 +1684,8 @@
       <c r="I3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
       <c r="L3" s="14" t="s">
         <v>24</v>
       </c>
@@ -1698,1399 +1695,1399 @@
       <c r="N3" s="15"/>
     </row>
     <row r="4" ht="15.75" spans="1:19">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="20"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:19">
-      <c r="A5" s="17">
+      <c r="A5" s="16">
         <v>1001</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="16">
         <v>1</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <v>20</v>
       </c>
-      <c r="F5" s="17">
-        <v>450</v>
-      </c>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="16">
+        <v>100</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <v>0</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16">
         <v>500</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="16">
         <f>IF(H5=0,I5,($O$1*H5/100+1)*I5)</f>
         <v>500</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="20">
         <f>J5/SUM($J$5:$J$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22" t="s">
+      <c r="M5" s="21"/>
+      <c r="N5" s="21" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:19">
-      <c r="A6" s="17">
+      <c r="A6" s="16">
         <v>1002</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>1</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>20</v>
       </c>
-      <c r="F6" s="17">
-        <v>450</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="F6" s="16">
+        <v>100</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="16">
         <v>0</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="16">
         <v>500</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="16">
         <f t="shared" ref="J6:J34" si="0">IF(H6=0,I6,($O$1*H6/100+1)*I6)</f>
         <v>500</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="20">
         <f t="shared" ref="K6:K34" si="1">J6/SUM($J$5:$J$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="L6" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="17">
+      <c r="A7" s="16">
         <v>1003</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="16">
         <v>1</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <v>20</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <v>450</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <v>0</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <v>500</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="20">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L7" s="22" t="s">
+      <c r="L7" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="17">
+      <c r="A8" s="16">
         <v>2001</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>2</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="18">
         <v>20</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="16">
         <v>450</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="16">
         <v>0</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="16">
         <v>300</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="16">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="20">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L8" s="22" t="s">
+      <c r="L8" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="17">
+      <c r="A9" s="16">
         <v>2002</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="16">
         <v>2</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="18">
         <v>20</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="16">
         <v>450</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="16">
         <v>0</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="16">
         <v>300</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="16">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="20">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L9" s="22" t="s">
+      <c r="L9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="17">
+      <c r="A10" s="16">
         <v>2003</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>2</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="18">
         <v>20</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <v>450</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="16">
         <v>0</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="16">
         <v>300</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="20">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L10" s="22" t="s">
+      <c r="L10" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="17">
+      <c r="A11" s="16">
         <v>3001</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="16">
         <v>3</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="18">
         <v>20</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <v>450</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="16">
         <v>0</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="16">
         <v>100</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="20">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L11" s="22" t="s">
+      <c r="L11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="17">
+      <c r="A12" s="16">
         <v>3002</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>3</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="18">
         <v>20</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="16">
         <v>450</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="16">
         <v>0</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="16">
         <v>10</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="16">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="20">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="L12" s="22" t="s">
+      <c r="L12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="17">
+      <c r="A13" s="16">
         <v>3003</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="16">
         <v>3</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="18">
         <v>20</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="16">
         <v>450</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <v>0</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="16">
         <v>100</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="20">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L13" s="22" t="s">
+      <c r="L13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="17">
+      <c r="A14" s="16">
         <v>4001</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="16">
         <v>4</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="18">
         <v>20</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="16">
         <v>450</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="16">
         <v>0</v>
       </c>
-      <c r="I14" s="17">
-        <v>50</v>
-      </c>
-      <c r="J14" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K14" s="21">
+      <c r="I14" s="16">
+        <v>50</v>
+      </c>
+      <c r="J14" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K14" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L14" s="22" t="s">
+      <c r="L14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="17">
+      <c r="A15" s="16">
         <v>4002</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="16">
         <v>4</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="19" t="s">
+      <c r="C15" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="18">
         <v>20</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="16">
         <v>450</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="16">
         <v>0</v>
       </c>
-      <c r="I15" s="17">
-        <v>50</v>
-      </c>
-      <c r="J15" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K15" s="21">
+      <c r="I15" s="16">
+        <v>50</v>
+      </c>
+      <c r="J15" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K15" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L15" s="22" t="s">
+      <c r="L15" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="17">
+      <c r="A16" s="16">
         <v>4003</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="16">
         <v>4</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="18">
         <v>20</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="16">
         <v>450</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="16">
         <v>0</v>
       </c>
-      <c r="I16" s="17">
-        <v>50</v>
-      </c>
-      <c r="J16" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K16" s="21">
+      <c r="I16" s="16">
+        <v>50</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K16" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L16" s="22" t="s">
+      <c r="L16" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="17">
+      <c r="A17" s="16">
         <v>5001</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="16">
         <v>5</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="18">
         <v>20</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="16">
         <v>450</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="16">
         <v>0</v>
       </c>
-      <c r="I17" s="17">
-        <v>50</v>
-      </c>
-      <c r="J17" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K17" s="21">
+      <c r="I17" s="16">
+        <v>50</v>
+      </c>
+      <c r="J17" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K17" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L17" s="22" t="s">
+      <c r="L17" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="17">
+      <c r="A18" s="16">
         <v>5002</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="16">
         <v>5</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="18">
         <v>20</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="16">
         <v>450</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="16">
         <v>0</v>
       </c>
-      <c r="I18" s="17">
-        <v>50</v>
-      </c>
-      <c r="J18" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K18" s="21">
+      <c r="I18" s="16">
+        <v>50</v>
+      </c>
+      <c r="J18" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K18" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L18" s="22" t="s">
+      <c r="L18" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="17">
+      <c r="A19" s="16">
         <v>5003</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="16">
         <v>5</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="18">
         <v>20</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="16">
         <v>450</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="16">
         <v>0</v>
       </c>
-      <c r="I19" s="17">
-        <v>50</v>
-      </c>
-      <c r="J19" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K19" s="21">
+      <c r="I19" s="16">
+        <v>50</v>
+      </c>
+      <c r="J19" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K19" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L19" s="22" t="s">
+      <c r="L19" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="17">
+      <c r="A20" s="16">
         <v>1004</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="16">
         <v>1</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="18">
         <v>20</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="16">
         <v>450</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G20" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="17">
-        <v>50</v>
-      </c>
-      <c r="I20" s="17">
+      <c r="H20" s="16">
+        <v>50</v>
+      </c>
+      <c r="I20" s="16">
         <v>500</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="16">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="20">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L20" s="22" t="s">
+      <c r="L20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="17">
+      <c r="A21" s="16">
         <v>1005</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <v>1</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="18">
         <v>20</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="16">
         <v>450</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="17">
-        <v>50</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="H21" s="16">
+        <v>50</v>
+      </c>
+      <c r="I21" s="16">
         <v>500</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="16">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K21" s="21">
+      <c r="K21" s="20">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L21" s="22" t="s">
+      <c r="L21" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="17">
+      <c r="A22" s="16">
         <v>1006</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="16">
         <v>1</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="18">
         <v>20</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="16">
         <v>450</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="17">
-        <v>50</v>
-      </c>
-      <c r="I22" s="17">
+      <c r="H22" s="16">
+        <v>50</v>
+      </c>
+      <c r="I22" s="16">
         <v>500</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="16">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="20">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="L22" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="17">
+      <c r="A23" s="16">
         <v>2004</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="16">
         <v>2</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="18">
         <v>20</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="16">
         <v>450</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="17">
-        <v>50</v>
-      </c>
-      <c r="I23" s="17">
+      <c r="H23" s="16">
+        <v>50</v>
+      </c>
+      <c r="I23" s="16">
         <v>300</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="16">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K23" s="21">
+      <c r="K23" s="20">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L23" s="22" t="s">
+      <c r="L23" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="17">
+      <c r="A24" s="16">
         <v>2005</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="16">
         <v>2</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="18">
         <v>20</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="16">
         <v>450</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="17">
-        <v>50</v>
-      </c>
-      <c r="I24" s="17">
+      <c r="H24" s="16">
+        <v>50</v>
+      </c>
+      <c r="I24" s="16">
         <v>300</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="16">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="20">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L24" s="22" t="s">
+      <c r="L24" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="17">
+      <c r="A25" s="16">
         <v>2006</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="16">
         <v>2</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="18">
         <v>20</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="16">
         <v>450</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="17">
-        <v>50</v>
-      </c>
-      <c r="I25" s="17">
+      <c r="H25" s="16">
+        <v>50</v>
+      </c>
+      <c r="I25" s="16">
         <v>300</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="16">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="20">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L25" s="22" t="s">
+      <c r="L25" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="17">
+      <c r="A26" s="16">
         <v>3004</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <v>3</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="18">
         <v>20</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="16">
         <v>450</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="17">
-        <v>50</v>
-      </c>
-      <c r="I26" s="17">
+      <c r="H26" s="16">
+        <v>50</v>
+      </c>
+      <c r="I26" s="16">
         <v>100</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="20">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L26" s="22" t="s">
+      <c r="L26" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="17">
+      <c r="A27" s="16">
         <v>3005</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>3</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="18">
         <v>20</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="16">
         <v>450</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H27" s="17">
-        <v>50</v>
-      </c>
-      <c r="I27" s="17">
+      <c r="H27" s="16">
+        <v>50</v>
+      </c>
+      <c r="I27" s="16">
         <v>10</v>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="16">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K27" s="21">
+      <c r="K27" s="20">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="L27" s="22" t="s">
+      <c r="L27" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="17">
+      <c r="A28" s="16">
         <v>3006</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <v>3</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="18">
         <v>20</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="16">
         <v>450</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G28" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="17">
-        <v>50</v>
-      </c>
-      <c r="I28" s="17">
+      <c r="H28" s="16">
+        <v>50</v>
+      </c>
+      <c r="I28" s="16">
         <v>100</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K28" s="21">
+      <c r="K28" s="20">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L28" s="22" t="s">
+      <c r="L28" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="17">
+      <c r="A29" s="16">
         <v>4004</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <v>4</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="18">
         <v>20</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="16">
         <v>450</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="17">
-        <v>50</v>
-      </c>
-      <c r="I29" s="17">
-        <v>50</v>
-      </c>
-      <c r="J29" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K29" s="21">
+      <c r="H29" s="16">
+        <v>50</v>
+      </c>
+      <c r="I29" s="16">
+        <v>50</v>
+      </c>
+      <c r="J29" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K29" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L29" s="22" t="s">
+      <c r="L29" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="17">
+      <c r="A30" s="16">
         <v>4005</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <v>4</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="18">
         <v>20</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="16">
         <v>450</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="17">
-        <v>50</v>
-      </c>
-      <c r="I30" s="17">
-        <v>50</v>
-      </c>
-      <c r="J30" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K30" s="21">
+      <c r="H30" s="16">
+        <v>50</v>
+      </c>
+      <c r="I30" s="16">
+        <v>50</v>
+      </c>
+      <c r="J30" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K30" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L30" s="22" t="s">
+      <c r="L30" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="17">
+      <c r="A31" s="16">
         <v>4006</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="16">
         <v>4</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="18">
         <v>20</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="16">
         <v>450</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="17">
-        <v>50</v>
-      </c>
-      <c r="I31" s="17">
-        <v>50</v>
-      </c>
-      <c r="J31" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K31" s="21">
+      <c r="H31" s="16">
+        <v>50</v>
+      </c>
+      <c r="I31" s="16">
+        <v>50</v>
+      </c>
+      <c r="J31" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K31" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L31" s="22" t="s">
+      <c r="L31" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="17">
+      <c r="A32" s="16">
         <v>5004</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="16">
         <v>5</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="18">
         <v>20</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="16">
         <v>450</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="17">
-        <v>50</v>
-      </c>
-      <c r="I32" s="17">
-        <v>50</v>
-      </c>
-      <c r="J32" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K32" s="21">
+      <c r="H32" s="16">
+        <v>50</v>
+      </c>
+      <c r="I32" s="16">
+        <v>50</v>
+      </c>
+      <c r="J32" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K32" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L32" s="22" t="s">
+      <c r="L32" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="17">
+      <c r="A33" s="16">
         <v>5005</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <v>5</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="18">
         <v>20</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="16">
         <v>450</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="17">
-        <v>50</v>
-      </c>
-      <c r="I33" s="17">
-        <v>50</v>
-      </c>
-      <c r="J33" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K33" s="21">
+      <c r="H33" s="16">
+        <v>50</v>
+      </c>
+      <c r="I33" s="16">
+        <v>50</v>
+      </c>
+      <c r="J33" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K33" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L33" s="22" t="s">
+      <c r="L33" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="17">
+      <c r="A34" s="16">
         <v>5006</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <v>5</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="18">
         <v>20</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="16">
         <v>450</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="17">
-        <v>50</v>
-      </c>
-      <c r="I34" s="17">
-        <v>50</v>
-      </c>
-      <c r="J34" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K34" s="21">
+      <c r="H34" s="16">
+        <v>50</v>
+      </c>
+      <c r="I34" s="16">
+        <v>50</v>
+      </c>
+      <c r="J34" s="16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="K34" s="20">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L34" s="22" t="s">
+      <c r="L34" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
     </row>
     <row r="39" ht="17.25" spans="1:14">
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
     </row>
     <row r="47" spans="1:14">
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
     </row>
     <row r="49" spans="3:7">
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
     </row>
     <row r="50" spans="3:7">
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
     </row>
     <row r="51" spans="3:7">
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
     </row>
     <row r="52" spans="3:7">
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
     </row>
     <row r="53" ht="14.25" spans="3:7">
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
     </row>
     <row r="54" spans="3:7">
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
     </row>
     <row r="55" spans="3:7">
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
     </row>
     <row r="56" spans="3:7">
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
     </row>
     <row r="57" spans="3:7">
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
     </row>
     <row r="58" spans="3:7">
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
     </row>
     <row r="59" spans="3:7">
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
     </row>
     <row r="60" spans="3:7">
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="M1:N1 M4:N4 G17:G18 G14:G15 G11:G12 G4:G9 A4:B4 G1 A1:B1 M61:N63 N35:N60 N6 N8:N19 N2:N3" formula="1"/>
+    <ignoredError sqref="N2:N3 N8:N19 N6 N35:N60 M61:N63 A1:B1 G1 A4:B4 G4:G9 G11:G12 G14:G15 G17:G18 M4:N4 M1:N1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
@@ -265,6 +265,78 @@
     <t>固定</t>
   </si>
   <si>
+    <t>1025201_1125201_4</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>1025202_1125202_4</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>1025203_1125203_4</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>1025301_1125301_6</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>1025302_1125302_6</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>1025303_1125303_6</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
+    <t>1025401_1125401_8</t>
+  </si>
+  <si>
+    <t>马拉松客</t>
+  </si>
+  <si>
+    <t>1025402_1125402_8</t>
+  </si>
+  <si>
+    <t>极限玩家</t>
+  </si>
+  <si>
+    <t>1025403_1125403_8</t>
+  </si>
+  <si>
+    <t>科技极客</t>
+  </si>
+  <si>
+    <t>1025501_1125501_10</t>
+  </si>
+  <si>
+    <t>创业新贵</t>
+  </si>
+  <si>
+    <t>1025502_1125502_10</t>
+  </si>
+  <si>
+    <t>摸金校尉</t>
+  </si>
+  <si>
+    <t>1025503_1125503_10</t>
+  </si>
+  <si>
+    <t>氪金大佬</t>
+  </si>
+  <si>
     <t>1025104_1125104_2</t>
   </si>
   <si>
@@ -283,24 +355,6 @@
     <t>街拍达人</t>
   </si>
   <si>
-    <t>1025201_1125201_4</t>
-  </si>
-  <si>
-    <t>运动健将</t>
-  </si>
-  <si>
-    <t>1025202_1125202_4</t>
-  </si>
-  <si>
-    <t>跑酷少年</t>
-  </si>
-  <si>
-    <t>1025203_1125203_4</t>
-  </si>
-  <si>
-    <t>滑板高手</t>
-  </si>
-  <si>
     <t>1025204_1125204_4</t>
   </si>
   <si>
@@ -319,24 +373,6 @@
     <t>优雅女神</t>
   </si>
   <si>
-    <t>1025301_1125301_6</t>
-  </si>
-  <si>
-    <t>健身狂魔</t>
-  </si>
-  <si>
-    <t>1025302_1125302_6</t>
-  </si>
-  <si>
-    <t>单车骑士</t>
-  </si>
-  <si>
-    <t>1025303_1125303_6</t>
-  </si>
-  <si>
-    <t>登山行者</t>
-  </si>
-  <si>
     <t>1025304_1125304_6</t>
   </si>
   <si>
@@ -355,24 +391,6 @@
     <t>民谣歌手</t>
   </si>
   <si>
-    <t>1025401_1125401_8</t>
-  </si>
-  <si>
-    <t>马拉松客</t>
-  </si>
-  <si>
-    <t>1025402_1125402_8</t>
-  </si>
-  <si>
-    <t>极限玩家</t>
-  </si>
-  <si>
-    <t>1025403_1125403_8</t>
-  </si>
-  <si>
-    <t>科技极客</t>
-  </si>
-  <si>
     <t>1025404_1125404_8</t>
   </si>
   <si>
@@ -389,24 +407,6 @@
   </si>
   <si>
     <t>古典乐迷</t>
-  </si>
-  <si>
-    <t>1025501_1125501_10</t>
-  </si>
-  <si>
-    <t>创业新贵</t>
-  </si>
-  <si>
-    <t>1025502_1125502_10</t>
-  </si>
-  <si>
-    <t>摸金校尉</t>
-  </si>
-  <si>
-    <t>1025503_1125503_10</t>
-  </si>
-  <si>
-    <t>氪金大佬</t>
   </si>
   <si>
     <t>1025504_1125504_10</t>
@@ -449,7 +449,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,6 +462,11 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -680,23 +685,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1032,55 +1043,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="8" borderId="0">
@@ -1095,132 +1103,141 @@
     <xf numFmtId="0" fontId="31" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
@@ -1232,10 +1249,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1577,1517 +1594,1517 @@
     <col min="19" max="19" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:19">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-    </row>
-    <row r="2" s="3" customFormat="1" ht="21" customHeight="1" spans="1:19">
-      <c r="A2" s="12" t="s">
+      <c r="O1" s="4"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+    </row>
+    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:19">
+      <c r="A2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="12" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="16"/>
+      <c r="H2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14" t="s">
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="15"/>
-    </row>
-    <row r="3" s="3" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A3" s="12" t="s">
+      <c r="N2" s="17"/>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:19">
+      <c r="A3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="14" t="s">
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="15"/>
+      <c r="N3" s="17"/>
     </row>
     <row r="4" ht="15.75" spans="1:19">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="19"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="21"/>
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:19">
-      <c r="A5" s="16">
+      <c r="A5" s="18">
         <v>1001</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="18">
         <v>1</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="20">
         <v>20</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="18">
         <v>100</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="18">
         <v>0</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="18">
         <v>500</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="18">
         <f>IF(H5=0,I5,($O$1*H5/100+1)*I5)</f>
         <v>500</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="22">
         <f>J5/SUM($J$5:$J$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L5" s="21" t="s">
+      <c r="L5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21" t="s">
+      <c r="M5" s="23"/>
+      <c r="N5" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:19">
-      <c r="A6" s="16">
+      <c r="A6" s="18">
         <v>1002</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="18">
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="20">
         <v>20</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="18">
         <v>100</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="18">
         <v>0</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="18">
         <v>500</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="18">
         <f t="shared" ref="J6:J34" si="0">IF(H6=0,I6,($O$1*H6/100+1)*I6)</f>
         <v>500</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="22">
         <f t="shared" ref="K6:K34" si="1">J6/SUM($J$5:$J$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="16">
+      <c r="A7" s="18">
         <v>1003</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="18">
         <v>1</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="20">
         <v>20</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="18">
         <v>450</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="18">
         <v>0</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="18">
         <v>500</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L7" s="21" t="s">
+      <c r="L7" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="16">
+      <c r="A8" s="18">
         <v>2001</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="18">
         <v>2</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="20">
         <v>20</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="18">
         <v>450</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="18">
         <v>0</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="18">
         <v>300</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L8" s="21" t="s">
+      <c r="L8" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="16">
+      <c r="A9" s="18">
         <v>2002</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="18">
         <v>2</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <v>20</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="18">
         <v>450</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="18">
         <v>0</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="18">
         <v>300</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L9" s="21" t="s">
+      <c r="L9" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="16">
+      <c r="A10" s="18">
         <v>2003</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="18">
         <v>2</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="20">
         <v>20</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="18">
         <v>450</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="18">
         <v>0</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="18">
         <v>300</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="16">
+      <c r="A11" s="18">
         <v>3001</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="18">
         <v>3</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="20">
         <v>20</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="18">
         <v>450</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="18">
         <v>0</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="18">
         <v>100</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="16">
+      <c r="A12" s="18">
         <v>3002</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="18">
         <v>3</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="20">
         <v>20</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="18">
         <v>450</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="18">
         <v>0</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="18">
         <v>10</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="22">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="L12" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="16">
+      <c r="A13" s="18">
         <v>3003</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="18">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="20">
         <v>20</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="18">
         <v>450</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="18">
         <v>0</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="18">
         <v>100</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="16">
+      <c r="A14" s="18">
         <v>4001</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="18">
         <v>4</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="20">
         <v>20</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="18">
         <v>450</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="18">
         <v>0</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="18">
         <v>50</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K14" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L14" s="21" t="s">
+      <c r="L14" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="16">
+      <c r="A15" s="18">
         <v>4002</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="18">
         <v>4</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="20">
         <v>20</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="18">
         <v>450</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="18">
         <v>0</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="18">
         <v>50</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K15" s="20">
+      <c r="K15" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L15" s="21" t="s">
+      <c r="L15" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="16">
+      <c r="A16" s="18">
         <v>4003</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="18">
         <v>4</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="20">
         <v>20</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="18">
         <v>450</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="18">
         <v>0</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="18">
         <v>50</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L16" s="21" t="s">
+      <c r="L16" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="16">
+      <c r="A17" s="18">
         <v>5001</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="18">
         <v>5</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="20">
         <v>20</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="18">
         <v>450</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="18">
         <v>0</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="18">
         <v>50</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L17" s="21" t="s">
+      <c r="L17" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="16">
+      <c r="A18" s="18">
         <v>5002</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="18">
         <v>5</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="20">
         <v>20</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="18">
         <v>450</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="18">
         <v>0</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="18">
         <v>50</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K18" s="20">
+      <c r="K18" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L18" s="21" t="s">
+      <c r="L18" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="16">
+      <c r="A19" s="18">
         <v>5003</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="18">
         <v>5</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="20">
         <v>20</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="18">
         <v>450</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="18">
         <v>0</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="18">
         <v>50</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K19" s="20">
+      <c r="K19" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L19" s="21" t="s">
+      <c r="L19" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="16">
+      <c r="A20" s="18">
         <v>1004</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="18">
         <v>1</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="20">
         <v>20</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="18">
         <v>450</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="18">
         <v>50</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="18">
         <v>500</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L20" s="21" t="s">
+      <c r="L20" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="16">
+      <c r="A21" s="18">
         <v>1005</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="18">
         <v>1</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="20">
         <v>20</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="18">
         <v>450</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="18">
         <v>50</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="18">
         <v>500</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K21" s="20">
+      <c r="K21" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L21" s="21" t="s">
+      <c r="L21" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="16">
+      <c r="A22" s="18">
         <v>1006</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="18">
         <v>1</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="20">
         <v>20</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="18">
         <v>450</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="18">
         <v>50</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="18">
         <v>500</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K22" s="20">
+      <c r="K22" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L22" s="21" t="s">
+      <c r="L22" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="16">
+      <c r="A23" s="18">
         <v>2004</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="18">
         <v>2</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="20">
         <v>20</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="18">
         <v>450</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="18">
         <v>50</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="18">
         <v>300</v>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K23" s="20">
+      <c r="K23" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L23" s="21" t="s">
+      <c r="L23" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="16">
+      <c r="A24" s="18">
         <v>2005</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="18">
         <v>2</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="20">
         <v>20</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="18">
         <v>450</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="18">
         <v>50</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="18">
         <v>300</v>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K24" s="20">
+      <c r="K24" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L24" s="21" t="s">
+      <c r="L24" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="16">
+      <c r="A25" s="18">
         <v>2006</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="18">
         <v>2</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="20">
         <v>20</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="18">
         <v>450</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="18">
         <v>50</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="18">
         <v>300</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K25" s="20">
+      <c r="K25" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L25" s="21" t="s">
+      <c r="L25" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="16">
+      <c r="A26" s="18">
         <v>3004</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="18">
         <v>3</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="20">
         <v>20</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="18">
         <v>450</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="18">
         <v>50</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="18">
         <v>100</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K26" s="20">
+      <c r="K26" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L26" s="21" t="s">
+      <c r="L26" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="16">
+      <c r="A27" s="18">
         <v>3005</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="18">
         <v>3</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="20">
         <v>20</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="18">
         <v>450</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="18">
         <v>50</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="18">
         <v>10</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K27" s="20">
+      <c r="K27" s="22">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="L27" s="21" t="s">
+      <c r="L27" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="16">
+      <c r="A28" s="18">
         <v>3006</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="18">
         <v>3</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="20">
         <v>20</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="18">
         <v>450</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="18">
         <v>50</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="18">
         <v>100</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K28" s="20">
+      <c r="K28" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L28" s="21" t="s">
+      <c r="L28" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="16">
+      <c r="A29" s="18">
         <v>4004</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="18">
         <v>4</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="20">
         <v>20</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="18">
         <v>450</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="18">
         <v>50</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="18">
         <v>50</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K29" s="20">
+      <c r="K29" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L29" s="21" t="s">
+      <c r="L29" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="16">
+      <c r="A30" s="18">
         <v>4005</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="18">
         <v>4</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="20">
         <v>20</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="18">
         <v>450</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="18">
         <v>50</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="18">
         <v>50</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K30" s="20">
+      <c r="K30" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L30" s="21" t="s">
+      <c r="L30" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="16">
+      <c r="A31" s="18">
         <v>4006</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="18">
         <v>4</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="20">
         <v>20</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="18">
         <v>450</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="18">
         <v>50</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="18">
         <v>50</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K31" s="20">
+      <c r="K31" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L31" s="21" t="s">
+      <c r="L31" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="16">
+      <c r="A32" s="18">
         <v>5004</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="18">
         <v>5</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="20">
         <v>20</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="18">
         <v>450</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="18">
         <v>50</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="18">
         <v>50</v>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K32" s="20">
+      <c r="K32" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L32" s="21" t="s">
+      <c r="L32" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="16">
+      <c r="A33" s="18">
         <v>5005</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="18">
         <v>5</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="20">
         <v>20</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="18">
         <v>450</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="18">
         <v>50</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="18">
         <v>50</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K33" s="20">
+      <c r="K33" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L33" s="21" t="s">
+      <c r="L33" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="23"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="16">
+      <c r="A34" s="18">
         <v>5006</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="18">
         <v>5</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="20">
         <v>20</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="18">
         <v>450</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="18">
         <v>50</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="18">
         <v>50</v>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K34" s="20">
+      <c r="K34" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L34" s="21" t="s">
+      <c r="L34" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="23"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
     </row>
     <row r="39" ht="17.25" spans="1:14">
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
+      <c r="C39" s="25"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
     </row>
     <row r="47" spans="1:14">
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
     </row>
     <row r="49" spans="3:7">
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
     </row>
     <row r="50" spans="3:7">
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
     </row>
     <row r="51" spans="3:7">
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
     </row>
     <row r="52" spans="3:7">
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
     </row>
     <row r="53" ht="14.25" spans="3:7">
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
+      <c r="C53" s="26"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
     </row>
     <row r="54" spans="3:7">
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
     </row>
     <row r="55" spans="3:7">
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
     </row>
     <row r="56" spans="3:7">
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
     </row>
     <row r="57" spans="3:7">
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
     </row>
     <row r="58" spans="3:7">
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
     </row>
     <row r="59" spans="3:7">
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
     </row>
     <row r="60" spans="3:7">
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="N2:N3 N8:N19 N6 N35:N60 M61:N63 A1:B1 G1 A4:B4 G4:G9 G11:G12 G14:G15 G17:G18 M4:N4 M1:N1" formula="1"/>
+    <ignoredError sqref="M1:N1 M4:N4 G17:G18 G14:G15 G11:G12 G4:G9 A4:B4 G1 A1:B1 M61:N63 N35:N60 N6 N8:N19 N2:N3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3096,7 +3113,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F5:J59"/>
+  <dimension ref="F5:V59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="5" spans="6:10">
@@ -3218,7 +3235,7 @@
         <v>1109_2000</v>
       </c>
     </row>
-    <row r="17" spans="6:10">
+    <row r="17" spans="6:22">
       <c r="F17">
         <v>1110</v>
       </c>
@@ -3230,7 +3247,7 @@
         <v>1110_1000</v>
       </c>
     </row>
-    <row r="18" spans="6:10">
+    <row r="18" spans="6:22">
       <c r="F18">
         <v>1111</v>
       </c>
@@ -3242,7 +3259,7 @@
         <v>1111_1000</v>
       </c>
     </row>
-    <row r="19" spans="6:10">
+    <row r="19" spans="6:22">
       <c r="F19">
         <v>1112</v>
       </c>
@@ -3254,7 +3271,7 @@
         <v>1112_1000</v>
       </c>
     </row>
-    <row r="20" spans="6:10">
+    <row r="20" spans="6:22">
       <c r="F20">
         <v>1201</v>
       </c>
@@ -3266,7 +3283,7 @@
         <v>1201_0</v>
       </c>
     </row>
-    <row r="21" spans="6:10">
+    <row r="21" spans="6:22">
       <c r="F21">
         <v>1202</v>
       </c>
@@ -3278,7 +3295,7 @@
         <v>1202_0</v>
       </c>
     </row>
-    <row r="27" spans="6:10">
+    <row r="27" spans="6:22">
       <c r="F27" t="s">
         <v>91</v>
       </c>
@@ -3289,7 +3306,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="6:10">
+    <row r="30" ht="16.5" spans="6:22">
       <c r="F30" s="1">
         <v>1025101</v>
       </c>
@@ -3303,8 +3320,30 @@
         <f>_xlfn.TEXTJOIN("_",TRUE,F30,G30,H30)</f>
         <v>1025101_1125101_2</v>
       </c>
-    </row>
-    <row r="31" spans="6:10">
+      <c r="M30" s="1">
+        <v>1025101</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1125101</v>
+      </c>
+      <c r="O30">
+        <v>2</v>
+      </c>
+      <c r="P30" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,M30,N30,O30)</f>
+        <v>1025101_1125101_2</v>
+      </c>
+      <c r="R30" t="s">
+        <v>27</v>
+      </c>
+      <c r="U30" s="2">
+        <v>1025101</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="6:22">
       <c r="F31" s="1">
         <v>1025102</v>
       </c>
@@ -3318,8 +3357,30 @@
         <f t="shared" ref="J31:J59" si="1">_xlfn.TEXTJOIN("_",TRUE,F31,G31,H31)</f>
         <v>1025102_1125102_2</v>
       </c>
-    </row>
-    <row r="32" spans="6:10">
+      <c r="M31" s="1">
+        <v>1025102</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1125102</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+      <c r="P31" t="str">
+        <f t="shared" ref="P31:P59" si="2">_xlfn.TEXTJOIN("_",TRUE,M31,N31,O31)</f>
+        <v>1025102_1125102_2</v>
+      </c>
+      <c r="R31" t="s">
+        <v>32</v>
+      </c>
+      <c r="U31" s="2">
+        <v>1025102</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="6:22">
       <c r="F32" s="1">
         <v>1025103</v>
       </c>
@@ -3333,8 +3394,30 @@
         <f t="shared" si="1"/>
         <v>1025103_1125103_2</v>
       </c>
-    </row>
-    <row r="33" spans="6:10">
+      <c r="M32" s="1">
+        <v>1025103</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1125103</v>
+      </c>
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="P32" t="str">
+        <f t="shared" si="2"/>
+        <v>1025103_1125103_2</v>
+      </c>
+      <c r="R32" t="s">
+        <v>34</v>
+      </c>
+      <c r="U32" s="2">
+        <v>1025103</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="6:22">
       <c r="F33" s="1">
         <v>1025104</v>
       </c>
@@ -3348,8 +3431,30 @@
         <f t="shared" si="1"/>
         <v>1025104_1125104_2</v>
       </c>
-    </row>
-    <row r="34" spans="6:10">
+      <c r="M33" s="1">
+        <v>1025201</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1125201</v>
+      </c>
+      <c r="O33">
+        <v>4</v>
+      </c>
+      <c r="P33" t="str">
+        <f t="shared" si="2"/>
+        <v>1025201_1125201_4</v>
+      </c>
+      <c r="R33" t="s">
+        <v>37</v>
+      </c>
+      <c r="U33" s="2">
+        <v>1025104</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="6:22">
       <c r="F34" s="1">
         <v>1025105</v>
       </c>
@@ -3363,8 +3468,30 @@
         <f t="shared" si="1"/>
         <v>1025105_1125105_2</v>
       </c>
-    </row>
-    <row r="35" spans="6:10">
+      <c r="M34" s="1">
+        <v>1025202</v>
+      </c>
+      <c r="N34" s="1">
+        <v>1125202</v>
+      </c>
+      <c r="O34">
+        <v>4</v>
+      </c>
+      <c r="P34" t="str">
+        <f t="shared" si="2"/>
+        <v>1025202_1125202_4</v>
+      </c>
+      <c r="R34" t="s">
+        <v>39</v>
+      </c>
+      <c r="U34" s="2">
+        <v>1025105</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="6:22">
       <c r="F35" s="1">
         <v>1025106</v>
       </c>
@@ -3378,8 +3505,30 @@
         <f t="shared" si="1"/>
         <v>1025106_1125106_2</v>
       </c>
-    </row>
-    <row r="36" spans="6:10">
+      <c r="M35" s="1">
+        <v>1025203</v>
+      </c>
+      <c r="N35" s="1">
+        <v>1125203</v>
+      </c>
+      <c r="O35">
+        <v>4</v>
+      </c>
+      <c r="P35" t="str">
+        <f t="shared" si="2"/>
+        <v>1025203_1125203_4</v>
+      </c>
+      <c r="R35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35" s="2">
+        <v>1025106</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="6:22">
       <c r="F36" s="1">
         <v>1025201</v>
       </c>
@@ -3393,8 +3542,30 @@
         <f t="shared" si="1"/>
         <v>1025201_1125201_4</v>
       </c>
-    </row>
-    <row r="37" spans="6:10">
+      <c r="M36" s="1">
+        <v>1025301</v>
+      </c>
+      <c r="N36" s="1">
+        <v>1125301</v>
+      </c>
+      <c r="O36">
+        <v>6</v>
+      </c>
+      <c r="P36" t="str">
+        <f t="shared" si="2"/>
+        <v>1025301_1125301_6</v>
+      </c>
+      <c r="R36" t="s">
+        <v>43</v>
+      </c>
+      <c r="U36" s="3">
+        <v>1025201</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="6:22">
       <c r="F37" s="1">
         <v>1025202</v>
       </c>
@@ -3408,8 +3579,30 @@
         <f t="shared" si="1"/>
         <v>1025202_1125202_4</v>
       </c>
-    </row>
-    <row r="38" spans="6:10">
+      <c r="M37" s="1">
+        <v>1025302</v>
+      </c>
+      <c r="N37" s="1">
+        <v>1125302</v>
+      </c>
+      <c r="O37">
+        <v>6</v>
+      </c>
+      <c r="P37" t="str">
+        <f t="shared" si="2"/>
+        <v>1025302_1125302_6</v>
+      </c>
+      <c r="R37" t="s">
+        <v>45</v>
+      </c>
+      <c r="U37" s="3">
+        <v>1025202</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="6:22">
       <c r="F38" s="1">
         <v>1025203</v>
       </c>
@@ -3423,8 +3616,30 @@
         <f t="shared" si="1"/>
         <v>1025203_1125203_4</v>
       </c>
-    </row>
-    <row r="39" spans="6:10">
+      <c r="M38" s="1">
+        <v>1025303</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1125303</v>
+      </c>
+      <c r="O38">
+        <v>6</v>
+      </c>
+      <c r="P38" t="str">
+        <f t="shared" si="2"/>
+        <v>1025303_1125303_6</v>
+      </c>
+      <c r="R38" t="s">
+        <v>47</v>
+      </c>
+      <c r="U38" s="3">
+        <v>1025203</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="6:22">
       <c r="F39" s="1">
         <v>1025204</v>
       </c>
@@ -3438,8 +3653,30 @@
         <f t="shared" si="1"/>
         <v>1025204_1125204_4</v>
       </c>
-    </row>
-    <row r="40" spans="6:10">
+      <c r="M39" s="1">
+        <v>1025401</v>
+      </c>
+      <c r="N39" s="1">
+        <v>1125401</v>
+      </c>
+      <c r="O39">
+        <v>8</v>
+      </c>
+      <c r="P39" t="str">
+        <f t="shared" si="2"/>
+        <v>1025401_1125401_8</v>
+      </c>
+      <c r="R39" t="s">
+        <v>49</v>
+      </c>
+      <c r="U39" s="3">
+        <v>1025204</v>
+      </c>
+      <c r="V39" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="6:22">
       <c r="F40" s="1">
         <v>1025205</v>
       </c>
@@ -3453,8 +3690,30 @@
         <f t="shared" si="1"/>
         <v>1025205_1125205_4</v>
       </c>
-    </row>
-    <row r="41" spans="6:10">
+      <c r="M40" s="1">
+        <v>1025402</v>
+      </c>
+      <c r="N40" s="1">
+        <v>1125402</v>
+      </c>
+      <c r="O40">
+        <v>8</v>
+      </c>
+      <c r="P40" t="str">
+        <f t="shared" si="2"/>
+        <v>1025402_1125402_8</v>
+      </c>
+      <c r="R40" t="s">
+        <v>51</v>
+      </c>
+      <c r="U40" s="3">
+        <v>1025205</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="6:22">
       <c r="F41" s="1">
         <v>1025206</v>
       </c>
@@ -3468,8 +3727,30 @@
         <f t="shared" si="1"/>
         <v>1025206_1125206_4</v>
       </c>
-    </row>
-    <row r="42" spans="6:10">
+      <c r="M41" s="1">
+        <v>1025403</v>
+      </c>
+      <c r="N41" s="1">
+        <v>1125403</v>
+      </c>
+      <c r="O41">
+        <v>8</v>
+      </c>
+      <c r="P41" t="str">
+        <f t="shared" si="2"/>
+        <v>1025403_1125403_8</v>
+      </c>
+      <c r="R41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U41" s="3">
+        <v>1025206</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="6:22">
       <c r="F42" s="1">
         <v>1025301</v>
       </c>
@@ -3483,8 +3764,30 @@
         <f t="shared" si="1"/>
         <v>1025301_1125301_6</v>
       </c>
-    </row>
-    <row r="43" spans="6:10">
+      <c r="M42" s="1">
+        <v>1025501</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1125501</v>
+      </c>
+      <c r="O42">
+        <v>10</v>
+      </c>
+      <c r="P42" t="str">
+        <f t="shared" si="2"/>
+        <v>1025501_1125501_10</v>
+      </c>
+      <c r="R42" t="s">
+        <v>55</v>
+      </c>
+      <c r="U42" s="2">
+        <v>1025301</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="6:22">
       <c r="F43" s="1">
         <v>1025302</v>
       </c>
@@ -3498,8 +3801,30 @@
         <f t="shared" si="1"/>
         <v>1025302_1125302_6</v>
       </c>
-    </row>
-    <row r="44" spans="6:10">
+      <c r="M43" s="1">
+        <v>1025502</v>
+      </c>
+      <c r="N43" s="1">
+        <v>1125502</v>
+      </c>
+      <c r="O43">
+        <v>10</v>
+      </c>
+      <c r="P43" t="str">
+        <f t="shared" si="2"/>
+        <v>1025502_1125502_10</v>
+      </c>
+      <c r="R43" t="s">
+        <v>57</v>
+      </c>
+      <c r="U43" s="2">
+        <v>1025302</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="6:22">
       <c r="F44" s="1">
         <v>1025303</v>
       </c>
@@ -3513,8 +3838,30 @@
         <f t="shared" si="1"/>
         <v>1025303_1125303_6</v>
       </c>
-    </row>
-    <row r="45" spans="6:10">
+      <c r="M44" s="1">
+        <v>1025503</v>
+      </c>
+      <c r="N44" s="1">
+        <v>1125503</v>
+      </c>
+      <c r="O44">
+        <v>10</v>
+      </c>
+      <c r="P44" t="str">
+        <f t="shared" si="2"/>
+        <v>1025503_1125503_10</v>
+      </c>
+      <c r="R44" t="s">
+        <v>59</v>
+      </c>
+      <c r="U44" s="2">
+        <v>1025303</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="6:22">
       <c r="F45" s="1">
         <v>1025304</v>
       </c>
@@ -3528,8 +3875,30 @@
         <f t="shared" si="1"/>
         <v>1025304_1125304_6</v>
       </c>
-    </row>
-    <row r="46" spans="6:10">
+      <c r="M45" s="1">
+        <v>1025104</v>
+      </c>
+      <c r="N45" s="1">
+        <v>1125104</v>
+      </c>
+      <c r="O45">
+        <v>2</v>
+      </c>
+      <c r="P45" t="str">
+        <f t="shared" si="2"/>
+        <v>1025104_1125104_2</v>
+      </c>
+      <c r="R45" t="s">
+        <v>61</v>
+      </c>
+      <c r="U45" s="2">
+        <v>1025304</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="6:22">
       <c r="F46" s="1">
         <v>1025305</v>
       </c>
@@ -3543,8 +3912,30 @@
         <f t="shared" si="1"/>
         <v>1025305_1125305_6</v>
       </c>
-    </row>
-    <row r="47" spans="6:10">
+      <c r="M46" s="1">
+        <v>1025105</v>
+      </c>
+      <c r="N46" s="1">
+        <v>1125105</v>
+      </c>
+      <c r="O46">
+        <v>2</v>
+      </c>
+      <c r="P46" t="str">
+        <f t="shared" si="2"/>
+        <v>1025105_1125105_2</v>
+      </c>
+      <c r="R46" t="s">
+        <v>63</v>
+      </c>
+      <c r="U46" s="2">
+        <v>1025305</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="6:22">
       <c r="F47" s="1">
         <v>1025306</v>
       </c>
@@ -3558,8 +3949,30 @@
         <f t="shared" si="1"/>
         <v>1025306_1125306_6</v>
       </c>
-    </row>
-    <row r="48" spans="6:10">
+      <c r="M47" s="1">
+        <v>1025106</v>
+      </c>
+      <c r="N47" s="1">
+        <v>1125106</v>
+      </c>
+      <c r="O47">
+        <v>2</v>
+      </c>
+      <c r="P47" t="str">
+        <f t="shared" si="2"/>
+        <v>1025106_1125106_2</v>
+      </c>
+      <c r="R47" t="s">
+        <v>65</v>
+      </c>
+      <c r="U47" s="2">
+        <v>1025306</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="6:22">
       <c r="F48" s="1">
         <v>1025401</v>
       </c>
@@ -3573,8 +3986,30 @@
         <f t="shared" si="1"/>
         <v>1025401_1125401_8</v>
       </c>
-    </row>
-    <row r="49" spans="6:10">
+      <c r="M48" s="1">
+        <v>1025204</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1125204</v>
+      </c>
+      <c r="O48">
+        <v>4</v>
+      </c>
+      <c r="P48" t="str">
+        <f t="shared" si="2"/>
+        <v>1025204_1125204_4</v>
+      </c>
+      <c r="R48" t="s">
+        <v>67</v>
+      </c>
+      <c r="U48" s="3">
+        <v>1025401</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="6:22">
       <c r="F49" s="1">
         <v>1025402</v>
       </c>
@@ -3588,8 +4023,30 @@
         <f t="shared" si="1"/>
         <v>1025402_1125402_8</v>
       </c>
-    </row>
-    <row r="50" spans="6:10">
+      <c r="M49" s="1">
+        <v>1025205</v>
+      </c>
+      <c r="N49" s="1">
+        <v>1125205</v>
+      </c>
+      <c r="O49">
+        <v>4</v>
+      </c>
+      <c r="P49" t="str">
+        <f t="shared" si="2"/>
+        <v>1025205_1125205_4</v>
+      </c>
+      <c r="R49" t="s">
+        <v>69</v>
+      </c>
+      <c r="U49" s="3">
+        <v>1025402</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="6:22">
       <c r="F50" s="1">
         <v>1025403</v>
       </c>
@@ -3603,8 +4060,30 @@
         <f t="shared" si="1"/>
         <v>1025403_1125403_8</v>
       </c>
-    </row>
-    <row r="51" spans="6:10">
+      <c r="M50" s="1">
+        <v>1025206</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1125206</v>
+      </c>
+      <c r="O50">
+        <v>4</v>
+      </c>
+      <c r="P50" t="str">
+        <f t="shared" si="2"/>
+        <v>1025206_1125206_4</v>
+      </c>
+      <c r="R50" t="s">
+        <v>71</v>
+      </c>
+      <c r="U50" s="3">
+        <v>1025403</v>
+      </c>
+      <c r="V50" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="6:22">
       <c r="F51" s="1">
         <v>1025404</v>
       </c>
@@ -3618,8 +4097,30 @@
         <f t="shared" si="1"/>
         <v>1025404_1125404_8</v>
       </c>
-    </row>
-    <row r="52" spans="6:10">
+      <c r="M51" s="1">
+        <v>1025304</v>
+      </c>
+      <c r="N51" s="1">
+        <v>1125304</v>
+      </c>
+      <c r="O51">
+        <v>6</v>
+      </c>
+      <c r="P51" t="str">
+        <f t="shared" si="2"/>
+        <v>1025304_1125304_6</v>
+      </c>
+      <c r="R51" t="s">
+        <v>73</v>
+      </c>
+      <c r="U51" s="3">
+        <v>1025404</v>
+      </c>
+      <c r="V51" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="6:22">
       <c r="F52" s="1">
         <v>1025405</v>
       </c>
@@ -3633,8 +4134,30 @@
         <f t="shared" si="1"/>
         <v>1025405_1125405_8</v>
       </c>
-    </row>
-    <row r="53" spans="6:10">
+      <c r="M52" s="1">
+        <v>1025305</v>
+      </c>
+      <c r="N52" s="1">
+        <v>1125305</v>
+      </c>
+      <c r="O52">
+        <v>6</v>
+      </c>
+      <c r="P52" t="str">
+        <f t="shared" si="2"/>
+        <v>1025305_1125305_6</v>
+      </c>
+      <c r="R52" t="s">
+        <v>75</v>
+      </c>
+      <c r="U52" s="3">
+        <v>1025405</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="6:22">
       <c r="F53" s="1">
         <v>1025406</v>
       </c>
@@ -3648,8 +4171,30 @@
         <f t="shared" si="1"/>
         <v>1025406_1125406_8</v>
       </c>
-    </row>
-    <row r="54" spans="6:10">
+      <c r="M53" s="1">
+        <v>1025306</v>
+      </c>
+      <c r="N53" s="1">
+        <v>1125306</v>
+      </c>
+      <c r="O53">
+        <v>6</v>
+      </c>
+      <c r="P53" t="str">
+        <f t="shared" si="2"/>
+        <v>1025306_1125306_6</v>
+      </c>
+      <c r="R53" t="s">
+        <v>77</v>
+      </c>
+      <c r="U53" s="3">
+        <v>1025406</v>
+      </c>
+      <c r="V53" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="6:22">
       <c r="F54" s="1">
         <v>1025501</v>
       </c>
@@ -3663,8 +4208,30 @@
         <f t="shared" si="1"/>
         <v>1025501_1125501_10</v>
       </c>
-    </row>
-    <row r="55" spans="6:10">
+      <c r="M54" s="1">
+        <v>1025404</v>
+      </c>
+      <c r="N54" s="1">
+        <v>1125404</v>
+      </c>
+      <c r="O54">
+        <v>8</v>
+      </c>
+      <c r="P54" t="str">
+        <f t="shared" si="2"/>
+        <v>1025404_1125404_8</v>
+      </c>
+      <c r="R54" t="s">
+        <v>79</v>
+      </c>
+      <c r="U54" s="2">
+        <v>1025501</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="6:22">
       <c r="F55" s="1">
         <v>1025502</v>
       </c>
@@ -3678,8 +4245,30 @@
         <f t="shared" si="1"/>
         <v>1025502_1125502_10</v>
       </c>
-    </row>
-    <row r="56" spans="6:10">
+      <c r="M55" s="1">
+        <v>1025405</v>
+      </c>
+      <c r="N55" s="1">
+        <v>1125405</v>
+      </c>
+      <c r="O55">
+        <v>8</v>
+      </c>
+      <c r="P55" t="str">
+        <f t="shared" si="2"/>
+        <v>1025405_1125405_8</v>
+      </c>
+      <c r="R55" t="s">
+        <v>81</v>
+      </c>
+      <c r="U55" s="2">
+        <v>1025502</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="6:22">
       <c r="F56" s="1">
         <v>1025503</v>
       </c>
@@ -3693,8 +4282,30 @@
         <f t="shared" si="1"/>
         <v>1025503_1125503_10</v>
       </c>
-    </row>
-    <row r="57" spans="6:10">
+      <c r="M56" s="1">
+        <v>1025406</v>
+      </c>
+      <c r="N56" s="1">
+        <v>1125406</v>
+      </c>
+      <c r="O56">
+        <v>8</v>
+      </c>
+      <c r="P56" t="str">
+        <f t="shared" si="2"/>
+        <v>1025406_1125406_8</v>
+      </c>
+      <c r="R56" t="s">
+        <v>83</v>
+      </c>
+      <c r="U56" s="2">
+        <v>1025503</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="6:22">
       <c r="F57" s="1">
         <v>1025504</v>
       </c>
@@ -3708,8 +4319,30 @@
         <f t="shared" si="1"/>
         <v>1025504_1125504_10</v>
       </c>
-    </row>
-    <row r="58" spans="6:10">
+      <c r="M57" s="1">
+        <v>1025504</v>
+      </c>
+      <c r="N57" s="1">
+        <v>1125504</v>
+      </c>
+      <c r="O57">
+        <v>10</v>
+      </c>
+      <c r="P57" t="str">
+        <f t="shared" si="2"/>
+        <v>1025504_1125504_10</v>
+      </c>
+      <c r="R57" t="s">
+        <v>85</v>
+      </c>
+      <c r="U57" s="2">
+        <v>1025504</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="6:22">
       <c r="F58" s="1">
         <v>1025505</v>
       </c>
@@ -3723,8 +4356,30 @@
         <f t="shared" si="1"/>
         <v>1025505_1125505_10</v>
       </c>
-    </row>
-    <row r="59" spans="6:10">
+      <c r="M58" s="1">
+        <v>1025505</v>
+      </c>
+      <c r="N58" s="1">
+        <v>1125505</v>
+      </c>
+      <c r="O58">
+        <v>10</v>
+      </c>
+      <c r="P58" t="str">
+        <f t="shared" si="2"/>
+        <v>1025505_1125505_10</v>
+      </c>
+      <c r="R58" t="s">
+        <v>87</v>
+      </c>
+      <c r="U58" s="2">
+        <v>1025505</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="6:22">
       <c r="F59" s="1">
         <v>1025506</v>
       </c>
@@ -3737,6 +4392,28 @@
       <c r="J59" t="str">
         <f t="shared" si="1"/>
         <v>1025506_1125506_10</v>
+      </c>
+      <c r="M59" s="1">
+        <v>1025506</v>
+      </c>
+      <c r="N59" s="1">
+        <v>1125506</v>
+      </c>
+      <c r="O59">
+        <v>10</v>
+      </c>
+      <c r="P59" t="str">
+        <f t="shared" si="2"/>
+        <v>1025506_1125506_10</v>
+      </c>
+      <c r="R59" t="s">
+        <v>89</v>
+      </c>
+      <c r="U59" s="2">
+        <v>1025506</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -33,7 +33,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -169,6 +169,9 @@
     <t>名称备注</t>
   </si>
   <si>
+    <t>资源</t>
+  </si>
+  <si>
     <t>无奖励的服务能力</t>
   </si>
   <si>
@@ -215,6 +218,9 @@
   </si>
   <si>
     <t>DuplicatetoShard</t>
+  </si>
+  <si>
+    <t>Resource</t>
   </si>
   <si>
     <t>BaseServiceCapacity</t>
@@ -1571,30 +1577,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
     <col min="2" max="2" width="8.375" customWidth="1"/>
     <col min="3" max="3" width="22.125" customWidth="1"/>
     <col min="4" max="4" width="8.375" customWidth="1"/>
-    <col min="5" max="5" width="21.5" customWidth="1"/>
-    <col min="6" max="6" width="15.25" customWidth="1"/>
-    <col min="7" max="7" width="8.375" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12.875" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="6.375" customWidth="1"/>
-    <col min="12" max="12" width="113.816666666667" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="48.375" customWidth="1"/>
-    <col min="16" max="16" width="13.125" customWidth="1"/>
-    <col min="17" max="17" width="17.25" customWidth="1"/>
-    <col min="18" max="18" width="17.625" customWidth="1"/>
-    <col min="19" max="19" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="18.8166666666667" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="8" width="8.375" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="6.375" customWidth="1"/>
+    <col min="13" max="13" width="113.816666666667" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="48.375" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="18" max="18" width="17.25" customWidth="1"/>
+    <col min="19" max="19" width="17.625" customWidth="1"/>
+    <col min="20" max="20" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:19">
+    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:20">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1610,16 +1617,16 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="9" t="s">
@@ -1628,96 +1635,105 @@
       <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4"/>
-      <c r="P1" s="12"/>
+      <c r="O1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4"/>
       <c r="Q1" s="12"/>
-      <c r="R1" s="13"/>
+      <c r="R1" s="12"/>
       <c r="S1" s="13"/>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:19">
+      <c r="T1" s="13"/>
+    </row>
+    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:20">
       <c r="A2" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16" t="s">
-        <v>14</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="16"/>
       <c r="I2" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>15</v>
+      </c>
       <c r="K2" s="16"/>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="16"/>
+      <c r="M2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="17"/>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:19">
+      <c r="O2" s="17"/>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:20">
       <c r="A3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="G3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="K3" s="14"/>
-      <c r="L3" s="16" t="s">
-        <v>24</v>
-      </c>
+      <c r="L3" s="14"/>
       <c r="M3" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="17"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:19">
+        <v>26</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="17"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:20">
       <c r="A4" s="18"/>
       <c r="B4" s="19"/>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
-      <c r="F4" s="19"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
@@ -1725,9 +1741,10 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="21"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:19">
+      <c r="N4" s="19"/>
+      <c r="O4" s="21"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:20">
       <c r="A5" s="18">
         <v>1001</v>
       </c>
@@ -1735,43 +1752,46 @@
         <v>1</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F5" s="20">
         <v>20</v>
       </c>
-      <c r="F5" s="18">
+      <c r="G5" s="18">
         <v>100</v>
       </c>
-      <c r="G5" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="18">
+      <c r="H5" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="18">
         <v>0</v>
       </c>
-      <c r="I5" s="18">
+      <c r="J5" s="18">
         <v>500</v>
       </c>
-      <c r="J5" s="18">
-        <f>IF(H5=0,I5,($O$1*H5/100+1)*I5)</f>
+      <c r="K5" s="18">
+        <f>IF(I5=0,J5,($P$1*I5/100+1)*J5)</f>
         <v>500</v>
       </c>
-      <c r="K5" s="22">
-        <f>J5/SUM($J$5:$J$34)</f>
+      <c r="L5" s="22">
+        <f>K5/SUM($K$5:$K$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L5" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:19">
+      <c r="M5" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:20">
       <c r="A6" s="18">
         <v>1002</v>
       </c>
@@ -1779,41 +1799,44 @@
         <v>1</v>
       </c>
       <c r="C6" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F6" s="20">
+        <v>20</v>
+      </c>
+      <c r="G6" s="18">
+        <v>100</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="18">
+        <v>0</v>
+      </c>
+      <c r="J6" s="18">
+        <v>500</v>
+      </c>
+      <c r="K6" s="18">
+        <f t="shared" ref="K6:K34" si="0">IF(I6=0,J6,($P$1*I6/100+1)*J6)</f>
+        <v>500</v>
+      </c>
+      <c r="L6" s="22">
+        <f t="shared" ref="L6:L34" si="1">K6/SUM($K$5:$K$34)</f>
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="M6" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="20">
-        <v>20</v>
-      </c>
-      <c r="F6" s="18">
-        <v>100</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="18">
-        <v>0</v>
-      </c>
-      <c r="I6" s="18">
-        <v>500</v>
-      </c>
-      <c r="J6" s="18">
-        <f t="shared" ref="J6:J34" si="0">IF(H6=0,I6,($O$1*H6/100+1)*I6)</f>
-        <v>500</v>
-      </c>
-      <c r="K6" s="22">
-        <f t="shared" ref="K6:K34" si="1">J6/SUM($J$5:$J$34)</f>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="23"/>
       <c r="N6" s="23"/>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="O6" s="23"/>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" s="18">
         <v>1003</v>
       </c>
@@ -1821,41 +1844,44 @@
         <v>1</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F7" s="20">
         <v>20</v>
       </c>
-      <c r="F7" s="18">
+      <c r="G7" s="18">
         <v>450</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="18">
+      <c r="H7" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="18">
         <v>0</v>
       </c>
-      <c r="I7" s="18">
+      <c r="J7" s="18">
         <v>500</v>
       </c>
-      <c r="J7" s="18">
+      <c r="K7" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K7" s="22">
+      <c r="L7" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L7" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="23"/>
+      <c r="M7" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N7" s="23"/>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="O7" s="23"/>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="18">
         <v>2001</v>
       </c>
@@ -1863,41 +1889,44 @@
         <v>2</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F8" s="20">
         <v>20</v>
       </c>
-      <c r="F8" s="18">
+      <c r="G8" s="18">
         <v>450</v>
       </c>
-      <c r="G8" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="18">
+      <c r="H8" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="18">
         <v>0</v>
       </c>
-      <c r="I8" s="18">
+      <c r="J8" s="18">
         <v>300</v>
       </c>
-      <c r="J8" s="18">
+      <c r="K8" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K8" s="22">
+      <c r="L8" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L8" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="23"/>
+      <c r="M8" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N8" s="23"/>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="O8" s="23"/>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="18">
         <v>2002</v>
       </c>
@@ -1905,41 +1934,44 @@
         <v>2</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E9" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F9" s="20">
         <v>20</v>
       </c>
-      <c r="F9" s="18">
+      <c r="G9" s="18">
         <v>450</v>
       </c>
-      <c r="G9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="18">
+      <c r="H9" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="18">
         <v>0</v>
       </c>
-      <c r="I9" s="18">
+      <c r="J9" s="18">
         <v>300</v>
       </c>
-      <c r="J9" s="18">
+      <c r="K9" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K9" s="22">
+      <c r="L9" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L9" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="23"/>
+      <c r="M9" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N9" s="23"/>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="O9" s="23"/>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" s="18">
         <v>2003</v>
       </c>
@@ -1947,41 +1979,44 @@
         <v>2</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F10" s="20">
         <v>20</v>
       </c>
-      <c r="F10" s="18">
+      <c r="G10" s="18">
         <v>450</v>
       </c>
-      <c r="G10" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="18">
+      <c r="H10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="18">
         <v>0</v>
       </c>
-      <c r="I10" s="18">
+      <c r="J10" s="18">
         <v>300</v>
       </c>
-      <c r="J10" s="18">
+      <c r="K10" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K10" s="22">
+      <c r="L10" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L10" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="23"/>
+      <c r="M10" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N10" s="23"/>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="O10" s="23"/>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" s="18">
         <v>3001</v>
       </c>
@@ -1989,41 +2024,44 @@
         <v>3</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E11" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F11" s="20">
         <v>20</v>
       </c>
-      <c r="F11" s="18">
+      <c r="G11" s="18">
         <v>450</v>
       </c>
-      <c r="G11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="18">
+      <c r="H11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="18">
         <v>0</v>
       </c>
-      <c r="I11" s="18">
+      <c r="J11" s="18">
         <v>100</v>
       </c>
-      <c r="J11" s="18">
+      <c r="K11" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K11" s="22">
+      <c r="L11" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L11" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="23"/>
+      <c r="M11" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N11" s="23"/>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="O11" s="23"/>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="18">
         <v>3002</v>
       </c>
@@ -2031,41 +2069,44 @@
         <v>3</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F12" s="20">
         <v>20</v>
       </c>
-      <c r="F12" s="18">
+      <c r="G12" s="18">
         <v>450</v>
       </c>
-      <c r="G12" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="18">
+      <c r="H12" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="18">
         <v>0</v>
       </c>
-      <c r="I12" s="18">
+      <c r="J12" s="18">
         <v>10</v>
       </c>
-      <c r="J12" s="18">
+      <c r="K12" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K12" s="22">
+      <c r="L12" s="22">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="L12" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M12" s="23"/>
+      <c r="M12" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N12" s="23"/>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="O12" s="23"/>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="18">
         <v>3003</v>
       </c>
@@ -2073,41 +2114,44 @@
         <v>3</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E13" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F13" s="20">
         <v>20</v>
       </c>
-      <c r="F13" s="18">
+      <c r="G13" s="18">
         <v>450</v>
       </c>
-      <c r="G13" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="18">
+      <c r="H13" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="18">
         <v>0</v>
       </c>
-      <c r="I13" s="18">
+      <c r="J13" s="18">
         <v>100</v>
       </c>
-      <c r="J13" s="18">
+      <c r="K13" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K13" s="22">
+      <c r="L13" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L13" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M13" s="23"/>
+      <c r="M13" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N13" s="23"/>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="O13" s="23"/>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" s="18">
         <v>4001</v>
       </c>
@@ -2115,41 +2159,44 @@
         <v>4</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F14" s="20">
         <v>20</v>
       </c>
-      <c r="F14" s="18">
+      <c r="G14" s="18">
         <v>450</v>
       </c>
-      <c r="G14" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="18">
+      <c r="H14" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="18">
         <v>0</v>
       </c>
-      <c r="I14" s="18">
+      <c r="J14" s="18">
         <v>50</v>
       </c>
-      <c r="J14" s="18">
+      <c r="K14" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K14" s="22">
+      <c r="L14" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L14" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14" s="23"/>
+      <c r="M14" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N14" s="23"/>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="O14" s="23"/>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="18">
         <v>4002</v>
       </c>
@@ -2157,41 +2204,44 @@
         <v>4</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F15" s="20">
+        <v>20</v>
+      </c>
+      <c r="G15" s="18">
+        <v>450</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="18">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18">
         <v>50</v>
       </c>
-      <c r="D15" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="20">
-        <v>20</v>
-      </c>
-      <c r="F15" s="18">
-        <v>450</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="18">
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <v>50</v>
-      </c>
-      <c r="J15" s="18">
+      <c r="K15" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K15" s="22">
+      <c r="L15" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L15" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="23"/>
+      <c r="M15" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N15" s="23"/>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="O15" s="23"/>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="18">
         <v>4003</v>
       </c>
@@ -2199,41 +2249,44 @@
         <v>4</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E16" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F16" s="20">
         <v>20</v>
       </c>
-      <c r="F16" s="18">
+      <c r="G16" s="18">
         <v>450</v>
       </c>
-      <c r="G16" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="18">
+      <c r="H16" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="18">
         <v>0</v>
       </c>
-      <c r="I16" s="18">
+      <c r="J16" s="18">
         <v>50</v>
       </c>
-      <c r="J16" s="18">
+      <c r="K16" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K16" s="22">
+      <c r="L16" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L16" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M16" s="23"/>
+      <c r="M16" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N16" s="23"/>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" s="23"/>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="18">
         <v>5001</v>
       </c>
@@ -2241,41 +2294,44 @@
         <v>5</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F17" s="20">
         <v>20</v>
       </c>
-      <c r="F17" s="18">
+      <c r="G17" s="18">
         <v>450</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="18">
+      <c r="H17" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="18">
         <v>0</v>
       </c>
-      <c r="I17" s="18">
+      <c r="J17" s="18">
         <v>50</v>
       </c>
-      <c r="J17" s="18">
+      <c r="K17" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K17" s="22">
+      <c r="L17" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L17" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M17" s="23"/>
+      <c r="M17" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N17" s="23"/>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" s="23"/>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="18">
         <v>5002</v>
       </c>
@@ -2283,41 +2339,44 @@
         <v>5</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F18" s="20">
         <v>20</v>
       </c>
-      <c r="F18" s="18">
+      <c r="G18" s="18">
         <v>450</v>
       </c>
-      <c r="G18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="18">
+      <c r="H18" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="18">
         <v>0</v>
       </c>
-      <c r="I18" s="18">
+      <c r="J18" s="18">
         <v>50</v>
       </c>
-      <c r="J18" s="18">
+      <c r="K18" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K18" s="22">
+      <c r="L18" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L18" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M18" s="23"/>
+      <c r="M18" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N18" s="23"/>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" s="23"/>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="18">
         <v>5003</v>
       </c>
@@ -2325,41 +2384,44 @@
         <v>5</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E19" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F19" s="20">
         <v>20</v>
       </c>
-      <c r="F19" s="18">
+      <c r="G19" s="18">
         <v>450</v>
       </c>
-      <c r="G19" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="18">
+      <c r="H19" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="18">
         <v>0</v>
       </c>
-      <c r="I19" s="18">
+      <c r="J19" s="18">
         <v>50</v>
       </c>
-      <c r="J19" s="18">
+      <c r="K19" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K19" s="22">
+      <c r="L19" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L19" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M19" s="23"/>
+      <c r="M19" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N19" s="23"/>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" s="23"/>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="18">
         <v>1004</v>
       </c>
@@ -2367,41 +2429,44 @@
         <v>1</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E20" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F20" s="20">
         <v>20</v>
       </c>
-      <c r="F20" s="18">
+      <c r="G20" s="18">
         <v>450</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="18">
+      <c r="H20" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="18">
         <v>50</v>
       </c>
-      <c r="I20" s="18">
+      <c r="J20" s="18">
         <v>500</v>
       </c>
-      <c r="J20" s="18">
+      <c r="K20" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K20" s="22">
+      <c r="L20" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L20" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M20" s="23"/>
+      <c r="M20" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N20" s="23"/>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" s="23"/>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="18">
         <v>1005</v>
       </c>
@@ -2409,41 +2474,44 @@
         <v>1</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E21" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F21" s="20">
         <v>20</v>
       </c>
-      <c r="F21" s="18">
+      <c r="G21" s="18">
         <v>450</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="18">
+      <c r="H21" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="18">
         <v>50</v>
       </c>
-      <c r="I21" s="18">
+      <c r="J21" s="18">
         <v>500</v>
       </c>
-      <c r="J21" s="18">
+      <c r="K21" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K21" s="22">
+      <c r="L21" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L21" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M21" s="23"/>
+      <c r="M21" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N21" s="23"/>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" s="23"/>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="18">
         <v>1006</v>
       </c>
@@ -2451,41 +2519,44 @@
         <v>1</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F22" s="20">
         <v>20</v>
       </c>
-      <c r="F22" s="18">
+      <c r="G22" s="18">
         <v>450</v>
       </c>
-      <c r="G22" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="18">
+      <c r="H22" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="18">
         <v>50</v>
       </c>
-      <c r="I22" s="18">
+      <c r="J22" s="18">
         <v>500</v>
       </c>
-      <c r="J22" s="18">
+      <c r="K22" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K22" s="22">
+      <c r="L22" s="22">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="L22" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M22" s="23"/>
+      <c r="M22" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N22" s="23"/>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" s="23"/>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="18">
         <v>2004</v>
       </c>
@@ -2493,41 +2564,44 @@
         <v>2</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E23" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F23" s="20">
         <v>20</v>
       </c>
-      <c r="F23" s="18">
+      <c r="G23" s="18">
         <v>450</v>
       </c>
-      <c r="G23" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="18">
+      <c r="H23" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="18">
         <v>50</v>
       </c>
-      <c r="I23" s="18">
+      <c r="J23" s="18">
         <v>300</v>
       </c>
-      <c r="J23" s="18">
+      <c r="K23" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K23" s="22">
+      <c r="L23" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L23" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M23" s="23"/>
+      <c r="M23" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N23" s="23"/>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" s="23"/>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="18">
         <v>2005</v>
       </c>
@@ -2535,41 +2609,44 @@
         <v>2</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E24" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F24" s="20">
         <v>20</v>
       </c>
-      <c r="F24" s="18">
+      <c r="G24" s="18">
         <v>450</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="18">
+      <c r="H24" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="18">
         <v>50</v>
       </c>
-      <c r="I24" s="18">
+      <c r="J24" s="18">
         <v>300</v>
       </c>
-      <c r="J24" s="18">
+      <c r="K24" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K24" s="22">
+      <c r="L24" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L24" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M24" s="23"/>
+      <c r="M24" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N24" s="23"/>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" s="23"/>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="18">
         <v>2006</v>
       </c>
@@ -2577,41 +2654,44 @@
         <v>2</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E25" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F25" s="20">
         <v>20</v>
       </c>
-      <c r="F25" s="18">
+      <c r="G25" s="18">
         <v>450</v>
       </c>
-      <c r="G25" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="18">
+      <c r="H25" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="18">
         <v>50</v>
       </c>
-      <c r="I25" s="18">
+      <c r="J25" s="18">
         <v>300</v>
       </c>
-      <c r="J25" s="18">
+      <c r="K25" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K25" s="22">
+      <c r="L25" s="22">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="L25" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M25" s="23"/>
+      <c r="M25" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N25" s="23"/>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" s="23"/>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="18">
         <v>3004</v>
       </c>
@@ -2619,41 +2699,44 @@
         <v>3</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E26" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F26" s="20">
         <v>20</v>
       </c>
-      <c r="F26" s="18">
+      <c r="G26" s="18">
         <v>450</v>
       </c>
-      <c r="G26" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="18">
+      <c r="H26" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="18">
         <v>50</v>
       </c>
-      <c r="I26" s="18">
+      <c r="J26" s="18">
         <v>100</v>
       </c>
-      <c r="J26" s="18">
+      <c r="K26" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K26" s="22">
+      <c r="L26" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L26" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M26" s="23"/>
+      <c r="M26" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N26" s="23"/>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" s="23"/>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="18">
         <v>3005</v>
       </c>
@@ -2661,41 +2744,44 @@
         <v>3</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E27" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F27" s="20">
         <v>20</v>
       </c>
-      <c r="F27" s="18">
+      <c r="G27" s="18">
         <v>450</v>
       </c>
-      <c r="G27" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="18">
+      <c r="H27" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="18">
         <v>50</v>
       </c>
-      <c r="I27" s="18">
+      <c r="J27" s="18">
         <v>10</v>
       </c>
-      <c r="J27" s="18">
+      <c r="K27" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K27" s="22">
+      <c r="L27" s="22">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="L27" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M27" s="23"/>
+      <c r="M27" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N27" s="23"/>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" s="23"/>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="18">
         <v>3006</v>
       </c>
@@ -2703,41 +2789,44 @@
         <v>3</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E28" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F28" s="20">
         <v>20</v>
       </c>
-      <c r="F28" s="18">
+      <c r="G28" s="18">
         <v>450</v>
       </c>
-      <c r="G28" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" s="18">
+      <c r="H28" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="18">
         <v>50</v>
       </c>
-      <c r="I28" s="18">
+      <c r="J28" s="18">
         <v>100</v>
       </c>
-      <c r="J28" s="18">
+      <c r="K28" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K28" s="22">
+      <c r="L28" s="22">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="L28" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M28" s="23"/>
+      <c r="M28" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N28" s="23"/>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" s="23"/>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="18">
         <v>4004</v>
       </c>
@@ -2745,41 +2834,44 @@
         <v>4</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E29" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F29" s="20">
         <v>20</v>
       </c>
-      <c r="F29" s="18">
+      <c r="G29" s="18">
         <v>450</v>
       </c>
-      <c r="G29" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="18">
-        <v>50</v>
+      <c r="H29" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="I29" s="18">
         <v>50</v>
       </c>
       <c r="J29" s="18">
+        <v>50</v>
+      </c>
+      <c r="K29" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K29" s="22">
+      <c r="L29" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L29" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M29" s="23"/>
+      <c r="M29" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N29" s="23"/>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" s="23"/>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="18">
         <v>4005</v>
       </c>
@@ -2787,41 +2879,44 @@
         <v>4</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E30" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F30" s="20">
         <v>20</v>
       </c>
-      <c r="F30" s="18">
+      <c r="G30" s="18">
         <v>450</v>
       </c>
-      <c r="G30" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="18">
-        <v>50</v>
+      <c r="H30" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="I30" s="18">
         <v>50</v>
       </c>
       <c r="J30" s="18">
+        <v>50</v>
+      </c>
+      <c r="K30" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K30" s="22">
+      <c r="L30" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L30" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M30" s="23"/>
+      <c r="M30" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N30" s="23"/>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" s="23"/>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="18">
         <v>4006</v>
       </c>
@@ -2829,41 +2924,44 @@
         <v>4</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E31" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F31" s="20">
         <v>20</v>
       </c>
-      <c r="F31" s="18">
+      <c r="G31" s="18">
         <v>450</v>
       </c>
-      <c r="G31" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H31" s="18">
-        <v>50</v>
+      <c r="H31" s="18" t="s">
+        <v>37</v>
       </c>
       <c r="I31" s="18">
         <v>50</v>
       </c>
       <c r="J31" s="18">
+        <v>50</v>
+      </c>
+      <c r="K31" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K31" s="22">
+      <c r="L31" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L31" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M31" s="23"/>
+      <c r="M31" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N31" s="23"/>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" s="23"/>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="18">
         <v>5004</v>
       </c>
@@ -2871,41 +2969,44 @@
         <v>5</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E32" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F32" s="20">
         <v>20</v>
       </c>
-      <c r="F32" s="18">
+      <c r="G32" s="18">
         <v>450</v>
       </c>
-      <c r="G32" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" s="18">
-        <v>50</v>
+      <c r="H32" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="I32" s="18">
         <v>50</v>
       </c>
       <c r="J32" s="18">
+        <v>50</v>
+      </c>
+      <c r="K32" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K32" s="22">
+      <c r="L32" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L32" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M32" s="23"/>
+      <c r="M32" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N32" s="23"/>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" s="23"/>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="18">
         <v>5005</v>
       </c>
@@ -2913,41 +3014,44 @@
         <v>5</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E33" s="20">
+        <v>1001</v>
+      </c>
+      <c r="F33" s="20">
         <v>20</v>
       </c>
-      <c r="F33" s="18">
+      <c r="G33" s="18">
         <v>450</v>
       </c>
-      <c r="G33" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" s="18">
-        <v>50</v>
+      <c r="H33" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="I33" s="18">
         <v>50</v>
       </c>
       <c r="J33" s="18">
+        <v>50</v>
+      </c>
+      <c r="K33" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K33" s="22">
+      <c r="L33" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L33" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M33" s="23"/>
+      <c r="M33" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N33" s="23"/>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" s="23"/>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="18">
         <v>5006</v>
       </c>
@@ -2955,156 +3059,155 @@
         <v>5</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E34" s="20">
+        <v>1002</v>
+      </c>
+      <c r="F34" s="20">
         <v>20</v>
       </c>
-      <c r="F34" s="18">
+      <c r="G34" s="18">
         <v>450</v>
       </c>
-      <c r="G34" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="18">
-        <v>50</v>
+      <c r="H34" s="18" t="s">
+        <v>37</v>
       </c>
       <c r="I34" s="18">
         <v>50</v>
       </c>
       <c r="J34" s="18">
+        <v>50</v>
+      </c>
+      <c r="K34" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="K34" s="22">
+      <c r="L34" s="22">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="L34" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="M34" s="23"/>
+      <c r="M34" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N34" s="23"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="F35" s="24"/>
+      <c r="O34" s="23"/>
+    </row>
+    <row r="35" spans="1:15">
       <c r="G35" s="24"/>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="F36" s="24"/>
+      <c r="H35" s="24"/>
+    </row>
+    <row r="36" spans="1:15">
       <c r="G36" s="24"/>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="F37" s="24"/>
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37" spans="1:15">
       <c r="G37" s="24"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="F38" s="24"/>
+      <c r="H37" s="24"/>
+    </row>
+    <row r="38" spans="1:15">
       <c r="G38" s="24"/>
-    </row>
-    <row r="39" ht="17.25" spans="1:14">
+      <c r="H38" s="24"/>
+    </row>
+    <row r="39" ht="17.25" spans="1:15">
       <c r="C39" s="25"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39" s="24"/>
       <c r="G39" s="24"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="F40" s="24"/>
+      <c r="H39" s="24"/>
+    </row>
+    <row r="40" spans="1:15">
       <c r="G40" s="24"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="F41" s="24"/>
+      <c r="H40" s="24"/>
+    </row>
+    <row r="41" spans="1:15">
       <c r="G41" s="24"/>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="F42" s="24"/>
+      <c r="H41" s="24"/>
+    </row>
+    <row r="42" spans="1:15">
       <c r="G42" s="24"/>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="F43" s="24"/>
+      <c r="H42" s="24"/>
+    </row>
+    <row r="43" spans="1:15">
       <c r="G43" s="24"/>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="F44" s="24"/>
+      <c r="H43" s="24"/>
+    </row>
+    <row r="44" spans="1:15">
       <c r="G44" s="24"/>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="F45" s="24"/>
+      <c r="H44" s="24"/>
+    </row>
+    <row r="45" spans="1:15">
       <c r="G45" s="24"/>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="F46" s="24"/>
+      <c r="H45" s="24"/>
+    </row>
+    <row r="46" spans="1:15">
       <c r="G46" s="24"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="F47" s="24"/>
+      <c r="H46" s="24"/>
+    </row>
+    <row r="47" spans="1:15">
       <c r="G47" s="24"/>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="F48" s="24"/>
+      <c r="H47" s="24"/>
+    </row>
+    <row r="48" spans="1:15">
       <c r="G48" s="24"/>
-    </row>
-    <row r="49" spans="3:7">
-      <c r="F49" s="24"/>
+      <c r="H48" s="24"/>
+    </row>
+    <row r="49" spans="3:8">
       <c r="G49" s="24"/>
-    </row>
-    <row r="50" spans="3:7">
-      <c r="F50" s="24"/>
+      <c r="H49" s="24"/>
+    </row>
+    <row r="50" spans="3:8">
       <c r="G50" s="24"/>
-    </row>
-    <row r="51" spans="3:7">
-      <c r="F51" s="24"/>
+      <c r="H50" s="24"/>
+    </row>
+    <row r="51" spans="3:8">
       <c r="G51" s="24"/>
-    </row>
-    <row r="52" spans="3:7">
-      <c r="F52" s="24"/>
+      <c r="H51" s="24"/>
+    </row>
+    <row r="52" spans="3:8">
       <c r="G52" s="24"/>
-    </row>
-    <row r="53" ht="14.25" spans="3:7">
+      <c r="H52" s="24"/>
+    </row>
+    <row r="53" ht="14.25" spans="3:8">
       <c r="C53" s="26"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53" s="24"/>
       <c r="G53" s="24"/>
-    </row>
-    <row r="54" spans="3:7">
-      <c r="F54" s="24"/>
+      <c r="H53" s="24"/>
+    </row>
+    <row r="54" spans="3:8">
       <c r="G54" s="24"/>
-    </row>
-    <row r="55" spans="3:7">
-      <c r="F55" s="24"/>
+      <c r="H54" s="24"/>
+    </row>
+    <row r="55" spans="3:8">
       <c r="G55" s="24"/>
-    </row>
-    <row r="56" spans="3:7">
-      <c r="F56" s="24"/>
+      <c r="H55" s="24"/>
+    </row>
+    <row r="56" spans="3:8">
       <c r="G56" s="24"/>
-    </row>
-    <row r="57" spans="3:7">
-      <c r="F57" s="24"/>
+      <c r="H56" s="24"/>
+    </row>
+    <row r="57" spans="3:8">
       <c r="G57" s="24"/>
-    </row>
-    <row r="58" spans="3:7">
-      <c r="F58" s="24"/>
+      <c r="H57" s="24"/>
+    </row>
+    <row r="58" spans="3:8">
       <c r="G58" s="24"/>
-    </row>
-    <row r="59" spans="3:7">
-      <c r="F59" s="24"/>
+      <c r="H58" s="24"/>
+    </row>
+    <row r="59" spans="3:8">
       <c r="G59" s="24"/>
-    </row>
-    <row r="60" spans="3:7">
-      <c r="F60" s="24"/>
+      <c r="H59" s="24"/>
+    </row>
+    <row r="60" spans="3:8">
       <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="M1:N1 M4:N4 G17:G18 G14:G15 G11:G12 G4:G9 A4:B4 G1 A1:B1 M61:N63 N35:N60 N6 N8:N19 N2:N3" formula="1"/>
+    <ignoredError sqref="O2:O3 O8:O19 O6 O35:O60 N61:O63 A1:B1 H1 A4:B4 H4:H9 H11:H12 H14:H15 H17:H18 N4:O4 N1:O1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3118,7 +3221,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -3297,13 +3400,13 @@
     </row>
     <row r="27" spans="6:22">
       <c r="F27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="6:22">
@@ -3334,13 +3437,13 @@
         <v>1025101_1125101_2</v>
       </c>
       <c r="R30" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="U30" s="2">
         <v>1025101</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="6:22">
@@ -3371,13 +3474,13 @@
         <v>1025102_1125102_2</v>
       </c>
       <c r="R31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U31" s="2">
         <v>1025102</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="6:22">
@@ -3408,13 +3511,13 @@
         <v>1025103_1125103_2</v>
       </c>
       <c r="R32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U32" s="2">
         <v>1025103</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="6:22">
@@ -3445,13 +3548,13 @@
         <v>1025201_1125201_4</v>
       </c>
       <c r="R33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U33" s="2">
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -3482,13 +3585,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U34" s="2">
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -3519,13 +3622,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="U35" s="2">
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -3556,13 +3659,13 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U36" s="3">
         <v>1025201</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="6:22">
@@ -3593,13 +3696,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -3630,13 +3733,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -3667,13 +3770,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -3704,13 +3807,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -3741,13 +3844,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -3778,13 +3881,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -3815,13 +3918,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -3852,13 +3955,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -3889,13 +3992,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -3926,13 +4029,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -3963,13 +4066,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4000,13 +4103,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4037,13 +4140,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4074,13 +4177,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4111,13 +4214,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -4148,13 +4251,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -4185,13 +4288,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -4222,13 +4325,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -4259,13 +4362,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -4296,13 +4399,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -4333,13 +4436,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -4370,13 +4473,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -4407,13 +4510,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -1760,9 +1760,7 @@
       <c r="E5" s="20">
         <v>1001</v>
       </c>
-      <c r="F5" s="20">
-        <v>20</v>
-      </c>
+      <c r="F5" s="20"/>
       <c r="G5" s="18">
         <v>100</v>
       </c>
@@ -1807,9 +1805,7 @@
       <c r="E6" s="20">
         <v>1002</v>
       </c>
-      <c r="F6" s="20">
-        <v>20</v>
-      </c>
+      <c r="F6" s="20"/>
       <c r="G6" s="18">
         <v>100</v>
       </c>
@@ -1852,9 +1848,7 @@
       <c r="E7" s="20">
         <v>1001</v>
       </c>
-      <c r="F7" s="20">
-        <v>20</v>
-      </c>
+      <c r="F7" s="20"/>
       <c r="G7" s="18">
         <v>450</v>
       </c>
@@ -1897,9 +1891,7 @@
       <c r="E8" s="20">
         <v>1002</v>
       </c>
-      <c r="F8" s="20">
-        <v>20</v>
-      </c>
+      <c r="F8" s="20"/>
       <c r="G8" s="18">
         <v>450</v>
       </c>
@@ -1942,9 +1934,7 @@
       <c r="E9" s="20">
         <v>1001</v>
       </c>
-      <c r="F9" s="20">
-        <v>20</v>
-      </c>
+      <c r="F9" s="20"/>
       <c r="G9" s="18">
         <v>450</v>
       </c>
@@ -1987,9 +1977,7 @@
       <c r="E10" s="20">
         <v>1002</v>
       </c>
-      <c r="F10" s="20">
-        <v>20</v>
-      </c>
+      <c r="F10" s="20"/>
       <c r="G10" s="18">
         <v>450</v>
       </c>
@@ -2032,9 +2020,7 @@
       <c r="E11" s="20">
         <v>1001</v>
       </c>
-      <c r="F11" s="20">
-        <v>20</v>
-      </c>
+      <c r="F11" s="20"/>
       <c r="G11" s="18">
         <v>450</v>
       </c>
@@ -2077,9 +2063,7 @@
       <c r="E12" s="20">
         <v>1002</v>
       </c>
-      <c r="F12" s="20">
-        <v>20</v>
-      </c>
+      <c r="F12" s="20"/>
       <c r="G12" s="18">
         <v>450</v>
       </c>
@@ -2122,9 +2106,7 @@
       <c r="E13" s="20">
         <v>1001</v>
       </c>
-      <c r="F13" s="20">
-        <v>20</v>
-      </c>
+      <c r="F13" s="20"/>
       <c r="G13" s="18">
         <v>450</v>
       </c>
@@ -2167,9 +2149,7 @@
       <c r="E14" s="20">
         <v>1002</v>
       </c>
-      <c r="F14" s="20">
-        <v>20</v>
-      </c>
+      <c r="F14" s="20"/>
       <c r="G14" s="18">
         <v>450</v>
       </c>
@@ -2212,9 +2192,7 @@
       <c r="E15" s="20">
         <v>1001</v>
       </c>
-      <c r="F15" s="20">
-        <v>20</v>
-      </c>
+      <c r="F15" s="20"/>
       <c r="G15" s="18">
         <v>450</v>
       </c>
@@ -2257,9 +2235,7 @@
       <c r="E16" s="20">
         <v>1002</v>
       </c>
-      <c r="F16" s="20">
-        <v>20</v>
-      </c>
+      <c r="F16" s="20"/>
       <c r="G16" s="18">
         <v>450</v>
       </c>
@@ -2302,9 +2278,7 @@
       <c r="E17" s="20">
         <v>1001</v>
       </c>
-      <c r="F17" s="20">
-        <v>20</v>
-      </c>
+      <c r="F17" s="20"/>
       <c r="G17" s="18">
         <v>450</v>
       </c>
@@ -2347,9 +2321,7 @@
       <c r="E18" s="20">
         <v>1002</v>
       </c>
-      <c r="F18" s="20">
-        <v>20</v>
-      </c>
+      <c r="F18" s="20"/>
       <c r="G18" s="18">
         <v>450</v>
       </c>
@@ -2392,9 +2364,7 @@
       <c r="E19" s="20">
         <v>1001</v>
       </c>
-      <c r="F19" s="20">
-        <v>20</v>
-      </c>
+      <c r="F19" s="20"/>
       <c r="G19" s="18">
         <v>450</v>
       </c>
@@ -2437,9 +2407,7 @@
       <c r="E20" s="20">
         <v>1002</v>
       </c>
-      <c r="F20" s="20">
-        <v>20</v>
-      </c>
+      <c r="F20" s="20"/>
       <c r="G20" s="18">
         <v>450</v>
       </c>
@@ -2482,9 +2450,7 @@
       <c r="E21" s="20">
         <v>1001</v>
       </c>
-      <c r="F21" s="20">
-        <v>20</v>
-      </c>
+      <c r="F21" s="20"/>
       <c r="G21" s="18">
         <v>450</v>
       </c>
@@ -2527,9 +2493,7 @@
       <c r="E22" s="20">
         <v>1002</v>
       </c>
-      <c r="F22" s="20">
-        <v>20</v>
-      </c>
+      <c r="F22" s="20"/>
       <c r="G22" s="18">
         <v>450</v>
       </c>
@@ -2572,9 +2536,7 @@
       <c r="E23" s="20">
         <v>1001</v>
       </c>
-      <c r="F23" s="20">
-        <v>20</v>
-      </c>
+      <c r="F23" s="20"/>
       <c r="G23" s="18">
         <v>450</v>
       </c>
@@ -2617,9 +2579,7 @@
       <c r="E24" s="20">
         <v>1002</v>
       </c>
-      <c r="F24" s="20">
-        <v>20</v>
-      </c>
+      <c r="F24" s="20"/>
       <c r="G24" s="18">
         <v>450</v>
       </c>
@@ -2662,9 +2622,7 @@
       <c r="E25" s="20">
         <v>1001</v>
       </c>
-      <c r="F25" s="20">
-        <v>20</v>
-      </c>
+      <c r="F25" s="20"/>
       <c r="G25" s="18">
         <v>450</v>
       </c>
@@ -2707,9 +2665,7 @@
       <c r="E26" s="20">
         <v>1002</v>
       </c>
-      <c r="F26" s="20">
-        <v>20</v>
-      </c>
+      <c r="F26" s="20"/>
       <c r="G26" s="18">
         <v>450</v>
       </c>
@@ -2752,9 +2708,7 @@
       <c r="E27" s="20">
         <v>1001</v>
       </c>
-      <c r="F27" s="20">
-        <v>20</v>
-      </c>
+      <c r="F27" s="20"/>
       <c r="G27" s="18">
         <v>450</v>
       </c>
@@ -2797,9 +2751,7 @@
       <c r="E28" s="20">
         <v>1002</v>
       </c>
-      <c r="F28" s="20">
-        <v>20</v>
-      </c>
+      <c r="F28" s="20"/>
       <c r="G28" s="18">
         <v>450</v>
       </c>
@@ -2842,9 +2794,7 @@
       <c r="E29" s="20">
         <v>1001</v>
       </c>
-      <c r="F29" s="20">
-        <v>20</v>
-      </c>
+      <c r="F29" s="20"/>
       <c r="G29" s="18">
         <v>450</v>
       </c>
@@ -2887,9 +2837,7 @@
       <c r="E30" s="20">
         <v>1002</v>
       </c>
-      <c r="F30" s="20">
-        <v>20</v>
-      </c>
+      <c r="F30" s="20"/>
       <c r="G30" s="18">
         <v>450</v>
       </c>
@@ -2932,9 +2880,7 @@
       <c r="E31" s="20">
         <v>1001</v>
       </c>
-      <c r="F31" s="20">
-        <v>20</v>
-      </c>
+      <c r="F31" s="20"/>
       <c r="G31" s="18">
         <v>450</v>
       </c>
@@ -2977,9 +2923,7 @@
       <c r="E32" s="20">
         <v>1002</v>
       </c>
-      <c r="F32" s="20">
-        <v>20</v>
-      </c>
+      <c r="F32" s="20"/>
       <c r="G32" s="18">
         <v>450</v>
       </c>
@@ -3022,9 +2966,7 @@
       <c r="E33" s="20">
         <v>1001</v>
       </c>
-      <c r="F33" s="20">
-        <v>20</v>
-      </c>
+      <c r="F33" s="20"/>
       <c r="G33" s="18">
         <v>450</v>
       </c>
@@ -3067,9 +3009,7 @@
       <c r="E34" s="20">
         <v>1002</v>
       </c>
-      <c r="F34" s="20">
-        <v>20</v>
-      </c>
+      <c r="F34" s="20"/>
       <c r="G34" s="18">
         <v>450</v>
       </c>
@@ -3207,7 +3147,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="O2:O3 O8:O19 O6 O35:O60 N61:O63 A1:B1 H1 A4:B4 H4:H9 H11:H12 H14:H15 H17:H18 N4:O4 N1:O1" formula="1"/>
+    <ignoredError sqref="N1:O1 N4:O4 H17:H18 H14:H15 H11:H12 H4:H9 A4:B4 H1 A1:B1 N61:O63 O35:O60 O6 O8:O19 O2:O3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -33,6 +33,28 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应的场景动画资源</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G1" authorId="0">
       <text>
         <r>
@@ -3147,7 +3169,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="N1:O1 N4:O4 H17:H18 H14:H15 H11:H12 H4:H9 A4:B4 H1 A1:B1 N61:O63 O35:O60 O6 O8:O19 O2:O3" formula="1"/>
+    <ignoredError sqref="O2:O3 O8:O19 O6 O35:O60 N61:O63 A1:B1 H1 A4:B4 H4:H9 H11:H12 H14:H15 H17:H18 N4:O4 N1:O1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -33,7 +33,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -77,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -126,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -149,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="99">
   <si>
     <t>ID</t>
   </si>
@@ -191,6 +191,9 @@
     <t>名称备注</t>
   </si>
   <si>
+    <t>是否默认解锁</t>
+  </si>
+  <si>
     <t>资源</t>
   </si>
   <si>
@@ -230,6 +233,9 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>boolean</t>
+  </si>
+  <si>
     <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
@@ -240,6 +246,9 @@
   </si>
   <si>
     <t>DuplicatetoShard</t>
+  </si>
+  <si>
+    <t>IsDefaultUnlocked</t>
   </si>
   <si>
     <t>Resource</t>
@@ -1201,7 +1210,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1267,6 +1276,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1599,31 +1611,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
     <col min="2" max="2" width="8.375" customWidth="1"/>
     <col min="3" max="3" width="22.125" customWidth="1"/>
     <col min="4" max="4" width="8.375" customWidth="1"/>
-    <col min="5" max="5" width="18.8166666666667" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
-    <col min="7" max="7" width="15.25" customWidth="1"/>
-    <col min="8" max="8" width="8.375" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="6.375" customWidth="1"/>
-    <col min="13" max="13" width="113.816666666667" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="48.375" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
-    <col min="18" max="18" width="17.25" customWidth="1"/>
-    <col min="19" max="19" width="17.625" customWidth="1"/>
-    <col min="20" max="20" width="15.375" customWidth="1"/>
+    <col min="5" max="6" width="18.8166666666667" customWidth="1"/>
+    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="8" max="8" width="15.25" customWidth="1"/>
+    <col min="9" max="9" width="8.375" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="6.375" customWidth="1"/>
+    <col min="14" max="14" width="113.816666666667" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="48.375" customWidth="1"/>
+    <col min="18" max="18" width="13.125" customWidth="1"/>
+    <col min="19" max="19" width="17.25" customWidth="1"/>
+    <col min="20" max="20" width="17.625" customWidth="1"/>
+    <col min="21" max="21" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:20">
+    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:21">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1642,16 +1654,16 @@
       <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
@@ -1660,103 +1672,112 @@
       <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="12"/>
+      <c r="P1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4"/>
       <c r="R1" s="12"/>
-      <c r="S1" s="13"/>
+      <c r="S1" s="12"/>
       <c r="T1" s="13"/>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:20">
+      <c r="U1" s="13"/>
+    </row>
+    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:21">
       <c r="A2" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16" t="s">
-        <v>15</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="16"/>
       <c r="J2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="L2" s="16"/>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="16"/>
+      <c r="N2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="17"/>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:20">
+      <c r="P2" s="17"/>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:21">
       <c r="A3" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="15"/>
-      <c r="E3" s="15" t="s">
-        <v>21</v>
+      <c r="E3" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="G3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="14"/>
+      <c r="H3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="L3" s="14"/>
-      <c r="M3" s="16" t="s">
-        <v>26</v>
-      </c>
+      <c r="M3" s="14"/>
       <c r="N3" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="17"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:20">
+        <v>29</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="17"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:21">
       <c r="A4" s="18"/>
       <c r="B4" s="19"/>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
-      <c r="G4" s="19"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -1764,9 +1785,10 @@
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
-      <c r="O4" s="21"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:20">
+      <c r="O4" s="19"/>
+      <c r="P4" s="21"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:21">
       <c r="A5" s="18">
         <v>1001</v>
       </c>
@@ -1774,44 +1796,47 @@
         <v>1</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="20">
+        <v>32</v>
+      </c>
+      <c r="E5" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="20">
         <v>1001</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="18">
+      <c r="G5" s="20"/>
+      <c r="H5" s="18">
         <v>100</v>
       </c>
-      <c r="H5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="18">
+      <c r="I5" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="18">
         <v>0</v>
       </c>
-      <c r="J5" s="18">
+      <c r="K5" s="18">
         <v>500</v>
       </c>
-      <c r="K5" s="18">
-        <f>IF(I5=0,J5,($P$1*I5/100+1)*J5)</f>
+      <c r="L5" s="18">
+        <f>IF(J5=0,K5,($Q$1*J5/100+1)*K5)</f>
         <v>500</v>
       </c>
-      <c r="L5" s="22">
-        <f>K5/SUM($K$5:$K$34)</f>
+      <c r="M5" s="23">
+        <f>L5/SUM($L$5:$L$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="M5" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:20">
+      <c r="N5" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:21">
       <c r="A6" s="18">
         <v>1002</v>
       </c>
@@ -1819,42 +1844,45 @@
         <v>1</v>
       </c>
       <c r="C6" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="20">
+        <v>1002</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="18">
+        <v>100</v>
+      </c>
+      <c r="I6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="J6" s="18">
+        <v>0</v>
+      </c>
+      <c r="K6" s="18">
+        <v>500</v>
+      </c>
+      <c r="L6" s="18">
+        <f t="shared" ref="L6:L34" si="0">IF(J6=0,K6,($Q$1*J6/100+1)*K6)</f>
+        <v>500</v>
+      </c>
+      <c r="M6" s="23">
+        <f t="shared" ref="M6:M34" si="1">L6/SUM($L$5:$L$34)</f>
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="N6" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="20">
-        <v>1002</v>
-      </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="18">
-        <v>100</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="18">
-        <v>0</v>
-      </c>
-      <c r="J6" s="18">
-        <v>500</v>
-      </c>
-      <c r="K6" s="18">
-        <f t="shared" ref="K6:K34" si="0">IF(I6=0,J6,($P$1*I6/100+1)*J6)</f>
-        <v>500</v>
-      </c>
-      <c r="L6" s="22">
-        <f t="shared" ref="L6:L34" si="1">K6/SUM($K$5:$K$34)</f>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="18">
         <v>1003</v>
       </c>
@@ -1862,42 +1890,45 @@
         <v>1</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="20">
+        <v>39</v>
+      </c>
+      <c r="E7" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
         <v>1001</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18">
+      <c r="G7" s="20"/>
+      <c r="H7" s="18">
         <v>450</v>
       </c>
-      <c r="H7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="18">
+      <c r="I7" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="18">
         <v>0</v>
       </c>
-      <c r="J7" s="18">
+      <c r="K7" s="18">
         <v>500</v>
       </c>
-      <c r="K7" s="18">
+      <c r="L7" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="L7" s="22">
+      <c r="M7" s="23">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="M7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="N7" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="18">
         <v>2001</v>
       </c>
@@ -1905,42 +1936,45 @@
         <v>2</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="20">
+        <v>42</v>
+      </c>
+      <c r="E8" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="20">
         <v>1002</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="18">
+      <c r="G8" s="20"/>
+      <c r="H8" s="18">
         <v>450</v>
       </c>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="18">
+      <c r="I8" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="18">
         <v>0</v>
       </c>
-      <c r="J8" s="18">
+      <c r="K8" s="18">
         <v>300</v>
       </c>
-      <c r="K8" s="18">
+      <c r="L8" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="L8" s="22">
+      <c r="M8" s="23">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="M8" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="N8" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="18">
         <v>2002</v>
       </c>
@@ -1948,42 +1982,45 @@
         <v>2</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="20">
+        <v>44</v>
+      </c>
+      <c r="E9" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="20">
         <v>1001</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="18">
+      <c r="G9" s="20"/>
+      <c r="H9" s="18">
         <v>450</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="18">
+      <c r="I9" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="18">
         <v>0</v>
       </c>
-      <c r="J9" s="18">
+      <c r="K9" s="18">
         <v>300</v>
       </c>
-      <c r="K9" s="18">
+      <c r="L9" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="L9" s="22">
+      <c r="M9" s="23">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="M9" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="N9" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="18">
         <v>2003</v>
       </c>
@@ -1991,42 +2028,45 @@
         <v>2</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="20">
+        <v>46</v>
+      </c>
+      <c r="E10" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="20">
         <v>1002</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="18">
+      <c r="G10" s="20"/>
+      <c r="H10" s="18">
         <v>450</v>
       </c>
-      <c r="H10" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="18">
+      <c r="I10" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="18">
         <v>0</v>
       </c>
-      <c r="J10" s="18">
+      <c r="K10" s="18">
         <v>300</v>
       </c>
-      <c r="K10" s="18">
+      <c r="L10" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="L10" s="22">
+      <c r="M10" s="23">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="M10" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="N10" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="18">
         <v>3001</v>
       </c>
@@ -2034,42 +2074,45 @@
         <v>3</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="20">
+        <v>48</v>
+      </c>
+      <c r="E11" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="20">
         <v>1001</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="18">
+      <c r="G11" s="20"/>
+      <c r="H11" s="18">
         <v>450</v>
       </c>
-      <c r="H11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="18">
+      <c r="I11" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="18">
         <v>0</v>
       </c>
-      <c r="J11" s="18">
+      <c r="K11" s="18">
         <v>100</v>
       </c>
-      <c r="K11" s="18">
+      <c r="L11" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L11" s="22">
+      <c r="M11" s="23">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="M11" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="N11" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="18">
         <v>3002</v>
       </c>
@@ -2077,42 +2120,45 @@
         <v>3</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="20">
+        <v>50</v>
+      </c>
+      <c r="E12" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="20">
         <v>1002</v>
       </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="18">
+      <c r="G12" s="20"/>
+      <c r="H12" s="18">
         <v>450</v>
       </c>
-      <c r="H12" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="18">
+      <c r="I12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="18">
         <v>0</v>
       </c>
-      <c r="J12" s="18">
+      <c r="K12" s="18">
         <v>10</v>
       </c>
-      <c r="K12" s="18">
+      <c r="L12" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L12" s="22">
+      <c r="M12" s="23">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="M12" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="N12" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="18">
         <v>3003</v>
       </c>
@@ -2120,42 +2166,45 @@
         <v>3</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="20">
+        <v>52</v>
+      </c>
+      <c r="E13" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="20">
         <v>1001</v>
       </c>
-      <c r="F13" s="20"/>
-      <c r="G13" s="18">
+      <c r="G13" s="20"/>
+      <c r="H13" s="18">
         <v>450</v>
       </c>
-      <c r="H13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="18">
+      <c r="I13" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="18">
         <v>0</v>
       </c>
-      <c r="J13" s="18">
+      <c r="K13" s="18">
         <v>100</v>
       </c>
-      <c r="K13" s="18">
+      <c r="L13" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L13" s="22">
+      <c r="M13" s="23">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="M13" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="N13" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="18">
         <v>4001</v>
       </c>
@@ -2163,42 +2212,45 @@
         <v>4</v>
       </c>
       <c r="C14" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <v>1002</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="18">
+        <v>450</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="18">
+        <v>0</v>
+      </c>
+      <c r="K14" s="18">
         <v>50</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="20">
-        <v>1002</v>
-      </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="18">
-        <v>450</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="18">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18">
-        <v>50</v>
-      </c>
-      <c r="K14" s="18">
+      <c r="L14" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L14" s="22">
+      <c r="M14" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M14" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="N14" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="18">
         <v>4002</v>
       </c>
@@ -2206,42 +2258,45 @@
         <v>4</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="20">
+        <v>56</v>
+      </c>
+      <c r="E15" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="20">
         <v>1001</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="18">
+      <c r="G15" s="20"/>
+      <c r="H15" s="18">
         <v>450</v>
       </c>
-      <c r="H15" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="18">
+      <c r="I15" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="18">
         <v>0</v>
       </c>
-      <c r="J15" s="18">
+      <c r="K15" s="18">
         <v>50</v>
       </c>
-      <c r="K15" s="18">
+      <c r="L15" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L15" s="22">
+      <c r="M15" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M15" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="N15" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="18">
         <v>4003</v>
       </c>
@@ -2249,42 +2304,45 @@
         <v>4</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="20">
+        <v>58</v>
+      </c>
+      <c r="E16" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="20">
         <v>1002</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="18">
+      <c r="G16" s="20"/>
+      <c r="H16" s="18">
         <v>450</v>
       </c>
-      <c r="H16" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="18">
+      <c r="I16" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="18">
         <v>0</v>
       </c>
-      <c r="J16" s="18">
+      <c r="K16" s="18">
         <v>50</v>
       </c>
-      <c r="K16" s="18">
+      <c r="L16" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L16" s="22">
+      <c r="M16" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M16" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="18">
         <v>5001</v>
       </c>
@@ -2292,42 +2350,45 @@
         <v>5</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="20">
+        <v>60</v>
+      </c>
+      <c r="E17" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="20">
         <v>1001</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="18">
+      <c r="G17" s="20"/>
+      <c r="H17" s="18">
         <v>450</v>
       </c>
-      <c r="H17" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="18">
+      <c r="I17" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="18">
         <v>0</v>
       </c>
-      <c r="J17" s="18">
+      <c r="K17" s="18">
         <v>50</v>
       </c>
-      <c r="K17" s="18">
+      <c r="L17" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L17" s="22">
+      <c r="M17" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M17" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="18">
         <v>5002</v>
       </c>
@@ -2335,42 +2396,45 @@
         <v>5</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="20">
+        <v>62</v>
+      </c>
+      <c r="E18" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="20">
         <v>1002</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="18">
+      <c r="G18" s="20"/>
+      <c r="H18" s="18">
         <v>450</v>
       </c>
-      <c r="H18" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="18">
+      <c r="I18" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="18">
         <v>0</v>
       </c>
-      <c r="J18" s="18">
+      <c r="K18" s="18">
         <v>50</v>
       </c>
-      <c r="K18" s="18">
+      <c r="L18" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L18" s="22">
+      <c r="M18" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M18" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="18">
         <v>5003</v>
       </c>
@@ -2378,42 +2442,45 @@
         <v>5</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="20">
+        <v>64</v>
+      </c>
+      <c r="E19" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="20">
         <v>1001</v>
       </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="18">
+      <c r="G19" s="20"/>
+      <c r="H19" s="18">
         <v>450</v>
       </c>
-      <c r="H19" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I19" s="18">
+      <c r="I19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="18">
         <v>0</v>
       </c>
-      <c r="J19" s="18">
+      <c r="K19" s="18">
         <v>50</v>
       </c>
-      <c r="K19" s="18">
+      <c r="L19" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L19" s="22">
+      <c r="M19" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M19" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="18">
         <v>1004</v>
       </c>
@@ -2421,42 +2488,45 @@
         <v>1</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="20">
+        <v>66</v>
+      </c>
+      <c r="E20" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="20">
         <v>1002</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="18">
+      <c r="G20" s="20"/>
+      <c r="H20" s="18">
         <v>450</v>
       </c>
-      <c r="H20" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="18">
+      <c r="I20" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="18">
         <v>50</v>
       </c>
-      <c r="J20" s="18">
+      <c r="K20" s="18">
         <v>500</v>
       </c>
-      <c r="K20" s="18">
+      <c r="L20" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="L20" s="22">
+      <c r="M20" s="23">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="M20" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="18">
         <v>1005</v>
       </c>
@@ -2464,42 +2534,45 @@
         <v>1</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="20">
+        <v>68</v>
+      </c>
+      <c r="E21" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="20">
         <v>1001</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="18">
+      <c r="G21" s="20"/>
+      <c r="H21" s="18">
         <v>450</v>
       </c>
-      <c r="H21" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="18">
+      <c r="I21" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="18">
         <v>50</v>
       </c>
-      <c r="J21" s="18">
+      <c r="K21" s="18">
         <v>500</v>
       </c>
-      <c r="K21" s="18">
+      <c r="L21" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="L21" s="22">
+      <c r="M21" s="23">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="M21" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="18">
         <v>1006</v>
       </c>
@@ -2507,42 +2580,45 @@
         <v>1</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="20">
+        <v>70</v>
+      </c>
+      <c r="E22" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="20">
         <v>1002</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="18">
+      <c r="G22" s="20"/>
+      <c r="H22" s="18">
         <v>450</v>
       </c>
-      <c r="H22" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I22" s="18">
+      <c r="I22" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="18">
         <v>50</v>
       </c>
-      <c r="J22" s="18">
+      <c r="K22" s="18">
         <v>500</v>
       </c>
-      <c r="K22" s="18">
+      <c r="L22" s="18">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="L22" s="22">
+      <c r="M22" s="23">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="M22" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="18">
         <v>2004</v>
       </c>
@@ -2550,42 +2626,45 @@
         <v>2</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="20">
+        <v>72</v>
+      </c>
+      <c r="E23" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="20">
         <v>1001</v>
       </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="18">
+      <c r="G23" s="20"/>
+      <c r="H23" s="18">
         <v>450</v>
       </c>
-      <c r="H23" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="18">
+      <c r="I23" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="18">
         <v>50</v>
       </c>
-      <c r="J23" s="18">
+      <c r="K23" s="18">
         <v>300</v>
       </c>
-      <c r="K23" s="18">
+      <c r="L23" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="L23" s="22">
+      <c r="M23" s="23">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="M23" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="18">
         <v>2005</v>
       </c>
@@ -2593,42 +2672,45 @@
         <v>2</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="20">
+        <v>74</v>
+      </c>
+      <c r="E24" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="20">
         <v>1002</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="18">
+      <c r="G24" s="20"/>
+      <c r="H24" s="18">
         <v>450</v>
       </c>
-      <c r="H24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="18">
+      <c r="I24" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="18">
         <v>50</v>
       </c>
-      <c r="J24" s="18">
+      <c r="K24" s="18">
         <v>300</v>
       </c>
-      <c r="K24" s="18">
+      <c r="L24" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="L24" s="22">
+      <c r="M24" s="23">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="M24" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="18">
         <v>2006</v>
       </c>
@@ -2636,42 +2718,45 @@
         <v>2</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="20">
+        <v>76</v>
+      </c>
+      <c r="E25" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="20">
         <v>1001</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="18">
+      <c r="G25" s="20"/>
+      <c r="H25" s="18">
         <v>450</v>
       </c>
-      <c r="H25" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="18">
+      <c r="I25" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="18">
         <v>50</v>
       </c>
-      <c r="J25" s="18">
+      <c r="K25" s="18">
         <v>300</v>
       </c>
-      <c r="K25" s="18">
+      <c r="L25" s="18">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="L25" s="22">
+      <c r="M25" s="23">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="M25" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="18">
         <v>3004</v>
       </c>
@@ -2679,42 +2764,45 @@
         <v>3</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="20">
+        <v>78</v>
+      </c>
+      <c r="E26" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="20">
         <v>1002</v>
       </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="18">
+      <c r="G26" s="20"/>
+      <c r="H26" s="18">
         <v>450</v>
       </c>
-      <c r="H26" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="18">
+      <c r="I26" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="18">
         <v>50</v>
       </c>
-      <c r="J26" s="18">
+      <c r="K26" s="18">
         <v>100</v>
       </c>
-      <c r="K26" s="18">
+      <c r="L26" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L26" s="22">
+      <c r="M26" s="23">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="M26" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="18">
         <v>3005</v>
       </c>
@@ -2722,42 +2810,45 @@
         <v>3</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="20">
+        <v>80</v>
+      </c>
+      <c r="E27" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="20">
         <v>1001</v>
       </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="18">
+      <c r="G27" s="20"/>
+      <c r="H27" s="18">
         <v>450</v>
       </c>
-      <c r="H27" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="18">
+      <c r="I27" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="18">
         <v>50</v>
       </c>
-      <c r="J27" s="18">
+      <c r="K27" s="18">
         <v>10</v>
       </c>
-      <c r="K27" s="18">
+      <c r="L27" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L27" s="22">
+      <c r="M27" s="23">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="M27" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="18">
         <v>3006</v>
       </c>
@@ -2765,42 +2856,45 @@
         <v>3</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="20">
+        <v>82</v>
+      </c>
+      <c r="E28" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="20">
         <v>1002</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="18">
+      <c r="G28" s="20"/>
+      <c r="H28" s="18">
         <v>450</v>
       </c>
-      <c r="H28" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="18">
+      <c r="I28" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J28" s="18">
         <v>50</v>
       </c>
-      <c r="J28" s="18">
+      <c r="K28" s="18">
         <v>100</v>
       </c>
-      <c r="K28" s="18">
+      <c r="L28" s="18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L28" s="22">
+      <c r="M28" s="23">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="M28" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="18">
         <v>4004</v>
       </c>
@@ -2808,42 +2902,45 @@
         <v>4</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="20">
+        <v>84</v>
+      </c>
+      <c r="E29" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="20">
         <v>1001</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="18">
+      <c r="G29" s="20"/>
+      <c r="H29" s="18">
         <v>450</v>
       </c>
-      <c r="H29" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="18">
-        <v>50</v>
+      <c r="I29" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="J29" s="18">
         <v>50</v>
       </c>
       <c r="K29" s="18">
+        <v>50</v>
+      </c>
+      <c r="L29" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L29" s="22">
+      <c r="M29" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M29" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="18">
         <v>4005</v>
       </c>
@@ -2851,42 +2948,45 @@
         <v>4</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E30" s="20">
+        <v>86</v>
+      </c>
+      <c r="E30" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="20">
         <v>1002</v>
       </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="18">
+      <c r="G30" s="20"/>
+      <c r="H30" s="18">
         <v>450</v>
       </c>
-      <c r="H30" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="18">
-        <v>50</v>
+      <c r="I30" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="J30" s="18">
         <v>50</v>
       </c>
       <c r="K30" s="18">
+        <v>50</v>
+      </c>
+      <c r="L30" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L30" s="22">
+      <c r="M30" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M30" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="18">
         <v>4006</v>
       </c>
@@ -2894,42 +2994,45 @@
         <v>4</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="20">
+        <v>88</v>
+      </c>
+      <c r="E31" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="20">
         <v>1001</v>
       </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="18">
+      <c r="G31" s="20"/>
+      <c r="H31" s="18">
         <v>450</v>
       </c>
-      <c r="H31" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I31" s="18">
-        <v>50</v>
+      <c r="I31" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="J31" s="18">
         <v>50</v>
       </c>
       <c r="K31" s="18">
+        <v>50</v>
+      </c>
+      <c r="L31" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L31" s="22">
+      <c r="M31" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M31" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="N31" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="18">
         <v>5004</v>
       </c>
@@ -2937,42 +3040,45 @@
         <v>5</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="20">
+        <v>90</v>
+      </c>
+      <c r="E32" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="20">
         <v>1002</v>
       </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="18">
+      <c r="G32" s="20"/>
+      <c r="H32" s="18">
         <v>450</v>
       </c>
-      <c r="H32" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="18">
-        <v>50</v>
+      <c r="I32" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="J32" s="18">
         <v>50</v>
       </c>
       <c r="K32" s="18">
+        <v>50</v>
+      </c>
+      <c r="L32" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L32" s="22">
+      <c r="M32" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M32" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N32" s="23"/>
-      <c r="O32" s="23"/>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="18">
         <v>5005</v>
       </c>
@@ -2980,42 +3086,45 @@
         <v>5</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" s="20">
+        <v>92</v>
+      </c>
+      <c r="E33" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="20">
         <v>1001</v>
       </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="18">
+      <c r="G33" s="20"/>
+      <c r="H33" s="18">
         <v>450</v>
       </c>
-      <c r="H33" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="18">
-        <v>50</v>
+      <c r="I33" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="J33" s="18">
         <v>50</v>
       </c>
       <c r="K33" s="18">
+        <v>50</v>
+      </c>
+      <c r="L33" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L33" s="22">
+      <c r="M33" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M33" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N33" s="23"/>
-      <c r="O33" s="23"/>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="18">
         <v>5006</v>
       </c>
@@ -3023,153 +3132,156 @@
         <v>5</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="E34" s="20">
+        <v>94</v>
+      </c>
+      <c r="E34" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="20">
         <v>1002</v>
       </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="18">
+      <c r="G34" s="20"/>
+      <c r="H34" s="18">
         <v>450</v>
       </c>
-      <c r="H34" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I34" s="18">
-        <v>50</v>
+      <c r="I34" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="J34" s="18">
         <v>50</v>
       </c>
       <c r="K34" s="18">
+        <v>50</v>
+      </c>
+      <c r="L34" s="18">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L34" s="22">
+      <c r="M34" s="23">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="M34" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N34" s="23"/>
-      <c r="O34" s="23"/>
-    </row>
-    <row r="35" spans="1:15">
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-    </row>
-    <row r="38" spans="1:15">
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-    </row>
-    <row r="39" ht="17.25" spans="1:15">
-      <c r="C39" s="25"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-    </row>
-    <row r="40" spans="1:15">
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-    </row>
-    <row r="41" spans="1:15">
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-    </row>
-    <row r="42" spans="1:15">
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-    </row>
-    <row r="43" spans="1:15">
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-    </row>
-    <row r="44" spans="1:15">
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-    </row>
-    <row r="45" spans="1:15">
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-    </row>
-    <row r="46" spans="1:15">
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-    </row>
-    <row r="47" spans="1:15">
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-    </row>
-    <row r="48" spans="1:15">
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-    </row>
-    <row r="49" spans="3:8">
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-    </row>
-    <row r="50" spans="3:8">
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-    </row>
-    <row r="51" spans="3:8">
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-    </row>
-    <row r="52" spans="3:8">
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-    </row>
-    <row r="53" ht="14.25" spans="3:8">
-      <c r="C53" s="26"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-    </row>
-    <row r="54" spans="3:8">
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-    </row>
-    <row r="55" spans="3:8">
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-    </row>
-    <row r="56" spans="3:8">
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-    </row>
-    <row r="57" spans="3:8">
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-    </row>
-    <row r="58" spans="3:8">
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-    </row>
-    <row r="59" spans="3:8">
-      <c r="G59" s="24"/>
-      <c r="H59" s="24"/>
-    </row>
-    <row r="60" spans="3:8">
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
+      <c r="N34" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+    </row>
+    <row r="39" ht="17.25" spans="1:16">
+      <c r="C39" s="26"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+    </row>
+    <row r="49" spans="3:9">
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+    </row>
+    <row r="50" spans="3:9">
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+    </row>
+    <row r="51" spans="3:9">
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+    </row>
+    <row r="52" spans="3:9">
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+    </row>
+    <row r="53" ht="14.25" spans="3:9">
+      <c r="C53" s="27"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+    </row>
+    <row r="54" spans="3:9">
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+    </row>
+    <row r="55" spans="3:9">
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+    </row>
+    <row r="56" spans="3:9">
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+    </row>
+    <row r="57" spans="3:9">
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+    </row>
+    <row r="58" spans="3:9">
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+    </row>
+    <row r="59" spans="3:9">
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+    </row>
+    <row r="60" spans="3:9">
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="O2:O3 O8:O19 O6 O35:O60 N61:O63 A1:B1 H1 A4:B4 H4:H9 H11:H12 H14:H15 H17:H18 N4:O4 N1:O1" formula="1"/>
+    <ignoredError sqref="O1:P1 O4:P4 I17:I18 I14:I15 I11:I12 I4:I9 A4:B4 I1 A1:B1 O61:P63 P35:P60 P6 P8:P19 P2:P3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3183,7 +3295,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -3362,13 +3474,13 @@
     </row>
     <row r="27" spans="6:22">
       <c r="F27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="6:22">
@@ -3399,13 +3511,13 @@
         <v>1025101_1125101_2</v>
       </c>
       <c r="R30" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="U30" s="2">
         <v>1025101</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="6:22">
@@ -3436,13 +3548,13 @@
         <v>1025102_1125102_2</v>
       </c>
       <c r="R31" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="U31" s="2">
         <v>1025102</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="6:22">
@@ -3473,13 +3585,13 @@
         <v>1025103_1125103_2</v>
       </c>
       <c r="R32" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="U32" s="2">
         <v>1025103</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="6:22">
@@ -3510,13 +3622,13 @@
         <v>1025201_1125201_4</v>
       </c>
       <c r="R33" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U33" s="2">
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -3547,13 +3659,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="U34" s="2">
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -3584,13 +3696,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U35" s="2">
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -3621,13 +3733,13 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="U36" s="3">
         <v>1025201</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="6:22">
@@ -3658,13 +3770,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -3695,13 +3807,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -3732,13 +3844,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -3769,13 +3881,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -3806,13 +3918,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -3843,13 +3955,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -3880,13 +3992,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -3917,13 +4029,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -3954,13 +4066,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -3991,13 +4103,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4028,13 +4140,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4065,13 +4177,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4102,13 +4214,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4139,13 +4251,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4176,13 +4288,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -4213,13 +4325,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -4250,13 +4362,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -4287,13 +4399,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -4324,13 +4436,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -4361,13 +4473,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -4398,13 +4510,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -4435,13 +4547,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -4472,13 +4584,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -33,7 +33,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -77,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -126,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -149,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="101">
   <si>
     <t>ID</t>
   </si>
@@ -194,6 +194,9 @@
     <t>是否默认解锁</t>
   </si>
   <si>
+    <t>场景 ID</t>
+  </si>
+  <si>
     <t>资源</t>
   </si>
   <si>
@@ -249,6 +252,9 @@
   </si>
   <si>
     <t>IsDefaultUnlocked</t>
+  </si>
+  <si>
+    <t>RegionID</t>
   </si>
   <si>
     <t>Resource</t>
@@ -486,7 +492,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,6 +569,12 @@
       <sz val="10.5"/>
       <color rgb="FF212529"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1080,137 +1092,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1235,6 +1247,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1280,6 +1295,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1289,10 +1307,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1611,31 +1629,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U60"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
     <col min="2" max="2" width="8.375" customWidth="1"/>
     <col min="3" max="3" width="22.125" customWidth="1"/>
     <col min="4" max="4" width="8.375" customWidth="1"/>
-    <col min="5" max="6" width="18.8166666666667" customWidth="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="15.25" customWidth="1"/>
-    <col min="9" max="9" width="8.375" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="12.875" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="6.375" customWidth="1"/>
-    <col min="14" max="14" width="113.816666666667" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="48.375" customWidth="1"/>
-    <col min="18" max="18" width="13.125" customWidth="1"/>
-    <col min="19" max="19" width="17.25" customWidth="1"/>
-    <col min="20" max="20" width="17.625" customWidth="1"/>
-    <col min="21" max="21" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="18.8166666666667" customWidth="1"/>
+    <col min="6" max="6" width="14.7" customWidth="1"/>
+    <col min="7" max="7" width="16.9083333333333" customWidth="1"/>
+    <col min="8" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="15.25" customWidth="1"/>
+    <col min="10" max="10" width="8.375" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="12.875" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="6.375" customWidth="1"/>
+    <col min="15" max="15" width="113.816666666667" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="48.375" customWidth="1"/>
+    <col min="19" max="19" width="13.125" customWidth="1"/>
+    <col min="20" max="20" width="17.25" customWidth="1"/>
+    <col min="21" max="21" width="17.625" customWidth="1"/>
+    <col min="22" max="22" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:21">
+    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:22">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1651,1637 +1671,1737 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
+      <c r="Q1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4"/>
+      <c r="S1" s="13"/>
       <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:21">
-      <c r="A2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+    </row>
+    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:22">
+      <c r="A2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="15"/>
+      <c r="B2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="16"/>
       <c r="E2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="17"/>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:21">
-      <c r="A3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="Q2" s="18"/>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:22">
+      <c r="A3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="C3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="16"/>
       <c r="E3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="G3" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="H3" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="I3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="16" t="s">
+      <c r="J3" s="17"/>
+      <c r="K3" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="L3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="17"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:21">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="21"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:21">
-      <c r="A5" s="18">
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="18"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:22">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="22"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:22">
+      <c r="A5" s="19">
         <v>1001</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <v>1</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="22" t="b">
+      <c r="C5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="24">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21">
         <v>1001</v>
       </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="18">
+      <c r="H5" s="21"/>
+      <c r="I5" s="19">
         <v>100</v>
       </c>
-      <c r="I5" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="18">
+      <c r="J5" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="19">
         <v>0</v>
       </c>
-      <c r="K5" s="18">
+      <c r="L5" s="19">
         <v>500</v>
       </c>
-      <c r="L5" s="18">
-        <f>IF(J5=0,K5,($Q$1*J5/100+1)*K5)</f>
+      <c r="M5" s="19">
+        <f>IF(K5=0,L5,($R$1*K5/100+1)*L5)</f>
         <v>500</v>
       </c>
-      <c r="M5" s="23">
-        <f>L5/SUM($L$5:$L$34)</f>
+      <c r="N5" s="25">
+        <f>M5/SUM($M$5:$M$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="N5" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24" t="s">
+      <c r="O5" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:22">
+      <c r="A6" s="19">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="19">
+        <v>1</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="24">
+        <v>1</v>
+      </c>
+      <c r="G6" s="21">
+        <v>1002</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="19">
+        <v>100</v>
+      </c>
+      <c r="J6" s="19" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:21">
-      <c r="A6" s="18">
-        <v>1002</v>
-      </c>
-      <c r="B6" s="18">
+      <c r="K6" s="19">
+        <v>0</v>
+      </c>
+      <c r="L6" s="19">
+        <v>500</v>
+      </c>
+      <c r="M6" s="19">
+        <f t="shared" ref="M6:M34" si="0">IF(K6=0,L6,($R$1*K6/100+1)*L6)</f>
+        <v>500</v>
+      </c>
+      <c r="N6" s="25">
+        <f t="shared" ref="N6:N34" si="1">M6/SUM($M$5:$M$34)</f>
+        <v>0.0859106529209622</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:22">
+      <c r="A7" s="19">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="19">
         <v>1</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="22" t="b">
+      <c r="C7" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="24">
         <v>1</v>
       </c>
-      <c r="F6" s="20">
-        <v>1002</v>
-      </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="18">
-        <v>100</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="18">
+      <c r="G7" s="21">
+        <v>1001</v>
+      </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="19">
+        <v>450</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="19">
         <v>0</v>
       </c>
-      <c r="K6" s="18">
+      <c r="L7" s="19">
         <v>500</v>
       </c>
-      <c r="L6" s="18">
-        <f t="shared" ref="L6:L34" si="0">IF(J6=0,K6,($Q$1*J6/100+1)*K6)</f>
-        <v>500</v>
-      </c>
-      <c r="M6" s="23">
-        <f t="shared" ref="M6:M34" si="1">L6/SUM($L$5:$L$34)</f>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="18">
-        <v>1003</v>
-      </c>
-      <c r="B7" s="18">
-        <v>1</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="20">
-        <v>1001</v>
-      </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="18">
-        <v>450</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="18">
-        <v>0</v>
-      </c>
-      <c r="K7" s="18">
-        <v>500</v>
-      </c>
-      <c r="L7" s="18">
+      <c r="M7" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="M7" s="23">
+      <c r="N7" s="25">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="N7" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="18">
+      <c r="O7" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:22">
+      <c r="A8" s="19">
         <v>2001</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <v>2</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="22" t="b">
+      <c r="C8" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="24">
+        <v>1</v>
+      </c>
+      <c r="G8" s="21">
         <v>1002</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="18">
+      <c r="H8" s="21"/>
+      <c r="I8" s="19">
         <v>450</v>
       </c>
-      <c r="I8" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="18">
+      <c r="J8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="19">
         <v>0</v>
       </c>
-      <c r="K8" s="18">
+      <c r="L8" s="19">
         <v>300</v>
       </c>
-      <c r="L8" s="18">
+      <c r="M8" s="19">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="M8" s="23">
+      <c r="N8" s="25">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="N8" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="18">
+      <c r="O8" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:22">
+      <c r="A9" s="19">
         <v>2002</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <v>2</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="22" t="b">
+      <c r="C9" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="24">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21">
         <v>1001</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="18">
+      <c r="H9" s="21"/>
+      <c r="I9" s="19">
         <v>450</v>
       </c>
-      <c r="I9" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="18">
+      <c r="J9" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="19">
         <v>0</v>
       </c>
-      <c r="K9" s="18">
+      <c r="L9" s="19">
         <v>300</v>
       </c>
-      <c r="L9" s="18">
+      <c r="M9" s="19">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="M9" s="23">
+      <c r="N9" s="25">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="N9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="18">
+      <c r="O9" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:22">
+      <c r="A10" s="19">
         <v>2003</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <v>2</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="22" t="b">
+      <c r="C10" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="24">
+        <v>1</v>
+      </c>
+      <c r="G10" s="21">
         <v>1002</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="18">
+      <c r="H10" s="21"/>
+      <c r="I10" s="19">
         <v>450</v>
       </c>
-      <c r="I10" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="18">
+      <c r="J10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="19">
         <v>0</v>
       </c>
-      <c r="K10" s="18">
+      <c r="L10" s="19">
         <v>300</v>
       </c>
-      <c r="L10" s="18">
+      <c r="M10" s="19">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="M10" s="23">
+      <c r="N10" s="25">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="N10" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="18">
+      <c r="O10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:22">
+      <c r="A11" s="19">
         <v>3001</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <v>3</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="22" t="b">
+      <c r="C11" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11" s="21">
         <v>1001</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="18">
+      <c r="H11" s="21"/>
+      <c r="I11" s="19">
         <v>450</v>
       </c>
-      <c r="I11" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="18">
+      <c r="J11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="19">
         <v>0</v>
       </c>
-      <c r="K11" s="18">
+      <c r="L11" s="19">
         <v>100</v>
       </c>
-      <c r="L11" s="18">
+      <c r="M11" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="M11" s="23">
+      <c r="N11" s="25">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="N11" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="18">
+      <c r="O11" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:22">
+      <c r="A12" s="19">
         <v>3002</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>3</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="22" t="b">
+      <c r="C12" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="24">
+        <v>1</v>
+      </c>
+      <c r="G12" s="21">
         <v>1002</v>
       </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="18">
+      <c r="H12" s="21"/>
+      <c r="I12" s="19">
         <v>450</v>
       </c>
-      <c r="I12" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="18">
+      <c r="J12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="19">
         <v>0</v>
       </c>
-      <c r="K12" s="18">
+      <c r="L12" s="19">
         <v>10</v>
       </c>
-      <c r="L12" s="18">
+      <c r="M12" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M12" s="23">
+      <c r="N12" s="25">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="N12" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="18">
+      <c r="O12" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:22">
+      <c r="A13" s="19">
         <v>3003</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>3</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="22" t="b">
+      <c r="C13" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="24">
+        <v>1</v>
+      </c>
+      <c r="G13" s="21">
         <v>1001</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="18">
+      <c r="H13" s="21"/>
+      <c r="I13" s="19">
         <v>450</v>
       </c>
-      <c r="I13" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="18">
+      <c r="J13" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="19">
         <v>0</v>
       </c>
-      <c r="K13" s="18">
+      <c r="L13" s="19">
         <v>100</v>
       </c>
-      <c r="L13" s="18">
+      <c r="M13" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="M13" s="23">
+      <c r="N13" s="25">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="N13" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="18">
+      <c r="O13" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:22">
+      <c r="A14" s="19">
         <v>4001</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <v>4</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="22" t="b">
+      <c r="C14" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="24">
+        <v>1</v>
+      </c>
+      <c r="G14" s="21">
         <v>1002</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="18">
+      <c r="H14" s="21"/>
+      <c r="I14" s="19">
         <v>450</v>
       </c>
-      <c r="I14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="18">
+      <c r="J14" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="19">
         <v>0</v>
       </c>
-      <c r="K14" s="18">
+      <c r="L14" s="19">
         <v>50</v>
       </c>
-      <c r="L14" s="18">
+      <c r="M14" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M14" s="23">
+      <c r="N14" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N14" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="18">
+      <c r="O14" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:22">
+      <c r="A15" s="19">
         <v>4002</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <v>4</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="22" t="b">
+      <c r="C15" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="24">
+        <v>1</v>
+      </c>
+      <c r="G15" s="21">
         <v>1001</v>
       </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="18">
+      <c r="H15" s="21"/>
+      <c r="I15" s="19">
         <v>450</v>
       </c>
-      <c r="I15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="18">
+      <c r="J15" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="19">
         <v>0</v>
       </c>
-      <c r="K15" s="18">
+      <c r="L15" s="19">
         <v>50</v>
       </c>
-      <c r="L15" s="18">
+      <c r="M15" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M15" s="23">
+      <c r="N15" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N15" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="18">
+      <c r="O15" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:22">
+      <c r="A16" s="19">
         <v>4003</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <v>4</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="22" t="b">
+      <c r="C16" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="24">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21">
         <v>1002</v>
       </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="18">
+      <c r="H16" s="21"/>
+      <c r="I16" s="19">
         <v>450</v>
       </c>
-      <c r="I16" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J16" s="18">
+      <c r="J16" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="19">
         <v>0</v>
       </c>
-      <c r="K16" s="18">
+      <c r="L16" s="19">
         <v>50</v>
       </c>
-      <c r="L16" s="18">
+      <c r="M16" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M16" s="23">
+      <c r="N16" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N16" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="18">
+      <c r="O16" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:17">
+      <c r="A17" s="19">
         <v>5001</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="19">
         <v>5</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="22" t="b">
+      <c r="C17" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="24">
+        <v>1</v>
+      </c>
+      <c r="G17" s="21">
         <v>1001</v>
       </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="18">
+      <c r="H17" s="21"/>
+      <c r="I17" s="19">
         <v>450</v>
       </c>
-      <c r="I17" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="18">
+      <c r="J17" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="19">
         <v>0</v>
       </c>
-      <c r="K17" s="18">
+      <c r="L17" s="19">
         <v>50</v>
       </c>
-      <c r="L17" s="18">
+      <c r="M17" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M17" s="23">
+      <c r="N17" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N17" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="18">
+      <c r="O17" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:17">
+      <c r="A18" s="19">
         <v>5002</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="19">
         <v>5</v>
       </c>
-      <c r="C18" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="22" t="b">
+      <c r="C18" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="24">
+        <v>1</v>
+      </c>
+      <c r="G18" s="21">
         <v>1002</v>
       </c>
-      <c r="G18" s="20"/>
-      <c r="H18" s="18">
+      <c r="H18" s="21"/>
+      <c r="I18" s="19">
         <v>450</v>
       </c>
-      <c r="I18" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="18">
+      <c r="J18" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="19">
         <v>0</v>
       </c>
-      <c r="K18" s="18">
+      <c r="L18" s="19">
         <v>50</v>
       </c>
-      <c r="L18" s="18">
+      <c r="M18" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M18" s="23">
+      <c r="N18" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N18" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="18">
+      <c r="O18" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:17">
+      <c r="A19" s="19">
         <v>5003</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="19">
         <v>5</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="22" t="b">
+      <c r="C19" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="24">
+        <v>1</v>
+      </c>
+      <c r="G19" s="21">
         <v>1001</v>
       </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="18">
+      <c r="H19" s="21"/>
+      <c r="I19" s="19">
         <v>450</v>
       </c>
-      <c r="I19" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J19" s="18">
+      <c r="J19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="19">
         <v>0</v>
       </c>
-      <c r="K19" s="18">
+      <c r="L19" s="19">
         <v>50</v>
       </c>
-      <c r="L19" s="18">
+      <c r="M19" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M19" s="23">
+      <c r="N19" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N19" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="18">
+      <c r="O19" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:17">
+      <c r="A20" s="19">
         <v>1004</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="19">
         <v>1</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="22" t="b">
+      <c r="C20" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="24">
+        <v>1</v>
+      </c>
+      <c r="G20" s="21">
         <v>1002</v>
       </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="18">
+      <c r="H20" s="21"/>
+      <c r="I20" s="19">
         <v>450</v>
       </c>
-      <c r="I20" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="18">
+      <c r="J20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="19">
         <v>50</v>
       </c>
-      <c r="K20" s="18">
+      <c r="L20" s="19">
         <v>500</v>
       </c>
-      <c r="L20" s="18">
+      <c r="M20" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="M20" s="23">
+      <c r="N20" s="25">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="N20" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="18">
+      <c r="O20" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:17">
+      <c r="A21" s="19">
         <v>1005</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="19">
         <v>1</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="22" t="b">
+      <c r="C21" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="24">
+        <v>1</v>
+      </c>
+      <c r="G21" s="21">
         <v>1001</v>
       </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="18">
+      <c r="H21" s="21"/>
+      <c r="I21" s="19">
         <v>450</v>
       </c>
-      <c r="I21" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="18">
+      <c r="J21" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="19">
         <v>50</v>
       </c>
-      <c r="K21" s="18">
+      <c r="L21" s="19">
         <v>500</v>
       </c>
-      <c r="L21" s="18">
+      <c r="M21" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="M21" s="23">
+      <c r="N21" s="25">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="N21" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="18">
+      <c r="O21" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:17">
+      <c r="A22" s="19">
         <v>1006</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="19">
         <v>1</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="22" t="b">
+      <c r="C22" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="24">
+        <v>1</v>
+      </c>
+      <c r="G22" s="21">
         <v>1002</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="18">
+      <c r="H22" s="21"/>
+      <c r="I22" s="19">
         <v>450</v>
       </c>
-      <c r="I22" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J22" s="18">
+      <c r="J22" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="19">
         <v>50</v>
       </c>
-      <c r="K22" s="18">
+      <c r="L22" s="19">
         <v>500</v>
       </c>
-      <c r="L22" s="18">
+      <c r="M22" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="M22" s="23">
+      <c r="N22" s="25">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="N22" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="18">
+      <c r="O22" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:17">
+      <c r="A23" s="19">
         <v>2004</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="19">
         <v>2</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="22" t="b">
+      <c r="C23" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="24">
+        <v>1</v>
+      </c>
+      <c r="G23" s="21">
         <v>1001</v>
       </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="18">
+      <c r="H23" s="21"/>
+      <c r="I23" s="19">
         <v>450</v>
       </c>
-      <c r="I23" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="18">
+      <c r="J23" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="19">
         <v>50</v>
       </c>
-      <c r="K23" s="18">
+      <c r="L23" s="19">
         <v>300</v>
       </c>
-      <c r="L23" s="18">
+      <c r="M23" s="19">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="M23" s="23">
+      <c r="N23" s="25">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="N23" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="18">
+      <c r="O23" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:17">
+      <c r="A24" s="19">
         <v>2005</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="19">
         <v>2</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="22" t="b">
+      <c r="C24" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="21">
         <v>1002</v>
       </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="18">
+      <c r="H24" s="21"/>
+      <c r="I24" s="19">
         <v>450</v>
       </c>
-      <c r="I24" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J24" s="18">
+      <c r="J24" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="19">
         <v>50</v>
       </c>
-      <c r="K24" s="18">
+      <c r="L24" s="19">
         <v>300</v>
       </c>
-      <c r="L24" s="18">
+      <c r="M24" s="19">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="M24" s="23">
+      <c r="N24" s="25">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="N24" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="18">
+      <c r="O24" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:17">
+      <c r="A25" s="19">
         <v>2006</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="19">
         <v>2</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="22" t="b">
+      <c r="C25" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="24">
+        <v>1</v>
+      </c>
+      <c r="G25" s="21">
         <v>1001</v>
       </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="18">
+      <c r="H25" s="21"/>
+      <c r="I25" s="19">
         <v>450</v>
       </c>
-      <c r="I25" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="18">
+      <c r="J25" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="19">
         <v>50</v>
       </c>
-      <c r="K25" s="18">
+      <c r="L25" s="19">
         <v>300</v>
       </c>
-      <c r="L25" s="18">
+      <c r="M25" s="19">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="M25" s="23">
+      <c r="N25" s="25">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="N25" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="18">
+      <c r="O25" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:17">
+      <c r="A26" s="19">
         <v>3004</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="19">
         <v>3</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="22" t="b">
+      <c r="C26" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="24">
+        <v>1</v>
+      </c>
+      <c r="G26" s="21">
         <v>1002</v>
       </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="18">
+      <c r="H26" s="21"/>
+      <c r="I26" s="19">
         <v>450</v>
       </c>
-      <c r="I26" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="18">
+      <c r="J26" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="19">
         <v>50</v>
       </c>
-      <c r="K26" s="18">
+      <c r="L26" s="19">
         <v>100</v>
       </c>
-      <c r="L26" s="18">
+      <c r="M26" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="M26" s="23">
+      <c r="N26" s="25">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="N26" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="18">
+      <c r="O26" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:17">
+      <c r="A27" s="19">
         <v>3005</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <v>3</v>
       </c>
-      <c r="C27" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="22" t="b">
+      <c r="C27" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="24">
+        <v>1</v>
+      </c>
+      <c r="G27" s="21">
         <v>1001</v>
       </c>
-      <c r="G27" s="20"/>
-      <c r="H27" s="18">
+      <c r="H27" s="21"/>
+      <c r="I27" s="19">
         <v>450</v>
       </c>
-      <c r="I27" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="18">
+      <c r="J27" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="19">
         <v>50</v>
       </c>
-      <c r="K27" s="18">
+      <c r="L27" s="19">
         <v>10</v>
       </c>
-      <c r="L27" s="18">
+      <c r="M27" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M27" s="23">
+      <c r="N27" s="25">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="N27" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="18">
+      <c r="O27" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:17">
+      <c r="A28" s="19">
         <v>3006</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="19">
         <v>3</v>
       </c>
-      <c r="C28" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="22" t="b">
+      <c r="C28" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="24">
+        <v>1</v>
+      </c>
+      <c r="G28" s="21">
         <v>1002</v>
       </c>
-      <c r="G28" s="20"/>
-      <c r="H28" s="18">
+      <c r="H28" s="21"/>
+      <c r="I28" s="19">
         <v>450</v>
       </c>
-      <c r="I28" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" s="18">
+      <c r="J28" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="19">
         <v>50</v>
       </c>
-      <c r="K28" s="18">
+      <c r="L28" s="19">
         <v>100</v>
       </c>
-      <c r="L28" s="18">
+      <c r="M28" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="M28" s="23">
+      <c r="N28" s="25">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="N28" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" s="18">
+      <c r="O28" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:17">
+      <c r="A29" s="19">
         <v>4004</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="19">
         <v>4</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="22" t="b">
+      <c r="C29" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="24">
+        <v>1</v>
+      </c>
+      <c r="G29" s="21">
         <v>1001</v>
       </c>
-      <c r="G29" s="20"/>
-      <c r="H29" s="18">
+      <c r="H29" s="21"/>
+      <c r="I29" s="19">
         <v>450</v>
       </c>
-      <c r="I29" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="18">
+      <c r="J29" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="19">
         <v>50</v>
       </c>
-      <c r="K29" s="18">
+      <c r="L29" s="19">
         <v>50</v>
       </c>
-      <c r="L29" s="18">
+      <c r="M29" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M29" s="23">
+      <c r="N29" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N29" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="18">
+      <c r="O29" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:17">
+      <c r="A30" s="19">
         <v>4005</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="19">
         <v>4</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="22" t="b">
+      <c r="C30" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="24">
+        <v>1</v>
+      </c>
+      <c r="G30" s="21">
         <v>1002</v>
       </c>
-      <c r="G30" s="20"/>
-      <c r="H30" s="18">
+      <c r="H30" s="21"/>
+      <c r="I30" s="19">
         <v>450</v>
       </c>
-      <c r="I30" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="18">
+      <c r="J30" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="19">
         <v>50</v>
       </c>
-      <c r="K30" s="18">
+      <c r="L30" s="19">
         <v>50</v>
       </c>
-      <c r="L30" s="18">
+      <c r="M30" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M30" s="23">
+      <c r="N30" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N30" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" s="18">
+      <c r="O30" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:17">
+      <c r="A31" s="19">
         <v>4006</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="19">
         <v>4</v>
       </c>
-      <c r="C31" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="22" t="b">
+      <c r="C31" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="24">
+        <v>1</v>
+      </c>
+      <c r="G31" s="21">
         <v>1001</v>
       </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="18">
+      <c r="H31" s="21"/>
+      <c r="I31" s="19">
         <v>450</v>
       </c>
-      <c r="I31" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J31" s="18">
+      <c r="J31" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K31" s="19">
         <v>50</v>
       </c>
-      <c r="K31" s="18">
+      <c r="L31" s="19">
         <v>50</v>
       </c>
-      <c r="L31" s="18">
+      <c r="M31" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M31" s="23">
+      <c r="N31" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N31" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" s="18">
+      <c r="O31" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:17">
+      <c r="A32" s="19">
         <v>5004</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="19">
         <v>5</v>
       </c>
-      <c r="C32" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="22" t="b">
+      <c r="C32" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="24">
+        <v>1</v>
+      </c>
+      <c r="G32" s="21">
         <v>1002</v>
       </c>
-      <c r="G32" s="20"/>
-      <c r="H32" s="18">
+      <c r="H32" s="21"/>
+      <c r="I32" s="19">
         <v>450</v>
       </c>
-      <c r="I32" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" s="18">
+      <c r="J32" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="19">
         <v>50</v>
       </c>
-      <c r="K32" s="18">
+      <c r="L32" s="19">
         <v>50</v>
       </c>
-      <c r="L32" s="18">
+      <c r="M32" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M32" s="23">
+      <c r="N32" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N32" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O32" s="24"/>
-      <c r="P32" s="24"/>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="18">
+      <c r="O32" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:17">
+      <c r="A33" s="19">
         <v>5005</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="19">
         <v>5</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="22" t="b">
+      <c r="C33" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="24">
+        <v>1</v>
+      </c>
+      <c r="G33" s="21">
         <v>1001</v>
       </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="18">
+      <c r="H33" s="21"/>
+      <c r="I33" s="19">
         <v>450</v>
       </c>
-      <c r="I33" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="18">
+      <c r="J33" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" s="19">
         <v>50</v>
       </c>
-      <c r="K33" s="18">
+      <c r="L33" s="19">
         <v>50</v>
       </c>
-      <c r="L33" s="18">
+      <c r="M33" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M33" s="23">
+      <c r="N33" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N33" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O33" s="24"/>
-      <c r="P33" s="24"/>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="18">
+      <c r="O33" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:17">
+      <c r="A34" s="19">
         <v>5006</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="19">
         <v>5</v>
       </c>
-      <c r="C34" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E34" s="22" t="b">
+      <c r="C34" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="24">
+        <v>1</v>
+      </c>
+      <c r="G34" s="21">
         <v>1002</v>
       </c>
-      <c r="G34" s="20"/>
-      <c r="H34" s="18">
+      <c r="H34" s="21"/>
+      <c r="I34" s="19">
         <v>450</v>
       </c>
-      <c r="I34" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="J34" s="18">
+      <c r="J34" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K34" s="19">
         <v>50</v>
       </c>
-      <c r="K34" s="18">
+      <c r="L34" s="19">
         <v>50</v>
       </c>
-      <c r="L34" s="18">
+      <c r="M34" s="19">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M34" s="23">
+      <c r="N34" s="25">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="N34" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O34" s="24"/>
-      <c r="P34" s="24"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-    </row>
-    <row r="39" ht="17.25" spans="1:16">
-      <c r="C39" s="26"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="H47" s="25"/>
-      <c r="I47" s="25"/>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-    </row>
-    <row r="49" spans="3:9">
-      <c r="H49" s="25"/>
-      <c r="I49" s="25"/>
-    </row>
-    <row r="50" spans="3:9">
-      <c r="H50" s="25"/>
-      <c r="I50" s="25"/>
-    </row>
-    <row r="51" spans="3:9">
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
-    </row>
-    <row r="52" spans="3:9">
-      <c r="H52" s="25"/>
-      <c r="I52" s="25"/>
-    </row>
-    <row r="53" ht="14.25" spans="3:9">
-      <c r="C53" s="27"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="25"/>
-    </row>
-    <row r="54" spans="3:9">
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-    </row>
-    <row r="55" spans="3:9">
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-    </row>
-    <row r="56" spans="3:9">
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-    </row>
-    <row r="57" spans="3:9">
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-    </row>
-    <row r="58" spans="3:9">
-      <c r="H58" s="25"/>
-      <c r="I58" s="25"/>
-    </row>
-    <row r="59" spans="3:9">
-      <c r="H59" s="25"/>
-      <c r="I59" s="25"/>
-    </row>
-    <row r="60" spans="3:9">
-      <c r="H60" s="25"/>
-      <c r="I60" s="25"/>
+      <c r="O34" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+    </row>
+    <row r="39" ht="17.25" spans="1:17">
+      <c r="C39" s="28"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="I45" s="27"/>
+      <c r="J45" s="27"/>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+    </row>
+    <row r="49" spans="3:10">
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+    </row>
+    <row r="50" spans="3:10">
+      <c r="I50" s="27"/>
+      <c r="J50" s="27"/>
+    </row>
+    <row r="51" spans="3:10">
+      <c r="I51" s="27"/>
+      <c r="J51" s="27"/>
+    </row>
+    <row r="52" spans="3:10">
+      <c r="I52" s="27"/>
+      <c r="J52" s="27"/>
+    </row>
+    <row r="53" ht="14.25" spans="3:10">
+      <c r="C53" s="29"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+    </row>
+    <row r="54" spans="3:10">
+      <c r="I54" s="27"/>
+      <c r="J54" s="27"/>
+    </row>
+    <row r="55" spans="3:10">
+      <c r="I55" s="27"/>
+      <c r="J55" s="27"/>
+    </row>
+    <row r="56" spans="3:10">
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+    </row>
+    <row r="57" spans="3:10">
+      <c r="I57" s="27"/>
+      <c r="J57" s="27"/>
+    </row>
+    <row r="58" spans="3:10">
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+    </row>
+    <row r="59" spans="3:10">
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+    </row>
+    <row r="60" spans="3:10">
+      <c r="I60" s="27"/>
+      <c r="J60" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="O1:P1 O4:P4 I17:I18 I14:I15 I11:I12 I4:I9 A4:B4 I1 A1:B1 O61:P63 P35:P60 P6 P8:P19 P2:P3" formula="1"/>
+    <ignoredError sqref="Q2:Q3 Q8:Q19 Q6 Q35:Q60 P61:Q63 A1:B1 J1 A4:B4 J4:J9 J11:J12 J14:J15 J17:J18 P4:Q4 P1:Q1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3295,7 +3415,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -3474,13 +3594,13 @@
     </row>
     <row r="27" spans="6:22">
       <c r="F27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="6:22">
@@ -3511,13 +3631,13 @@
         <v>1025101_1125101_2</v>
       </c>
       <c r="R30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U30" s="2">
         <v>1025101</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="6:22">
@@ -3548,13 +3668,13 @@
         <v>1025102_1125102_2</v>
       </c>
       <c r="R31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U31" s="2">
         <v>1025102</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="6:22">
@@ -3585,13 +3705,13 @@
         <v>1025103_1125103_2</v>
       </c>
       <c r="R32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U32" s="2">
         <v>1025103</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="6:22">
@@ -3622,13 +3742,13 @@
         <v>1025201_1125201_4</v>
       </c>
       <c r="R33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U33" s="2">
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -3659,13 +3779,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U34" s="2">
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -3696,13 +3816,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U35" s="2">
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -3733,13 +3853,13 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U36" s="3">
         <v>1025201</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="6:22">
@@ -3770,13 +3890,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -3807,13 +3927,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -3844,13 +3964,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -3881,13 +4001,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -3918,13 +4038,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -3955,13 +4075,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -3992,13 +4112,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -4029,13 +4149,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -4066,13 +4186,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -4103,13 +4223,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4140,13 +4260,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4177,13 +4297,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4214,13 +4334,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4251,13 +4371,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4288,13 +4408,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -4325,13 +4445,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -4362,13 +4482,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -4399,13 +4519,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -4436,13 +4556,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -4473,13 +4593,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -4510,13 +4630,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -4547,13 +4667,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -4584,13 +4704,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -766,6 +766,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -851,12 +857,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1098,7 +1098,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
@@ -1122,16 +1122,16 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="8">
@@ -1140,42 +1140,42 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1222,7 +1222,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1292,17 +1292,29 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1819,25 +1831,25 @@
       <c r="Q4" s="22"/>
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:22">
-      <c r="A5" s="19">
+      <c r="A5" s="23">
         <v>1001</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="23">
         <v>1</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="23" t="b">
+      <c r="E5" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="26">
         <v>1</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="24">
         <v>1001</v>
       </c>
       <c r="H5" s="21"/>
@@ -1857,38 +1869,38 @@
         <f>IF(K5=0,L5,($R$1*K5/100+1)*L5)</f>
         <v>500</v>
       </c>
-      <c r="N5" s="25">
+      <c r="N5" s="27">
         <f>M5/SUM($M$5:$M$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="O5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26" t="s">
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:22">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>1002</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="23">
         <v>1</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="23" t="b">
+      <c r="E6" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="26">
         <v>1</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="24">
         <v>1002</v>
       </c>
       <c r="H6" s="21"/>
@@ -1908,36 +1920,36 @@
         <f t="shared" ref="M6:M34" si="0">IF(K6=0,L6,($R$1*K6/100+1)*L6)</f>
         <v>500</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="27">
         <f t="shared" ref="N6:N34" si="1">M6/SUM($M$5:$M$34)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="O6" s="26" t="s">
+      <c r="O6" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
     </row>
     <row r="7" ht="16.5" spans="1:22">
-      <c r="A7" s="19">
+      <c r="A7" s="23">
         <v>1003</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="23" t="b">
+      <c r="E7" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="26">
         <v>1</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="24">
         <v>1001</v>
       </c>
       <c r="H7" s="21"/>
@@ -1957,15 +1969,15 @@
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="27">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
     </row>
     <row r="8" ht="16.5" spans="1:22">
       <c r="A8" s="19">
@@ -1980,10 +1992,10 @@
       <c r="D8" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="23" t="b">
+      <c r="E8" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="30">
         <v>1</v>
       </c>
       <c r="G8" s="21">
@@ -2006,15 +2018,15 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="27">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="O8" s="26" t="s">
+      <c r="O8" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
     </row>
     <row r="9" ht="16.5" spans="1:22">
       <c r="A9" s="19">
@@ -2029,10 +2041,10 @@
       <c r="D9" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="23" t="b">
+      <c r="E9" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="30">
         <v>1</v>
       </c>
       <c r="G9" s="21">
@@ -2055,15 +2067,15 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="27">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="O9" s="26" t="s">
+      <c r="O9" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
     </row>
     <row r="10" ht="16.5" spans="1:22">
       <c r="A10" s="19">
@@ -2078,10 +2090,10 @@
       <c r="D10" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="23" t="b">
+      <c r="E10" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="30">
         <v>1</v>
       </c>
       <c r="G10" s="21">
@@ -2104,15 +2116,15 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="27">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="O10" s="26" t="s">
+      <c r="O10" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
     </row>
     <row r="11" ht="16.5" spans="1:22">
       <c r="A11" s="19">
@@ -2127,10 +2139,10 @@
       <c r="D11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="23" t="b">
+      <c r="E11" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="30">
         <v>1</v>
       </c>
       <c r="G11" s="21">
@@ -2153,15 +2165,15 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="27">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="O11" s="26" t="s">
+      <c r="O11" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
     </row>
     <row r="12" ht="16.5" spans="1:22">
       <c r="A12" s="19">
@@ -2176,10 +2188,10 @@
       <c r="D12" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="23" t="b">
+      <c r="E12" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="30">
         <v>1</v>
       </c>
       <c r="G12" s="21">
@@ -2202,15 +2214,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="27">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="O12" s="26" t="s">
+      <c r="O12" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
     </row>
     <row r="13" ht="16.5" spans="1:22">
       <c r="A13" s="19">
@@ -2225,10 +2237,10 @@
       <c r="D13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="23" t="b">
+      <c r="E13" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="30">
         <v>1</v>
       </c>
       <c r="G13" s="21">
@@ -2251,15 +2263,15 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="27">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="O13" s="26" t="s">
+      <c r="O13" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
     </row>
     <row r="14" ht="16.5" spans="1:22">
       <c r="A14" s="19">
@@ -2274,10 +2286,10 @@
       <c r="D14" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="23" t="b">
+      <c r="E14" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="30">
         <v>1</v>
       </c>
       <c r="G14" s="21">
@@ -2300,15 +2312,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O14" s="26" t="s">
+      <c r="O14" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
     </row>
     <row r="15" ht="16.5" spans="1:22">
       <c r="A15" s="19">
@@ -2323,10 +2335,10 @@
       <c r="D15" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="23" t="b">
+      <c r="E15" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="30">
         <v>1</v>
       </c>
       <c r="G15" s="21">
@@ -2349,15 +2361,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N15" s="25">
+      <c r="N15" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O15" s="26" t="s">
+      <c r="O15" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
     </row>
     <row r="16" ht="16.5" spans="1:22">
       <c r="A16" s="19">
@@ -2372,10 +2384,10 @@
       <c r="D16" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="23" t="b">
+      <c r="E16" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="30">
         <v>1</v>
       </c>
       <c r="G16" s="21">
@@ -2398,36 +2410,36 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O16" s="26" t="s">
+      <c r="O16" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
     </row>
     <row r="17" ht="16.5" spans="1:17">
-      <c r="A17" s="19">
+      <c r="A17" s="23">
         <v>5001</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="23">
         <v>5</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="23" t="b">
+      <c r="E17" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="26">
         <v>1</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="24">
         <v>1001</v>
       </c>
       <c r="H17" s="21"/>
@@ -2447,15 +2459,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O17" s="26" t="s">
+      <c r="O17" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
     </row>
     <row r="18" ht="16.5" spans="1:17">
       <c r="A18" s="19">
@@ -2470,10 +2482,10 @@
       <c r="D18" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="23" t="b">
+      <c r="E18" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="30">
         <v>1</v>
       </c>
       <c r="G18" s="21">
@@ -2496,15 +2508,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N18" s="25">
+      <c r="N18" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O18" s="26" t="s">
+      <c r="O18" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
     </row>
     <row r="19" ht="16.5" spans="1:17">
       <c r="A19" s="19">
@@ -2519,10 +2531,10 @@
       <c r="D19" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="23" t="b">
+      <c r="E19" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="30">
         <v>1</v>
       </c>
       <c r="G19" s="21">
@@ -2545,36 +2557,36 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N19" s="25">
+      <c r="N19" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O19" s="26" t="s">
+      <c r="O19" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
     </row>
     <row r="20" ht="16.5" spans="1:17">
-      <c r="A20" s="19">
+      <c r="A20" s="23">
         <v>1004</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="23">
         <v>1</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="23" t="b">
+      <c r="E20" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="26">
         <v>1</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="24">
         <v>1002</v>
       </c>
       <c r="H20" s="21"/>
@@ -2594,36 +2606,36 @@
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N20" s="25">
+      <c r="N20" s="27">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="O20" s="26" t="s">
+      <c r="O20" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
     </row>
     <row r="21" ht="16.5" spans="1:17">
-      <c r="A21" s="19">
+      <c r="A21" s="23">
         <v>1005</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="23">
         <v>1</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="23" t="b">
+      <c r="E21" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="26">
         <v>1</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="24">
         <v>1001</v>
       </c>
       <c r="H21" s="21"/>
@@ -2643,15 +2655,15 @@
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N21" s="25">
+      <c r="N21" s="27">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="O21" s="26" t="s">
+      <c r="O21" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
     </row>
     <row r="22" ht="16.5" spans="1:17">
       <c r="A22" s="19">
@@ -2666,10 +2678,10 @@
       <c r="D22" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="23" t="b">
+      <c r="E22" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="30">
         <v>1</v>
       </c>
       <c r="G22" s="21">
@@ -2692,15 +2704,15 @@
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="27">
         <f t="shared" si="1"/>
         <v>0.0859106529209622</v>
       </c>
-      <c r="O22" s="26" t="s">
+      <c r="O22" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
     </row>
     <row r="23" ht="16.5" spans="1:17">
       <c r="A23" s="19">
@@ -2715,10 +2727,10 @@
       <c r="D23" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="23" t="b">
+      <c r="E23" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="30">
         <v>1</v>
       </c>
       <c r="G23" s="21">
@@ -2741,15 +2753,15 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="27">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="O23" s="26" t="s">
+      <c r="O23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
     </row>
     <row r="24" ht="16.5" spans="1:17">
       <c r="A24" s="19">
@@ -2764,10 +2776,10 @@
       <c r="D24" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="23" t="b">
+      <c r="E24" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="30">
         <v>1</v>
       </c>
       <c r="G24" s="21">
@@ -2790,15 +2802,15 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="27">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="O24" s="26" t="s">
+      <c r="O24" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
     </row>
     <row r="25" ht="16.5" spans="1:17">
       <c r="A25" s="19">
@@ -2813,10 +2825,10 @@
       <c r="D25" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="23" t="b">
+      <c r="E25" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="30">
         <v>1</v>
       </c>
       <c r="G25" s="21">
@@ -2839,15 +2851,15 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="N25" s="25">
+      <c r="N25" s="27">
         <f t="shared" si="1"/>
         <v>0.0515463917525773</v>
       </c>
-      <c r="O25" s="26" t="s">
+      <c r="O25" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
     </row>
     <row r="26" ht="16.5" spans="1:17">
       <c r="A26" s="19">
@@ -2862,10 +2874,10 @@
       <c r="D26" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="23" t="b">
+      <c r="E26" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="30">
         <v>1</v>
       </c>
       <c r="G26" s="21">
@@ -2888,15 +2900,15 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N26" s="25">
+      <c r="N26" s="27">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="O26" s="26" t="s">
+      <c r="O26" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
     </row>
     <row r="27" ht="16.5" spans="1:17">
       <c r="A27" s="19">
@@ -2911,10 +2923,10 @@
       <c r="D27" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="23" t="b">
+      <c r="E27" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="30">
         <v>1</v>
       </c>
       <c r="G27" s="21">
@@ -2937,15 +2949,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N27" s="25">
+      <c r="N27" s="27">
         <f t="shared" si="1"/>
         <v>0.00171821305841924</v>
       </c>
-      <c r="O27" s="26" t="s">
+      <c r="O27" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
     </row>
     <row r="28" ht="16.5" spans="1:17">
       <c r="A28" s="19">
@@ -2960,10 +2972,10 @@
       <c r="D28" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="23" t="b">
+      <c r="E28" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="30">
         <v>1</v>
       </c>
       <c r="G28" s="21">
@@ -2986,15 +2998,15 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="27">
         <f t="shared" si="1"/>
         <v>0.0171821305841924</v>
       </c>
-      <c r="O28" s="26" t="s">
+      <c r="O28" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
     </row>
     <row r="29" ht="16.5" spans="1:17">
       <c r="A29" s="19">
@@ -3009,10 +3021,10 @@
       <c r="D29" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="23" t="b">
+      <c r="E29" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="30">
         <v>1</v>
       </c>
       <c r="G29" s="21">
@@ -3035,15 +3047,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O29" s="26" t="s">
+      <c r="O29" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
     </row>
     <row r="30" ht="16.5" spans="1:17">
       <c r="A30" s="19">
@@ -3058,10 +3070,10 @@
       <c r="D30" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="23" t="b">
+      <c r="E30" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="30">
         <v>1</v>
       </c>
       <c r="G30" s="21">
@@ -3084,15 +3096,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N30" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O30" s="26" t="s">
+      <c r="O30" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
     </row>
     <row r="31" ht="16.5" spans="1:17">
       <c r="A31" s="19">
@@ -3107,10 +3119,10 @@
       <c r="D31" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="23" t="b">
+      <c r="E31" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="30">
         <v>1</v>
       </c>
       <c r="G31" s="21">
@@ -3133,15 +3145,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N31" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O31" s="26" t="s">
+      <c r="O31" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
     </row>
     <row r="32" ht="16.5" spans="1:17">
       <c r="A32" s="19">
@@ -3156,10 +3168,10 @@
       <c r="D32" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="23" t="b">
+      <c r="E32" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="30">
         <v>1</v>
       </c>
       <c r="G32" s="21">
@@ -3182,15 +3194,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N32" s="25">
+      <c r="N32" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O32" s="26" t="s">
+      <c r="O32" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
     </row>
     <row r="33" ht="16.5" spans="1:17">
       <c r="A33" s="19">
@@ -3205,10 +3217,10 @@
       <c r="D33" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="E33" s="23" t="b">
+      <c r="E33" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="30">
         <v>1</v>
       </c>
       <c r="G33" s="21">
@@ -3231,36 +3243,36 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N33" s="25">
+      <c r="N33" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O33" s="26" t="s">
+      <c r="O33" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
     </row>
     <row r="34" ht="16.5" spans="1:17">
-      <c r="A34" s="19">
+      <c r="A34" s="23">
         <v>5006</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="23">
         <v>5</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E34" s="23" t="b">
+      <c r="E34" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="26">
         <v>1</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="24">
         <v>1002</v>
       </c>
       <c r="H34" s="21"/>
@@ -3280,128 +3292,128 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N34" s="25">
+      <c r="N34" s="27">
         <f t="shared" si="1"/>
         <v>0.00859106529209622</v>
       </c>
-      <c r="O34" s="26" t="s">
+      <c r="O34" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="1:17">
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
     </row>
     <row r="36" spans="1:17">
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
     </row>
     <row r="37" spans="1:17">
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
     </row>
     <row r="38" spans="1:17">
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
     </row>
     <row r="39" ht="17.25" spans="1:17">
-      <c r="C39" s="28"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
+      <c r="C39" s="32"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
     </row>
     <row r="40" spans="1:17">
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
     </row>
     <row r="41" spans="1:17">
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
     </row>
     <row r="42" spans="1:17">
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
     </row>
     <row r="43" spans="1:17">
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
     </row>
     <row r="44" spans="1:17">
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
     </row>
     <row r="45" spans="1:17">
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
     </row>
     <row r="46" spans="1:17">
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
     </row>
     <row r="47" spans="1:17">
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
     </row>
     <row r="48" spans="1:17">
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
     </row>
     <row r="49" spans="3:10">
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
     </row>
     <row r="50" spans="3:10">
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="31"/>
     </row>
     <row r="51" spans="3:10">
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
     </row>
     <row r="52" spans="3:10">
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
     </row>
     <row r="53" ht="14.25" spans="3:10">
-      <c r="C53" s="29"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
+      <c r="C53" s="33"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
     </row>
     <row r="54" spans="3:10">
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
     </row>
     <row r="55" spans="3:10">
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
     </row>
     <row r="56" spans="3:10">
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="31"/>
     </row>
     <row r="57" spans="3:10">
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
     </row>
     <row r="58" spans="3:10">
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
     </row>
     <row r="59" spans="3:10">
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
+      <c r="I59" s="31"/>
+      <c r="J59" s="31"/>
     </row>
     <row r="60" spans="3:10">
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="Q2:Q3 Q8:Q19 Q6 Q35:Q60 P61:Q63 A1:B1 J1 A4:B4 J4:J9 J11:J12 J14:J15 J17:J18 P4:Q4 P1:Q1" formula="1"/>
+    <ignoredError sqref="P1:Q1 P4:Q4 J17:J18 J14:J15 J11:J12 J4:J9 A4:B4 J1 A1:B1 P61:Q63 Q35:Q60 Q6 Q8:Q19 Q2:Q3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -278,7 +278,7 @@
     <t>TargetArea</t>
   </si>
   <si>
-    <t>1025101_1125101_2</t>
+    <t>1025101_1125101_10</t>
   </si>
   <si>
     <t>街头潮人</t>
@@ -293,13 +293,13 @@
     <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
   </si>
   <si>
-    <t>1025102_1125102_2</t>
+    <t>1025102_1125102_10</t>
   </si>
   <si>
     <t>复古绅士</t>
   </si>
   <si>
-    <t>1025103_1125103_2</t>
+    <t>1025103_1125103_10</t>
   </si>
   <si>
     <t>酷盖少年</t>
@@ -308,55 +308,55 @@
     <t>固定</t>
   </si>
   <si>
-    <t>1025201_1125201_4</t>
+    <t>1025201_1125201_10</t>
   </si>
   <si>
     <t>运动健将</t>
   </si>
   <si>
-    <t>1025202_1125202_4</t>
+    <t>1025202_1125202_10</t>
   </si>
   <si>
     <t>跑酷少年</t>
   </si>
   <si>
-    <t>1025203_1125203_4</t>
+    <t>1025203_1125203_10</t>
   </si>
   <si>
     <t>滑板高手</t>
   </si>
   <si>
-    <t>1025301_1125301_6</t>
+    <t>1025301_1125301_10</t>
   </si>
   <si>
     <t>健身狂魔</t>
   </si>
   <si>
-    <t>1025302_1125302_6</t>
+    <t>1025302_1125302_10</t>
   </si>
   <si>
     <t>单车骑士</t>
   </si>
   <si>
-    <t>1025303_1125303_6</t>
+    <t>1025303_1125303_10</t>
   </si>
   <si>
     <t>登山行者</t>
   </si>
   <si>
-    <t>1025401_1125401_8</t>
+    <t>1025401_1125401_10</t>
   </si>
   <si>
     <t>马拉松客</t>
   </si>
   <si>
-    <t>1025402_1125402_8</t>
+    <t>1025402_1125402_10</t>
   </si>
   <si>
     <t>极限玩家</t>
   </si>
   <si>
-    <t>1025403_1125403_8</t>
+    <t>1025403_1125403_10</t>
   </si>
   <si>
     <t>科技极客</t>
@@ -380,73 +380,73 @@
     <t>氪金大佬</t>
   </si>
   <si>
-    <t>1025104_1125104_2</t>
+    <t>1025104_1125104_10</t>
   </si>
   <si>
     <t>潮流先锋</t>
   </si>
   <si>
-    <t>1025105_1125105_2</t>
+    <t>1025105_1125105_10</t>
   </si>
   <si>
     <t>时尚教主</t>
   </si>
   <si>
-    <t>1025106_1125106_2</t>
+    <t>1025106_1125106_10</t>
   </si>
   <si>
     <t>街拍达人</t>
   </si>
   <si>
-    <t>1025204_1125204_4</t>
+    <t>1025204_1125204_10</t>
   </si>
   <si>
     <t>甜心辣妹</t>
   </si>
   <si>
-    <t>1025205_1125205_4</t>
+    <t>1025205_1125205_10</t>
   </si>
   <si>
     <t>活力少女</t>
   </si>
   <si>
-    <t>1025206_1125206_4</t>
+    <t>1025206_1125206_10</t>
   </si>
   <si>
     <t>优雅女神</t>
   </si>
   <si>
-    <t>1025304_1125304_6</t>
+    <t>1025304_1125304_10</t>
   </si>
   <si>
     <t>文艺青年</t>
   </si>
   <si>
-    <t>1025305_1125305_6</t>
+    <t>1025305_1125305_10</t>
   </si>
   <si>
     <t>书香少女</t>
   </si>
   <si>
-    <t>1025306_1125306_6</t>
+    <t>1025306_1125306_10</t>
   </si>
   <si>
     <t>民谣歌手</t>
   </si>
   <si>
-    <t>1025404_1125404_8</t>
+    <t>1025404_1125404_10</t>
   </si>
   <si>
     <t>独立画家</t>
   </si>
   <si>
-    <t>1025405_1125405_8</t>
+    <t>1025405_1125405_10</t>
   </si>
   <si>
     <t>浪漫诗人</t>
   </si>
   <si>
-    <t>1025406_1125406_8</t>
+    <t>1025406_1125406_10</t>
   </si>
   <si>
     <t>古典乐迷</t>
@@ -1950,11 +1950,11 @@
         <v>1</v>
       </c>
       <c r="G7" s="24">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="H7" s="21"/>
       <c r="I7" s="19">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>42</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="19">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>35</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="H9" s="21"/>
       <c r="I9" s="19">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>35</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="H10" s="21"/>
       <c r="I10" s="19">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="J10" s="19" t="s">
         <v>42</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="H11" s="21"/>
       <c r="I11" s="19">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="J11" s="19" t="s">
         <v>35</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="19">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="J12" s="19" t="s">
         <v>35</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="19">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="J13" s="19" t="s">
         <v>42</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="19">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="J14" s="19" t="s">
         <v>35</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="19">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>35</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="H16" s="21"/>
       <c r="I16" s="19">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="J16" s="19" t="s">
         <v>42</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H17" s="21"/>
       <c r="I17" s="19">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J17" s="19" t="s">
         <v>35</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="19">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J18" s="19" t="s">
         <v>35</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="H19" s="21"/>
       <c r="I19" s="19">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J19" s="19" t="s">
         <v>42</v>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="24">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="H20" s="21"/>
       <c r="I20" s="19">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>35</v>
@@ -2636,11 +2636,11 @@
         <v>1</v>
       </c>
       <c r="G21" s="24">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="H21" s="21"/>
       <c r="I21" s="19">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="J21" s="19" t="s">
         <v>35</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="19">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="J22" s="19" t="s">
         <v>42</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="19">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="J23" s="19" t="s">
         <v>35</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="19">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>35</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="H25" s="21"/>
       <c r="I25" s="19">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="J25" s="19" t="s">
         <v>42</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="H26" s="21"/>
       <c r="I26" s="19">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>35</v>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H27" s="21"/>
       <c r="I27" s="19">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>35</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="H28" s="21"/>
       <c r="I28" s="19">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="J28" s="19" t="s">
         <v>42</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H29" s="21"/>
       <c r="I29" s="19">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="J29" s="19" t="s">
         <v>35</v>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H30" s="21"/>
       <c r="I30" s="19">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="J30" s="19" t="s">
         <v>35</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="19">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="J31" s="19" t="s">
         <v>42</v>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="H32" s="21"/>
       <c r="I32" s="19">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J32" s="19" t="s">
         <v>35</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="H33" s="21"/>
       <c r="I33" s="19">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J33" s="19" t="s">
         <v>35</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="H34" s="21"/>
       <c r="I34" s="19">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J34" s="19" t="s">
         <v>42</v>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -2440,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="24">
-        <v>1001</v>
+        <v>5001</v>
       </c>
       <c r="H17" s="21"/>
       <c r="I17" s="19">
@@ -3273,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="24">
-        <v>1002</v>
+        <v>5006</v>
       </c>
       <c r="H34" s="21"/>
       <c r="I34" s="19">
@@ -3413,7 +3413,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="P1:Q1 P4:Q4 J17:J18 J14:J15 J11:J12 J4:J9 A4:B4 J1 A1:B1 P61:Q63 Q35:Q60 Q6 Q8:Q19 Q2:Q3" formula="1"/>
+    <ignoredError sqref="Q2:Q3 Q8:Q19 Q6 Q35:Q60 P61:Q63 A1:B1 J1 A4:B4 J4:J9 J11:J12 J14:J15 J17:J18 P4:Q4 P1:Q1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -167,8 +172,9 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-读取交互区域表中的ID；该区域中的具体设备随机选择
-注： 先不配置 前端是随机行走观光点的  。服务器在使用~~  </t>
+按配置的建筑ID依次进行交互，
+当交互次数＜交互建筑点时，能交互到哪个建筑就到哪个建筑
+当交互次数＞交互建筑点（未解锁）时，剩余的交互次数舍弃直接离去；  </t>
         </r>
       </text>
     </comment>
@@ -177,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -287,7 +293,7 @@
     <t>随机</t>
   </si>
   <si>
-    <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_2000|1108_2000|1109_2000|1110_1000|1111_1000|1112_1000|1201_0|1202_0</t>
+    <t>1102_1103_1104_1105_1106_1107_1108_1109_1110_1111_1112_1202</t>
   </si>
   <si>
     <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
@@ -299,6 +305,9 @@
     <t>复古绅士</t>
   </si>
   <si>
+    <t>1102_1110_1107_1109_1108_1112</t>
+  </si>
+  <si>
     <t>1025103_1125103_10</t>
   </si>
   <si>
@@ -308,6 +317,9 @@
     <t>固定</t>
   </si>
   <si>
+    <t>1102_1106_1202_1111_1112_1108_1109_1107_1110</t>
+  </si>
+  <si>
     <t>1025201_1125201_10</t>
   </si>
   <si>
@@ -444,6 +456,9 @@
   </si>
   <si>
     <t>浪漫诗人</t>
+  </si>
+  <si>
+    <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_3000|1108_3000|1109_3000|1110_3000|1111_3000|1112_3000|1201_2000|1202_2000</t>
   </si>
   <si>
     <t>1025406_1125406_10</t>
@@ -1222,7 +1237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1317,6 +1332,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1658,9 +1676,8 @@
     <col min="12" max="12" width="12.875" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="6.375" customWidth="1"/>
-    <col min="15" max="15" width="113.816666666667" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="48.375" customWidth="1"/>
+    <col min="15" max="15" width="37.7833333333333" customWidth="1"/>
+    <col min="16" max="17" width="66.0333333333333" customWidth="1"/>
     <col min="19" max="19" width="13.125" customWidth="1"/>
     <col min="20" max="20" width="17.25" customWidth="1"/>
     <col min="21" max="21" width="17.625" customWidth="1"/>
@@ -1854,13 +1871,13 @@
       </c>
       <c r="H5" s="21"/>
       <c r="I5" s="19">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K5" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L5" s="19">
         <v>500</v>
@@ -1871,12 +1888,12 @@
       </c>
       <c r="N5" s="27">
         <f>M5/SUM($M$5:$M$34)</f>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="O5" s="28" t="s">
+        <v>0.0617283950617284</v>
+      </c>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P5" s="28"/>
       <c r="Q5" s="28" t="s">
         <v>37</v>
       </c>
@@ -1905,13 +1922,13 @@
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="19">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J6" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K6" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L6" s="19">
         <v>500</v>
@@ -1922,12 +1939,12 @@
       </c>
       <c r="N6" s="27">
         <f t="shared" ref="N6:N34" si="1">M6/SUM($M$5:$M$34)</f>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="O6" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="28"/>
+        <v>0.0617283950617284</v>
+      </c>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q6" s="28"/>
     </row>
     <row r="7" ht="16.5" spans="1:22">
@@ -1938,10 +1955,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="25" t="b">
         <v>0</v>
@@ -1954,13 +1971,13 @@
       </c>
       <c r="H7" s="21"/>
       <c r="I7" s="19">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L7" s="19">
         <v>500</v>
@@ -1971,12 +1988,12 @@
       </c>
       <c r="N7" s="27">
         <f t="shared" si="1"/>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="O7" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P7" s="28"/>
+        <v>0.0617283950617284</v>
+      </c>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q7" s="28"/>
     </row>
     <row r="8" ht="16.5" spans="1:22">
@@ -1987,10 +2004,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="29" t="b">
         <v>0</v>
@@ -2003,29 +2020,29 @@
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="19">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K8" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L8" s="19">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M8" s="19">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="N8" s="27">
         <f t="shared" si="1"/>
-        <v>0.0515463917525773</v>
-      </c>
-      <c r="O8" s="28" t="s">
+        <v>0.0432098765432099</v>
+      </c>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P8" s="28"/>
       <c r="Q8" s="28"/>
     </row>
     <row r="9" ht="16.5" spans="1:22">
@@ -2036,10 +2053,10 @@
         <v>2</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" s="29" t="b">
         <v>0</v>
@@ -2052,29 +2069,29 @@
       </c>
       <c r="H9" s="21"/>
       <c r="I9" s="19">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K9" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L9" s="19">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M9" s="19">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="N9" s="27">
         <f t="shared" si="1"/>
-        <v>0.0515463917525773</v>
-      </c>
-      <c r="O9" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P9" s="28"/>
+        <v>0.0432098765432099</v>
+      </c>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q9" s="28"/>
     </row>
     <row r="10" ht="16.5" spans="1:22">
@@ -2085,10 +2102,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" s="29" t="b">
         <v>0</v>
@@ -2101,29 +2118,29 @@
       </c>
       <c r="H10" s="21"/>
       <c r="I10" s="19">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L10" s="19">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M10" s="19">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="N10" s="27">
         <f t="shared" si="1"/>
-        <v>0.0515463917525773</v>
-      </c>
-      <c r="O10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P10" s="28"/>
+        <v>0.0432098765432099</v>
+      </c>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q10" s="28"/>
     </row>
     <row r="11" ht="16.5" spans="1:22">
@@ -2134,10 +2151,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="29" t="b">
         <v>0</v>
@@ -2150,29 +2167,29 @@
       </c>
       <c r="H11" s="21"/>
       <c r="I11" s="19">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="J11" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K11" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L11" s="19">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M11" s="19">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N11" s="27">
         <f t="shared" si="1"/>
-        <v>0.0171821305841924</v>
-      </c>
-      <c r="O11" s="28" t="s">
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P11" s="28"/>
       <c r="Q11" s="28"/>
     </row>
     <row r="12" ht="16.5" spans="1:22">
@@ -2183,10 +2200,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="29" t="b">
         <v>0</v>
@@ -2199,29 +2216,29 @@
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="19">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="J12" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K12" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L12" s="19">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="M12" s="19">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="N12" s="27">
         <f t="shared" si="1"/>
-        <v>0.00171821305841924</v>
-      </c>
-      <c r="O12" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P12" s="28"/>
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q12" s="28"/>
     </row>
     <row r="13" ht="16.5" spans="1:22">
@@ -2232,10 +2249,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E13" s="29" t="b">
         <v>0</v>
@@ -2248,29 +2265,29 @@
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="19">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K13" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L13" s="19">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M13" s="19">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N13" s="27">
         <f t="shared" si="1"/>
-        <v>0.0171821305841924</v>
-      </c>
-      <c r="O13" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P13" s="28"/>
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q13" s="28"/>
     </row>
     <row r="14" ht="16.5" spans="1:22">
@@ -2281,10 +2298,10 @@
         <v>4</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E14" s="29" t="b">
         <v>0</v>
@@ -2297,29 +2314,29 @@
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="19">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J14" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K14" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L14" s="19">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M14" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N14" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
-      </c>
-      <c r="O14" s="28" t="s">
+        <v>0.0185185185185185</v>
+      </c>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P14" s="28"/>
       <c r="Q14" s="28"/>
     </row>
     <row r="15" ht="16.5" spans="1:22">
@@ -2330,10 +2347,10 @@
         <v>4</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15" s="29" t="b">
         <v>0</v>
@@ -2346,29 +2363,29 @@
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="19">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K15" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L15" s="19">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M15" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N15" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
-      </c>
-      <c r="O15" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P15" s="28"/>
+        <v>0.0185185185185185</v>
+      </c>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q15" s="28"/>
     </row>
     <row r="16" ht="16.5" spans="1:22">
@@ -2379,10 +2396,10 @@
         <v>4</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E16" s="29" t="b">
         <v>0</v>
@@ -2395,29 +2412,29 @@
       </c>
       <c r="H16" s="21"/>
       <c r="I16" s="19">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K16" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L16" s="19">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N16" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
-      </c>
-      <c r="O16" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P16" s="28"/>
+        <v>0.0185185185185185</v>
+      </c>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q16" s="28"/>
     </row>
     <row r="17" ht="16.5" spans="1:17">
@@ -2428,10 +2445,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" s="25" t="b">
         <v>0</v>
@@ -2444,29 +2461,29 @@
       </c>
       <c r="H17" s="21"/>
       <c r="I17" s="19">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J17" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K17" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L17" s="19">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N17" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
-      </c>
-      <c r="O17" s="28" t="s">
+        <v>0.0123456790123457</v>
+      </c>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P17" s="28"/>
       <c r="Q17" s="28"/>
     </row>
     <row r="18" ht="16.5" spans="1:17">
@@ -2477,10 +2494,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E18" s="29" t="b">
         <v>0</v>
@@ -2493,29 +2510,29 @@
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="19">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J18" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K18" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L18" s="19">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M18" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N18" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
-      </c>
-      <c r="O18" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P18" s="28"/>
+        <v>0.0123456790123457</v>
+      </c>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q18" s="28"/>
     </row>
     <row r="19" ht="16.5" spans="1:17">
@@ -2526,10 +2543,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E19" s="29" t="b">
         <v>0</v>
@@ -2542,29 +2559,29 @@
       </c>
       <c r="H19" s="21"/>
       <c r="I19" s="19">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K19" s="19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L19" s="19">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M19" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N19" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
-      </c>
-      <c r="O19" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P19" s="28"/>
+        <v>0.0123456790123457</v>
+      </c>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q19" s="28"/>
     </row>
     <row r="20" ht="16.5" spans="1:17">
@@ -2575,10 +2592,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E20" s="25" t="b">
         <v>0</v>
@@ -2591,7 +2608,7 @@
       </c>
       <c r="H20" s="21"/>
       <c r="I20" s="19">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>35</v>
@@ -2608,12 +2625,12 @@
       </c>
       <c r="N20" s="27">
         <f t="shared" si="1"/>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="O20" s="28" t="s">
+        <v>0.0617283950617284</v>
+      </c>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P20" s="28"/>
       <c r="Q20" s="28"/>
     </row>
     <row r="21" ht="16.5" spans="1:17">
@@ -2624,10 +2641,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E21" s="25" t="b">
         <v>0</v>
@@ -2640,7 +2657,7 @@
       </c>
       <c r="H21" s="21"/>
       <c r="I21" s="19">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J21" s="19" t="s">
         <v>35</v>
@@ -2657,12 +2674,12 @@
       </c>
       <c r="N21" s="27">
         <f t="shared" si="1"/>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="O21" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="28"/>
+        <v>0.0617283950617284</v>
+      </c>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q21" s="28"/>
     </row>
     <row r="22" ht="16.5" spans="1:17">
@@ -2673,10 +2690,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E22" s="29" t="b">
         <v>0</v>
@@ -2689,10 +2706,10 @@
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="19">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K22" s="19">
         <v>50</v>
@@ -2706,12 +2723,12 @@
       </c>
       <c r="N22" s="27">
         <f t="shared" si="1"/>
-        <v>0.0859106529209622</v>
-      </c>
-      <c r="O22" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P22" s="28"/>
+        <v>0.0617283950617284</v>
+      </c>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q22" s="28"/>
     </row>
     <row r="23" ht="16.5" spans="1:17">
@@ -2722,10 +2739,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E23" s="29" t="b">
         <v>0</v>
@@ -2738,7 +2755,7 @@
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="19">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="J23" s="19" t="s">
         <v>35</v>
@@ -2747,20 +2764,20 @@
         <v>50</v>
       </c>
       <c r="L23" s="19">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M23" s="19">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="N23" s="27">
         <f t="shared" si="1"/>
-        <v>0.0515463917525773</v>
-      </c>
-      <c r="O23" s="28" t="s">
+        <v>0.0432098765432099</v>
+      </c>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P23" s="28"/>
       <c r="Q23" s="28"/>
     </row>
     <row r="24" ht="16.5" spans="1:17">
@@ -2771,10 +2788,10 @@
         <v>2</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E24" s="29" t="b">
         <v>0</v>
@@ -2787,7 +2804,7 @@
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="19">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>35</v>
@@ -2796,20 +2813,20 @@
         <v>50</v>
       </c>
       <c r="L24" s="19">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M24" s="19">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="N24" s="27">
         <f t="shared" si="1"/>
-        <v>0.0515463917525773</v>
-      </c>
-      <c r="O24" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P24" s="28"/>
+        <v>0.0432098765432099</v>
+      </c>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q24" s="28"/>
     </row>
     <row r="25" ht="16.5" spans="1:17">
@@ -2820,10 +2837,10 @@
         <v>2</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E25" s="29" t="b">
         <v>0</v>
@@ -2836,29 +2853,29 @@
       </c>
       <c r="H25" s="21"/>
       <c r="I25" s="19">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="J25" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K25" s="19">
         <v>50</v>
       </c>
       <c r="L25" s="19">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M25" s="19">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="N25" s="27">
         <f t="shared" si="1"/>
-        <v>0.0515463917525773</v>
-      </c>
-      <c r="O25" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P25" s="28"/>
+        <v>0.0432098765432099</v>
+      </c>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q25" s="28"/>
     </row>
     <row r="26" ht="16.5" spans="1:17">
@@ -2869,10 +2886,10 @@
         <v>3</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E26" s="29" t="b">
         <v>0</v>
@@ -2885,7 +2902,7 @@
       </c>
       <c r="H26" s="21"/>
       <c r="I26" s="19">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>35</v>
@@ -2894,20 +2911,20 @@
         <v>50</v>
       </c>
       <c r="L26" s="19">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M26" s="19">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N26" s="27">
         <f t="shared" si="1"/>
-        <v>0.0171821305841924</v>
-      </c>
-      <c r="O26" s="28" t="s">
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P26" s="28"/>
       <c r="Q26" s="28"/>
     </row>
     <row r="27" ht="16.5" spans="1:17">
@@ -2918,10 +2935,10 @@
         <v>3</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E27" s="29" t="b">
         <v>0</v>
@@ -2934,7 +2951,7 @@
       </c>
       <c r="H27" s="21"/>
       <c r="I27" s="19">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>35</v>
@@ -2943,20 +2960,20 @@
         <v>50</v>
       </c>
       <c r="L27" s="19">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="M27" s="19">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="N27" s="27">
         <f t="shared" si="1"/>
-        <v>0.00171821305841924</v>
-      </c>
-      <c r="O27" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P27" s="28"/>
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="Q27" s="28"/>
     </row>
     <row r="28" ht="16.5" spans="1:17">
@@ -2967,10 +2984,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E28" s="29" t="b">
         <v>0</v>
@@ -2983,29 +3000,29 @@
       </c>
       <c r="H28" s="21"/>
       <c r="I28" s="19">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" s="19">
         <v>50</v>
       </c>
       <c r="L28" s="19">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M28" s="19">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N28" s="27">
         <f t="shared" si="1"/>
-        <v>0.0171821305841924</v>
-      </c>
-      <c r="O28" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P28" s="28"/>
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="Q28" s="28"/>
     </row>
     <row r="29" ht="16.5" spans="1:17">
@@ -3016,10 +3033,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E29" s="29" t="b">
         <v>0</v>
@@ -3032,7 +3049,7 @@
       </c>
       <c r="H29" s="21"/>
       <c r="I29" s="19">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J29" s="19" t="s">
         <v>35</v>
@@ -3041,20 +3058,20 @@
         <v>50</v>
       </c>
       <c r="L29" s="19">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M29" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N29" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
-      </c>
-      <c r="O29" s="28" t="s">
+        <v>0.0185185185185185</v>
+      </c>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="P29" s="28"/>
       <c r="Q29" s="28"/>
     </row>
     <row r="30" ht="16.5" spans="1:17">
@@ -3065,10 +3082,10 @@
         <v>4</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E30" s="29" t="b">
         <v>0</v>
@@ -3081,7 +3098,7 @@
       </c>
       <c r="H30" s="21"/>
       <c r="I30" s="19">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J30" s="19" t="s">
         <v>35</v>
@@ -3090,18 +3107,18 @@
         <v>50</v>
       </c>
       <c r="L30" s="19">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M30" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N30" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
+        <v>0.0185185185185185</v>
       </c>
       <c r="O30" s="28" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P30" s="28"/>
       <c r="Q30" s="28"/>
@@ -3114,10 +3131,10 @@
         <v>4</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E31" s="29" t="b">
         <v>0</v>
@@ -3130,27 +3147,27 @@
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="19">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J31" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" s="19">
         <v>50</v>
       </c>
       <c r="L31" s="19">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M31" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N31" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
+        <v>0.0185185185185185</v>
       </c>
       <c r="O31" s="28" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P31" s="28"/>
       <c r="Q31" s="28"/>
@@ -3163,10 +3180,10 @@
         <v>5</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E32" s="29" t="b">
         <v>0</v>
@@ -3179,7 +3196,7 @@
       </c>
       <c r="H32" s="21"/>
       <c r="I32" s="19">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J32" s="19" t="s">
         <v>35</v>
@@ -3188,18 +3205,18 @@
         <v>50</v>
       </c>
       <c r="L32" s="19">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M32" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N32" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
+        <v>0.0123456790123457</v>
       </c>
       <c r="O32" s="28" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P32" s="28"/>
       <c r="Q32" s="28"/>
@@ -3212,10 +3229,10 @@
         <v>5</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E33" s="29" t="b">
         <v>0</v>
@@ -3228,7 +3245,7 @@
       </c>
       <c r="H33" s="21"/>
       <c r="I33" s="19">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J33" s="19" t="s">
         <v>35</v>
@@ -3237,18 +3254,18 @@
         <v>50</v>
       </c>
       <c r="L33" s="19">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M33" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N33" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
+        <v>0.0123456790123457</v>
       </c>
       <c r="O33" s="28" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P33" s="28"/>
       <c r="Q33" s="28"/>
@@ -3261,10 +3278,10 @@
         <v>5</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E34" s="25" t="b">
         <v>0</v>
@@ -3277,27 +3294,27 @@
       </c>
       <c r="H34" s="21"/>
       <c r="I34" s="19">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K34" s="19">
         <v>50</v>
       </c>
       <c r="L34" s="19">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M34" s="19">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N34" s="27">
         <f t="shared" si="1"/>
-        <v>0.00859106529209622</v>
+        <v>0.0123456790123457</v>
       </c>
       <c r="O34" s="28" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P34" s="28"/>
       <c r="Q34" s="28"/>
@@ -3305,23 +3322,28 @@
     <row r="35" spans="1:17">
       <c r="I35" s="31"/>
       <c r="J35" s="31"/>
+      <c r="M35" s="32"/>
     </row>
     <row r="36" spans="1:17">
       <c r="I36" s="31"/>
       <c r="J36" s="31"/>
+      <c r="M36" s="32"/>
     </row>
     <row r="37" spans="1:17">
       <c r="I37" s="31"/>
       <c r="J37" s="31"/>
+      <c r="M37" s="32"/>
     </row>
     <row r="38" spans="1:17">
       <c r="I38" s="31"/>
       <c r="J38" s="31"/>
+      <c r="M38" s="32"/>
     </row>
     <row r="39" ht="17.25" spans="1:17">
-      <c r="C39" s="32"/>
+      <c r="C39" s="33"/>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
+      <c r="M39" s="32"/>
     </row>
     <row r="40" spans="1:17">
       <c r="I40" s="31"/>
@@ -3376,7 +3398,7 @@
       <c r="J52" s="31"/>
     </row>
     <row r="53" ht="14.25" spans="3:10">
-      <c r="C53" s="33"/>
+      <c r="C53" s="34"/>
       <c r="I53" s="31"/>
       <c r="J53" s="31"/>
     </row>
@@ -3422,12 +3444,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F5:V59"/>
+  <dimension ref="B5:V59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -3544,7 +3566,11 @@
         <v>1109_2000</v>
       </c>
     </row>
-    <row r="17" spans="6:22">
+    <row r="17" spans="2:22">
+      <c r="B17" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B18:B29)</f>
+        <v>1102_1103_1104_1105_1106_1107_1108_1109_1110_1111_1112_1202</v>
+      </c>
       <c r="F17">
         <v>1110</v>
       </c>
@@ -3556,7 +3582,10 @@
         <v>1110_1000</v>
       </c>
     </row>
-    <row r="18" spans="6:22">
+    <row r="18" spans="2:22">
+      <c r="B18">
+        <v>1102</v>
+      </c>
       <c r="F18">
         <v>1111</v>
       </c>
@@ -3568,7 +3597,10 @@
         <v>1111_1000</v>
       </c>
     </row>
-    <row r="19" spans="6:22">
+    <row r="19" spans="2:22">
+      <c r="B19">
+        <v>1103</v>
+      </c>
       <c r="F19">
         <v>1112</v>
       </c>
@@ -3580,7 +3612,10 @@
         <v>1112_1000</v>
       </c>
     </row>
-    <row r="20" spans="6:22">
+    <row r="20" spans="2:22">
+      <c r="B20">
+        <v>1104</v>
+      </c>
       <c r="F20">
         <v>1201</v>
       </c>
@@ -3592,7 +3627,10 @@
         <v>1201_0</v>
       </c>
     </row>
-    <row r="21" spans="6:22">
+    <row r="21" spans="2:22">
+      <c r="B21">
+        <v>1105</v>
+      </c>
       <c r="F21">
         <v>1202</v>
       </c>
@@ -3604,18 +3642,56 @@
         <v>1202_0</v>
       </c>
     </row>
-    <row r="27" spans="6:22">
+    <row r="22" spans="2:22">
+      <c r="B22">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="B27">
+        <v>1111</v>
+      </c>
       <c r="F27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="6:22">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="B28">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22">
+      <c r="B29">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="2:22">
       <c r="F30" s="1">
         <v>1025101</v>
       </c>
@@ -3652,7 +3728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="6:22">
+    <row r="31" ht="16.5" spans="2:22">
       <c r="F31" s="1">
         <v>1025102</v>
       </c>
@@ -3689,7 +3765,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="6:22">
+    <row r="32" ht="16.5" spans="2:22">
       <c r="F32" s="1">
         <v>1025103</v>
       </c>
@@ -3717,13 +3793,13 @@
         <v>1025103_1125103_2</v>
       </c>
       <c r="R32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U32" s="2">
         <v>1025103</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="6:22">
@@ -3754,13 +3830,13 @@
         <v>1025201_1125201_4</v>
       </c>
       <c r="R33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U33" s="2">
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -3791,13 +3867,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U34" s="2">
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -3828,13 +3904,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U35" s="2">
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -3865,13 +3941,13 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U36" s="3">
         <v>1025201</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="6:22">
@@ -3902,13 +3978,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -3939,13 +4015,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -3976,13 +4052,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4013,13 +4089,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -4050,13 +4126,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -4087,13 +4163,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -4124,13 +4200,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -4161,13 +4237,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -4198,13 +4274,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -4235,13 +4311,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4272,13 +4348,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4309,13 +4385,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4346,13 +4422,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4383,13 +4459,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4420,13 +4496,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -4457,13 +4533,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -4494,13 +4570,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -4531,13 +4607,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -4568,13 +4644,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -4605,13 +4681,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -4642,13 +4718,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -4679,13 +4755,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -4716,13 +4792,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,52 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0">
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1-表示常规游客，可通过抽卡获取
+2-表示付费游客，不能通过抽卡获取</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+是否显示在前端的游客列表中</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -82,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -131,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -154,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -183,11 +228,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>是否显示</t>
+  </si>
+  <si>
     <t>游客品质</t>
   </si>
   <si>
@@ -239,18 +290,24 @@
     <t>int</t>
   </si>
   <si>
+    <t>boolean</t>
+  </si>
+  <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>boolean</t>
-  </si>
-  <si>
     <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>IsVisible</t>
+  </si>
+  <si>
     <t>Quality</t>
   </si>
   <si>
@@ -483,6 +540,36 @@
   </si>
   <si>
     <t>高定女王</t>
+  </si>
+  <si>
+    <t>1025901_0_0</t>
+  </si>
+  <si>
+    <t>独立女士</t>
+  </si>
+  <si>
+    <t>1025902_0_0</t>
+  </si>
+  <si>
+    <t>夜色女神</t>
+  </si>
+  <si>
+    <t>1025903_0_0</t>
+  </si>
+  <si>
+    <t>优雅名媛</t>
+  </si>
+  <si>
+    <t>1025904_0_0</t>
+  </si>
+  <si>
+    <t>时尚先锋</t>
+  </si>
+  <si>
+    <t>1025905_0_0</t>
+  </si>
+  <si>
+    <t>商务精英</t>
   </si>
   <si>
     <t>交互ID</t>
@@ -507,7 +594,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,12 +677,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1107,137 +1188,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1310,12 +1391,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1331,16 +1412,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1659,32 +1752,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:X60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
-    <col min="2" max="2" width="8.375" customWidth="1"/>
-    <col min="3" max="3" width="22.125" customWidth="1"/>
-    <col min="4" max="4" width="8.375" customWidth="1"/>
-    <col min="5" max="5" width="18.8166666666667" customWidth="1"/>
-    <col min="6" max="6" width="14.7" customWidth="1"/>
-    <col min="7" max="7" width="16.9083333333333" customWidth="1"/>
-    <col min="8" max="8" width="21.5" customWidth="1"/>
-    <col min="9" max="9" width="15.25" customWidth="1"/>
-    <col min="10" max="10" width="8.375" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="12.875" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="6.375" customWidth="1"/>
-    <col min="15" max="15" width="37.7833333333333" customWidth="1"/>
-    <col min="16" max="17" width="66.0333333333333" customWidth="1"/>
-    <col min="19" max="19" width="13.125" customWidth="1"/>
-    <col min="20" max="20" width="17.25" customWidth="1"/>
-    <col min="21" max="21" width="17.625" customWidth="1"/>
-    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="2" max="4" width="8.375" customWidth="1"/>
+    <col min="5" max="5" width="22.125" customWidth="1"/>
+    <col min="6" max="6" width="8.375" customWidth="1"/>
+    <col min="7" max="7" width="18.8166666666667" customWidth="1"/>
+    <col min="8" max="8" width="14.7" customWidth="1"/>
+    <col min="9" max="9" width="16.9083333333333" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="11" width="15.25" customWidth="1"/>
+    <col min="12" max="12" width="8.375" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="12.875" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="6.375" customWidth="1"/>
+    <col min="17" max="17" width="37.7833333333333" customWidth="1"/>
+    <col min="18" max="19" width="66.0333333333333" customWidth="1"/>
+    <col min="21" max="21" width="13.125" customWidth="1"/>
+    <col min="22" max="22" width="17.25" customWidth="1"/>
+    <col min="23" max="23" width="17.625" customWidth="1"/>
+    <col min="24" max="24" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:22">
+    <row r="1" s="4" customFormat="1" ht="15.75" spans="1:24">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1700,1742 +1793,2126 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:22">
+      <c r="R1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+    </row>
+    <row r="2" s="5" customFormat="1" ht="21" customHeight="1" spans="1:24">
       <c r="A2" s="15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>17</v>
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="18"/>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:22">
+        <v>19</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="18"/>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="15.75" spans="1:24">
       <c r="A3" s="15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="C3" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="D3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="E3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="F3" s="16"/>
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="17"/>
+      <c r="H3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="K3" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="18"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:22">
+      <c r="L3" s="17"/>
+      <c r="M3" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="18"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:24">
       <c r="A4" s="19"/>
       <c r="B4" s="20"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
-      <c r="Q4" s="22"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:22">
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="22"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:24">
       <c r="A5" s="23">
         <v>1001</v>
       </c>
       <c r="B5" s="23">
         <v>1</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="26">
-        <v>1</v>
-      </c>
-      <c r="G5" s="24">
+      <c r="C5" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23">
+        <v>1</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="26">
+        <v>1</v>
+      </c>
+      <c r="I5" s="25">
         <v>1001</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="19">
+      <c r="J5" s="21"/>
+      <c r="K5" s="19">
         <v>600</v>
       </c>
-      <c r="J5" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="19">
+      <c r="L5" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="19">
         <v>50</v>
       </c>
-      <c r="L5" s="19">
+      <c r="N5" s="19">
         <v>500</v>
       </c>
-      <c r="M5" s="19">
-        <f>IF(K5=0,L5,($R$1*K5/100+1)*L5)</f>
+      <c r="O5" s="19">
+        <f>IF(M5=0,N5,($T$1*M5/100+1)*N5)</f>
         <v>500</v>
       </c>
-      <c r="N5" s="27">
-        <f>M5/SUM($M$5:$M$34)</f>
+      <c r="P5" s="27">
+        <f>O5/SUM($O$5:$O$34)</f>
         <v>0.0617283950617284</v>
       </c>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:22">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:24">
       <c r="A6" s="23">
         <v>1002</v>
       </c>
       <c r="B6" s="23">
         <v>1</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="C6" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="23">
+        <v>1</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="26">
+        <v>1</v>
+      </c>
+      <c r="I6" s="25">
+        <v>1002</v>
+      </c>
+      <c r="J6" s="21"/>
+      <c r="K6" s="19">
+        <v>600</v>
+      </c>
+      <c r="L6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="26">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24">
-        <v>1002</v>
-      </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="19">
-        <v>600</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="19">
+      <c r="M6" s="19">
         <v>50</v>
       </c>
-      <c r="L6" s="19">
+      <c r="N6" s="19">
         <v>500</v>
       </c>
-      <c r="M6" s="19">
-        <f t="shared" ref="M6:M34" si="0">IF(K6=0,L6,($R$1*K6/100+1)*L6)</f>
+      <c r="O6" s="19">
+        <f t="shared" ref="O6:O34" si="0">IF(M6=0,N6,($T$1*M6/100+1)*N6)</f>
         <v>500</v>
       </c>
-      <c r="N6" s="27">
-        <f t="shared" ref="N6:N34" si="1">M6/SUM($M$5:$M$34)</f>
+      <c r="P6" s="27">
+        <f t="shared" ref="P6:P34" si="1">O6/SUM($O$5:$O$34)</f>
         <v>0.0617283950617284</v>
       </c>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q6" s="28"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:22">
+      <c r="R6" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S6" s="28"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:24">
       <c r="A7" s="23">
         <v>1003</v>
       </c>
       <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="25" t="b">
+      <c r="C7" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="23">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="26">
-        <v>1</v>
-      </c>
-      <c r="G7" s="24">
+      <c r="H7" s="26">
+        <v>1</v>
+      </c>
+      <c r="I7" s="25">
         <v>1003</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="19">
+      <c r="J7" s="21"/>
+      <c r="K7" s="19">
         <v>600</v>
       </c>
-      <c r="J7" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="19">
+      <c r="L7" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="19">
         <v>50</v>
       </c>
-      <c r="L7" s="19">
+      <c r="N7" s="19">
         <v>500</v>
       </c>
-      <c r="M7" s="19">
+      <c r="O7" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N7" s="27">
+      <c r="P7" s="27">
         <f t="shared" si="1"/>
         <v>0.0617283950617284</v>
       </c>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q7" s="28"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:22">
+      <c r="R7" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S7" s="28"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:24">
       <c r="A8" s="19">
         <v>2001</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="21">
+        <v>1</v>
+      </c>
+      <c r="C8" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19">
         <v>2</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="29" t="b">
+      <c r="E8" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
-        <v>1</v>
-      </c>
-      <c r="G8" s="21">
+      <c r="H8" s="30">
+        <v>1</v>
+      </c>
+      <c r="I8" s="21">
         <v>1002</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="19">
+      <c r="J8" s="21"/>
+      <c r="K8" s="19">
         <v>600</v>
       </c>
-      <c r="J8" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="19">
+      <c r="L8" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="19">
         <v>50</v>
       </c>
-      <c r="L8" s="19">
+      <c r="N8" s="19">
         <v>350</v>
       </c>
-      <c r="M8" s="19">
+      <c r="O8" s="19">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="N8" s="27">
+      <c r="P8" s="27">
         <f t="shared" si="1"/>
         <v>0.0432098765432099</v>
       </c>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q8" s="28"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:22">
+      <c r="R8" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8" s="28"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:24">
       <c r="A9" s="19">
         <v>2002</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="21">
+        <v>1</v>
+      </c>
+      <c r="C9" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19">
         <v>2</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="29" t="b">
+      <c r="E9" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="30">
-        <v>1</v>
-      </c>
-      <c r="G9" s="21">
+      <c r="H9" s="30">
+        <v>1</v>
+      </c>
+      <c r="I9" s="21">
         <v>1001</v>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="19">
+      <c r="J9" s="21"/>
+      <c r="K9" s="19">
         <v>600</v>
       </c>
-      <c r="J9" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="19">
+      <c r="L9" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="19">
         <v>50</v>
       </c>
-      <c r="L9" s="19">
+      <c r="N9" s="19">
         <v>350</v>
       </c>
-      <c r="M9" s="19">
+      <c r="O9" s="19">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="N9" s="27">
+      <c r="P9" s="27">
         <f t="shared" si="1"/>
         <v>0.0432098765432099</v>
       </c>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q9" s="28"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:22">
+      <c r="R9" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S9" s="28"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:24">
       <c r="A10" s="19">
         <v>2003</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="21">
+        <v>1</v>
+      </c>
+      <c r="C10" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19">
         <v>2</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="21" t="s">
+      <c r="E10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="30">
+        <v>1</v>
+      </c>
+      <c r="I10" s="21">
+        <v>1002</v>
+      </c>
+      <c r="J10" s="21"/>
+      <c r="K10" s="19">
+        <v>600</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="19">
         <v>50</v>
       </c>
-      <c r="E10" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="30">
-        <v>1</v>
-      </c>
-      <c r="G10" s="21">
-        <v>1002</v>
-      </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="19">
-        <v>600</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="19">
-        <v>50</v>
-      </c>
-      <c r="L10" s="19">
+      <c r="N10" s="19">
         <v>350</v>
       </c>
-      <c r="M10" s="19">
+      <c r="O10" s="19">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="N10" s="27">
+      <c r="P10" s="27">
         <f t="shared" si="1"/>
         <v>0.0432098765432099</v>
       </c>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q10" s="28"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:22">
+      <c r="R10" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S10" s="28"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:24">
       <c r="A11" s="19">
         <v>3001</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="21">
+        <v>1</v>
+      </c>
+      <c r="C11" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19">
         <v>3</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="29" t="b">
+      <c r="E11" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="30">
-        <v>1</v>
-      </c>
-      <c r="G11" s="21">
+      <c r="H11" s="30">
+        <v>1</v>
+      </c>
+      <c r="I11" s="21">
         <v>1001</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="19">
+      <c r="J11" s="21"/>
+      <c r="K11" s="19">
         <v>600</v>
       </c>
-      <c r="J11" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="19">
+      <c r="L11" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="19">
         <v>50</v>
       </c>
-      <c r="L11" s="19">
+      <c r="N11" s="19">
         <v>250</v>
       </c>
-      <c r="M11" s="19">
+      <c r="O11" s="19">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="N11" s="27">
+      <c r="P11" s="27">
         <f t="shared" si="1"/>
         <v>0.0308641975308642</v>
       </c>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q11" s="28"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:22">
+      <c r="R11" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S11" s="28"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:24">
       <c r="A12" s="19">
         <v>3002</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="21">
+        <v>1</v>
+      </c>
+      <c r="C12" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="19">
         <v>3</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="29" t="b">
+      <c r="E12" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="30">
-        <v>1</v>
-      </c>
-      <c r="G12" s="21">
+      <c r="H12" s="30">
+        <v>1</v>
+      </c>
+      <c r="I12" s="21">
         <v>1002</v>
       </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="19">
+      <c r="J12" s="21"/>
+      <c r="K12" s="19">
         <v>600</v>
       </c>
-      <c r="J12" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="19">
+      <c r="L12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="19">
         <v>50</v>
       </c>
-      <c r="L12" s="19">
+      <c r="N12" s="19">
         <v>250</v>
       </c>
-      <c r="M12" s="19">
+      <c r="O12" s="19">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="N12" s="27">
+      <c r="P12" s="27">
         <f t="shared" si="1"/>
         <v>0.0308641975308642</v>
       </c>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q12" s="28"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:22">
+      <c r="R12" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S12" s="28"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:24">
       <c r="A13" s="19">
         <v>3003</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="21">
+        <v>1</v>
+      </c>
+      <c r="C13" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19">
         <v>3</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="29" t="b">
+      <c r="E13" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="30">
-        <v>1</v>
-      </c>
-      <c r="G13" s="21">
+      <c r="H13" s="30">
+        <v>1</v>
+      </c>
+      <c r="I13" s="21">
         <v>1001</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="19">
+      <c r="J13" s="21"/>
+      <c r="K13" s="19">
         <v>600</v>
       </c>
-      <c r="J13" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="19">
+      <c r="L13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13" s="19">
         <v>50</v>
       </c>
-      <c r="L13" s="19">
+      <c r="N13" s="19">
         <v>250</v>
       </c>
-      <c r="M13" s="19">
+      <c r="O13" s="19">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="N13" s="27">
+      <c r="P13" s="27">
         <f t="shared" si="1"/>
         <v>0.0308641975308642</v>
       </c>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q13" s="28"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:22">
+      <c r="R13" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S13" s="28"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:24">
       <c r="A14" s="19">
         <v>4001</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="21">
+        <v>1</v>
+      </c>
+      <c r="C14" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19">
         <v>4</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="29" t="b">
+      <c r="E14" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="30">
-        <v>1</v>
-      </c>
-      <c r="G14" s="21">
+      <c r="H14" s="30">
+        <v>1</v>
+      </c>
+      <c r="I14" s="21">
         <v>1002</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="19">
+      <c r="J14" s="21"/>
+      <c r="K14" s="19">
         <v>600</v>
       </c>
-      <c r="J14" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="19">
+      <c r="L14" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M14" s="19">
         <v>50</v>
       </c>
-      <c r="L14" s="19">
+      <c r="N14" s="19">
         <v>150</v>
       </c>
-      <c r="M14" s="19">
+      <c r="O14" s="19">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="N14" s="27">
+      <c r="P14" s="27">
         <f t="shared" si="1"/>
         <v>0.0185185185185185</v>
       </c>
-      <c r="O14" s="28"/>
-      <c r="P14" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q14" s="28"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:22">
+      <c r="R14" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S14" s="28"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:24">
       <c r="A15" s="19">
         <v>4002</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="21">
+        <v>1</v>
+      </c>
+      <c r="C15" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19">
         <v>4</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="29" t="b">
+      <c r="E15" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F15" s="30">
-        <v>1</v>
-      </c>
-      <c r="G15" s="21">
+      <c r="H15" s="30">
+        <v>1</v>
+      </c>
+      <c r="I15" s="21">
         <v>1001</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="19">
+      <c r="J15" s="21"/>
+      <c r="K15" s="19">
         <v>600</v>
       </c>
-      <c r="J15" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="19">
+      <c r="L15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M15" s="19">
         <v>50</v>
       </c>
-      <c r="L15" s="19">
+      <c r="N15" s="19">
         <v>150</v>
       </c>
-      <c r="M15" s="19">
+      <c r="O15" s="19">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="N15" s="27">
+      <c r="P15" s="27">
         <f t="shared" si="1"/>
         <v>0.0185185185185185</v>
       </c>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q15" s="28"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:22">
+      <c r="R15" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S15" s="28"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:24">
       <c r="A16" s="19">
         <v>4003</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="21">
+        <v>1</v>
+      </c>
+      <c r="C16" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19">
         <v>4</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="29" t="b">
+      <c r="E16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="30">
-        <v>1</v>
-      </c>
-      <c r="G16" s="21">
+      <c r="H16" s="30">
+        <v>1</v>
+      </c>
+      <c r="I16" s="21">
         <v>1002</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="19">
+      <c r="J16" s="21"/>
+      <c r="K16" s="19">
         <v>600</v>
       </c>
-      <c r="J16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K16" s="19">
+      <c r="L16" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="19">
         <v>50</v>
       </c>
-      <c r="L16" s="19">
+      <c r="N16" s="19">
         <v>150</v>
       </c>
-      <c r="M16" s="19">
+      <c r="O16" s="19">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="N16" s="27">
+      <c r="P16" s="27">
         <f t="shared" si="1"/>
         <v>0.0185185185185185</v>
       </c>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q16" s="28"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:17">
+      <c r="R16" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S16" s="28"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:19">
       <c r="A17" s="23">
         <v>5001</v>
       </c>
       <c r="B17" s="23">
+        <v>1</v>
+      </c>
+      <c r="C17" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="23">
         <v>5</v>
       </c>
-      <c r="C17" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="25" t="b">
+      <c r="E17" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="26">
-        <v>1</v>
-      </c>
-      <c r="G17" s="24">
+      <c r="H17" s="26">
+        <v>1</v>
+      </c>
+      <c r="I17" s="25">
         <v>5001</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="19">
+      <c r="J17" s="21"/>
+      <c r="K17" s="19">
         <v>600</v>
       </c>
-      <c r="J17" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="19">
+      <c r="L17" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M17" s="19">
         <v>50</v>
       </c>
-      <c r="L17" s="19">
+      <c r="N17" s="19">
         <v>100</v>
       </c>
-      <c r="M17" s="19">
+      <c r="O17" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N17" s="27">
+      <c r="P17" s="27">
         <f t="shared" si="1"/>
         <v>0.0123456790123457</v>
       </c>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q17" s="28"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:17">
+      <c r="R17" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S17" s="28"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:19">
       <c r="A18" s="19">
         <v>5002</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="19">
         <v>5</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="29" t="b">
+      <c r="E18" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="30">
-        <v>1</v>
-      </c>
-      <c r="G18" s="21">
+      <c r="H18" s="30">
+        <v>1</v>
+      </c>
+      <c r="I18" s="21">
         <v>1002</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="19">
+      <c r="J18" s="21"/>
+      <c r="K18" s="19">
         <v>600</v>
       </c>
-      <c r="J18" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K18" s="19">
+      <c r="L18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="19">
         <v>50</v>
       </c>
-      <c r="L18" s="19">
+      <c r="N18" s="19">
         <v>100</v>
       </c>
-      <c r="M18" s="19">
+      <c r="O18" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N18" s="27">
+      <c r="P18" s="27">
         <f t="shared" si="1"/>
         <v>0.0123456790123457</v>
       </c>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q18" s="28"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:17">
+      <c r="R18" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" s="28"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:19">
       <c r="A19" s="19">
         <v>5003</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="21">
+        <v>1</v>
+      </c>
+      <c r="C19" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="19">
         <v>5</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="29" t="b">
+      <c r="E19" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F19" s="30">
-        <v>1</v>
-      </c>
-      <c r="G19" s="21">
+      <c r="H19" s="30">
+        <v>1</v>
+      </c>
+      <c r="I19" s="21">
         <v>1001</v>
       </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="19">
+      <c r="J19" s="21"/>
+      <c r="K19" s="19">
         <v>600</v>
       </c>
-      <c r="J19" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K19" s="19">
+      <c r="L19" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" s="19">
         <v>50</v>
       </c>
-      <c r="L19" s="19">
+      <c r="N19" s="19">
         <v>100</v>
       </c>
-      <c r="M19" s="19">
+      <c r="O19" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N19" s="27">
+      <c r="P19" s="27">
         <f t="shared" si="1"/>
         <v>0.0123456790123457</v>
       </c>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q19" s="28"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:17">
+      <c r="R19" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S19" s="28"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:19">
       <c r="A20" s="23">
         <v>1004</v>
       </c>
       <c r="B20" s="23">
         <v>1</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="25" t="b">
+      <c r="C20" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="23">
+        <v>1</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="F20" s="26">
-        <v>1</v>
-      </c>
-      <c r="G20" s="24">
+      <c r="H20" s="26">
+        <v>1</v>
+      </c>
+      <c r="I20" s="25">
         <v>1004</v>
       </c>
-      <c r="H20" s="21"/>
-      <c r="I20" s="19">
+      <c r="J20" s="21"/>
+      <c r="K20" s="19">
         <v>600</v>
       </c>
-      <c r="J20" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K20" s="19">
+      <c r="L20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M20" s="19">
         <v>50</v>
       </c>
-      <c r="L20" s="19">
+      <c r="N20" s="19">
         <v>500</v>
       </c>
-      <c r="M20" s="19">
+      <c r="O20" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N20" s="27">
+      <c r="P20" s="27">
         <f t="shared" si="1"/>
         <v>0.0617283950617284</v>
       </c>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q20" s="28"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:17">
+      <c r="R20" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S20" s="28"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:19">
       <c r="A21" s="23">
         <v>1005</v>
       </c>
       <c r="B21" s="23">
         <v>1</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="25" t="b">
+      <c r="C21" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="23">
+        <v>1</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="F21" s="26">
-        <v>1</v>
-      </c>
-      <c r="G21" s="24">
+      <c r="H21" s="26">
+        <v>1</v>
+      </c>
+      <c r="I21" s="25">
         <v>1005</v>
       </c>
-      <c r="H21" s="21"/>
-      <c r="I21" s="19">
+      <c r="J21" s="21"/>
+      <c r="K21" s="19">
         <v>600</v>
       </c>
-      <c r="J21" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K21" s="19">
+      <c r="L21" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21" s="19">
         <v>50</v>
       </c>
-      <c r="L21" s="19">
+      <c r="N21" s="19">
         <v>500</v>
       </c>
-      <c r="M21" s="19">
+      <c r="O21" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N21" s="27">
+      <c r="P21" s="27">
         <f t="shared" si="1"/>
         <v>0.0617283950617284</v>
       </c>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q21" s="28"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:17">
+      <c r="R21" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="28"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:19">
       <c r="A22" s="19">
         <v>1006</v>
       </c>
-      <c r="B22" s="19">
-        <v>1</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="29" t="b">
+      <c r="B22" s="21">
+        <v>1</v>
+      </c>
+      <c r="C22" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="19">
+        <v>1</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F22" s="30">
-        <v>1</v>
-      </c>
-      <c r="G22" s="21">
+      <c r="H22" s="30">
+        <v>1</v>
+      </c>
+      <c r="I22" s="21">
         <v>1002</v>
       </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="19">
+      <c r="J22" s="21"/>
+      <c r="K22" s="19">
         <v>600</v>
       </c>
-      <c r="J22" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K22" s="19">
+      <c r="L22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M22" s="19">
         <v>50</v>
       </c>
-      <c r="L22" s="19">
+      <c r="N22" s="19">
         <v>500</v>
       </c>
-      <c r="M22" s="19">
+      <c r="O22" s="19">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="N22" s="27">
+      <c r="P22" s="27">
         <f t="shared" si="1"/>
         <v>0.0617283950617284</v>
       </c>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q22" s="28"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:17">
+      <c r="R22" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S22" s="28"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:19">
       <c r="A23" s="19">
         <v>2004</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="21">
+        <v>1</v>
+      </c>
+      <c r="C23" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19">
         <v>2</v>
       </c>
-      <c r="C23" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="29" t="b">
+      <c r="E23" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F23" s="30">
-        <v>1</v>
-      </c>
-      <c r="G23" s="21">
+      <c r="H23" s="30">
+        <v>1</v>
+      </c>
+      <c r="I23" s="21">
         <v>1001</v>
       </c>
-      <c r="H23" s="21"/>
-      <c r="I23" s="19">
+      <c r="J23" s="21"/>
+      <c r="K23" s="19">
         <v>600</v>
       </c>
-      <c r="J23" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K23" s="19">
+      <c r="L23" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M23" s="19">
         <v>50</v>
       </c>
-      <c r="L23" s="19">
+      <c r="N23" s="19">
         <v>350</v>
       </c>
-      <c r="M23" s="19">
+      <c r="O23" s="19">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="N23" s="27">
+      <c r="P23" s="27">
         <f t="shared" si="1"/>
         <v>0.0432098765432099</v>
       </c>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q23" s="28"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:17">
+      <c r="R23" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S23" s="28"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:19">
       <c r="A24" s="19">
         <v>2005</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="21">
+        <v>1</v>
+      </c>
+      <c r="C24" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="19">
         <v>2</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="29" t="b">
+      <c r="E24" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F24" s="30">
-        <v>1</v>
-      </c>
-      <c r="G24" s="21">
+      <c r="H24" s="30">
+        <v>1</v>
+      </c>
+      <c r="I24" s="21">
         <v>1002</v>
       </c>
-      <c r="H24" s="21"/>
-      <c r="I24" s="19">
+      <c r="J24" s="21"/>
+      <c r="K24" s="19">
         <v>600</v>
       </c>
-      <c r="J24" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K24" s="19">
+      <c r="L24" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M24" s="19">
         <v>50</v>
       </c>
-      <c r="L24" s="19">
+      <c r="N24" s="19">
         <v>350</v>
       </c>
-      <c r="M24" s="19">
+      <c r="O24" s="19">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="N24" s="27">
+      <c r="P24" s="27">
         <f t="shared" si="1"/>
         <v>0.0432098765432099</v>
       </c>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q24" s="28"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:17">
+      <c r="R24" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S24" s="28"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:19">
       <c r="A25" s="19">
         <v>2006</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="21">
+        <v>1</v>
+      </c>
+      <c r="C25" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="19">
         <v>2</v>
       </c>
-      <c r="C25" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="29" t="b">
+      <c r="E25" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F25" s="30">
-        <v>1</v>
-      </c>
-      <c r="G25" s="21">
+      <c r="H25" s="30">
+        <v>1</v>
+      </c>
+      <c r="I25" s="21">
         <v>1001</v>
       </c>
-      <c r="H25" s="21"/>
-      <c r="I25" s="19">
+      <c r="J25" s="21"/>
+      <c r="K25" s="19">
         <v>600</v>
       </c>
-      <c r="J25" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="19">
+      <c r="L25" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M25" s="19">
         <v>50</v>
       </c>
-      <c r="L25" s="19">
+      <c r="N25" s="19">
         <v>350</v>
       </c>
-      <c r="M25" s="19">
+      <c r="O25" s="19">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="N25" s="27">
+      <c r="P25" s="27">
         <f t="shared" si="1"/>
         <v>0.0432098765432099</v>
       </c>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q25" s="28"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:17">
+      <c r="R25" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S25" s="28"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:19">
       <c r="A26" s="19">
         <v>3004</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="21">
+        <v>1</v>
+      </c>
+      <c r="C26" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="19">
         <v>3</v>
       </c>
-      <c r="C26" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="29" t="b">
+      <c r="E26" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G26" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F26" s="30">
-        <v>1</v>
-      </c>
-      <c r="G26" s="21">
+      <c r="H26" s="30">
+        <v>1</v>
+      </c>
+      <c r="I26" s="21">
         <v>1002</v>
       </c>
-      <c r="H26" s="21"/>
-      <c r="I26" s="19">
+      <c r="J26" s="21"/>
+      <c r="K26" s="19">
         <v>600</v>
       </c>
-      <c r="J26" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="19">
+      <c r="L26" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26" s="19">
         <v>50</v>
       </c>
-      <c r="L26" s="19">
+      <c r="N26" s="19">
         <v>250</v>
       </c>
-      <c r="M26" s="19">
+      <c r="O26" s="19">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="N26" s="27">
+      <c r="P26" s="27">
         <f t="shared" si="1"/>
         <v>0.0308641975308642</v>
       </c>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q26" s="28"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:17">
+      <c r="R26" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S26" s="28"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:19">
       <c r="A27" s="19">
         <v>3005</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="21">
+        <v>1</v>
+      </c>
+      <c r="C27" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="19">
         <v>3</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E27" s="29" t="b">
+      <c r="E27" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F27" s="30">
-        <v>1</v>
-      </c>
-      <c r="G27" s="21">
+      <c r="H27" s="30">
+        <v>1</v>
+      </c>
+      <c r="I27" s="21">
         <v>1001</v>
       </c>
-      <c r="H27" s="21"/>
-      <c r="I27" s="19">
+      <c r="J27" s="21"/>
+      <c r="K27" s="19">
         <v>600</v>
       </c>
-      <c r="J27" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="19">
+      <c r="L27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27" s="19">
         <v>50</v>
       </c>
-      <c r="L27" s="19">
+      <c r="N27" s="19">
         <v>250</v>
       </c>
-      <c r="M27" s="19">
+      <c r="O27" s="19">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="N27" s="27">
+      <c r="P27" s="27">
         <f t="shared" si="1"/>
         <v>0.0308641975308642</v>
       </c>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="Q27" s="28"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:17">
+      <c r="R27" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" s="28"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:19">
       <c r="A28" s="19">
         <v>3006</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="21">
+        <v>1</v>
+      </c>
+      <c r="C28" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="19">
         <v>3</v>
       </c>
-      <c r="C28" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="29" t="b">
+      <c r="E28" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F28" s="30">
-        <v>1</v>
-      </c>
-      <c r="G28" s="21">
+      <c r="H28" s="30">
+        <v>1</v>
+      </c>
+      <c r="I28" s="21">
         <v>1002</v>
       </c>
-      <c r="H28" s="21"/>
-      <c r="I28" s="19">
+      <c r="J28" s="21"/>
+      <c r="K28" s="19">
         <v>600</v>
       </c>
-      <c r="J28" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K28" s="19">
+      <c r="L28" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M28" s="19">
         <v>50</v>
       </c>
-      <c r="L28" s="19">
+      <c r="N28" s="19">
         <v>250</v>
       </c>
-      <c r="M28" s="19">
+      <c r="O28" s="19">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="N28" s="27">
+      <c r="P28" s="27">
         <f t="shared" si="1"/>
         <v>0.0308641975308642</v>
       </c>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28" t="s">
-        <v>44</v>
-      </c>
       <c r="Q28" s="28"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:17">
+      <c r="R28" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S28" s="28"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:19">
       <c r="A29" s="19">
         <v>4004</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="21">
+        <v>1</v>
+      </c>
+      <c r="C29" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="19">
         <v>4</v>
       </c>
-      <c r="C29" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="29" t="b">
+      <c r="E29" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" s="30">
-        <v>1</v>
-      </c>
-      <c r="G29" s="21">
+      <c r="H29" s="30">
+        <v>1</v>
+      </c>
+      <c r="I29" s="21">
         <v>1001</v>
       </c>
-      <c r="H29" s="21"/>
-      <c r="I29" s="19">
+      <c r="J29" s="21"/>
+      <c r="K29" s="19">
         <v>600</v>
       </c>
-      <c r="J29" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K29" s="19">
+      <c r="L29" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M29" s="19">
         <v>50</v>
       </c>
-      <c r="L29" s="19">
+      <c r="N29" s="19">
         <v>150</v>
       </c>
-      <c r="M29" s="19">
+      <c r="O29" s="19">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="N29" s="27">
+      <c r="P29" s="27">
         <f t="shared" si="1"/>
         <v>0.0185185185185185</v>
       </c>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="Q29" s="28"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:17">
+      <c r="R29" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S29" s="28"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:19">
       <c r="A30" s="19">
         <v>4005</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="21">
+        <v>1</v>
+      </c>
+      <c r="C30" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="19">
         <v>4</v>
       </c>
-      <c r="C30" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="29" t="b">
+      <c r="E30" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G30" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F30" s="30">
-        <v>1</v>
-      </c>
-      <c r="G30" s="21">
+      <c r="H30" s="30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="21">
         <v>1002</v>
       </c>
-      <c r="H30" s="21"/>
-      <c r="I30" s="19">
+      <c r="J30" s="21"/>
+      <c r="K30" s="19">
         <v>600</v>
       </c>
-      <c r="J30" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K30" s="19">
+      <c r="L30" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30" s="19">
         <v>50</v>
       </c>
-      <c r="L30" s="19">
+      <c r="N30" s="19">
         <v>150</v>
       </c>
-      <c r="M30" s="19">
+      <c r="O30" s="19">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="N30" s="27">
+      <c r="P30" s="27">
         <f t="shared" si="1"/>
         <v>0.0185185185185185</v>
       </c>
-      <c r="O30" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="28"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:17">
+      <c r="Q30" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:19">
       <c r="A31" s="19">
         <v>4006</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="21">
+        <v>1</v>
+      </c>
+      <c r="C31" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="19">
         <v>4</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="29" t="b">
+      <c r="E31" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F31" s="30">
-        <v>1</v>
-      </c>
-      <c r="G31" s="21">
+      <c r="H31" s="30">
+        <v>1</v>
+      </c>
+      <c r="I31" s="21">
         <v>1001</v>
       </c>
-      <c r="H31" s="21"/>
-      <c r="I31" s="19">
+      <c r="J31" s="21"/>
+      <c r="K31" s="19">
         <v>600</v>
       </c>
-      <c r="J31" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K31" s="19">
+      <c r="L31" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M31" s="19">
         <v>50</v>
       </c>
-      <c r="L31" s="19">
+      <c r="N31" s="19">
         <v>150</v>
       </c>
-      <c r="M31" s="19">
+      <c r="O31" s="19">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="N31" s="27">
+      <c r="P31" s="27">
         <f t="shared" si="1"/>
         <v>0.0185185185185185</v>
       </c>
-      <c r="O31" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:17">
+      <c r="Q31" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:19">
       <c r="A32" s="19">
         <v>5004</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="21">
+        <v>1</v>
+      </c>
+      <c r="C32" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="19">
         <v>5</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="29" t="b">
+      <c r="E32" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F32" s="30">
-        <v>1</v>
-      </c>
-      <c r="G32" s="21">
+      <c r="H32" s="30">
+        <v>1</v>
+      </c>
+      <c r="I32" s="21">
         <v>1002</v>
       </c>
-      <c r="H32" s="21"/>
-      <c r="I32" s="19">
+      <c r="J32" s="21"/>
+      <c r="K32" s="19">
         <v>600</v>
       </c>
-      <c r="J32" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="19">
+      <c r="L32" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M32" s="19">
         <v>50</v>
       </c>
-      <c r="L32" s="19">
+      <c r="N32" s="19">
         <v>100</v>
       </c>
-      <c r="M32" s="19">
+      <c r="O32" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N32" s="27">
+      <c r="P32" s="27">
         <f t="shared" si="1"/>
         <v>0.0123456790123457</v>
       </c>
-      <c r="O32" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:17">
+      <c r="Q32" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:19">
       <c r="A33" s="19">
         <v>5005</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="21">
+        <v>1</v>
+      </c>
+      <c r="C33" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="19">
         <v>5</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="29" t="b">
+      <c r="E33" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G33" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="F33" s="30">
-        <v>1</v>
-      </c>
-      <c r="G33" s="21">
+      <c r="H33" s="30">
+        <v>1</v>
+      </c>
+      <c r="I33" s="21">
         <v>1001</v>
       </c>
-      <c r="H33" s="21"/>
-      <c r="I33" s="19">
+      <c r="J33" s="21"/>
+      <c r="K33" s="19">
         <v>600</v>
       </c>
-      <c r="J33" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="19">
+      <c r="L33" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M33" s="19">
         <v>50</v>
       </c>
-      <c r="L33" s="19">
+      <c r="N33" s="19">
         <v>100</v>
       </c>
-      <c r="M33" s="19">
+      <c r="O33" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N33" s="27">
+      <c r="P33" s="27">
         <f t="shared" si="1"/>
         <v>0.0123456790123457</v>
       </c>
-      <c r="O33" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="28"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:17">
+      <c r="Q33" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:19">
       <c r="A34" s="23">
         <v>5006</v>
       </c>
       <c r="B34" s="23">
+        <v>1</v>
+      </c>
+      <c r="C34" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="23">
         <v>5</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="25" t="b">
+      <c r="E34" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="F34" s="26">
-        <v>1</v>
-      </c>
-      <c r="G34" s="24">
+      <c r="H34" s="26">
+        <v>1</v>
+      </c>
+      <c r="I34" s="25">
         <v>5006</v>
       </c>
-      <c r="H34" s="21"/>
-      <c r="I34" s="19">
+      <c r="J34" s="21"/>
+      <c r="K34" s="19">
         <v>600</v>
       </c>
-      <c r="J34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K34" s="19">
+      <c r="L34" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M34" s="19">
         <v>50</v>
       </c>
-      <c r="L34" s="19">
+      <c r="N34" s="19">
         <v>100</v>
       </c>
-      <c r="M34" s="19">
+      <c r="O34" s="19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N34" s="27">
+      <c r="P34" s="27">
         <f t="shared" si="1"/>
         <v>0.0123456790123457</v>
       </c>
-      <c r="O34" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="M35" s="32"/>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="M36" s="32"/>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="M37" s="32"/>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="M38" s="32"/>
-    </row>
-    <row r="39" ht="17.25" spans="1:17">
-      <c r="C39" s="33"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="M39" s="32"/>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-    </row>
-    <row r="42" spans="1:17">
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-    </row>
-    <row r="43" spans="1:17">
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-    </row>
-    <row r="44" spans="1:17">
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-    </row>
-    <row r="45" spans="1:17">
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-    </row>
-    <row r="46" spans="1:17">
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-    </row>
-    <row r="47" spans="1:17">
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-    </row>
-    <row r="48" spans="1:17">
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-    </row>
-    <row r="49" spans="3:10">
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-    </row>
-    <row r="50" spans="3:10">
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-    </row>
-    <row r="51" spans="3:10">
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-    </row>
-    <row r="52" spans="3:10">
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-    </row>
-    <row r="53" ht="14.25" spans="3:10">
-      <c r="C53" s="34"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-    </row>
-    <row r="54" spans="3:10">
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-    </row>
-    <row r="55" spans="3:10">
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-    </row>
-    <row r="56" spans="3:10">
-      <c r="I56" s="31"/>
-      <c r="J56" s="31"/>
-    </row>
-    <row r="57" spans="3:10">
-      <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
-    </row>
-    <row r="58" spans="3:10">
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-    </row>
-    <row r="59" spans="3:10">
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-    </row>
-    <row r="60" spans="3:10">
-      <c r="I60" s="31"/>
-      <c r="J60" s="31"/>
+      <c r="Q34" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A35" s="31">
+        <v>9001</v>
+      </c>
+      <c r="B35" s="32">
+        <v>2</v>
+      </c>
+      <c r="C35" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="32">
+        <v>9</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="G35" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="32">
+        <v>1</v>
+      </c>
+      <c r="I35" s="32">
+        <v>1004</v>
+      </c>
+      <c r="J35" s="33"/>
+      <c r="K35" s="34">
+        <v>200</v>
+      </c>
+      <c r="L35" s="35"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="36"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R35" s="33"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A36" s="31">
+        <v>9002</v>
+      </c>
+      <c r="B36" s="32">
+        <v>2</v>
+      </c>
+      <c r="C36" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="32">
+        <v>9</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="G36" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="32">
+        <v>1</v>
+      </c>
+      <c r="I36" s="32">
+        <v>1004</v>
+      </c>
+      <c r="J36" s="33"/>
+      <c r="K36" s="34">
+        <v>200</v>
+      </c>
+      <c r="L36" s="35"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R36" s="33"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A37" s="31">
+        <v>9003</v>
+      </c>
+      <c r="B37" s="32">
+        <v>2</v>
+      </c>
+      <c r="C37" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" s="32">
+        <v>9</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="32">
+        <v>1</v>
+      </c>
+      <c r="I37" s="32">
+        <v>1004</v>
+      </c>
+      <c r="J37" s="33"/>
+      <c r="K37" s="34">
+        <v>200</v>
+      </c>
+      <c r="L37" s="35"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R37" s="33"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A38" s="31">
+        <v>9004</v>
+      </c>
+      <c r="B38" s="32">
+        <v>2</v>
+      </c>
+      <c r="C38" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="32">
+        <v>9</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="32">
+        <v>1</v>
+      </c>
+      <c r="I38" s="32">
+        <v>1003</v>
+      </c>
+      <c r="J38" s="33"/>
+      <c r="K38" s="34">
+        <v>200</v>
+      </c>
+      <c r="L38" s="35"/>
+      <c r="M38" s="33"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R38" s="33"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A39" s="31">
+        <v>9005</v>
+      </c>
+      <c r="B39" s="32">
+        <v>2</v>
+      </c>
+      <c r="C39" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="32">
+        <v>9</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="32">
+        <v>1</v>
+      </c>
+      <c r="I39" s="32">
+        <v>1003</v>
+      </c>
+      <c r="J39" s="33"/>
+      <c r="K39" s="34">
+        <v>200</v>
+      </c>
+      <c r="L39" s="35"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R39" s="33"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="K40" s="37"/>
+      <c r="L40" s="37"/>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="K41" s="37"/>
+      <c r="L41" s="37"/>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="K42" s="37"/>
+      <c r="L42" s="37"/>
+    </row>
+    <row r="43" spans="1:19">
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
+    </row>
+    <row r="44" spans="1:19">
+      <c r="K44" s="37"/>
+      <c r="L44" s="37"/>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="K45" s="37"/>
+      <c r="L45" s="37"/>
+    </row>
+    <row r="46" spans="1:19">
+      <c r="K46" s="37"/>
+      <c r="L46" s="37"/>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="K47" s="37"/>
+      <c r="L47" s="37"/>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="K48" s="37"/>
+      <c r="L48" s="37"/>
+    </row>
+    <row r="49" spans="5:12">
+      <c r="K49" s="37"/>
+      <c r="L49" s="37"/>
+    </row>
+    <row r="50" spans="5:12">
+      <c r="K50" s="37"/>
+      <c r="L50" s="37"/>
+    </row>
+    <row r="51" spans="5:12">
+      <c r="K51" s="37"/>
+      <c r="L51" s="37"/>
+    </row>
+    <row r="52" spans="5:12">
+      <c r="K52" s="37"/>
+      <c r="L52" s="37"/>
+    </row>
+    <row r="53" ht="14.25" spans="5:12">
+      <c r="E53" s="38"/>
+      <c r="K53" s="37"/>
+      <c r="L53" s="37"/>
+    </row>
+    <row r="54" spans="5:12">
+      <c r="K54" s="37"/>
+      <c r="L54" s="37"/>
+    </row>
+    <row r="55" spans="5:12">
+      <c r="K55" s="37"/>
+      <c r="L55" s="37"/>
+    </row>
+    <row r="56" spans="5:12">
+      <c r="K56" s="37"/>
+      <c r="L56" s="37"/>
+    </row>
+    <row r="57" spans="5:12">
+      <c r="K57" s="37"/>
+      <c r="L57" s="37"/>
+    </row>
+    <row r="58" spans="5:12">
+      <c r="K58" s="37"/>
+      <c r="L58" s="37"/>
+    </row>
+    <row r="59" spans="5:12">
+      <c r="K59" s="37"/>
+      <c r="L59" s="37"/>
+    </row>
+    <row r="60" spans="5:12">
+      <c r="K60" s="37"/>
+      <c r="L60" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="Q2:Q3 Q8:Q19 Q6 Q35:Q60 P61:Q63 A1:B1 J1 A4:B4 J4:J9 J11:J12 J14:J15 J17:J18 P4:Q4 P1:Q1" formula="1"/>
+    <ignoredError sqref="D1 D4 R1:S1 R4:S4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 R61:S63 S35:S60 S6 S8:S19 S2:S3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3449,7 +3926,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -3672,13 +4149,13 @@
         <v>1111</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="H27" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -3719,13 +4196,13 @@
         <v>1025101_1125101_2</v>
       </c>
       <c r="R30" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U30" s="2">
         <v>1025101</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="2:22">
@@ -3756,13 +4233,13 @@
         <v>1025102_1125102_2</v>
       </c>
       <c r="R31" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="U31" s="2">
         <v>1025102</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="2:22">
@@ -3793,13 +4270,13 @@
         <v>1025103_1125103_2</v>
       </c>
       <c r="R32" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="U32" s="2">
         <v>1025103</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="6:22">
@@ -3830,13 +4307,13 @@
         <v>1025201_1125201_4</v>
       </c>
       <c r="R33" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U33" s="2">
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -3867,13 +4344,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="U34" s="2">
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -3904,13 +4381,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="U35" s="2">
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -3941,13 +4418,13 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="U36" s="3">
         <v>1025201</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="6:22">
@@ -3978,13 +4455,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -4015,13 +4492,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -4052,13 +4529,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4089,13 +4566,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -4126,13 +4603,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -4163,13 +4640,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -4200,13 +4677,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -4237,13 +4714,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -4274,13 +4751,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -4311,13 +4788,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4348,13 +4825,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4385,13 +4862,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4422,13 +4899,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4459,13 +4936,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4496,13 +4973,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -4533,13 +5010,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -4570,13 +5047,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -4607,13 +5084,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -4644,13 +5121,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -4681,13 +5158,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -4718,13 +5195,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -4755,13 +5232,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -4792,13 +5269,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -350,57 +350,63 @@
     <t>随机</t>
   </si>
   <si>
+    <t>1101_1102_1110_1107_1103_1104_1105_1202</t>
+  </si>
+  <si>
+    <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
+  </si>
+  <si>
+    <t>1025102_1125102_10</t>
+  </si>
+  <si>
+    <t>复古绅士</t>
+  </si>
+  <si>
+    <t>1101_1102_1107_1110_1103_1104_1105_1202</t>
+  </si>
+  <si>
+    <t>1025103_1125103_10</t>
+  </si>
+  <si>
+    <t>酷盖少年</t>
+  </si>
+  <si>
+    <t>固定</t>
+  </si>
+  <si>
+    <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_3000|1108_3000|1109_3000|1110_3000|1111_3000|1112_3000|1202_2000</t>
+  </si>
+  <si>
+    <t>1025201_1125201_10</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>1025202_1125202_10</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>1101_1102_1103_1104_1105_1106_1110_1107</t>
+  </si>
+  <si>
+    <t>1025203_1125203_10</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>1025301_1125301_10</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
     <t>1102_1103_1104_1105_1106_1107_1108_1109_1110_1111_1112_1202</t>
   </si>
   <si>
-    <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
-  </si>
-  <si>
-    <t>1025102_1125102_10</t>
-  </si>
-  <si>
-    <t>复古绅士</t>
-  </si>
-  <si>
-    <t>1102_1110_1107_1109_1108_1112</t>
-  </si>
-  <si>
-    <t>1025103_1125103_10</t>
-  </si>
-  <si>
-    <t>酷盖少年</t>
-  </si>
-  <si>
-    <t>固定</t>
-  </si>
-  <si>
-    <t>1102_1106_1202_1111_1112_1108_1109_1107_1110</t>
-  </si>
-  <si>
-    <t>1025201_1125201_10</t>
-  </si>
-  <si>
-    <t>运动健将</t>
-  </si>
-  <si>
-    <t>1025202_1125202_10</t>
-  </si>
-  <si>
-    <t>跑酷少年</t>
-  </si>
-  <si>
-    <t>1025203_1125203_10</t>
-  </si>
-  <si>
-    <t>滑板高手</t>
-  </si>
-  <si>
-    <t>1025301_1125301_10</t>
-  </si>
-  <si>
-    <t>健身狂魔</t>
-  </si>
-  <si>
     <t>1025302_1125302_10</t>
   </si>
   <si>
@@ -419,6 +425,9 @@
     <t>马拉松客</t>
   </si>
   <si>
+    <t>1110_1107_1109_1108_1111_1202_1103_1102_1101_1107</t>
+  </si>
+  <si>
     <t>1025402_1125402_10</t>
   </si>
   <si>
@@ -479,6 +488,9 @@
     <t>活力少女</t>
   </si>
   <si>
+    <t>1109_1108_1112_1111_1202_1106_1105_1104_1103</t>
+  </si>
+  <si>
     <t>1025206_1125206_10</t>
   </si>
   <si>
@@ -513,9 +525,6 @@
   </si>
   <si>
     <t>浪漫诗人</t>
-  </si>
-  <si>
-    <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_3000|1108_3000|1109_3000|1110_3000|1111_3000|1112_3000|1201_2000|1202_2000</t>
   </si>
   <si>
     <t>1025406_1125406_10</t>
@@ -1318,7 +1327,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1414,12 +1423,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2121,10 +2124,10 @@
         <f t="shared" si="1"/>
         <v>0.0617283950617284</v>
       </c>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28" t="s">
+      <c r="Q7" s="28" t="s">
         <v>48</v>
       </c>
+      <c r="R7" s="28"/>
       <c r="S7" s="28"/>
     </row>
     <row r="8" ht="16.5" spans="1:24">
@@ -2178,7 +2181,7 @@
       </c>
       <c r="Q8" s="28"/>
       <c r="R8" s="28" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S8" s="28"/>
     </row>
@@ -2233,7 +2236,7 @@
       </c>
       <c r="Q9" s="28"/>
       <c r="R9" s="28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="S9" s="28"/>
     </row>
@@ -2251,10 +2254,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" s="29" t="b">
         <v>0</v>
@@ -2286,10 +2289,10 @@
         <f t="shared" si="1"/>
         <v>0.0432098765432099</v>
       </c>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28" t="s">
+      <c r="Q10" s="28" t="s">
         <v>48</v>
       </c>
+      <c r="R10" s="28"/>
       <c r="S10" s="28"/>
     </row>
     <row r="11" ht="16.5" spans="1:24">
@@ -2306,10 +2309,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="29" t="b">
         <v>0</v>
@@ -2343,7 +2346,7 @@
       </c>
       <c r="Q11" s="28"/>
       <c r="R11" s="28" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="S11" s="28"/>
     </row>
@@ -2361,10 +2364,10 @@
         <v>3</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G12" s="29" t="b">
         <v>0</v>
@@ -2398,7 +2401,7 @@
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="S12" s="28"/>
     </row>
@@ -2416,10 +2419,10 @@
         <v>3</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13" s="29" t="b">
         <v>0</v>
@@ -2451,10 +2454,10 @@
         <f t="shared" si="1"/>
         <v>0.0308641975308642</v>
       </c>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28" t="s">
+      <c r="Q13" s="28" t="s">
         <v>48</v>
       </c>
+      <c r="R13" s="28"/>
       <c r="S13" s="28"/>
     </row>
     <row r="14" ht="16.5" spans="1:24">
@@ -2471,10 +2474,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" s="29" t="b">
         <v>0</v>
@@ -2508,7 +2511,7 @@
       </c>
       <c r="Q14" s="28"/>
       <c r="R14" s="28" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="S14" s="28"/>
     </row>
@@ -2526,10 +2529,10 @@
         <v>4</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G15" s="29" t="b">
         <v>0</v>
@@ -2563,7 +2566,7 @@
       </c>
       <c r="Q15" s="28"/>
       <c r="R15" s="28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="S15" s="28"/>
     </row>
@@ -2581,10 +2584,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G16" s="29" t="b">
         <v>0</v>
@@ -2616,10 +2619,10 @@
         <f t="shared" si="1"/>
         <v>0.0185185185185185</v>
       </c>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28" t="s">
+      <c r="Q16" s="28" t="s">
         <v>48</v>
       </c>
+      <c r="R16" s="28"/>
       <c r="S16" s="28"/>
     </row>
     <row r="17" ht="16.5" spans="1:19">
@@ -2636,10 +2639,10 @@
         <v>5</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G17" s="24" t="b">
         <v>0</v>
@@ -2673,7 +2676,7 @@
       </c>
       <c r="Q17" s="28"/>
       <c r="R17" s="28" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="S17" s="28"/>
     </row>
@@ -2691,10 +2694,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G18" s="29" t="b">
         <v>0</v>
@@ -2728,7 +2731,7 @@
       </c>
       <c r="Q18" s="28"/>
       <c r="R18" s="28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="S18" s="28"/>
     </row>
@@ -2746,10 +2749,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G19" s="29" t="b">
         <v>0</v>
@@ -2781,10 +2784,10 @@
         <f t="shared" si="1"/>
         <v>0.0123456790123457</v>
       </c>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28" t="s">
+      <c r="Q19" s="28" t="s">
         <v>48</v>
       </c>
+      <c r="R19" s="28"/>
       <c r="S19" s="28"/>
     </row>
     <row r="20" ht="16.5" spans="1:19">
@@ -2801,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G20" s="24" t="b">
         <v>0</v>
@@ -2856,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G21" s="24" t="b">
         <v>0</v>
@@ -2911,10 +2914,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G22" s="29" t="b">
         <v>0</v>
@@ -2948,7 +2951,7 @@
       </c>
       <c r="Q22" s="28"/>
       <c r="R22" s="28" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="S22" s="28"/>
     </row>
@@ -2966,10 +2969,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G23" s="29" t="b">
         <v>0</v>
@@ -3003,7 +3006,7 @@
       </c>
       <c r="Q23" s="28"/>
       <c r="R23" s="28" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="S23" s="28"/>
     </row>
@@ -3021,10 +3024,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G24" s="29" t="b">
         <v>0</v>
@@ -3058,7 +3061,7 @@
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="28" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="S24" s="28"/>
     </row>
@@ -3076,10 +3079,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G25" s="29" t="b">
         <v>0</v>
@@ -3113,7 +3116,7 @@
       </c>
       <c r="Q25" s="28"/>
       <c r="R25" s="28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="S25" s="28"/>
     </row>
@@ -3131,10 +3134,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G26" s="29" t="b">
         <v>0</v>
@@ -3168,7 +3171,7 @@
       </c>
       <c r="Q26" s="28"/>
       <c r="R26" s="28" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S26" s="28"/>
     </row>
@@ -3186,10 +3189,10 @@
         <v>3</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G27" s="29" t="b">
         <v>0</v>
@@ -3223,7 +3226,7 @@
       </c>
       <c r="Q27" s="28"/>
       <c r="R27" s="28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="S27" s="28"/>
     </row>
@@ -3241,10 +3244,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G28" s="29" t="b">
         <v>0</v>
@@ -3278,7 +3281,7 @@
       </c>
       <c r="Q28" s="28"/>
       <c r="R28" s="28" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="S28" s="28"/>
     </row>
@@ -3296,10 +3299,10 @@
         <v>4</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G29" s="29" t="b">
         <v>0</v>
@@ -3333,7 +3336,7 @@
       </c>
       <c r="Q29" s="28"/>
       <c r="R29" s="28" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="S29" s="28"/>
     </row>
@@ -3351,10 +3354,10 @@
         <v>4</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G30" s="29" t="b">
         <v>0</v>
@@ -3387,7 +3390,7 @@
         <v>0.0185185185185185</v>
       </c>
       <c r="Q30" s="28" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
@@ -3406,10 +3409,10 @@
         <v>4</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G31" s="29" t="b">
         <v>0</v>
@@ -3442,7 +3445,7 @@
         <v>0.0185185185185185</v>
       </c>
       <c r="Q31" s="28" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
@@ -3461,10 +3464,10 @@
         <v>5</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G32" s="29" t="b">
         <v>0</v>
@@ -3497,7 +3500,7 @@
         <v>0.0123456790123457</v>
       </c>
       <c r="Q32" s="28" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -3516,10 +3519,10 @@
         <v>5</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G33" s="29" t="b">
         <v>0</v>
@@ -3552,7 +3555,7 @@
         <v>0.0123456790123457</v>
       </c>
       <c r="Q33" s="28" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="R33" s="28"/>
       <c r="S33" s="28"/>
@@ -3571,10 +3574,10 @@
         <v>5</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G34" s="24" t="b">
         <v>0</v>
@@ -3607,7 +3610,7 @@
         <v>0.0123456790123457</v>
       </c>
       <c r="Q34" s="28" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="R34" s="28"/>
       <c r="S34" s="28"/>
@@ -3616,303 +3619,303 @@
       <c r="A35" s="31">
         <v>9001</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="19">
         <v>2</v>
       </c>
       <c r="C35" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="19">
         <v>9</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F35" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>108</v>
       </c>
       <c r="G35" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H35" s="32">
-        <v>1</v>
-      </c>
-      <c r="I35" s="32">
+      <c r="H35" s="19">
+        <v>1</v>
+      </c>
+      <c r="I35" s="19">
         <v>1004</v>
       </c>
-      <c r="J35" s="33"/>
-      <c r="K35" s="34">
+      <c r="J35" s="28"/>
+      <c r="K35" s="32">
         <v>200</v>
       </c>
-      <c r="L35" s="35"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="28"/>
       <c r="Q35" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="R35" s="33"/>
+        <v>48</v>
+      </c>
+      <c r="R35" s="28"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:19">
       <c r="A36" s="31">
         <v>9002</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="19">
         <v>2</v>
       </c>
       <c r="C36" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="19">
         <v>9</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>110</v>
       </c>
       <c r="G36" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H36" s="32">
-        <v>1</v>
-      </c>
-      <c r="I36" s="32">
+      <c r="H36" s="19">
+        <v>1</v>
+      </c>
+      <c r="I36" s="19">
         <v>1004</v>
       </c>
-      <c r="J36" s="33"/>
-      <c r="K36" s="34">
+      <c r="J36" s="28"/>
+      <c r="K36" s="32">
         <v>200</v>
       </c>
-      <c r="L36" s="35"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="36"/>
-      <c r="P36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="34"/>
+      <c r="P36" s="28"/>
       <c r="Q36" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="R36" s="33"/>
+        <v>48</v>
+      </c>
+      <c r="R36" s="28"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:19">
       <c r="A37" s="31">
         <v>9003</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="19">
         <v>2</v>
       </c>
       <c r="C37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D37" s="19">
         <v>9</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>112</v>
       </c>
       <c r="G37" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H37" s="32">
-        <v>1</v>
-      </c>
-      <c r="I37" s="32">
+      <c r="H37" s="19">
+        <v>1</v>
+      </c>
+      <c r="I37" s="19">
         <v>1004</v>
       </c>
-      <c r="J37" s="33"/>
-      <c r="K37" s="34">
+      <c r="J37" s="28"/>
+      <c r="K37" s="32">
         <v>200</v>
       </c>
-      <c r="L37" s="35"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="36"/>
-      <c r="P37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="28"/>
       <c r="Q37" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="R37" s="33"/>
+        <v>48</v>
+      </c>
+      <c r="R37" s="28"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:19">
       <c r="A38" s="31">
         <v>9004</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="19">
         <v>2</v>
       </c>
       <c r="C38" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="19">
         <v>9</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="F38" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>114</v>
       </c>
       <c r="G38" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H38" s="32">
-        <v>1</v>
-      </c>
-      <c r="I38" s="32">
+      <c r="H38" s="19">
+        <v>1</v>
+      </c>
+      <c r="I38" s="19">
         <v>1003</v>
       </c>
-      <c r="J38" s="33"/>
-      <c r="K38" s="34">
+      <c r="J38" s="28"/>
+      <c r="K38" s="32">
         <v>200</v>
       </c>
-      <c r="L38" s="35"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="36"/>
-      <c r="P38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="34"/>
+      <c r="P38" s="28"/>
       <c r="Q38" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="R38" s="33"/>
+        <v>48</v>
+      </c>
+      <c r="R38" s="28"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:19">
       <c r="A39" s="31">
         <v>9005</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="19">
         <v>2</v>
       </c>
       <c r="C39" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="19">
         <v>9</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F39" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>116</v>
       </c>
       <c r="G39" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H39" s="32">
-        <v>1</v>
-      </c>
-      <c r="I39" s="32">
+      <c r="H39" s="19">
+        <v>1</v>
+      </c>
+      <c r="I39" s="19">
         <v>1003</v>
       </c>
-      <c r="J39" s="33"/>
-      <c r="K39" s="34">
+      <c r="J39" s="28"/>
+      <c r="K39" s="32">
         <v>200</v>
       </c>
-      <c r="L39" s="35"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="34"/>
+      <c r="P39" s="28"/>
       <c r="Q39" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="R39" s="33"/>
+        <v>48</v>
+      </c>
+      <c r="R39" s="28"/>
     </row>
     <row r="40" spans="1:19">
-      <c r="K40" s="37"/>
-      <c r="L40" s="37"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
     </row>
     <row r="41" spans="1:19">
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
     </row>
     <row r="42" spans="1:19">
-      <c r="K42" s="37"/>
-      <c r="L42" s="37"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
     </row>
     <row r="43" spans="1:19">
-      <c r="K43" s="37"/>
-      <c r="L43" s="37"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="K44" s="37"/>
-      <c r="L44" s="37"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
     </row>
     <row r="45" spans="1:19">
-      <c r="K45" s="37"/>
-      <c r="L45" s="37"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="35"/>
     </row>
     <row r="46" spans="1:19">
-      <c r="K46" s="37"/>
-      <c r="L46" s="37"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="K47" s="37"/>
-      <c r="L47" s="37"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
     </row>
     <row r="48" spans="1:19">
-      <c r="K48" s="37"/>
-      <c r="L48" s="37"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35"/>
     </row>
     <row r="49" spans="5:12">
-      <c r="K49" s="37"/>
-      <c r="L49" s="37"/>
+      <c r="K49" s="35"/>
+      <c r="L49" s="35"/>
     </row>
     <row r="50" spans="5:12">
-      <c r="K50" s="37"/>
-      <c r="L50" s="37"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
     </row>
     <row r="51" spans="5:12">
-      <c r="K51" s="37"/>
-      <c r="L51" s="37"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
     </row>
     <row r="52" spans="5:12">
-      <c r="K52" s="37"/>
-      <c r="L52" s="37"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
     </row>
     <row r="53" ht="14.25" spans="5:12">
-      <c r="E53" s="38"/>
-      <c r="K53" s="37"/>
-      <c r="L53" s="37"/>
+      <c r="E53" s="36"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
     </row>
     <row r="54" spans="5:12">
-      <c r="K54" s="37"/>
-      <c r="L54" s="37"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
     </row>
     <row r="55" spans="5:12">
-      <c r="K55" s="37"/>
-      <c r="L55" s="37"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="35"/>
     </row>
     <row r="56" spans="5:12">
-      <c r="K56" s="37"/>
-      <c r="L56" s="37"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
     </row>
     <row r="57" spans="5:12">
-      <c r="K57" s="37"/>
-      <c r="L57" s="37"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
     </row>
     <row r="58" spans="5:12">
-      <c r="K58" s="37"/>
-      <c r="L58" s="37"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
     </row>
     <row r="59" spans="5:12">
-      <c r="K59" s="37"/>
-      <c r="L59" s="37"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
     </row>
     <row r="60" spans="5:12">
-      <c r="K60" s="37"/>
-      <c r="L60" s="37"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D1 D4 R1:S1 R4:S4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 R61:S63 S35:S60 S6 S8:S19 S2:S3" formula="1"/>
+    <ignoredError sqref="S2:S3 S8:S19 S6 S35:S60 R61:S63 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 R4:S4 R1:S1 D4 D1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3926,7 +3929,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -4149,13 +4152,13 @@
         <v>1111</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -4313,7 +4316,7 @@
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -4350,7 +4353,7 @@
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -4381,13 +4384,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U35" s="2">
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -4418,7 +4421,7 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U36" s="3">
         <v>1025201</v>
@@ -4455,7 +4458,7 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
@@ -4492,13 +4495,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -4529,13 +4532,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4566,13 +4569,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -4603,13 +4606,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -4640,13 +4643,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -4677,13 +4680,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -4714,13 +4717,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -4751,13 +4754,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -4788,13 +4791,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4825,13 +4828,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4862,13 +4865,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4899,13 +4902,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4936,13 +4939,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4973,13 +4976,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -5010,13 +5013,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -5047,13 +5050,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -5084,13 +5087,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -5121,13 +5124,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -5158,13 +5161,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -5195,13 +5198,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -5232,13 +5235,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -5269,13 +5272,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -350,7 +350,7 @@
     <t>随机</t>
   </si>
   <si>
-    <t>1101_1102_1110_1107_1103_1104_1105_1202</t>
+    <t>1101_1102_1103_1104_1105_1106_1202_1111_1112_1108_1109_1110_1107</t>
   </si>
   <si>
     <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
@@ -362,7 +362,7 @@
     <t>复古绅士</t>
   </si>
   <si>
-    <t>1101_1102_1107_1110_1103_1104_1105_1202</t>
+    <t>1101_1107_1110_1102_1105_1104_1103_1106_1202_1111_1112_1108_1109</t>
   </si>
   <si>
     <t>1025103_1125103_10</t>
@@ -383,15 +383,15 @@
     <t>运动健将</t>
   </si>
   <si>
+    <t>1110_1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1101</t>
+  </si>
+  <si>
     <t>1025202_1125202_10</t>
   </si>
   <si>
     <t>跑酷少年</t>
   </si>
   <si>
-    <t>1101_1102_1103_1104_1105_1106_1110_1107</t>
-  </si>
-  <si>
     <t>1025203_1125203_10</t>
   </si>
   <si>
@@ -404,9 +404,6 @@
     <t>健身狂魔</t>
   </si>
   <si>
-    <t>1102_1103_1104_1105_1106_1107_1108_1109_1110_1111_1112_1202</t>
-  </si>
-  <si>
     <t>1025302_1125302_10</t>
   </si>
   <si>
@@ -425,15 +422,15 @@
     <t>马拉松客</t>
   </si>
   <si>
-    <t>1110_1107_1109_1108_1111_1202_1103_1102_1101_1107</t>
-  </si>
-  <si>
     <t>1025402_1125402_10</t>
   </si>
   <si>
     <t>极限玩家</t>
   </si>
   <si>
+    <t>1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1110_1101</t>
+  </si>
+  <si>
     <t>1025403_1125403_10</t>
   </si>
   <si>
@@ -486,9 +483,6 @@
   </si>
   <si>
     <t>活力少女</t>
-  </si>
-  <si>
-    <t>1109_1108_1112_1111_1202_1106_1105_1104_1103</t>
   </si>
   <si>
     <t>1025206_1125206_10</t>
@@ -2181,7 +2175,7 @@
       </c>
       <c r="Q8" s="28"/>
       <c r="R8" s="28" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="S8" s="28"/>
     </row>
@@ -2199,10 +2193,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" s="29" t="b">
         <v>0</v>
@@ -2236,7 +2230,7 @@
       </c>
       <c r="Q9" s="28"/>
       <c r="R9" s="28" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="S9" s="28"/>
     </row>
@@ -2346,7 +2340,7 @@
       </c>
       <c r="Q11" s="28"/>
       <c r="R11" s="28" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="S11" s="28"/>
     </row>
@@ -2364,10 +2358,10 @@
         <v>3</v>
       </c>
       <c r="E12" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>59</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>60</v>
       </c>
       <c r="G12" s="29" t="b">
         <v>0</v>
@@ -2401,7 +2395,7 @@
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="S12" s="28"/>
     </row>
@@ -2419,10 +2413,10 @@
         <v>3</v>
       </c>
       <c r="E13" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>61</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>62</v>
       </c>
       <c r="G13" s="29" t="b">
         <v>0</v>
@@ -2474,10 +2468,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="G14" s="29" t="b">
         <v>0</v>
@@ -2511,7 +2505,7 @@
       </c>
       <c r="Q14" s="28"/>
       <c r="R14" s="28" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="S14" s="28"/>
     </row>
@@ -2529,10 +2523,10 @@
         <v>4</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G15" s="29" t="b">
         <v>0</v>
@@ -2566,7 +2560,7 @@
       </c>
       <c r="Q15" s="28"/>
       <c r="R15" s="28" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="S15" s="28"/>
     </row>
@@ -2584,10 +2578,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="G16" s="29" t="b">
         <v>0</v>
@@ -2639,10 +2633,10 @@
         <v>5</v>
       </c>
       <c r="E17" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="25" t="s">
         <v>70</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>71</v>
       </c>
       <c r="G17" s="24" t="b">
         <v>0</v>
@@ -2676,7 +2670,7 @@
       </c>
       <c r="Q17" s="28"/>
       <c r="R17" s="28" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="S17" s="28"/>
     </row>
@@ -2694,10 +2688,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="G18" s="29" t="b">
         <v>0</v>
@@ -2731,7 +2725,7 @@
       </c>
       <c r="Q18" s="28"/>
       <c r="R18" s="28" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="S18" s="28"/>
     </row>
@@ -2749,10 +2743,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="21" t="s">
         <v>74</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>75</v>
       </c>
       <c r="G19" s="29" t="b">
         <v>0</v>
@@ -2804,10 +2798,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="25" t="s">
         <v>76</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>77</v>
       </c>
       <c r="G20" s="24" t="b">
         <v>0</v>
@@ -2841,7 +2835,7 @@
       </c>
       <c r="Q20" s="28"/>
       <c r="R20" s="28" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="S20" s="28"/>
     </row>
@@ -2859,10 +2853,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="25" t="s">
         <v>78</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>79</v>
       </c>
       <c r="G21" s="24" t="b">
         <v>0</v>
@@ -2896,7 +2890,7 @@
       </c>
       <c r="Q21" s="28"/>
       <c r="R21" s="28" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="S21" s="28"/>
     </row>
@@ -2914,10 +2908,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="G22" s="29" t="b">
         <v>0</v>
@@ -2951,7 +2945,7 @@
       </c>
       <c r="Q22" s="28"/>
       <c r="R22" s="28" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="S22" s="28"/>
     </row>
@@ -2969,10 +2963,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="21" t="s">
         <v>82</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>83</v>
       </c>
       <c r="G23" s="29" t="b">
         <v>0</v>
@@ -3006,7 +3000,7 @@
       </c>
       <c r="Q23" s="28"/>
       <c r="R23" s="28" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="S23" s="28"/>
     </row>
@@ -3024,10 +3018,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="G24" s="29" t="b">
         <v>0</v>
@@ -3061,7 +3055,7 @@
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="28" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="S24" s="28"/>
     </row>
@@ -3079,10 +3073,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G25" s="29" t="b">
         <v>0</v>
@@ -3134,10 +3128,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G26" s="29" t="b">
         <v>0</v>
@@ -3171,7 +3165,7 @@
       </c>
       <c r="Q26" s="28"/>
       <c r="R26" s="28" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="S26" s="28"/>
     </row>
@@ -3189,10 +3183,10 @@
         <v>3</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G27" s="29" t="b">
         <v>0</v>
@@ -3226,7 +3220,7 @@
       </c>
       <c r="Q27" s="28"/>
       <c r="R27" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S27" s="28"/>
     </row>
@@ -3244,10 +3238,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G28" s="29" t="b">
         <v>0</v>
@@ -3281,7 +3275,7 @@
       </c>
       <c r="Q28" s="28"/>
       <c r="R28" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S28" s="28"/>
     </row>
@@ -3299,10 +3293,10 @@
         <v>4</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G29" s="29" t="b">
         <v>0</v>
@@ -3336,7 +3330,7 @@
       </c>
       <c r="Q29" s="28"/>
       <c r="R29" s="28" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="S29" s="28"/>
     </row>
@@ -3354,10 +3348,10 @@
         <v>4</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G30" s="29" t="b">
         <v>0</v>
@@ -3409,10 +3403,10 @@
         <v>4</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G31" s="29" t="b">
         <v>0</v>
@@ -3464,10 +3458,10 @@
         <v>5</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G32" s="29" t="b">
         <v>0</v>
@@ -3519,10 +3513,10 @@
         <v>5</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G33" s="29" t="b">
         <v>0</v>
@@ -3574,10 +3568,10 @@
         <v>5</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G34" s="24" t="b">
         <v>0</v>
@@ -3629,10 +3623,10 @@
         <v>9</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G35" s="29" t="b">
         <v>0</v>
@@ -3671,10 +3665,10 @@
         <v>9</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G36" s="29" t="b">
         <v>0</v>
@@ -3713,10 +3707,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G37" s="29" t="b">
         <v>0</v>
@@ -3755,10 +3749,10 @@
         <v>9</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G38" s="29" t="b">
         <v>0</v>
@@ -3797,10 +3791,10 @@
         <v>9</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G39" s="29" t="b">
         <v>0</v>
@@ -3915,7 +3909,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="S2:S3 S8:S19 S6 S35:S60 R61:S63 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 R4:S4 R1:S1 D4 D1" formula="1"/>
+    <ignoredError sqref="D1 D4 R1:S1 R4:S4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 R61:S63 S35:S60 S6 S8:S19 S2:S3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3929,7 +3923,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -4152,13 +4146,13 @@
         <v>1111</v>
       </c>
       <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" t="s">
         <v>118</v>
-      </c>
-      <c r="G27" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -4316,7 +4310,7 @@
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -4347,13 +4341,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U34" s="2">
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -4390,7 +4384,7 @@
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -4458,13 +4452,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -4495,7 +4489,7 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
@@ -4532,13 +4526,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4569,13 +4563,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -4606,13 +4600,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -4643,7 +4637,7 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
@@ -4680,13 +4674,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -4717,13 +4711,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -4754,13 +4748,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -4791,13 +4785,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4828,13 +4822,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4865,13 +4859,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4902,13 +4896,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4939,13 +4933,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4976,13 +4970,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -5013,13 +5007,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -5050,13 +5044,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -5087,13 +5081,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -5124,13 +5118,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -5161,13 +5155,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -5198,13 +5192,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -5235,13 +5229,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -5272,13 +5266,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -362,36 +362,39 @@
     <t>复古绅士</t>
   </si>
   <si>
+    <t>1102_1107_1110_1101_1105_1104_1103_1106_1202_1111_1112_1108_1109</t>
+  </si>
+  <si>
+    <t>1025103_1125103_10</t>
+  </si>
+  <si>
+    <t>酷盖少年</t>
+  </si>
+  <si>
+    <t>固定</t>
+  </si>
+  <si>
+    <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_3000|1108_3000|1109_3000|1110_3000|1111_3000|1112_3000|1202_2000</t>
+  </si>
+  <si>
+    <t>1025201_1125201_10</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>1110_1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1101</t>
+  </si>
+  <si>
+    <t>1025202_1125202_10</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
     <t>1101_1107_1110_1102_1105_1104_1103_1106_1202_1111_1112_1108_1109</t>
   </si>
   <si>
-    <t>1025103_1125103_10</t>
-  </si>
-  <si>
-    <t>酷盖少年</t>
-  </si>
-  <si>
-    <t>固定</t>
-  </si>
-  <si>
-    <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_3000|1108_3000|1109_3000|1110_3000|1111_3000|1112_3000|1202_2000</t>
-  </si>
-  <si>
-    <t>1025201_1125201_10</t>
-  </si>
-  <si>
-    <t>运动健将</t>
-  </si>
-  <si>
-    <t>1110_1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1101</t>
-  </si>
-  <si>
-    <t>1025202_1125202_10</t>
-  </si>
-  <si>
-    <t>跑酷少年</t>
-  </si>
-  <si>
     <t>1025203_1125203_10</t>
   </si>
   <si>
@@ -471,6 +474,9 @@
   </si>
   <si>
     <t>街拍达人</t>
+  </si>
+  <si>
+    <t>1103_1104_1101_1102_1105_1106_1202_1111_1112_1108_1109_1110_1107</t>
   </si>
   <si>
     <t>1025204_1125204_10</t>
@@ -833,12 +839,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2230,7 +2236,7 @@
       </c>
       <c r="Q9" s="28"/>
       <c r="R9" s="28" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S9" s="28"/>
     </row>
@@ -2248,10 +2254,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" s="29" t="b">
         <v>0</v>
@@ -2303,10 +2309,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" s="29" t="b">
         <v>0</v>
@@ -2358,10 +2364,10 @@
         <v>3</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12" s="29" t="b">
         <v>0</v>
@@ -2395,7 +2401,7 @@
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S12" s="28"/>
     </row>
@@ -2413,10 +2419,10 @@
         <v>3</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" s="29" t="b">
         <v>0</v>
@@ -2468,10 +2474,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="29" t="b">
         <v>0</v>
@@ -2523,10 +2529,10 @@
         <v>4</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" s="29" t="b">
         <v>0</v>
@@ -2560,7 +2566,7 @@
       </c>
       <c r="Q15" s="28"/>
       <c r="R15" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S15" s="28"/>
     </row>
@@ -2578,10 +2584,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="29" t="b">
         <v>0</v>
@@ -2633,10 +2639,10 @@
         <v>5</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="24" t="b">
         <v>0</v>
@@ -2688,10 +2694,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" s="29" t="b">
         <v>0</v>
@@ -2725,7 +2731,7 @@
       </c>
       <c r="Q18" s="28"/>
       <c r="R18" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S18" s="28"/>
     </row>
@@ -2743,10 +2749,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19" s="29" t="b">
         <v>0</v>
@@ -2798,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="24" t="b">
         <v>0</v>
@@ -2853,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" s="24" t="b">
         <v>0</v>
@@ -2890,7 +2896,7 @@
       </c>
       <c r="Q21" s="28"/>
       <c r="R21" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S21" s="28"/>
     </row>
@@ -2908,10 +2914,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" s="29" t="b">
         <v>0</v>
@@ -2945,7 +2951,7 @@
       </c>
       <c r="Q22" s="28"/>
       <c r="R22" s="28" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="S22" s="28"/>
     </row>
@@ -2963,10 +2969,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G23" s="29" t="b">
         <v>0</v>
@@ -3000,7 +3006,7 @@
       </c>
       <c r="Q23" s="28"/>
       <c r="R23" s="28" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S23" s="28"/>
     </row>
@@ -3018,10 +3024,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G24" s="29" t="b">
         <v>0</v>
@@ -3055,7 +3061,7 @@
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="28" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S24" s="28"/>
     </row>
@@ -3073,10 +3079,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G25" s="29" t="b">
         <v>0</v>
@@ -3128,10 +3134,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G26" s="29" t="b">
         <v>0</v>
@@ -3165,7 +3171,7 @@
       </c>
       <c r="Q26" s="28"/>
       <c r="R26" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S26" s="28"/>
     </row>
@@ -3183,10 +3189,10 @@
         <v>3</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G27" s="29" t="b">
         <v>0</v>
@@ -3238,10 +3244,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G28" s="29" t="b">
         <v>0</v>
@@ -3275,7 +3281,7 @@
       </c>
       <c r="Q28" s="28"/>
       <c r="R28" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S28" s="28"/>
     </row>
@@ -3293,10 +3299,10 @@
         <v>4</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G29" s="29" t="b">
         <v>0</v>
@@ -3330,7 +3336,7 @@
       </c>
       <c r="Q29" s="28"/>
       <c r="R29" s="28" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S29" s="28"/>
     </row>
@@ -3348,10 +3354,10 @@
         <v>4</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G30" s="29" t="b">
         <v>0</v>
@@ -3403,10 +3409,10 @@
         <v>4</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G31" s="29" t="b">
         <v>0</v>
@@ -3458,10 +3464,10 @@
         <v>5</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G32" s="29" t="b">
         <v>0</v>
@@ -3513,10 +3519,10 @@
         <v>5</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G33" s="29" t="b">
         <v>0</v>
@@ -3568,10 +3574,10 @@
         <v>5</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G34" s="24" t="b">
         <v>0</v>
@@ -3623,10 +3629,10 @@
         <v>9</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G35" s="29" t="b">
         <v>0</v>
@@ -3665,10 +3671,10 @@
         <v>9</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G36" s="29" t="b">
         <v>0</v>
@@ -3707,10 +3713,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G37" s="29" t="b">
         <v>0</v>
@@ -3749,10 +3755,10 @@
         <v>9</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G38" s="29" t="b">
         <v>0</v>
@@ -3791,10 +3797,10 @@
         <v>9</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G39" s="29" t="b">
         <v>0</v>
@@ -3909,7 +3915,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D1 D4 R1:S1 R4:S4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 R61:S63 S35:S60 S6 S8:S19 S2:S3" formula="1"/>
+    <ignoredError sqref="S2:S3 S8:S19 S6 S35:S60 R61:S63 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 R4:S4 R1:S1 D4 D1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3923,7 +3929,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -4146,13 +4152,13 @@
         <v>1111</v>
       </c>
       <c r="F27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -4310,7 +4316,7 @@
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -4347,7 +4353,7 @@
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -4378,13 +4384,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U35" s="2">
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -4415,7 +4421,7 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U36" s="3">
         <v>1025201</v>
@@ -4452,7 +4458,7 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U37" s="3">
         <v>1025202</v>
@@ -4489,13 +4495,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U38" s="3">
         <v>1025203</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -4526,13 +4532,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U39" s="3">
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4563,13 +4569,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U40" s="3">
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -4600,13 +4606,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -4637,13 +4643,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -4674,13 +4680,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -4711,13 +4717,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -4748,13 +4754,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -4785,13 +4791,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4822,13 +4828,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4859,13 +4865,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -4896,13 +4902,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -4933,13 +4939,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4970,13 +4976,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -5007,13 +5013,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -5044,13 +5050,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -5081,13 +5087,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -5118,13 +5124,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -5155,13 +5161,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U56" s="2">
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -5192,13 +5198,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U57" s="2">
         <v>1025504</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -5229,13 +5235,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="U58" s="2">
         <v>1025505</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -5266,13 +5272,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U59" s="2">
         <v>1025506</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="122">
   <si>
     <t>ID</t>
   </si>
@@ -374,187 +374,190 @@
     <t>固定</t>
   </si>
   <si>
+    <t>1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1110_1101</t>
+  </si>
+  <si>
+    <t>1025201_1125201_10</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>1110_1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1101</t>
+  </si>
+  <si>
+    <t>1025202_1125202_10</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>1101_1107_1110_1102_1105_1104_1103_1106_1202_1111_1112_1108_1109</t>
+  </si>
+  <si>
+    <t>1025203_1125203_10</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>1025301_1125301_10</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>1025302_1125302_10</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>1025303_1125303_10</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
+    <t>1025401_1125401_10</t>
+  </si>
+  <si>
+    <t>马拉松客</t>
+  </si>
+  <si>
+    <t>1025402_1125402_10</t>
+  </si>
+  <si>
+    <t>极限玩家</t>
+  </si>
+  <si>
+    <t>1025403_1125403_10</t>
+  </si>
+  <si>
+    <t>科技极客</t>
+  </si>
+  <si>
+    <t>1025501_1125501_10</t>
+  </si>
+  <si>
+    <t>创业新贵</t>
+  </si>
+  <si>
+    <t>1025502_1125502_10</t>
+  </si>
+  <si>
+    <t>摸金校尉</t>
+  </si>
+  <si>
+    <t>1025503_1125503_10</t>
+  </si>
+  <si>
+    <t>氪金大佬</t>
+  </si>
+  <si>
+    <t>1025104_1125104_10</t>
+  </si>
+  <si>
+    <t>潮流先锋</t>
+  </si>
+  <si>
+    <t>1025105_1125105_10</t>
+  </si>
+  <si>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>1025106_1125106_10</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>1103_1104_1101_1102_1105_1106_1202_1111_1112_1108_1109_1110_1107</t>
+  </si>
+  <si>
+    <t>1025204_1125204_10</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>1025205_1125205_10</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>1025206_1125206_10</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>1025304_1125304_10</t>
+  </si>
+  <si>
+    <t>文艺青年</t>
+  </si>
+  <si>
+    <t>1025305_1125305_10</t>
+  </si>
+  <si>
+    <t>书香少女</t>
+  </si>
+  <si>
+    <t>1025306_1125306_10</t>
+  </si>
+  <si>
+    <t>民谣歌手</t>
+  </si>
+  <si>
+    <t>1025404_1125404_10</t>
+  </si>
+  <si>
+    <t>独立画家</t>
+  </si>
+  <si>
+    <t>1025405_1125405_10</t>
+  </si>
+  <si>
+    <t>浪漫诗人</t>
+  </si>
+  <si>
+    <t>1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1110_1101_1107</t>
+  </si>
+  <si>
+    <t>1025406_1125406_10</t>
+  </si>
+  <si>
+    <t>古典乐迷</t>
+  </si>
+  <si>
+    <t>1025504_1125504_10</t>
+  </si>
+  <si>
+    <t>穿搭博主</t>
+  </si>
+  <si>
+    <t>1025505_1125505_10</t>
+  </si>
+  <si>
+    <t>美妆新秀</t>
+  </si>
+  <si>
+    <t>1025506_1125506_10</t>
+  </si>
+  <si>
+    <t>高定女王</t>
+  </si>
+  <si>
+    <t>1025901_0_0</t>
+  </si>
+  <si>
+    <t>独立女士</t>
+  </si>
+  <si>
     <t>1102_3000|1103_3000|1104_3000|1105_3000|1106_3000|1107_3000|1108_3000|1109_3000|1110_3000|1111_3000|1112_3000|1202_2000</t>
-  </si>
-  <si>
-    <t>1025201_1125201_10</t>
-  </si>
-  <si>
-    <t>运动健将</t>
-  </si>
-  <si>
-    <t>1110_1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1101</t>
-  </si>
-  <si>
-    <t>1025202_1125202_10</t>
-  </si>
-  <si>
-    <t>跑酷少年</t>
-  </si>
-  <si>
-    <t>1101_1107_1110_1102_1105_1104_1103_1106_1202_1111_1112_1108_1109</t>
-  </si>
-  <si>
-    <t>1025203_1125203_10</t>
-  </si>
-  <si>
-    <t>滑板高手</t>
-  </si>
-  <si>
-    <t>1025301_1125301_10</t>
-  </si>
-  <si>
-    <t>健身狂魔</t>
-  </si>
-  <si>
-    <t>1025302_1125302_10</t>
-  </si>
-  <si>
-    <t>单车骑士</t>
-  </si>
-  <si>
-    <t>1025303_1125303_10</t>
-  </si>
-  <si>
-    <t>登山行者</t>
-  </si>
-  <si>
-    <t>1025401_1125401_10</t>
-  </si>
-  <si>
-    <t>马拉松客</t>
-  </si>
-  <si>
-    <t>1025402_1125402_10</t>
-  </si>
-  <si>
-    <t>极限玩家</t>
-  </si>
-  <si>
-    <t>1107_1109_1108_1112_1111_1202_1106_1105_1104_1103_1102_1110_1101</t>
-  </si>
-  <si>
-    <t>1025403_1125403_10</t>
-  </si>
-  <si>
-    <t>科技极客</t>
-  </si>
-  <si>
-    <t>1025501_1125501_10</t>
-  </si>
-  <si>
-    <t>创业新贵</t>
-  </si>
-  <si>
-    <t>1025502_1125502_10</t>
-  </si>
-  <si>
-    <t>摸金校尉</t>
-  </si>
-  <si>
-    <t>1025503_1125503_10</t>
-  </si>
-  <si>
-    <t>氪金大佬</t>
-  </si>
-  <si>
-    <t>1025104_1125104_10</t>
-  </si>
-  <si>
-    <t>潮流先锋</t>
-  </si>
-  <si>
-    <t>1025105_1125105_10</t>
-  </si>
-  <si>
-    <t>时尚教主</t>
-  </si>
-  <si>
-    <t>1025106_1125106_10</t>
-  </si>
-  <si>
-    <t>街拍达人</t>
-  </si>
-  <si>
-    <t>1103_1104_1101_1102_1105_1106_1202_1111_1112_1108_1109_1110_1107</t>
-  </si>
-  <si>
-    <t>1025204_1125204_10</t>
-  </si>
-  <si>
-    <t>甜心辣妹</t>
-  </si>
-  <si>
-    <t>1025205_1125205_10</t>
-  </si>
-  <si>
-    <t>活力少女</t>
-  </si>
-  <si>
-    <t>1025206_1125206_10</t>
-  </si>
-  <si>
-    <t>优雅女神</t>
-  </si>
-  <si>
-    <t>1025304_1125304_10</t>
-  </si>
-  <si>
-    <t>文艺青年</t>
-  </si>
-  <si>
-    <t>1025305_1125305_10</t>
-  </si>
-  <si>
-    <t>书香少女</t>
-  </si>
-  <si>
-    <t>1025306_1125306_10</t>
-  </si>
-  <si>
-    <t>民谣歌手</t>
-  </si>
-  <si>
-    <t>1025404_1125404_10</t>
-  </si>
-  <si>
-    <t>独立画家</t>
-  </si>
-  <si>
-    <t>1025405_1125405_10</t>
-  </si>
-  <si>
-    <t>浪漫诗人</t>
-  </si>
-  <si>
-    <t>1025406_1125406_10</t>
-  </si>
-  <si>
-    <t>古典乐迷</t>
-  </si>
-  <si>
-    <t>1025504_1125504_10</t>
-  </si>
-  <si>
-    <t>穿搭博主</t>
-  </si>
-  <si>
-    <t>1025505_1125505_10</t>
-  </si>
-  <si>
-    <t>美妆新秀</t>
-  </si>
-  <si>
-    <t>1025506_1125506_10</t>
-  </si>
-  <si>
-    <t>高定女王</t>
-  </si>
-  <si>
-    <t>1025901_0_0</t>
-  </si>
-  <si>
-    <t>独立女士</t>
   </si>
   <si>
     <t>1025902_0_0</t>
@@ -839,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1327,7 +1330,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1434,6 +1437,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2002,15 +2008,15 @@
         <v>50</v>
       </c>
       <c r="N5" s="19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="O5" s="19">
         <f>IF(M5=0,N5,($T$1*M5/100+1)*N5)</f>
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="P5" s="27">
         <f>O5/SUM($O$5:$O$34)</f>
-        <v>0.0617283950617284</v>
+        <v>0.075</v>
       </c>
       <c r="Q5" s="28"/>
       <c r="R5" s="28" t="s">
@@ -2059,15 +2065,15 @@
         <v>50</v>
       </c>
       <c r="N6" s="19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:O34" si="0">IF(M6=0,N6,($T$1*M6/100+1)*N6)</f>
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="P6" s="27">
         <f t="shared" ref="P6:P34" si="1">O6/SUM($O$5:$O$34)</f>
-        <v>0.0617283950617284</v>
+        <v>0.075</v>
       </c>
       <c r="Q6" s="28"/>
       <c r="R6" s="28" t="s">
@@ -2114,20 +2120,20 @@
         <v>50</v>
       </c>
       <c r="N7" s="19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="P7" s="27">
         <f t="shared" si="1"/>
-        <v>0.0617283950617284</v>
-      </c>
-      <c r="Q7" s="28" t="s">
+        <v>0.075</v>
+      </c>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="28"/>
       <c r="S7" s="28"/>
     </row>
     <row r="8" ht="16.5" spans="1:24">
@@ -2169,15 +2175,15 @@
         <v>50</v>
       </c>
       <c r="N8" s="19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="P8" s="27">
         <f t="shared" si="1"/>
-        <v>0.0432098765432099</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="Q8" s="28"/>
       <c r="R8" s="28" t="s">
@@ -2224,15 +2230,15 @@
         <v>50</v>
       </c>
       <c r="N9" s="19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="P9" s="27">
         <f t="shared" si="1"/>
-        <v>0.0432098765432099</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="Q9" s="28"/>
       <c r="R9" s="28" t="s">
@@ -2279,20 +2285,20 @@
         <v>50</v>
       </c>
       <c r="N10" s="19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="P10" s="27">
         <f t="shared" si="1"/>
-        <v>0.0432098765432099</v>
-      </c>
-      <c r="Q10" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" s="28"/>
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="S10" s="28"/>
     </row>
     <row r="11" ht="16.5" spans="1:24">
@@ -2334,15 +2340,15 @@
         <v>50</v>
       </c>
       <c r="N11" s="19">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="P11" s="27">
         <f t="shared" si="1"/>
-        <v>0.0308641975308642</v>
+        <v>0.025</v>
       </c>
       <c r="Q11" s="28"/>
       <c r="R11" s="28" t="s">
@@ -2389,15 +2395,15 @@
         <v>50</v>
       </c>
       <c r="N12" s="19">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O12" s="19">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="P12" s="27">
         <f t="shared" si="1"/>
-        <v>0.0308641975308642</v>
+        <v>0.025</v>
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28" t="s">
@@ -2444,20 +2450,20 @@
         <v>50</v>
       </c>
       <c r="N13" s="19">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O13" s="19">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="P13" s="27">
         <f t="shared" si="1"/>
-        <v>0.0308641975308642</v>
-      </c>
-      <c r="Q13" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R13" s="28"/>
+        <v>0.025</v>
+      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="S13" s="28"/>
     </row>
     <row r="14" ht="16.5" spans="1:24">
@@ -2499,15 +2505,15 @@
         <v>50</v>
       </c>
       <c r="N14" s="19">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="O14" s="19">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="P14" s="27">
         <f t="shared" si="1"/>
-        <v>0.0185185185185185</v>
+        <v>0.0166666666666667</v>
       </c>
       <c r="Q14" s="28"/>
       <c r="R14" s="28" t="s">
@@ -2554,19 +2560,19 @@
         <v>50</v>
       </c>
       <c r="N15" s="19">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="O15" s="19">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="P15" s="27">
         <f t="shared" si="1"/>
-        <v>0.0185185185185185</v>
+        <v>0.0166666666666667</v>
       </c>
       <c r="Q15" s="28"/>
       <c r="R15" s="28" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="S15" s="28"/>
     </row>
@@ -2584,10 +2590,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="G16" s="29" t="b">
         <v>0</v>
@@ -2609,20 +2615,20 @@
         <v>50</v>
       </c>
       <c r="N16" s="19">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="O16" s="19">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="P16" s="27">
         <f t="shared" si="1"/>
-        <v>0.0185185185185185</v>
-      </c>
-      <c r="Q16" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R16" s="28"/>
+        <v>0.0166666666666667</v>
+      </c>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="S16" s="28"/>
     </row>
     <row r="17" ht="16.5" spans="1:19">
@@ -2639,10 +2645,10 @@
         <v>5</v>
       </c>
       <c r="E17" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="25" t="s">
         <v>70</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>71</v>
       </c>
       <c r="G17" s="24" t="b">
         <v>0</v>
@@ -2672,7 +2678,7 @@
       </c>
       <c r="P17" s="27">
         <f t="shared" si="1"/>
-        <v>0.0123456790123457</v>
+        <v>0.00833333333333333</v>
       </c>
       <c r="Q17" s="28"/>
       <c r="R17" s="28" t="s">
@@ -2694,10 +2700,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="G18" s="29" t="b">
         <v>0</v>
@@ -2727,11 +2733,11 @@
       </c>
       <c r="P18" s="27">
         <f t="shared" si="1"/>
-        <v>0.0123456790123457</v>
+        <v>0.00833333333333333</v>
       </c>
       <c r="Q18" s="28"/>
       <c r="R18" s="28" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="S18" s="28"/>
     </row>
@@ -2749,10 +2755,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="21" t="s">
         <v>74</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>75</v>
       </c>
       <c r="G19" s="29" t="b">
         <v>0</v>
@@ -2782,12 +2788,12 @@
       </c>
       <c r="P19" s="27">
         <f t="shared" si="1"/>
-        <v>0.0123456790123457</v>
-      </c>
-      <c r="Q19" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R19" s="28"/>
+        <v>0.00833333333333333</v>
+      </c>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="S19" s="28"/>
     </row>
     <row r="20" ht="16.5" spans="1:19">
@@ -2804,10 +2810,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="25" t="s">
         <v>76</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>77</v>
       </c>
       <c r="G20" s="24" t="b">
         <v>0</v>
@@ -2829,15 +2835,15 @@
         <v>50</v>
       </c>
       <c r="N20" s="19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="O20" s="19">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="P20" s="27">
         <f t="shared" si="1"/>
-        <v>0.0617283950617284</v>
+        <v>0.075</v>
       </c>
       <c r="Q20" s="28"/>
       <c r="R20" s="28" t="s">
@@ -2859,10 +2865,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="25" t="s">
         <v>78</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>79</v>
       </c>
       <c r="G21" s="24" t="b">
         <v>0</v>
@@ -2884,19 +2890,19 @@
         <v>50</v>
       </c>
       <c r="N21" s="19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="O21" s="19">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="P21" s="27">
         <f t="shared" si="1"/>
-        <v>0.0617283950617284</v>
+        <v>0.075</v>
       </c>
       <c r="Q21" s="28"/>
       <c r="R21" s="28" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="S21" s="28"/>
     </row>
@@ -2914,10 +2920,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="G22" s="29" t="b">
         <v>0</v>
@@ -2939,19 +2945,19 @@
         <v>50</v>
       </c>
       <c r="N22" s="19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="O22" s="19">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="P22" s="27">
         <f t="shared" si="1"/>
-        <v>0.0617283950617284</v>
+        <v>0.075</v>
       </c>
       <c r="Q22" s="28"/>
       <c r="R22" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S22" s="28"/>
     </row>
@@ -2969,10 +2975,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="G23" s="29" t="b">
         <v>0</v>
@@ -2994,15 +3000,15 @@
         <v>50</v>
       </c>
       <c r="N23" s="19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="O23" s="19">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="P23" s="27">
         <f t="shared" si="1"/>
-        <v>0.0432098765432099</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="Q23" s="28"/>
       <c r="R23" s="28" t="s">
@@ -3024,10 +3030,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="G24" s="29" t="b">
         <v>0</v>
@@ -3049,15 +3055,15 @@
         <v>50</v>
       </c>
       <c r="N24" s="19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="O24" s="19">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="P24" s="27">
         <f t="shared" si="1"/>
-        <v>0.0432098765432099</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="28" t="s">
@@ -3079,10 +3085,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="21" t="s">
         <v>87</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>88</v>
       </c>
       <c r="G25" s="29" t="b">
         <v>0</v>
@@ -3104,15 +3110,15 @@
         <v>50</v>
       </c>
       <c r="N25" s="19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="O25" s="19">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="P25" s="27">
         <f t="shared" si="1"/>
-        <v>0.0432098765432099</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="Q25" s="28"/>
       <c r="R25" s="28" t="s">
@@ -3134,10 +3140,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>90</v>
       </c>
       <c r="G26" s="29" t="b">
         <v>0</v>
@@ -3159,19 +3165,19 @@
         <v>50</v>
       </c>
       <c r="N26" s="19">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O26" s="19">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="P26" s="27">
         <f t="shared" si="1"/>
-        <v>0.0308641975308642</v>
+        <v>0.025</v>
       </c>
       <c r="Q26" s="28"/>
       <c r="R26" s="28" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="S26" s="28"/>
     </row>
@@ -3189,10 +3195,10 @@
         <v>3</v>
       </c>
       <c r="E27" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="21" t="s">
         <v>91</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>92</v>
       </c>
       <c r="G27" s="29" t="b">
         <v>0</v>
@@ -3214,15 +3220,15 @@
         <v>50</v>
       </c>
       <c r="N27" s="19">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O27" s="19">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="P27" s="27">
         <f t="shared" si="1"/>
-        <v>0.0308641975308642</v>
+        <v>0.025</v>
       </c>
       <c r="Q27" s="28"/>
       <c r="R27" s="28" t="s">
@@ -3244,10 +3250,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="21" t="s">
         <v>93</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>94</v>
       </c>
       <c r="G28" s="29" t="b">
         <v>0</v>
@@ -3269,19 +3275,19 @@
         <v>50</v>
       </c>
       <c r="N28" s="19">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="O28" s="19">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="P28" s="27">
         <f t="shared" si="1"/>
-        <v>0.0308641975308642</v>
+        <v>0.025</v>
       </c>
       <c r="Q28" s="28"/>
       <c r="R28" s="28" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="S28" s="28"/>
     </row>
@@ -3299,10 +3305,10 @@
         <v>4</v>
       </c>
       <c r="E29" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="21" t="s">
         <v>95</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>96</v>
       </c>
       <c r="G29" s="29" t="b">
         <v>0</v>
@@ -3324,15 +3330,15 @@
         <v>50</v>
       </c>
       <c r="N29" s="19">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="O29" s="19">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="P29" s="27">
         <f t="shared" si="1"/>
-        <v>0.0185185185185185</v>
+        <v>0.0166666666666667</v>
       </c>
       <c r="Q29" s="28"/>
       <c r="R29" s="28" t="s">
@@ -3354,10 +3360,10 @@
         <v>4</v>
       </c>
       <c r="E30" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="21" t="s">
         <v>97</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="G30" s="29" t="b">
         <v>0</v>
@@ -3379,20 +3385,20 @@
         <v>50</v>
       </c>
       <c r="N30" s="19">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="O30" s="19">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="P30" s="27">
         <f t="shared" si="1"/>
-        <v>0.0185185185185185</v>
-      </c>
-      <c r="Q30" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R30" s="28"/>
+        <v>0.0166666666666667</v>
+      </c>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28" t="s">
+        <v>98</v>
+      </c>
       <c r="S30" s="28"/>
     </row>
     <row r="31" ht="16.5" spans="1:19">
@@ -3434,20 +3440,20 @@
         <v>50</v>
       </c>
       <c r="N31" s="19">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="O31" s="19">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="P31" s="27">
         <f t="shared" si="1"/>
-        <v>0.0185185185185185</v>
-      </c>
-      <c r="Q31" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R31" s="28"/>
+        <v>0.0166666666666667</v>
+      </c>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28" t="s">
+        <v>98</v>
+      </c>
       <c r="S31" s="28"/>
     </row>
     <row r="32" ht="16.5" spans="1:19">
@@ -3497,12 +3503,12 @@
       </c>
       <c r="P32" s="27">
         <f t="shared" si="1"/>
-        <v>0.0123456790123457</v>
-      </c>
-      <c r="Q32" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R32" s="28"/>
+        <v>0.00833333333333333</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28" t="s">
+        <v>51</v>
+      </c>
       <c r="S32" s="28"/>
     </row>
     <row r="33" ht="16.5" spans="1:19">
@@ -3552,12 +3558,12 @@
       </c>
       <c r="P33" s="27">
         <f t="shared" si="1"/>
-        <v>0.0123456790123457</v>
-      </c>
-      <c r="Q33" s="28" t="s">
+        <v>0.00833333333333333</v>
+      </c>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="R33" s="28"/>
       <c r="S33" s="28"/>
     </row>
     <row r="34" ht="16.5" spans="1:19">
@@ -3607,12 +3613,12 @@
       </c>
       <c r="P34" s="27">
         <f t="shared" si="1"/>
-        <v>0.0123456790123457</v>
-      </c>
-      <c r="Q34" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R34" s="28"/>
+        <v>0.00833333333333333</v>
+      </c>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28" t="s">
+        <v>98</v>
+      </c>
       <c r="S34" s="28"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:19">
@@ -3653,7 +3659,7 @@
       <c r="O35" s="34"/>
       <c r="P35" s="28"/>
       <c r="Q35" s="28" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="R35" s="28"/>
     </row>
@@ -3671,10 +3677,10 @@
         <v>9</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G36" s="29" t="b">
         <v>0</v>
@@ -3695,7 +3701,7 @@
       <c r="O36" s="34"/>
       <c r="P36" s="28"/>
       <c r="Q36" s="28" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="R36" s="28"/>
     </row>
@@ -3713,10 +3719,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G37" s="29" t="b">
         <v>0</v>
@@ -3737,7 +3743,7 @@
       <c r="O37" s="34"/>
       <c r="P37" s="28"/>
       <c r="Q37" s="28" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="R37" s="28"/>
     </row>
@@ -3755,10 +3761,10 @@
         <v>9</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G38" s="29" t="b">
         <v>0</v>
@@ -3779,7 +3785,7 @@
       <c r="O38" s="34"/>
       <c r="P38" s="28"/>
       <c r="Q38" s="28" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="R38" s="28"/>
     </row>
@@ -3797,10 +3803,10 @@
         <v>9</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G39" s="29" t="b">
         <v>0</v>
@@ -3821,29 +3827,34 @@
       <c r="O39" s="34"/>
       <c r="P39" s="28"/>
       <c r="Q39" s="28" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="R39" s="28"/>
     </row>
     <row r="40" spans="1:19">
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
+      <c r="P40" s="36"/>
     </row>
     <row r="41" spans="1:19">
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
+      <c r="P41" s="36"/>
     </row>
     <row r="42" spans="1:19">
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
+      <c r="P42" s="36"/>
     </row>
     <row r="43" spans="1:19">
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
+      <c r="P43" s="36"/>
     </row>
     <row r="44" spans="1:19">
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
+      <c r="P44" s="36"/>
     </row>
     <row r="45" spans="1:19">
       <c r="K45" s="35"/>
@@ -3878,7 +3889,7 @@
       <c r="L52" s="35"/>
     </row>
     <row r="53" ht="14.25" spans="5:12">
-      <c r="E53" s="36"/>
+      <c r="E53" s="37"/>
       <c r="K53" s="35"/>
       <c r="L53" s="35"/>
     </row>
@@ -3915,7 +3926,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="S2:S3 S8:S19 S6 S35:S60 R61:S63 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 R4:S4 R1:S1 D4 D1" formula="1"/>
+    <ignoredError sqref="D1 D4 R1:S1 R4:S4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 S35:S63 S6 S8:S19 S2:S3" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -3929,7 +3940,7 @@
   <sheetData>
     <row r="5" spans="6:10">
       <c r="F5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="6:10">
@@ -4152,13 +4163,13 @@
         <v>1111</v>
       </c>
       <c r="F27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -4316,7 +4327,7 @@
         <v>1025104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -4353,7 +4364,7 @@
         <v>1025105</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -4390,7 +4401,7 @@
         <v>1025106</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -4538,7 +4549,7 @@
         <v>1025204</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4575,7 +4586,7 @@
         <v>1025205</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -4606,13 +4617,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U41" s="3">
         <v>1025206</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -4643,7 +4654,7 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U42" s="2">
         <v>1025301</v>
@@ -4680,7 +4691,7 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U43" s="2">
         <v>1025302</v>
@@ -4717,7 +4728,7 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U44" s="2">
         <v>1025303</v>
@@ -4754,13 +4765,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U45" s="2">
         <v>1025304</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -4791,13 +4802,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U46" s="2">
         <v>1025305</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -4828,13 +4839,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U47" s="2">
         <v>1025306</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -4865,7 +4876,7 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U48" s="3">
         <v>1025401</v>
@@ -4902,7 +4913,7 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U49" s="3">
         <v>1025402</v>
@@ -4939,13 +4950,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="U50" s="3">
         <v>1025403</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -4976,13 +4987,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U51" s="3">
         <v>1025404</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -5013,13 +5024,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U52" s="3">
         <v>1025405</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -5050,7 +5061,7 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U53" s="3">
         <v>1025406</v>
@@ -5087,13 +5098,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U54" s="2">
         <v>1025501</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -5124,13 +5135,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U55" s="2">
         <v>1025502</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -5167,7 +5178,7 @@
         <v>1025503</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -2162,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="21">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="19">
@@ -2272,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="21">
-        <v>1002</v>
+        <v>5001</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="19">
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="21">
-        <v>1001</v>
+        <v>5001</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="19">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="21">
-        <v>1002</v>
+        <v>5001</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="19">
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="21">
-        <v>1001</v>
+        <v>5006</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="19">
@@ -3042,7 +3042,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="21">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="19">
@@ -3097,7 +3097,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="21">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="19">
@@ -3152,7 +3152,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="21">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="19">
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="21">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="19">
@@ -3262,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="21">
-        <v>1002</v>
+        <v>5006</v>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="19">
@@ -3317,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="21">
-        <v>1001</v>
+        <v>5006</v>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="19">
@@ -3372,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="21">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="19">
@@ -3427,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="21">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="J31" s="21"/>
       <c r="K31" s="19">
@@ -3482,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="21">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="19">
@@ -3537,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="21">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="J33" s="21"/>
       <c r="K33" s="19">
@@ -3926,7 +3926,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D1 D4 R1:S1 R4:S4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 S35:S63 S6 S8:S19 S2:S3" formula="1"/>
+    <ignoredError sqref="S2:S3 S8:S19 S6 S35:S63 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 R4:S4 R1:S1 D4 D1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -171,8 +171,7 @@
           <t xml:space="preserve">
 知名度影响各种品质游客（已解锁）出现在赌场的权重
 知名度参数设置为为0时，与基础刷新权重一样；
-公式：（个人知名度*设置的知名度/参数100+1）*基础刷新权重
-</t>
+根据当前知名度处理的实际权重值  =  当前知名度 / 知名度预期上限（全局表配置 10000） × 知名度要求值（awareness） + 基础刷新权重（BaseWeight）</t>
         </r>
       </text>
     </comment>
@@ -288,7 +287,7 @@
     <t>行为模式</t>
   </si>
   <si>
-    <t>服务要求值</t>
+    <t>知名度要求值</t>
   </si>
   <si>
     <t>基础刷新权重</t>
@@ -4019,7 +4018,6 @@
       <c r="K35" s="39"/>
       <c r="L35" s="39"/>
       <c r="P35" s="40"/>
-      <c r="Q35"/>
       <c r="R35" s="41"/>
       <c r="S35" s="41"/>
     </row>
@@ -4027,7 +4025,6 @@
       <c r="K36" s="39"/>
       <c r="L36" s="39"/>
       <c r="P36" s="40"/>
-      <c r="Q36"/>
       <c r="R36" s="41"/>
       <c r="S36" s="41"/>
     </row>
@@ -4035,7 +4032,6 @@
       <c r="K37" s="39"/>
       <c r="L37" s="39"/>
       <c r="P37" s="40"/>
-      <c r="Q37"/>
       <c r="R37" s="41"/>
       <c r="S37" s="41"/>
     </row>
@@ -4043,7 +4039,6 @@
       <c r="K38" s="39"/>
       <c r="L38" s="39"/>
       <c r="P38" s="40"/>
-      <c r="Q38"/>
       <c r="R38" s="41"/>
       <c r="S38" s="41"/>
     </row>
@@ -4051,7 +4046,6 @@
       <c r="K39" s="39"/>
       <c r="L39" s="39"/>
       <c r="P39" s="40"/>
-      <c r="Q39"/>
       <c r="R39" s="41"/>
       <c r="S39" s="41"/>
     </row>
@@ -4125,7 +4119,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D1 D4 U1:V1 U4:V4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 V35:V58 V6 V8:V19 V2:V3" formula="1"/>
+    <ignoredError sqref="V2:V3 V8:V19 V6 V35:V58 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 U4:V4 U1:V1 D4 D1" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -244,12 +244,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+概率为百分比</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="122">
   <si>
     <t>ID</t>
   </si>
@@ -311,6 +333,9 @@
     <t>指定区域</t>
   </si>
   <si>
+    <t>特殊交互建筑与概率</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -368,6 +393,9 @@
     <t>TargetArea</t>
   </si>
   <si>
+    <t>SpecialInteraction</t>
+  </si>
+  <si>
     <t>1025101_1125101_10</t>
   </si>
   <si>
@@ -380,7 +408,7 @@
     <t>1101_1102_1103_1104_1105_1106_1202_1111_1112_1108_1109_1110_1107</t>
   </si>
   <si>
-    <t>有奖励去建筑交互权重字段，无奖励去指定区域字段</t>
+    <t>1301_30</t>
   </si>
   <si>
     <t>1025102_1125102_10</t>
@@ -1352,7 +1380,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1403,6 +1431,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1798,7 +1829,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA55"/>
+  <dimension ref="A1:AB55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
@@ -1819,15 +1850,16 @@
     <col min="18" max="19" width="6.375" customWidth="1"/>
     <col min="20" max="20" width="37.7833333333333" customWidth="1"/>
     <col min="21" max="21" width="66.0333333333333" customWidth="1"/>
-    <col min="22" max="22" width="9.40833333333333" customWidth="1"/>
-    <col min="23" max="23" width="12.875"/>
-    <col min="24" max="24" width="13.125" customWidth="1"/>
-    <col min="25" max="25" width="17.25" customWidth="1"/>
-    <col min="26" max="26" width="17.625" customWidth="1"/>
-    <col min="27" max="27" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="17.675" customWidth="1"/>
+    <col min="23" max="23" width="16.775" customWidth="1"/>
+    <col min="24" max="24" width="12.875"/>
+    <col min="25" max="25" width="13.125" customWidth="1"/>
+    <col min="26" max="26" width="17.25" customWidth="1"/>
+    <col min="27" max="27" width="17.625" customWidth="1"/>
+    <col min="28" max="28" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="15.75" spans="1:27">
+    <row r="1" s="3" customFormat="1" ht="15.75" spans="1:28">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1892,182 +1924,192 @@
       <c r="V1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="W1"/>
+      <c r="W1" s="18" t="s">
+        <v>21</v>
+      </c>
       <c r="X1"/>
       <c r="Y1"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-    </row>
-    <row r="2" s="4" customFormat="1" ht="21" customHeight="1" spans="1:27">
-      <c r="A2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>21</v>
+      <c r="Z1"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+    </row>
+    <row r="2" s="4" customFormat="1" ht="21" customHeight="1" spans="1:28">
+      <c r="A2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21" t="s">
+      <c r="I2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" s="23"/>
-      <c r="W2"/>
+      <c r="V2" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="W2" s="24"/>
       <c r="X2"/>
       <c r="Y2"/>
-    </row>
-    <row r="3" s="4" customFormat="1" ht="15.75" spans="1:27">
-      <c r="A3" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="Z2"/>
+    </row>
+    <row r="3" s="4" customFormat="1" ht="15.75" spans="1:28">
+      <c r="A3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="E3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="21"/>
       <c r="G3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="I3" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="J3" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21" t="s">
+      <c r="K3" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="L3" s="22"/>
+      <c r="M3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="21" t="s">
+      <c r="N3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="21" t="s">
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="23"/>
-      <c r="W3"/>
+      <c r="U3" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" s="24"/>
       <c r="X3"/>
       <c r="Y3"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:27">
+      <c r="Z3"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:28">
       <c r="A4" s="2"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="28"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:27">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:28">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="29" t="b">
+      <c r="C5" s="30" t="b">
         <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="31">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30">
+      <c r="E5" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="32">
+        <v>1</v>
+      </c>
+      <c r="I5" s="31">
         <v>1001</v>
       </c>
-      <c r="J5" s="26"/>
+      <c r="J5" s="27"/>
       <c r="K5" s="2">
         <v>600</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="32">
+        <v>43</v>
+      </c>
+      <c r="M5" s="33">
         <f>D5^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -2075,11 +2117,11 @@
         <f>_xlfn.XLOOKUP($D5,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O5" s="33">
+      <c r="O5" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M5+Q5</f>
         <v>8400</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="35">
         <f>O5/SUM($O$5:$O$34)</f>
         <v>0.0689621200926063</v>
       </c>
@@ -2087,55 +2129,56 @@
         <f>N5</f>
         <v>8300</v>
       </c>
-      <c r="R5" s="35">
+      <c r="R5" s="36">
         <f>Q5/SUM($Q$5:$Q$34)</f>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S5" s="35"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:27">
+      <c r="S5" s="36"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="V5" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" s="37"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:28">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="29" t="b">
+      <c r="C6" s="30" t="b">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="31">
-        <v>1</v>
-      </c>
-      <c r="I6" s="30">
+      <c r="E6" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="32">
+        <v>1</v>
+      </c>
+      <c r="I6" s="31">
         <v>1002</v>
       </c>
-      <c r="J6" s="26"/>
+      <c r="J6" s="27"/>
       <c r="K6" s="2">
         <v>600</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="32">
+        <v>43</v>
+      </c>
+      <c r="M6" s="33">
         <f>D6^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -2143,11 +2186,11 @@
         <f>_xlfn.XLOOKUP($D6,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O6" s="33">
+      <c r="O6" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M6+Q6</f>
         <v>8400</v>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="35">
         <f t="shared" ref="P6:P39" si="0">O6/SUM($O$5:$O$34)</f>
         <v>0.0689621200926063</v>
       </c>
@@ -2155,53 +2198,56 @@
         <f t="shared" ref="Q6:Q34" si="1">N6</f>
         <v>8300</v>
       </c>
-      <c r="R6" s="35">
+      <c r="R6" s="36">
         <f t="shared" ref="R6:R39" si="2">Q6/SUM($Q$5:$Q$34)</f>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S6" s="35"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="V6" s="36"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:27">
+      <c r="S6" s="36"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="V6" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W6" s="37"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:28">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="29" t="b">
+      <c r="C7" s="30" t="b">
         <v>1</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="29" t="b">
+      <c r="E7" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="30" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="31">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30">
+      <c r="H7" s="32">
+        <v>1</v>
+      </c>
+      <c r="I7" s="31">
         <v>1003</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="27"/>
       <c r="K7" s="2">
         <v>600</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="32">
+        <v>51</v>
+      </c>
+      <c r="M7" s="33">
         <f>D7^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -2209,11 +2255,11 @@
         <f>_xlfn.XLOOKUP($D7,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O7" s="33">
+      <c r="O7" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M7+Q7</f>
         <v>8400</v>
       </c>
-      <c r="P7" s="34">
+      <c r="P7" s="35">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -2221,53 +2267,56 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R7" s="35">
+      <c r="R7" s="36">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S7" s="35"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="V7" s="36"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:27">
+      <c r="S7" s="36"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="V7" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" s="37"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:28">
       <c r="A8" s="2">
         <v>2001</v>
       </c>
-      <c r="B8" s="26">
-        <v>1</v>
-      </c>
-      <c r="C8" s="26" t="b">
+      <c r="B8" s="27">
+        <v>1</v>
+      </c>
+      <c r="C8" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="37" t="b">
+      <c r="E8" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="38">
-        <v>1</v>
-      </c>
-      <c r="I8" s="26">
+      <c r="H8" s="39">
+        <v>1</v>
+      </c>
+      <c r="I8" s="27">
         <v>1003</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="27"/>
       <c r="K8" s="2">
         <v>600</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="32">
+        <v>43</v>
+      </c>
+      <c r="M8" s="33">
         <f>D8^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -2275,11 +2324,11 @@
         <f>_xlfn.XLOOKUP($D8,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M8+Q8</f>
         <v>4550</v>
       </c>
-      <c r="P8" s="34">
+      <c r="P8" s="35">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -2287,53 +2336,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R8" s="35">
+      <c r="R8" s="36">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S8" s="35"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="V8" s="36"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:27">
+      <c r="S8" s="36"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="V8" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W8" s="37"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:28">
       <c r="A9" s="2">
         <v>2002</v>
       </c>
-      <c r="B9" s="26">
-        <v>1</v>
-      </c>
-      <c r="C9" s="26" t="b">
+      <c r="B9" s="27">
+        <v>1</v>
+      </c>
+      <c r="C9" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="37" t="b">
+      <c r="E9" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="38">
-        <v>1</v>
-      </c>
-      <c r="I9" s="26">
+      <c r="H9" s="39">
+        <v>1</v>
+      </c>
+      <c r="I9" s="27">
         <v>1001</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="27"/>
       <c r="K9" s="2">
         <v>600</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" s="32">
+        <v>43</v>
+      </c>
+      <c r="M9" s="33">
         <f>D9^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -2341,11 +2393,11 @@
         <f>_xlfn.XLOOKUP($D9,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M9+Q9</f>
         <v>4550</v>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="35">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -2353,53 +2405,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R9" s="35">
+      <c r="R9" s="36">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S9" s="35"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="V9" s="36"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:27">
+      <c r="S9" s="36"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="V9" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W9" s="37"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:28">
       <c r="A10" s="2">
         <v>2003</v>
       </c>
-      <c r="B10" s="26">
-        <v>1</v>
-      </c>
-      <c r="C10" s="26" t="b">
+      <c r="B10" s="27">
+        <v>1</v>
+      </c>
+      <c r="C10" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="37" t="b">
+      <c r="E10" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="38">
-        <v>1</v>
-      </c>
-      <c r="I10" s="26">
+      <c r="H10" s="39">
+        <v>1</v>
+      </c>
+      <c r="I10" s="27">
         <v>5001</v>
       </c>
-      <c r="J10" s="26"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="2">
         <v>600</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="32">
+        <v>51</v>
+      </c>
+      <c r="M10" s="33">
         <f>D10^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -2407,11 +2462,11 @@
         <f>_xlfn.XLOOKUP($D10,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M10+Q10</f>
         <v>4550</v>
       </c>
-      <c r="P10" s="34">
+      <c r="P10" s="35">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -2419,53 +2474,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R10" s="35">
+      <c r="R10" s="36">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S10" s="35"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="V10" s="36"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:27">
+      <c r="S10" s="36"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="V10" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W10" s="37"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:28">
       <c r="A11" s="2">
         <v>3001</v>
       </c>
-      <c r="B11" s="26">
-        <v>1</v>
-      </c>
-      <c r="C11" s="26" t="b">
+      <c r="B11" s="27">
+        <v>1</v>
+      </c>
+      <c r="C11" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
       </c>
-      <c r="E11" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="37" t="b">
+      <c r="E11" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="38">
-        <v>1</v>
-      </c>
-      <c r="I11" s="26">
+      <c r="H11" s="39">
+        <v>1</v>
+      </c>
+      <c r="I11" s="27">
         <v>1001</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="27"/>
       <c r="K11" s="2">
         <v>600</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="32">
+        <v>43</v>
+      </c>
+      <c r="M11" s="33">
         <f>D11^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -2473,11 +2531,11 @@
         <f>_xlfn.XLOOKUP($D11,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O11" s="33">
+      <c r="O11" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M11+Q11</f>
         <v>2560</v>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="35">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -2485,53 +2543,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R11" s="35">
+      <c r="R11" s="36">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S11" s="35"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="V11" s="36"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:27">
+      <c r="S11" s="36"/>
+      <c r="T11" s="37"/>
+      <c r="U11" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="V11" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W11" s="37"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:28">
       <c r="A12" s="2">
         <v>3002</v>
       </c>
-      <c r="B12" s="26">
-        <v>1</v>
-      </c>
-      <c r="C12" s="26" t="b">
+      <c r="B12" s="27">
+        <v>1</v>
+      </c>
+      <c r="C12" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
       </c>
-      <c r="E12" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="37" t="b">
+      <c r="E12" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="38">
-        <v>1</v>
-      </c>
-      <c r="I12" s="26">
+      <c r="H12" s="39">
+        <v>1</v>
+      </c>
+      <c r="I12" s="27">
         <v>1002</v>
       </c>
-      <c r="J12" s="26"/>
+      <c r="J12" s="27"/>
       <c r="K12" s="2">
         <v>600</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" s="32">
+        <v>43</v>
+      </c>
+      <c r="M12" s="33">
         <f>D12^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -2539,11 +2600,11 @@
         <f>_xlfn.XLOOKUP($D12,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O12" s="33">
+      <c r="O12" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M12+Q12</f>
         <v>2560</v>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="35">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -2551,53 +2612,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R12" s="35">
+      <c r="R12" s="36">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S12" s="35"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="V12" s="36"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:27">
+      <c r="S12" s="36"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="V12" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W12" s="37"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:28">
       <c r="A13" s="2">
         <v>3003</v>
       </c>
-      <c r="B13" s="26">
-        <v>1</v>
-      </c>
-      <c r="C13" s="26" t="b">
+      <c r="B13" s="27">
+        <v>1</v>
+      </c>
+      <c r="C13" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="37" t="b">
+      <c r="E13" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="38">
-        <v>1</v>
-      </c>
-      <c r="I13" s="26">
+      <c r="H13" s="39">
+        <v>1</v>
+      </c>
+      <c r="I13" s="27">
         <v>5001</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="27"/>
       <c r="K13" s="2">
         <v>600</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M13" s="32">
+        <v>51</v>
+      </c>
+      <c r="M13" s="33">
         <f>D13^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -2605,11 +2669,11 @@
         <f>_xlfn.XLOOKUP($D13,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M13+Q13</f>
         <v>2560</v>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="35">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -2617,53 +2681,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R13" s="35">
+      <c r="R13" s="36">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S13" s="35"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="V13" s="36"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:27">
+      <c r="S13" s="36"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="V13" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W13" s="37"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:28">
       <c r="A14" s="2">
         <v>4001</v>
       </c>
-      <c r="B14" s="26">
-        <v>1</v>
-      </c>
-      <c r="C14" s="26" t="b">
+      <c r="B14" s="27">
+        <v>1</v>
+      </c>
+      <c r="C14" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D14" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="37" t="b">
+      <c r="E14" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="38">
-        <v>1</v>
-      </c>
-      <c r="I14" s="26">
+      <c r="H14" s="39">
+        <v>1</v>
+      </c>
+      <c r="I14" s="27">
         <v>5001</v>
       </c>
-      <c r="J14" s="26"/>
+      <c r="J14" s="27"/>
       <c r="K14" s="2">
         <v>600</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M14" s="32">
+        <v>43</v>
+      </c>
+      <c r="M14" s="33">
         <f>D14^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -2671,11 +2738,11 @@
         <f>_xlfn.XLOOKUP($D14,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M14+Q14</f>
         <v>2153</v>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="35">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -2683,53 +2750,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R14" s="35">
+      <c r="R14" s="36">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S14" s="35"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="V14" s="36"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:27">
+      <c r="S14" s="36"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="V14" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W14" s="37"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:28">
       <c r="A15" s="2">
         <v>4002</v>
       </c>
-      <c r="B15" s="26">
-        <v>1</v>
-      </c>
-      <c r="C15" s="26" t="b">
+      <c r="B15" s="27">
+        <v>1</v>
+      </c>
+      <c r="C15" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="37" t="b">
+      <c r="E15" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H15" s="38">
-        <v>1</v>
-      </c>
-      <c r="I15" s="26">
+      <c r="H15" s="39">
+        <v>1</v>
+      </c>
+      <c r="I15" s="27">
         <v>1001</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="27"/>
       <c r="K15" s="2">
         <v>600</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M15" s="32">
+        <v>43</v>
+      </c>
+      <c r="M15" s="33">
         <f>D15^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -2737,11 +2807,11 @@
         <f>_xlfn.XLOOKUP($D15,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O15" s="33">
+      <c r="O15" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M15+Q15</f>
         <v>2153</v>
       </c>
-      <c r="P15" s="34">
+      <c r="P15" s="35">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -2749,53 +2819,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R15" s="35">
+      <c r="R15" s="36">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S15" s="35"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="V15" s="36"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:27">
+      <c r="S15" s="36"/>
+      <c r="T15" s="37"/>
+      <c r="U15" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="V15" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W15" s="37"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:28">
       <c r="A16" s="2">
         <v>4003</v>
       </c>
-      <c r="B16" s="26">
-        <v>1</v>
-      </c>
-      <c r="C16" s="26" t="b">
+      <c r="B16" s="27">
+        <v>1</v>
+      </c>
+      <c r="C16" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="37" t="b">
+      <c r="E16" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="38">
-        <v>1</v>
-      </c>
-      <c r="I16" s="26">
+      <c r="H16" s="39">
+        <v>1</v>
+      </c>
+      <c r="I16" s="27">
         <v>1002</v>
       </c>
-      <c r="J16" s="26"/>
+      <c r="J16" s="27"/>
       <c r="K16" s="2">
         <v>600</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M16" s="32">
+        <v>51</v>
+      </c>
+      <c r="M16" s="33">
         <f>D16^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -2803,11 +2876,11 @@
         <f>_xlfn.XLOOKUP($D16,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O16" s="33">
+      <c r="O16" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M16+Q16</f>
         <v>2153</v>
       </c>
-      <c r="P16" s="34">
+      <c r="P16" s="35">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -2815,53 +2888,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R16" s="35">
+      <c r="R16" s="36">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S16" s="35"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:22">
+      <c r="S16" s="36"/>
+      <c r="T16" s="37"/>
+      <c r="U16" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="V16" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W16" s="37"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:23">
       <c r="A17" s="1">
         <v>5001</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="29" t="b">
+      <c r="C17" s="30" t="b">
         <v>1</v>
       </c>
       <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="29" t="b">
+      <c r="E17" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="30" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="31">
-        <v>1</v>
-      </c>
-      <c r="I17" s="30">
+      <c r="H17" s="32">
+        <v>1</v>
+      </c>
+      <c r="I17" s="31">
         <v>5001</v>
       </c>
-      <c r="J17" s="26"/>
+      <c r="J17" s="27"/>
       <c r="K17" s="2">
         <v>600</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M17" s="32">
+        <v>43</v>
+      </c>
+      <c r="M17" s="33">
         <f>D17^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -2869,11 +2945,11 @@
         <f>_xlfn.XLOOKUP($D17,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O17" s="33">
+      <c r="O17" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M17+Q17</f>
         <v>2638</v>
       </c>
-      <c r="P17" s="34">
+      <c r="P17" s="35">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -2881,53 +2957,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R17" s="35">
+      <c r="R17" s="36">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S17" s="35"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="V17" s="36"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:22">
+      <c r="S17" s="36"/>
+      <c r="T17" s="37"/>
+      <c r="U17" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="V17" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W17" s="37"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:23">
       <c r="A18" s="2">
         <v>5002</v>
       </c>
-      <c r="B18" s="26">
-        <v>1</v>
-      </c>
-      <c r="C18" s="26" t="b">
+      <c r="B18" s="27">
+        <v>1</v>
+      </c>
+      <c r="C18" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D18" s="2">
         <v>5</v>
       </c>
-      <c r="E18" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="37" t="b">
+      <c r="E18" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="38">
-        <v>1</v>
-      </c>
-      <c r="I18" s="26">
+      <c r="H18" s="39">
+        <v>1</v>
+      </c>
+      <c r="I18" s="27">
         <v>1002</v>
       </c>
-      <c r="J18" s="26"/>
+      <c r="J18" s="27"/>
       <c r="K18" s="2">
         <v>600</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M18" s="32">
+        <v>43</v>
+      </c>
+      <c r="M18" s="33">
         <f>D18^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -2935,11 +3014,11 @@
         <f>_xlfn.XLOOKUP($D18,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O18" s="33">
+      <c r="O18" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M18+Q18</f>
         <v>2638</v>
       </c>
-      <c r="P18" s="34">
+      <c r="P18" s="35">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -2947,53 +3026,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R18" s="35">
+      <c r="R18" s="36">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S18" s="35"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="V18" s="36"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:22">
+      <c r="S18" s="36"/>
+      <c r="T18" s="37"/>
+      <c r="U18" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="V18" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W18" s="37"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:23">
       <c r="A19" s="2">
         <v>5003</v>
       </c>
-      <c r="B19" s="26">
-        <v>1</v>
-      </c>
-      <c r="C19" s="26" t="b">
+      <c r="B19" s="27">
+        <v>1</v>
+      </c>
+      <c r="C19" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D19" s="2">
         <v>5</v>
       </c>
-      <c r="E19" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="37" t="b">
+      <c r="E19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="38">
-        <v>1</v>
-      </c>
-      <c r="I19" s="26">
+      <c r="H19" s="39">
+        <v>1</v>
+      </c>
+      <c r="I19" s="27">
         <v>1001</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="27"/>
       <c r="K19" s="2">
         <v>600</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M19" s="32">
+        <v>51</v>
+      </c>
+      <c r="M19" s="33">
         <f>D19^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -3001,11 +3083,11 @@
         <f>_xlfn.XLOOKUP($D19,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O19" s="33">
+      <c r="O19" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M19+Q19</f>
         <v>2638</v>
       </c>
-      <c r="P19" s="34">
+      <c r="P19" s="35">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -3013,53 +3095,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R19" s="35">
+      <c r="R19" s="36">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S19" s="35"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="V19" s="36"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:22">
+      <c r="S19" s="36"/>
+      <c r="T19" s="37"/>
+      <c r="U19" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="V19" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W19" s="37"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:23">
       <c r="A20" s="1">
         <v>1004</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="29" t="b">
+      <c r="C20" s="30" t="b">
         <v>1</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
-      <c r="E20" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="29" t="b">
+      <c r="E20" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="30" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="31">
-        <v>1</v>
-      </c>
-      <c r="I20" s="30">
+      <c r="H20" s="32">
+        <v>1</v>
+      </c>
+      <c r="I20" s="31">
         <v>1004</v>
       </c>
-      <c r="J20" s="26"/>
+      <c r="J20" s="27"/>
       <c r="K20" s="2">
         <v>600</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M20" s="32">
+        <v>43</v>
+      </c>
+      <c r="M20" s="33">
         <f>D20^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -3067,11 +3152,11 @@
         <f>_xlfn.XLOOKUP($D20,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O20" s="33">
+      <c r="O20" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M20+Q20</f>
         <v>8400</v>
       </c>
-      <c r="P20" s="34">
+      <c r="P20" s="35">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -3079,53 +3164,56 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R20" s="35">
+      <c r="R20" s="36">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S20" s="35"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="V20" s="36"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:22">
+      <c r="S20" s="36"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="V20" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W20" s="37"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:23">
       <c r="A21" s="1">
         <v>1005</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="29" t="b">
+      <c r="C21" s="30" t="b">
         <v>1</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
-      <c r="E21" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="29" t="b">
+      <c r="E21" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="30" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="31">
-        <v>1</v>
-      </c>
-      <c r="I21" s="30">
+      <c r="H21" s="32">
+        <v>1</v>
+      </c>
+      <c r="I21" s="31">
         <v>1005</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="27"/>
       <c r="K21" s="2">
         <v>600</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" s="32">
+        <v>43</v>
+      </c>
+      <c r="M21" s="33">
         <f>D21^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -3133,11 +3221,11 @@
         <f>_xlfn.XLOOKUP($D21,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M21+Q21</f>
         <v>8400</v>
       </c>
-      <c r="P21" s="34">
+      <c r="P21" s="35">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -3145,53 +3233,56 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R21" s="35">
+      <c r="R21" s="36">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S21" s="35"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="V21" s="36"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:22">
+      <c r="S21" s="36"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="V21" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W21" s="37"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:23">
       <c r="A22" s="2">
         <v>1006</v>
       </c>
-      <c r="B22" s="26">
-        <v>1</v>
-      </c>
-      <c r="C22" s="26" t="b">
+      <c r="B22" s="27">
+        <v>1</v>
+      </c>
+      <c r="C22" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="37" t="b">
+      <c r="E22" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H22" s="38">
-        <v>1</v>
-      </c>
-      <c r="I22" s="26">
+      <c r="H22" s="39">
+        <v>1</v>
+      </c>
+      <c r="I22" s="27">
         <v>1002</v>
       </c>
-      <c r="J22" s="26"/>
+      <c r="J22" s="27"/>
       <c r="K22" s="2">
         <v>600</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M22" s="32">
+        <v>51</v>
+      </c>
+      <c r="M22" s="33">
         <f>D22^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -3199,11 +3290,11 @@
         <f>_xlfn.XLOOKUP($D22,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M22+Q22</f>
         <v>8400</v>
       </c>
-      <c r="P22" s="34">
+      <c r="P22" s="35">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -3211,53 +3302,56 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R22" s="35">
+      <c r="R22" s="36">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S22" s="35"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="V22" s="36"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:22">
+      <c r="S22" s="36"/>
+      <c r="T22" s="37"/>
+      <c r="U22" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="V22" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W22" s="37"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:23">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
-      <c r="B23" s="26">
-        <v>1</v>
-      </c>
-      <c r="C23" s="26" t="b">
+      <c r="B23" s="27">
+        <v>1</v>
+      </c>
+      <c r="C23" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
       </c>
-      <c r="E23" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="37" t="b">
+      <c r="E23" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H23" s="38">
-        <v>1</v>
-      </c>
-      <c r="I23" s="26">
+      <c r="H23" s="39">
+        <v>1</v>
+      </c>
+      <c r="I23" s="27">
         <v>5006</v>
       </c>
-      <c r="J23" s="26"/>
+      <c r="J23" s="27"/>
       <c r="K23" s="2">
         <v>600</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="32">
+        <v>43</v>
+      </c>
+      <c r="M23" s="33">
         <f>D23^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -3265,11 +3359,11 @@
         <f>_xlfn.XLOOKUP($D23,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O23" s="33">
+      <c r="O23" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M23+Q23</f>
         <v>4550</v>
       </c>
-      <c r="P23" s="34">
+      <c r="P23" s="35">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -3277,53 +3371,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R23" s="35">
+      <c r="R23" s="36">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S23" s="35"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="V23" s="36"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:22">
+      <c r="S23" s="36"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="V23" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W23" s="37"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:23">
       <c r="A24" s="2">
         <v>2005</v>
       </c>
-      <c r="B24" s="26">
-        <v>1</v>
-      </c>
-      <c r="C24" s="26" t="b">
+      <c r="B24" s="27">
+        <v>1</v>
+      </c>
+      <c r="C24" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
       </c>
-      <c r="E24" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="37" t="b">
+      <c r="E24" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="38">
-        <v>1</v>
-      </c>
-      <c r="I24" s="26">
+      <c r="H24" s="39">
+        <v>1</v>
+      </c>
+      <c r="I24" s="27">
         <v>1004</v>
       </c>
-      <c r="J24" s="26"/>
+      <c r="J24" s="27"/>
       <c r="K24" s="2">
         <v>600</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M24" s="32">
+        <v>43</v>
+      </c>
+      <c r="M24" s="33">
         <f>D24^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -3331,11 +3428,11 @@
         <f>_xlfn.XLOOKUP($D24,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M24+Q24</f>
         <v>4550</v>
       </c>
-      <c r="P24" s="34">
+      <c r="P24" s="35">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -3343,53 +3440,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R24" s="35">
+      <c r="R24" s="36">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S24" s="35"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="V24" s="36"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:22">
+      <c r="S24" s="36"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="V24" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W24" s="37"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:23">
       <c r="A25" s="2">
         <v>2006</v>
       </c>
-      <c r="B25" s="26">
-        <v>1</v>
-      </c>
-      <c r="C25" s="26" t="b">
+      <c r="B25" s="27">
+        <v>1</v>
+      </c>
+      <c r="C25" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
       </c>
-      <c r="E25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="37" t="b">
+      <c r="E25" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H25" s="38">
-        <v>1</v>
-      </c>
-      <c r="I25" s="26">
+      <c r="H25" s="39">
+        <v>1</v>
+      </c>
+      <c r="I25" s="27">
         <v>1005</v>
       </c>
-      <c r="J25" s="26"/>
+      <c r="J25" s="27"/>
       <c r="K25" s="2">
         <v>600</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M25" s="32">
+        <v>51</v>
+      </c>
+      <c r="M25" s="33">
         <f>D25^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -3397,11 +3497,11 @@
         <f>_xlfn.XLOOKUP($D25,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M25+Q25</f>
         <v>4550</v>
       </c>
-      <c r="P25" s="34">
+      <c r="P25" s="35">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -3409,53 +3509,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R25" s="35">
+      <c r="R25" s="36">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S25" s="35"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="V25" s="36"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:22">
+      <c r="S25" s="36"/>
+      <c r="T25" s="37"/>
+      <c r="U25" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="V25" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W25" s="37"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:23">
       <c r="A26" s="2">
         <v>3004</v>
       </c>
-      <c r="B26" s="26">
-        <v>1</v>
-      </c>
-      <c r="C26" s="26" t="b">
+      <c r="B26" s="27">
+        <v>1</v>
+      </c>
+      <c r="C26" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
       </c>
-      <c r="E26" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="G26" s="37" t="b">
+      <c r="E26" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="38">
-        <v>1</v>
-      </c>
-      <c r="I26" s="26">
+      <c r="H26" s="39">
+        <v>1</v>
+      </c>
+      <c r="I26" s="27">
         <v>1004</v>
       </c>
-      <c r="J26" s="26"/>
+      <c r="J26" s="27"/>
       <c r="K26" s="2">
         <v>600</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M26" s="32">
+        <v>43</v>
+      </c>
+      <c r="M26" s="33">
         <f>D26^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -3463,11 +3566,11 @@
         <f>_xlfn.XLOOKUP($D26,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O26" s="33">
+      <c r="O26" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M26+Q26</f>
         <v>2560</v>
       </c>
-      <c r="P26" s="34">
+      <c r="P26" s="35">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -3475,53 +3578,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R26" s="35">
+      <c r="R26" s="36">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S26" s="35"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="V26" s="36"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:22">
+      <c r="S26" s="36"/>
+      <c r="T26" s="37"/>
+      <c r="U26" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="V26" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W26" s="37"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:23">
       <c r="A27" s="2">
         <v>3005</v>
       </c>
-      <c r="B27" s="26">
-        <v>1</v>
-      </c>
-      <c r="C27" s="26" t="b">
+      <c r="B27" s="27">
+        <v>1</v>
+      </c>
+      <c r="C27" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>3</v>
       </c>
-      <c r="E27" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27" s="37" t="b">
+      <c r="E27" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H27" s="38">
-        <v>1</v>
-      </c>
-      <c r="I27" s="26">
+      <c r="H27" s="39">
+        <v>1</v>
+      </c>
+      <c r="I27" s="27">
         <v>1005</v>
       </c>
-      <c r="J27" s="26"/>
+      <c r="J27" s="27"/>
       <c r="K27" s="2">
         <v>600</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M27" s="32">
+        <v>43</v>
+      </c>
+      <c r="M27" s="33">
         <f>D27^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -3529,11 +3635,11 @@
         <f>_xlfn.XLOOKUP($D27,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M27+Q27</f>
         <v>2560</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -3541,53 +3647,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R27" s="35">
+      <c r="R27" s="36">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S27" s="35"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="V27" s="36"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:22">
+      <c r="S27" s="36"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="V27" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W27" s="37"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:23">
       <c r="A28" s="2">
         <v>3006</v>
       </c>
-      <c r="B28" s="26">
-        <v>1</v>
-      </c>
-      <c r="C28" s="26" t="b">
+      <c r="B28" s="27">
+        <v>1</v>
+      </c>
+      <c r="C28" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D28" s="2">
         <v>3</v>
       </c>
-      <c r="E28" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="37" t="b">
+      <c r="E28" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H28" s="38">
-        <v>1</v>
-      </c>
-      <c r="I28" s="26">
+      <c r="H28" s="39">
+        <v>1</v>
+      </c>
+      <c r="I28" s="27">
         <v>5006</v>
       </c>
-      <c r="J28" s="26"/>
+      <c r="J28" s="27"/>
       <c r="K28" s="2">
         <v>600</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M28" s="32">
+        <v>51</v>
+      </c>
+      <c r="M28" s="33">
         <f>D28^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -3595,11 +3704,11 @@
         <f>_xlfn.XLOOKUP($D28,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M28+Q28</f>
         <v>2560</v>
       </c>
-      <c r="P28" s="34">
+      <c r="P28" s="35">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -3607,53 +3716,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R28" s="35">
+      <c r="R28" s="36">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S28" s="35"/>
-      <c r="T28" s="36"/>
-      <c r="U28" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="V28" s="36"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:22">
+      <c r="S28" s="36"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="V28" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W28" s="37"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:23">
       <c r="A29" s="2">
         <v>4004</v>
       </c>
-      <c r="B29" s="26">
-        <v>1</v>
-      </c>
-      <c r="C29" s="26" t="b">
+      <c r="B29" s="27">
+        <v>1</v>
+      </c>
+      <c r="C29" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D29" s="2">
         <v>4</v>
       </c>
-      <c r="E29" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="G29" s="37" t="b">
+      <c r="E29" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H29" s="38">
-        <v>1</v>
-      </c>
-      <c r="I29" s="26">
+      <c r="H29" s="39">
+        <v>1</v>
+      </c>
+      <c r="I29" s="27">
         <v>5006</v>
       </c>
-      <c r="J29" s="26"/>
+      <c r="J29" s="27"/>
       <c r="K29" s="2">
         <v>600</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M29" s="32">
+        <v>43</v>
+      </c>
+      <c r="M29" s="33">
         <f>D29^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -3661,11 +3773,11 @@
         <f>_xlfn.XLOOKUP($D29,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O29" s="33">
+      <c r="O29" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M29+Q29</f>
         <v>2153</v>
       </c>
-      <c r="P29" s="34">
+      <c r="P29" s="35">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -3673,53 +3785,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R29" s="35">
+      <c r="R29" s="36">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S29" s="35"/>
-      <c r="T29" s="36"/>
-      <c r="U29" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="V29" s="36"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:22">
+      <c r="S29" s="36"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="V29" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W29" s="37"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:23">
       <c r="A30" s="2">
         <v>4005</v>
       </c>
-      <c r="B30" s="26">
-        <v>1</v>
-      </c>
-      <c r="C30" s="26" t="b">
+      <c r="B30" s="27">
+        <v>1</v>
+      </c>
+      <c r="C30" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D30" s="2">
         <v>4</v>
       </c>
-      <c r="E30" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" s="37" t="b">
+      <c r="E30" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="38">
-        <v>1</v>
-      </c>
-      <c r="I30" s="26">
+      <c r="H30" s="39">
+        <v>1</v>
+      </c>
+      <c r="I30" s="27">
         <v>1005</v>
       </c>
-      <c r="J30" s="26"/>
+      <c r="J30" s="27"/>
       <c r="K30" s="2">
         <v>600</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M30" s="32">
+        <v>43</v>
+      </c>
+      <c r="M30" s="33">
         <f>D30^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -3727,11 +3842,11 @@
         <f>_xlfn.XLOOKUP($D30,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M30+Q30</f>
         <v>2153</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -3739,53 +3854,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S30" s="35"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="V30" s="36"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:22">
+      <c r="S30" s="36"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="V30" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W30" s="37"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:23">
       <c r="A31" s="2">
         <v>4006</v>
       </c>
-      <c r="B31" s="26">
-        <v>1</v>
-      </c>
-      <c r="C31" s="26" t="b">
+      <c r="B31" s="27">
+        <v>1</v>
+      </c>
+      <c r="C31" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
       </c>
-      <c r="E31" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G31" s="37" t="b">
+      <c r="E31" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="38">
-        <v>1</v>
-      </c>
-      <c r="I31" s="26">
+      <c r="H31" s="39">
+        <v>1</v>
+      </c>
+      <c r="I31" s="27">
         <v>1004</v>
       </c>
-      <c r="J31" s="26"/>
+      <c r="J31" s="27"/>
       <c r="K31" s="2">
         <v>600</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M31" s="32">
+        <v>51</v>
+      </c>
+      <c r="M31" s="33">
         <f>D31^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -3793,11 +3911,11 @@
         <f>_xlfn.XLOOKUP($D31,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M31+Q31</f>
         <v>2153</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -3805,53 +3923,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="36">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S31" s="35"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="V31" s="36"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:22">
+      <c r="S31" s="36"/>
+      <c r="T31" s="37"/>
+      <c r="U31" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="V31" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W31" s="37"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:23">
       <c r="A32" s="2">
         <v>5004</v>
       </c>
-      <c r="B32" s="26">
-        <v>1</v>
-      </c>
-      <c r="C32" s="26" t="b">
+      <c r="B32" s="27">
+        <v>1</v>
+      </c>
+      <c r="C32" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D32" s="2">
         <v>5</v>
       </c>
-      <c r="E32" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G32" s="37" t="b">
+      <c r="E32" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H32" s="38">
-        <v>1</v>
-      </c>
-      <c r="I32" s="26">
+      <c r="H32" s="39">
+        <v>1</v>
+      </c>
+      <c r="I32" s="27">
         <v>1005</v>
       </c>
-      <c r="J32" s="26"/>
+      <c r="J32" s="27"/>
       <c r="K32" s="2">
         <v>600</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M32" s="32">
+        <v>43</v>
+      </c>
+      <c r="M32" s="33">
         <f>D32^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -3859,11 +3980,11 @@
         <f>_xlfn.XLOOKUP($D32,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O32" s="33">
+      <c r="O32" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M32+Q32</f>
         <v>2638</v>
       </c>
-      <c r="P32" s="34">
+      <c r="P32" s="35">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -3871,53 +3992,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R32" s="35">
+      <c r="R32" s="36">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S32" s="35"/>
-      <c r="T32" s="36"/>
-      <c r="U32" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="V32" s="36"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:22">
+      <c r="S32" s="36"/>
+      <c r="T32" s="37"/>
+      <c r="U32" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="V32" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W32" s="37"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:23">
       <c r="A33" s="2">
         <v>5005</v>
       </c>
-      <c r="B33" s="26">
-        <v>1</v>
-      </c>
-      <c r="C33" s="26" t="b">
+      <c r="B33" s="27">
+        <v>1</v>
+      </c>
+      <c r="C33" s="27" t="b">
         <v>1</v>
       </c>
       <c r="D33" s="2">
         <v>5</v>
       </c>
-      <c r="E33" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="G33" s="37" t="b">
+      <c r="E33" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="H33" s="38">
-        <v>1</v>
-      </c>
-      <c r="I33" s="26">
+      <c r="H33" s="39">
+        <v>1</v>
+      </c>
+      <c r="I33" s="27">
         <v>1004</v>
       </c>
-      <c r="J33" s="26"/>
+      <c r="J33" s="27"/>
       <c r="K33" s="2">
         <v>600</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M33" s="32">
+        <v>43</v>
+      </c>
+      <c r="M33" s="33">
         <f>D33^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -3925,11 +4049,11 @@
         <f>_xlfn.XLOOKUP($D33,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M33+Q33</f>
         <v>2638</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="35">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -3937,53 +4061,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S33" s="35"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="V33" s="36"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:22">
+      <c r="S33" s="36"/>
+      <c r="T33" s="37"/>
+      <c r="U33" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="V33" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W33" s="37"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:23">
       <c r="A34" s="1">
         <v>5006</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
-      <c r="C34" s="29" t="b">
+      <c r="C34" s="30" t="b">
         <v>1</v>
       </c>
       <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="G34" s="29" t="b">
+      <c r="E34" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="30" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="31">
-        <v>1</v>
-      </c>
-      <c r="I34" s="30">
+      <c r="H34" s="32">
+        <v>1</v>
+      </c>
+      <c r="I34" s="31">
         <v>5006</v>
       </c>
-      <c r="J34" s="26"/>
+      <c r="J34" s="27"/>
       <c r="K34" s="2">
         <v>600</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M34" s="32">
+        <v>51</v>
+      </c>
+      <c r="M34" s="33">
         <f>D34^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -3991,11 +4118,11 @@
         <f>_xlfn.XLOOKUP($D34,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="34">
         <f>Sheet1!$A$9/Sheet1!$C$9*M34+Q34</f>
         <v>2638</v>
       </c>
-      <c r="P34" s="34">
+      <c r="P34" s="35">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -4003,123 +4130,126 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R34" s="35">
+      <c r="R34" s="36">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S34" s="35"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="V34" s="36"/>
-    </row>
-    <row r="35" spans="1:22">
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="41"/>
-    </row>
-    <row r="36" spans="1:22">
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-    </row>
-    <row r="37" spans="1:22">
-      <c r="K37" s="39"/>
-      <c r="L37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="41"/>
-    </row>
-    <row r="38" spans="1:22">
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="41"/>
-    </row>
-    <row r="39" spans="1:22">
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="41"/>
-    </row>
-    <row r="40" spans="1:22">
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-    </row>
-    <row r="41" ht="15" spans="1:22">
+      <c r="S34" s="36"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="V34" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="W34" s="37"/>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="R35" s="42"/>
+      <c r="S35" s="42"/>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="R36" s="42"/>
+      <c r="S36" s="42"/>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="R37" s="42"/>
+      <c r="S37" s="42"/>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="K38" s="40"/>
+      <c r="L38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="R38" s="42"/>
+      <c r="S38" s="42"/>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="42"/>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
+    </row>
+    <row r="41" ht="15" spans="1:23">
       <c r="K41" s="14"/>
-      <c r="L41" s="39"/>
-    </row>
-    <row r="42" spans="1:22">
-      <c r="K42" s="39"/>
-      <c r="L42" s="39"/>
-    </row>
-    <row r="43" spans="1:22">
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-    </row>
-    <row r="44" spans="1:22">
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-    </row>
-    <row r="45" spans="1:22">
-      <c r="K45" s="39"/>
-      <c r="L45" s="39"/>
-    </row>
-    <row r="46" spans="1:22">
-      <c r="K46" s="39"/>
-      <c r="L46" s="39"/>
-    </row>
-    <row r="47" spans="1:22">
-      <c r="K47" s="39"/>
-      <c r="L47" s="39"/>
-    </row>
-    <row r="48" ht="14.25" spans="1:22">
-      <c r="E48" s="42"/>
-      <c r="K48" s="39"/>
-      <c r="L48" s="39"/>
+      <c r="L41" s="40"/>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="K42" s="40"/>
+      <c r="L42" s="40"/>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="K43" s="40"/>
+      <c r="L43" s="40"/>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="K44" s="40"/>
+      <c r="L44" s="40"/>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="K46" s="40"/>
+      <c r="L46" s="40"/>
+    </row>
+    <row r="47" spans="1:23">
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+    </row>
+    <row r="48" ht="14.25" spans="1:23">
+      <c r="E48" s="43"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="40"/>
     </row>
     <row r="49" spans="11:12">
-      <c r="K49" s="39"/>
-      <c r="L49" s="39"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="40"/>
     </row>
     <row r="50" spans="11:12">
-      <c r="K50" s="39"/>
-      <c r="L50" s="39"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
     </row>
     <row r="51" spans="11:12">
-      <c r="K51" s="39"/>
-      <c r="L51" s="39"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
     </row>
     <row r="52" spans="11:12">
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="40"/>
     </row>
     <row r="53" spans="11:12">
-      <c r="K53" s="39"/>
-      <c r="L53" s="39"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="40"/>
     </row>
     <row r="54" spans="11:12">
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40"/>
     </row>
     <row r="55" spans="11:12">
-      <c r="K55" s="39"/>
-      <c r="L55" s="39"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="V2:V3 V8:V19 V6 V35:V58 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 U4:V4 U1:V1 D4 D1" formula="1"/>
+    <ignoredError sqref="W2:W4 W1 D1 D4 U1 U4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 W35:W58 W6 W8:W19" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -4133,13 +4263,13 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4190,7 +4320,7 @@
         <v>553</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4211,11 +4341,11 @@
     </row>
     <row r="8" ht="15" spans="1:10">
       <c r="A8" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F8">
         <v>1101</v>
@@ -4249,11 +4379,11 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F10">
         <v>1103</v>
@@ -4450,13 +4580,13 @@
         <v>1111</v>
       </c>
       <c r="F27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -4497,13 +4627,13 @@
         <v>1025101_1125101_2</v>
       </c>
       <c r="R30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U30" s="7">
         <v>1025101</v>
       </c>
       <c r="V30" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="2:22">
@@ -4534,13 +4664,13 @@
         <v>1025102_1125102_2</v>
       </c>
       <c r="R31" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U31" s="7">
         <v>1025102</v>
       </c>
       <c r="V31" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="2:22">
@@ -4571,13 +4701,13 @@
         <v>1025103_1125103_2</v>
       </c>
       <c r="R32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U32" s="7">
         <v>1025103</v>
       </c>
       <c r="V32" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="6:22">
@@ -4608,13 +4738,13 @@
         <v>1025201_1125201_4</v>
       </c>
       <c r="R33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U33" s="7">
         <v>1025104</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -4645,13 +4775,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U34" s="7">
         <v>1025105</v>
       </c>
       <c r="V34" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -4682,13 +4812,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U35" s="7">
         <v>1025106</v>
       </c>
       <c r="V35" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -4719,13 +4849,13 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U36" s="8">
         <v>1025201</v>
       </c>
       <c r="V36" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="6:22">
@@ -4756,13 +4886,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U37" s="8">
         <v>1025202</v>
       </c>
       <c r="V37" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -4793,13 +4923,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U38" s="8">
         <v>1025203</v>
       </c>
       <c r="V38" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -4830,13 +4960,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="U39" s="8">
         <v>1025204</v>
       </c>
       <c r="V39" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4867,13 +4997,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U40" s="8">
         <v>1025205</v>
       </c>
       <c r="V40" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -4904,13 +5034,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U41" s="8">
         <v>1025206</v>
       </c>
       <c r="V41" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -4941,13 +5071,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U42" s="7">
         <v>1025301</v>
       </c>
       <c r="V42" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -4978,13 +5108,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U43" s="7">
         <v>1025302</v>
       </c>
       <c r="V43" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -5015,13 +5145,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="U44" s="7">
         <v>1025303</v>
       </c>
       <c r="V44" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -5052,13 +5182,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U45" s="7">
         <v>1025304</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -5089,13 +5219,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U46" s="7">
         <v>1025305</v>
       </c>
       <c r="V46" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -5126,13 +5256,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U47" s="7">
         <v>1025306</v>
       </c>
       <c r="V47" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -5163,13 +5293,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="U48" s="8">
         <v>1025401</v>
       </c>
       <c r="V48" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -5200,13 +5330,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="U49" s="8">
         <v>1025402</v>
       </c>
       <c r="V49" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -5237,13 +5367,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U50" s="8">
         <v>1025403</v>
       </c>
       <c r="V50" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -5274,13 +5404,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U51" s="8">
         <v>1025404</v>
       </c>
       <c r="V51" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -5311,13 +5441,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U52" s="8">
         <v>1025405</v>
       </c>
       <c r="V52" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -5348,13 +5478,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U53" s="8">
         <v>1025406</v>
       </c>
       <c r="V53" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -5385,13 +5515,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="U54" s="7">
         <v>1025501</v>
       </c>
       <c r="V54" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -5422,13 +5552,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="U55" s="7">
         <v>1025502</v>
       </c>
       <c r="V55" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -5459,13 +5589,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="U56" s="7">
         <v>1025503</v>
       </c>
       <c r="V56" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -5496,13 +5626,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U57" s="7">
         <v>1025504</v>
       </c>
       <c r="V57" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -5533,13 +5663,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U58" s="7">
         <v>1025505</v>
       </c>
       <c r="V58" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -5570,13 +5700,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="U59" s="7">
         <v>1025506</v>
       </c>
       <c r="V59" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -1380,7 +1380,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1431,9 +1431,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1924,155 +1921,155 @@
       <c r="V1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="18" t="s">
+      <c r="W1" s="17" t="s">
         <v>21</v>
       </c>
       <c r="X1"/>
       <c r="Y1"/>
       <c r="Z1"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
     </row>
     <row r="2" s="4" customFormat="1" ht="21" customHeight="1" spans="1:28">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="21"/>
+      <c r="F2" s="20"/>
       <c r="G2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22" t="s">
+      <c r="L2" s="21"/>
+      <c r="M2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22" t="s">
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="22" t="s">
+      <c r="U2" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="W2" s="24"/>
+      <c r="V2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" s="23"/>
       <c r="X2"/>
       <c r="Y2"/>
       <c r="Z2"/>
     </row>
     <row r="3" s="4" customFormat="1" ht="15.75" spans="1:28">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="21"/>
+      <c r="F3" s="20"/>
       <c r="G3" s="11" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22" t="s">
+      <c r="L3" s="21"/>
+      <c r="M3" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="22" t="s">
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="U3" s="22" t="s">
+      <c r="U3" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="V3" s="24" t="s">
+      <c r="V3" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="W3" s="24"/>
+      <c r="W3" s="23"/>
       <c r="X3"/>
       <c r="Y3"/>
       <c r="Z3"/>
     </row>
     <row r="4" ht="15.75" spans="1:28">
       <c r="A4" s="2"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:28">
       <c r="A5" s="1">
@@ -2081,35 +2078,35 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="30" t="b">
+      <c r="C5" s="29" t="b">
         <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="32">
-        <v>1</v>
-      </c>
-      <c r="I5" s="31">
+      <c r="G5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="31">
+        <v>1</v>
+      </c>
+      <c r="I5" s="30">
         <v>1001</v>
       </c>
-      <c r="J5" s="27"/>
+      <c r="J5" s="26"/>
       <c r="K5" s="2">
         <v>600</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="32">
         <f>D5^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -2117,11 +2114,11 @@
         <f>_xlfn.XLOOKUP($D5,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M5+Q5</f>
         <v>8400</v>
       </c>
-      <c r="P5" s="35">
+      <c r="P5" s="34">
         <f>O5/SUM($O$5:$O$34)</f>
         <v>0.0689621200926063</v>
       </c>
@@ -2129,19 +2126,19 @@
         <f>N5</f>
         <v>8300</v>
       </c>
-      <c r="R5" s="36">
+      <c r="R5" s="35">
         <f>Q5/SUM($Q$5:$Q$34)</f>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S5" s="36"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37" t="s">
+      <c r="S5" s="35"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="37" t="s">
+      <c r="V5" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W5" s="37"/>
+      <c r="W5" s="36"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:28">
       <c r="A6" s="1">
@@ -2150,35 +2147,35 @@
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="30" t="b">
+      <c r="C6" s="29" t="b">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="32">
-        <v>1</v>
-      </c>
-      <c r="I6" s="31">
+      <c r="G6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="31">
+        <v>1</v>
+      </c>
+      <c r="I6" s="30">
         <v>1002</v>
       </c>
-      <c r="J6" s="27"/>
+      <c r="J6" s="26"/>
       <c r="K6" s="2">
         <v>600</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="33">
+      <c r="M6" s="32">
         <f>D6^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -2186,11 +2183,11 @@
         <f>_xlfn.XLOOKUP($D6,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M6+Q6</f>
         <v>8400</v>
       </c>
-      <c r="P6" s="35">
+      <c r="P6" s="34">
         <f t="shared" ref="P6:P39" si="0">O6/SUM($O$5:$O$34)</f>
         <v>0.0689621200926063</v>
       </c>
@@ -2198,19 +2195,19 @@
         <f t="shared" ref="Q6:Q34" si="1">N6</f>
         <v>8300</v>
       </c>
-      <c r="R6" s="36">
+      <c r="R6" s="35">
         <f t="shared" ref="R6:R39" si="2">Q6/SUM($Q$5:$Q$34)</f>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S6" s="36"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37" t="s">
+      <c r="S6" s="35"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="V6" s="37" t="s">
+      <c r="V6" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="37"/>
+      <c r="W6" s="36"/>
     </row>
     <row r="7" ht="16.5" spans="1:28">
       <c r="A7" s="1">
@@ -2219,35 +2216,35 @@
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="30" t="b">
+      <c r="C7" s="29" t="b">
         <v>1</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="30" t="b">
+      <c r="G7" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="32">
-        <v>1</v>
-      </c>
-      <c r="I7" s="31">
+      <c r="H7" s="31">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30">
         <v>1003</v>
       </c>
-      <c r="J7" s="27"/>
+      <c r="J7" s="26"/>
       <c r="K7" s="2">
         <v>600</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="33">
+      <c r="M7" s="32">
         <f>D7^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -2255,11 +2252,11 @@
         <f>_xlfn.XLOOKUP($D7,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O7" s="34">
+      <c r="O7" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M7+Q7</f>
         <v>8400</v>
       </c>
-      <c r="P7" s="35">
+      <c r="P7" s="34">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -2267,56 +2264,56 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R7" s="36">
+      <c r="R7" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S7" s="36"/>
-      <c r="T7" s="37"/>
-      <c r="U7" s="37" t="s">
+      <c r="S7" s="35"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="V7" s="37" t="s">
+      <c r="V7" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W7" s="37"/>
+      <c r="W7" s="36"/>
     </row>
     <row r="8" ht="16.5" spans="1:28">
       <c r="A8" s="2">
         <v>2001</v>
       </c>
-      <c r="B8" s="27">
-        <v>1</v>
-      </c>
-      <c r="C8" s="27" t="b">
+      <c r="B8" s="26">
+        <v>1</v>
+      </c>
+      <c r="C8" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="38" t="b">
+      <c r="G8" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="39">
-        <v>1</v>
-      </c>
-      <c r="I8" s="27">
+      <c r="H8" s="38">
+        <v>1</v>
+      </c>
+      <c r="I8" s="26">
         <v>1003</v>
       </c>
-      <c r="J8" s="27"/>
+      <c r="J8" s="26"/>
       <c r="K8" s="2">
         <v>600</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M8" s="33">
+      <c r="M8" s="32">
         <f>D8^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -2324,11 +2321,11 @@
         <f>_xlfn.XLOOKUP($D8,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O8" s="34">
+      <c r="O8" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M8+Q8</f>
         <v>4550</v>
       </c>
-      <c r="P8" s="35">
+      <c r="P8" s="34">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -2336,56 +2333,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R8" s="36">
+      <c r="R8" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S8" s="36"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37" t="s">
+      <c r="S8" s="35"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="V8" s="37" t="s">
+      <c r="V8" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W8" s="37"/>
+      <c r="W8" s="36"/>
     </row>
     <row r="9" ht="16.5" spans="1:28">
       <c r="A9" s="2">
         <v>2002</v>
       </c>
-      <c r="B9" s="27">
-        <v>1</v>
-      </c>
-      <c r="C9" s="27" t="b">
+      <c r="B9" s="26">
+        <v>1</v>
+      </c>
+      <c r="C9" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="38" t="b">
+      <c r="G9" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="39">
-        <v>1</v>
-      </c>
-      <c r="I9" s="27">
+      <c r="H9" s="38">
+        <v>1</v>
+      </c>
+      <c r="I9" s="26">
         <v>1001</v>
       </c>
-      <c r="J9" s="27"/>
+      <c r="J9" s="26"/>
       <c r="K9" s="2">
         <v>600</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="33">
+      <c r="M9" s="32">
         <f>D9^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -2393,11 +2390,11 @@
         <f>_xlfn.XLOOKUP($D9,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O9" s="34">
+      <c r="O9" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M9+Q9</f>
         <v>4550</v>
       </c>
-      <c r="P9" s="35">
+      <c r="P9" s="34">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -2405,56 +2402,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R9" s="36">
+      <c r="R9" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S9" s="36"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37" t="s">
+      <c r="S9" s="35"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="V9" s="37" t="s">
+      <c r="V9" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="37"/>
+      <c r="W9" s="36"/>
     </row>
     <row r="10" ht="16.5" spans="1:28">
       <c r="A10" s="2">
         <v>2003</v>
       </c>
-      <c r="B10" s="27">
-        <v>1</v>
-      </c>
-      <c r="C10" s="27" t="b">
+      <c r="B10" s="26">
+        <v>1</v>
+      </c>
+      <c r="C10" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="38" t="b">
+      <c r="G10" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="39">
-        <v>1</v>
-      </c>
-      <c r="I10" s="27">
+      <c r="H10" s="38">
+        <v>1</v>
+      </c>
+      <c r="I10" s="26">
         <v>5001</v>
       </c>
-      <c r="J10" s="27"/>
+      <c r="J10" s="26"/>
       <c r="K10" s="2">
         <v>600</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10" s="32">
         <f>D10^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -2462,11 +2459,11 @@
         <f>_xlfn.XLOOKUP($D10,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O10" s="34">
+      <c r="O10" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M10+Q10</f>
         <v>4550</v>
       </c>
-      <c r="P10" s="35">
+      <c r="P10" s="34">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -2474,56 +2471,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R10" s="36">
+      <c r="R10" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S10" s="36"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37" t="s">
+      <c r="S10" s="35"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="V10" s="37" t="s">
+      <c r="V10" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W10" s="37"/>
+      <c r="W10" s="36"/>
     </row>
     <row r="11" ht="16.5" spans="1:28">
       <c r="A11" s="2">
         <v>3001</v>
       </c>
-      <c r="B11" s="27">
-        <v>1</v>
-      </c>
-      <c r="C11" s="27" t="b">
+      <c r="B11" s="26">
+        <v>1</v>
+      </c>
+      <c r="C11" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="38" t="b">
+      <c r="G11" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="39">
-        <v>1</v>
-      </c>
-      <c r="I11" s="27">
+      <c r="H11" s="38">
+        <v>1</v>
+      </c>
+      <c r="I11" s="26">
         <v>1001</v>
       </c>
-      <c r="J11" s="27"/>
+      <c r="J11" s="26"/>
       <c r="K11" s="2">
         <v>600</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M11" s="33">
+      <c r="M11" s="32">
         <f>D11^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -2531,11 +2528,11 @@
         <f>_xlfn.XLOOKUP($D11,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M11+Q11</f>
         <v>2560</v>
       </c>
-      <c r="P11" s="35">
+      <c r="P11" s="34">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -2543,56 +2540,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R11" s="36">
+      <c r="R11" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S11" s="36"/>
-      <c r="T11" s="37"/>
-      <c r="U11" s="37" t="s">
+      <c r="S11" s="35"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="V11" s="37" t="s">
+      <c r="V11" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W11" s="37"/>
+      <c r="W11" s="36"/>
     </row>
     <row r="12" ht="16.5" spans="1:28">
       <c r="A12" s="2">
         <v>3002</v>
       </c>
-      <c r="B12" s="27">
-        <v>1</v>
-      </c>
-      <c r="C12" s="27" t="b">
+      <c r="B12" s="26">
+        <v>1</v>
+      </c>
+      <c r="C12" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="38" t="b">
+      <c r="G12" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="39">
-        <v>1</v>
-      </c>
-      <c r="I12" s="27">
+      <c r="H12" s="38">
+        <v>1</v>
+      </c>
+      <c r="I12" s="26">
         <v>1002</v>
       </c>
-      <c r="J12" s="27"/>
+      <c r="J12" s="26"/>
       <c r="K12" s="2">
         <v>600</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M12" s="33">
+      <c r="M12" s="32">
         <f>D12^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -2600,11 +2597,11 @@
         <f>_xlfn.XLOOKUP($D12,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O12" s="34">
+      <c r="O12" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M12+Q12</f>
         <v>2560</v>
       </c>
-      <c r="P12" s="35">
+      <c r="P12" s="34">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -2612,56 +2609,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R12" s="36">
+      <c r="R12" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S12" s="36"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37" t="s">
+      <c r="S12" s="35"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="V12" s="37" t="s">
+      <c r="V12" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W12" s="37"/>
+      <c r="W12" s="36"/>
     </row>
     <row r="13" ht="16.5" spans="1:28">
       <c r="A13" s="2">
         <v>3003</v>
       </c>
-      <c r="B13" s="27">
-        <v>1</v>
-      </c>
-      <c r="C13" s="27" t="b">
+      <c r="B13" s="26">
+        <v>1</v>
+      </c>
+      <c r="C13" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="38" t="b">
+      <c r="G13" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="39">
-        <v>1</v>
-      </c>
-      <c r="I13" s="27">
+      <c r="H13" s="38">
+        <v>1</v>
+      </c>
+      <c r="I13" s="26">
         <v>5001</v>
       </c>
-      <c r="J13" s="27"/>
+      <c r="J13" s="26"/>
       <c r="K13" s="2">
         <v>600</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="32">
         <f>D13^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -2669,11 +2666,11 @@
         <f>_xlfn.XLOOKUP($D13,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M13+Q13</f>
         <v>2560</v>
       </c>
-      <c r="P13" s="35">
+      <c r="P13" s="34">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -2681,56 +2678,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R13" s="36">
+      <c r="R13" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S13" s="36"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37" t="s">
+      <c r="S13" s="35"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="V13" s="37" t="s">
+      <c r="V13" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W13" s="37"/>
+      <c r="W13" s="36"/>
     </row>
     <row r="14" ht="16.5" spans="1:28">
       <c r="A14" s="2">
         <v>4001</v>
       </c>
-      <c r="B14" s="27">
-        <v>1</v>
-      </c>
-      <c r="C14" s="27" t="b">
+      <c r="B14" s="26">
+        <v>1</v>
+      </c>
+      <c r="C14" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D14" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="38" t="b">
+      <c r="G14" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="39">
-        <v>1</v>
-      </c>
-      <c r="I14" s="27">
+      <c r="H14" s="38">
+        <v>1</v>
+      </c>
+      <c r="I14" s="26">
         <v>5001</v>
       </c>
-      <c r="J14" s="27"/>
+      <c r="J14" s="26"/>
       <c r="K14" s="2">
         <v>600</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="32">
         <f>D14^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -2738,11 +2735,11 @@
         <f>_xlfn.XLOOKUP($D14,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M14+Q14</f>
         <v>2153</v>
       </c>
-      <c r="P14" s="35">
+      <c r="P14" s="34">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -2750,56 +2747,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R14" s="36">
+      <c r="R14" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S14" s="36"/>
-      <c r="T14" s="37"/>
-      <c r="U14" s="37" t="s">
+      <c r="S14" s="35"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="V14" s="37" t="s">
+      <c r="V14" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W14" s="37"/>
+      <c r="W14" s="36"/>
     </row>
     <row r="15" ht="16.5" spans="1:28">
       <c r="A15" s="2">
         <v>4002</v>
       </c>
-      <c r="B15" s="27">
-        <v>1</v>
-      </c>
-      <c r="C15" s="27" t="b">
+      <c r="B15" s="26">
+        <v>1</v>
+      </c>
+      <c r="C15" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="38" t="b">
+      <c r="G15" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H15" s="39">
-        <v>1</v>
-      </c>
-      <c r="I15" s="27">
+      <c r="H15" s="38">
+        <v>1</v>
+      </c>
+      <c r="I15" s="26">
         <v>1001</v>
       </c>
-      <c r="J15" s="27"/>
+      <c r="J15" s="26"/>
       <c r="K15" s="2">
         <v>600</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M15" s="33">
+      <c r="M15" s="32">
         <f>D15^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -2807,11 +2804,11 @@
         <f>_xlfn.XLOOKUP($D15,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O15" s="34">
+      <c r="O15" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M15+Q15</f>
         <v>2153</v>
       </c>
-      <c r="P15" s="35">
+      <c r="P15" s="34">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -2819,56 +2816,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R15" s="36">
+      <c r="R15" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S15" s="36"/>
-      <c r="T15" s="37"/>
-      <c r="U15" s="37" t="s">
+      <c r="S15" s="35"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="V15" s="37" t="s">
+      <c r="V15" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W15" s="37"/>
+      <c r="W15" s="36"/>
     </row>
     <row r="16" ht="16.5" spans="1:28">
       <c r="A16" s="2">
         <v>4003</v>
       </c>
-      <c r="B16" s="27">
-        <v>1</v>
-      </c>
-      <c r="C16" s="27" t="b">
+      <c r="B16" s="26">
+        <v>1</v>
+      </c>
+      <c r="C16" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="38" t="b">
+      <c r="G16" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="39">
-        <v>1</v>
-      </c>
-      <c r="I16" s="27">
+      <c r="H16" s="38">
+        <v>1</v>
+      </c>
+      <c r="I16" s="26">
         <v>1002</v>
       </c>
-      <c r="J16" s="27"/>
+      <c r="J16" s="26"/>
       <c r="K16" s="2">
         <v>600</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="33">
+      <c r="M16" s="32">
         <f>D16^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -2876,11 +2873,11 @@
         <f>_xlfn.XLOOKUP($D16,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M16+Q16</f>
         <v>2153</v>
       </c>
-      <c r="P16" s="35">
+      <c r="P16" s="34">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -2888,19 +2885,19 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R16" s="36">
+      <c r="R16" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S16" s="36"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="37" t="s">
+      <c r="S16" s="35"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="V16" s="37" t="s">
+      <c r="V16" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W16" s="37"/>
+      <c r="W16" s="36"/>
     </row>
     <row r="17" ht="16.5" spans="1:23">
       <c r="A17" s="1">
@@ -2909,35 +2906,35 @@
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="30" t="b">
+      <c r="C17" s="29" t="b">
         <v>1</v>
       </c>
       <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="30" t="b">
+      <c r="G17" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="32">
-        <v>1</v>
-      </c>
-      <c r="I17" s="31">
+      <c r="H17" s="31">
+        <v>1</v>
+      </c>
+      <c r="I17" s="30">
         <v>5001</v>
       </c>
-      <c r="J17" s="27"/>
+      <c r="J17" s="26"/>
       <c r="K17" s="2">
         <v>600</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M17" s="33">
+      <c r="M17" s="32">
         <f>D17^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -2945,11 +2942,11 @@
         <f>_xlfn.XLOOKUP($D17,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M17+Q17</f>
         <v>2638</v>
       </c>
-      <c r="P17" s="35">
+      <c r="P17" s="34">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -2957,56 +2954,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R17" s="36">
+      <c r="R17" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S17" s="36"/>
-      <c r="T17" s="37"/>
-      <c r="U17" s="37" t="s">
+      <c r="S17" s="35"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="V17" s="37" t="s">
+      <c r="V17" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W17" s="37"/>
+      <c r="W17" s="36"/>
     </row>
     <row r="18" ht="16.5" spans="1:23">
       <c r="A18" s="2">
         <v>5002</v>
       </c>
-      <c r="B18" s="27">
-        <v>1</v>
-      </c>
-      <c r="C18" s="27" t="b">
+      <c r="B18" s="26">
+        <v>1</v>
+      </c>
+      <c r="C18" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D18" s="2">
         <v>5</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="38" t="b">
+      <c r="G18" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="39">
-        <v>1</v>
-      </c>
-      <c r="I18" s="27">
+      <c r="H18" s="38">
+        <v>1</v>
+      </c>
+      <c r="I18" s="26">
         <v>1002</v>
       </c>
-      <c r="J18" s="27"/>
+      <c r="J18" s="26"/>
       <c r="K18" s="2">
         <v>600</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M18" s="33">
+      <c r="M18" s="32">
         <f>D18^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -3014,11 +3011,11 @@
         <f>_xlfn.XLOOKUP($D18,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O18" s="34">
+      <c r="O18" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M18+Q18</f>
         <v>2638</v>
       </c>
-      <c r="P18" s="35">
+      <c r="P18" s="34">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -3026,56 +3023,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R18" s="36">
+      <c r="R18" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S18" s="36"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="37" t="s">
+      <c r="S18" s="35"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="V18" s="37" t="s">
+      <c r="V18" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W18" s="37"/>
+      <c r="W18" s="36"/>
     </row>
     <row r="19" ht="16.5" spans="1:23">
       <c r="A19" s="2">
         <v>5003</v>
       </c>
-      <c r="B19" s="27">
-        <v>1</v>
-      </c>
-      <c r="C19" s="27" t="b">
+      <c r="B19" s="26">
+        <v>1</v>
+      </c>
+      <c r="C19" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D19" s="2">
         <v>5</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="38" t="b">
+      <c r="G19" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="39">
-        <v>1</v>
-      </c>
-      <c r="I19" s="27">
+      <c r="H19" s="38">
+        <v>1</v>
+      </c>
+      <c r="I19" s="26">
         <v>1001</v>
       </c>
-      <c r="J19" s="27"/>
+      <c r="J19" s="26"/>
       <c r="K19" s="2">
         <v>600</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M19" s="33">
+      <c r="M19" s="32">
         <f>D19^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -3083,11 +3080,11 @@
         <f>_xlfn.XLOOKUP($D19,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O19" s="34">
+      <c r="O19" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M19+Q19</f>
         <v>2638</v>
       </c>
-      <c r="P19" s="35">
+      <c r="P19" s="34">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -3095,19 +3092,19 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R19" s="36">
+      <c r="R19" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S19" s="36"/>
-      <c r="T19" s="37"/>
-      <c r="U19" s="37" t="s">
+      <c r="S19" s="35"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="V19" s="37" t="s">
+      <c r="V19" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W19" s="37"/>
+      <c r="W19" s="36"/>
     </row>
     <row r="20" ht="16.5" spans="1:23">
       <c r="A20" s="1">
@@ -3116,35 +3113,35 @@
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="30" t="b">
+      <c r="C20" s="29" t="b">
         <v>1</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="30" t="b">
+      <c r="G20" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="32">
-        <v>1</v>
-      </c>
-      <c r="I20" s="31">
+      <c r="H20" s="31">
+        <v>1</v>
+      </c>
+      <c r="I20" s="30">
         <v>1004</v>
       </c>
-      <c r="J20" s="27"/>
+      <c r="J20" s="26"/>
       <c r="K20" s="2">
         <v>600</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M20" s="33">
+      <c r="M20" s="32">
         <f>D20^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -3152,11 +3149,11 @@
         <f>_xlfn.XLOOKUP($D20,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M20+Q20</f>
         <v>8400</v>
       </c>
-      <c r="P20" s="35">
+      <c r="P20" s="34">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -3164,19 +3161,19 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R20" s="36">
+      <c r="R20" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S20" s="36"/>
-      <c r="T20" s="37"/>
-      <c r="U20" s="37" t="s">
+      <c r="S20" s="35"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="V20" s="37" t="s">
+      <c r="V20" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W20" s="37"/>
+      <c r="W20" s="36"/>
     </row>
     <row r="21" ht="16.5" spans="1:23">
       <c r="A21" s="1">
@@ -3185,35 +3182,35 @@
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="30" t="b">
+      <c r="C21" s="29" t="b">
         <v>1</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="G21" s="30" t="b">
+      <c r="G21" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="32">
-        <v>1</v>
-      </c>
-      <c r="I21" s="31">
+      <c r="H21" s="31">
+        <v>1</v>
+      </c>
+      <c r="I21" s="30">
         <v>1005</v>
       </c>
-      <c r="J21" s="27"/>
+      <c r="J21" s="26"/>
       <c r="K21" s="2">
         <v>600</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="32">
         <f>D21^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -3221,11 +3218,11 @@
         <f>_xlfn.XLOOKUP($D21,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O21" s="34">
+      <c r="O21" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M21+Q21</f>
         <v>8400</v>
       </c>
-      <c r="P21" s="35">
+      <c r="P21" s="34">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -3233,56 +3230,56 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R21" s="36">
+      <c r="R21" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S21" s="36"/>
-      <c r="T21" s="37"/>
-      <c r="U21" s="37" t="s">
+      <c r="S21" s="35"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="V21" s="37" t="s">
+      <c r="V21" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W21" s="37"/>
+      <c r="W21" s="36"/>
     </row>
     <row r="22" ht="16.5" spans="1:23">
       <c r="A22" s="2">
         <v>1006</v>
       </c>
-      <c r="B22" s="27">
-        <v>1</v>
-      </c>
-      <c r="C22" s="27" t="b">
+      <c r="B22" s="26">
+        <v>1</v>
+      </c>
+      <c r="C22" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="G22" s="38" t="b">
+      <c r="G22" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H22" s="39">
-        <v>1</v>
-      </c>
-      <c r="I22" s="27">
+      <c r="H22" s="38">
+        <v>1</v>
+      </c>
+      <c r="I22" s="26">
         <v>1002</v>
       </c>
-      <c r="J22" s="27"/>
+      <c r="J22" s="26"/>
       <c r="K22" s="2">
         <v>600</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="32">
         <f>D22^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
@@ -3290,11 +3287,11 @@
         <f>_xlfn.XLOOKUP($D22,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O22" s="34">
+      <c r="O22" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M22+Q22</f>
         <v>8400</v>
       </c>
-      <c r="P22" s="35">
+      <c r="P22" s="34">
         <f t="shared" si="0"/>
         <v>0.0689621200926063</v>
       </c>
@@ -3302,56 +3299,56 @@
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R22" s="36">
+      <c r="R22" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S22" s="36"/>
-      <c r="T22" s="37"/>
-      <c r="U22" s="37" t="s">
+      <c r="S22" s="35"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="V22" s="37" t="s">
+      <c r="V22" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W22" s="37"/>
+      <c r="W22" s="36"/>
     </row>
     <row r="23" ht="16.5" spans="1:23">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
-      <c r="B23" s="27">
-        <v>1</v>
-      </c>
-      <c r="C23" s="27" t="b">
+      <c r="B23" s="26">
+        <v>1</v>
+      </c>
+      <c r="C23" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G23" s="38" t="b">
+      <c r="G23" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H23" s="39">
-        <v>1</v>
-      </c>
-      <c r="I23" s="27">
+      <c r="H23" s="38">
+        <v>1</v>
+      </c>
+      <c r="I23" s="26">
         <v>5006</v>
       </c>
-      <c r="J23" s="27"/>
+      <c r="J23" s="26"/>
       <c r="K23" s="2">
         <v>600</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M23" s="33">
+      <c r="M23" s="32">
         <f>D23^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -3359,11 +3356,11 @@
         <f>_xlfn.XLOOKUP($D23,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O23" s="34">
+      <c r="O23" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M23+Q23</f>
         <v>4550</v>
       </c>
-      <c r="P23" s="35">
+      <c r="P23" s="34">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -3371,56 +3368,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R23" s="36">
+      <c r="R23" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S23" s="36"/>
-      <c r="T23" s="37"/>
-      <c r="U23" s="37" t="s">
+      <c r="S23" s="35"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="V23" s="37" t="s">
+      <c r="V23" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W23" s="37"/>
+      <c r="W23" s="36"/>
     </row>
     <row r="24" ht="16.5" spans="1:23">
       <c r="A24" s="2">
         <v>2005</v>
       </c>
-      <c r="B24" s="27">
-        <v>1</v>
-      </c>
-      <c r="C24" s="27" t="b">
+      <c r="B24" s="26">
+        <v>1</v>
+      </c>
+      <c r="C24" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="G24" s="38" t="b">
+      <c r="G24" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="39">
-        <v>1</v>
-      </c>
-      <c r="I24" s="27">
+      <c r="H24" s="38">
+        <v>1</v>
+      </c>
+      <c r="I24" s="26">
         <v>1004</v>
       </c>
-      <c r="J24" s="27"/>
+      <c r="J24" s="26"/>
       <c r="K24" s="2">
         <v>600</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="32">
         <f>D24^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -3428,11 +3425,11 @@
         <f>_xlfn.XLOOKUP($D24,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O24" s="34">
+      <c r="O24" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M24+Q24</f>
         <v>4550</v>
       </c>
-      <c r="P24" s="35">
+      <c r="P24" s="34">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -3440,56 +3437,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R24" s="36">
+      <c r="R24" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S24" s="36"/>
-      <c r="T24" s="37"/>
-      <c r="U24" s="37" t="s">
+      <c r="S24" s="35"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="V24" s="37" t="s">
+      <c r="V24" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W24" s="37"/>
+      <c r="W24" s="36"/>
     </row>
     <row r="25" ht="16.5" spans="1:23">
       <c r="A25" s="2">
         <v>2006</v>
       </c>
-      <c r="B25" s="27">
-        <v>1</v>
-      </c>
-      <c r="C25" s="27" t="b">
+      <c r="B25" s="26">
+        <v>1</v>
+      </c>
+      <c r="C25" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="38" t="b">
+      <c r="G25" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H25" s="39">
-        <v>1</v>
-      </c>
-      <c r="I25" s="27">
+      <c r="H25" s="38">
+        <v>1</v>
+      </c>
+      <c r="I25" s="26">
         <v>1005</v>
       </c>
-      <c r="J25" s="27"/>
+      <c r="J25" s="26"/>
       <c r="K25" s="2">
         <v>600</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="32">
         <f>D25^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>400</v>
       </c>
@@ -3497,11 +3494,11 @@
         <f>_xlfn.XLOOKUP($D25,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O25" s="34">
+      <c r="O25" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M25+Q25</f>
         <v>4550</v>
       </c>
-      <c r="P25" s="35">
+      <c r="P25" s="34">
         <f t="shared" si="0"/>
         <v>0.0373544817168284</v>
       </c>
@@ -3509,56 +3506,56 @@
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R25" s="36">
+      <c r="R25" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S25" s="36"/>
-      <c r="T25" s="37"/>
-      <c r="U25" s="37" t="s">
+      <c r="S25" s="35"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="V25" s="37" t="s">
+      <c r="V25" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W25" s="37"/>
+      <c r="W25" s="36"/>
     </row>
     <row r="26" ht="16.5" spans="1:23">
       <c r="A26" s="2">
         <v>3004</v>
       </c>
-      <c r="B26" s="27">
-        <v>1</v>
-      </c>
-      <c r="C26" s="27" t="b">
+      <c r="B26" s="26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="G26" s="38" t="b">
+      <c r="G26" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="39">
-        <v>1</v>
-      </c>
-      <c r="I26" s="27">
+      <c r="H26" s="38">
+        <v>1</v>
+      </c>
+      <c r="I26" s="26">
         <v>1004</v>
       </c>
-      <c r="J26" s="27"/>
+      <c r="J26" s="26"/>
       <c r="K26" s="2">
         <v>600</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M26" s="33">
+      <c r="M26" s="32">
         <f>D26^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -3566,11 +3563,11 @@
         <f>_xlfn.XLOOKUP($D26,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O26" s="34">
+      <c r="O26" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M26+Q26</f>
         <v>2560</v>
       </c>
-      <c r="P26" s="35">
+      <c r="P26" s="34">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -3578,56 +3575,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R26" s="36">
+      <c r="R26" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S26" s="36"/>
-      <c r="T26" s="37"/>
-      <c r="U26" s="37" t="s">
+      <c r="S26" s="35"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="V26" s="37" t="s">
+      <c r="V26" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W26" s="37"/>
+      <c r="W26" s="36"/>
     </row>
     <row r="27" ht="16.5" spans="1:23">
       <c r="A27" s="2">
         <v>3005</v>
       </c>
-      <c r="B27" s="27">
-        <v>1</v>
-      </c>
-      <c r="C27" s="27" t="b">
+      <c r="B27" s="26">
+        <v>1</v>
+      </c>
+      <c r="C27" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>3</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="G27" s="38" t="b">
+      <c r="G27" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H27" s="39">
-        <v>1</v>
-      </c>
-      <c r="I27" s="27">
+      <c r="H27" s="38">
+        <v>1</v>
+      </c>
+      <c r="I27" s="26">
         <v>1005</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="26"/>
       <c r="K27" s="2">
         <v>600</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="32">
         <f>D27^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -3635,11 +3632,11 @@
         <f>_xlfn.XLOOKUP($D27,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M27+Q27</f>
         <v>2560</v>
       </c>
-      <c r="P27" s="35">
+      <c r="P27" s="34">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -3647,56 +3644,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R27" s="36">
+      <c r="R27" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S27" s="36"/>
-      <c r="T27" s="37"/>
-      <c r="U27" s="37" t="s">
+      <c r="S27" s="35"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="V27" s="37" t="s">
+      <c r="V27" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W27" s="37"/>
+      <c r="W27" s="36"/>
     </row>
     <row r="28" ht="16.5" spans="1:23">
       <c r="A28" s="2">
         <v>3006</v>
       </c>
-      <c r="B28" s="27">
-        <v>1</v>
-      </c>
-      <c r="C28" s="27" t="b">
+      <c r="B28" s="26">
+        <v>1</v>
+      </c>
+      <c r="C28" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D28" s="2">
         <v>3</v>
       </c>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G28" s="38" t="b">
+      <c r="G28" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H28" s="39">
-        <v>1</v>
-      </c>
-      <c r="I28" s="27">
+      <c r="H28" s="38">
+        <v>1</v>
+      </c>
+      <c r="I28" s="26">
         <v>5006</v>
       </c>
-      <c r="J28" s="27"/>
+      <c r="J28" s="26"/>
       <c r="K28" s="2">
         <v>600</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="32">
         <f>D28^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>900</v>
       </c>
@@ -3704,11 +3701,11 @@
         <f>_xlfn.XLOOKUP($D28,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M28+Q28</f>
         <v>2560</v>
       </c>
-      <c r="P28" s="35">
+      <c r="P28" s="34">
         <f t="shared" si="0"/>
         <v>0.0210170270758419</v>
       </c>
@@ -3716,56 +3713,56 @@
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R28" s="36">
+      <c r="R28" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S28" s="36"/>
-      <c r="T28" s="37"/>
-      <c r="U28" s="37" t="s">
+      <c r="S28" s="35"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="V28" s="37" t="s">
+      <c r="V28" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W28" s="37"/>
+      <c r="W28" s="36"/>
     </row>
     <row r="29" ht="16.5" spans="1:23">
       <c r="A29" s="2">
         <v>4004</v>
       </c>
-      <c r="B29" s="27">
-        <v>1</v>
-      </c>
-      <c r="C29" s="27" t="b">
+      <c r="B29" s="26">
+        <v>1</v>
+      </c>
+      <c r="C29" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D29" s="2">
         <v>4</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="G29" s="38" t="b">
+      <c r="G29" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H29" s="39">
-        <v>1</v>
-      </c>
-      <c r="I29" s="27">
+      <c r="H29" s="38">
+        <v>1</v>
+      </c>
+      <c r="I29" s="26">
         <v>5006</v>
       </c>
-      <c r="J29" s="27"/>
+      <c r="J29" s="26"/>
       <c r="K29" s="2">
         <v>600</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M29" s="33">
+      <c r="M29" s="32">
         <f>D29^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -3773,11 +3770,11 @@
         <f>_xlfn.XLOOKUP($D29,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O29" s="34">
+      <c r="O29" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M29+Q29</f>
         <v>2153</v>
       </c>
-      <c r="P29" s="35">
+      <c r="P29" s="34">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -3785,56 +3782,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R29" s="36">
+      <c r="R29" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S29" s="36"/>
-      <c r="T29" s="37"/>
-      <c r="U29" s="37" t="s">
+      <c r="S29" s="35"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="V29" s="37" t="s">
+      <c r="V29" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W29" s="37"/>
+      <c r="W29" s="36"/>
     </row>
     <row r="30" ht="16.5" spans="1:23">
       <c r="A30" s="2">
         <v>4005</v>
       </c>
-      <c r="B30" s="27">
-        <v>1</v>
-      </c>
-      <c r="C30" s="27" t="b">
+      <c r="B30" s="26">
+        <v>1</v>
+      </c>
+      <c r="C30" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D30" s="2">
         <v>4</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="G30" s="38" t="b">
+      <c r="G30" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="39">
-        <v>1</v>
-      </c>
-      <c r="I30" s="27">
+      <c r="H30" s="38">
+        <v>1</v>
+      </c>
+      <c r="I30" s="26">
         <v>1005</v>
       </c>
-      <c r="J30" s="27"/>
+      <c r="J30" s="26"/>
       <c r="K30" s="2">
         <v>600</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="32">
         <f>D30^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -3842,11 +3839,11 @@
         <f>_xlfn.XLOOKUP($D30,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M30+Q30</f>
         <v>2153</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="34">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -3854,56 +3851,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S30" s="36"/>
-      <c r="T30" s="37"/>
-      <c r="U30" s="37" t="s">
+      <c r="S30" s="35"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="V30" s="37" t="s">
+      <c r="V30" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W30" s="37"/>
+      <c r="W30" s="36"/>
     </row>
     <row r="31" ht="16.5" spans="1:23">
       <c r="A31" s="2">
         <v>4006</v>
       </c>
-      <c r="B31" s="27">
-        <v>1</v>
-      </c>
-      <c r="C31" s="27" t="b">
+      <c r="B31" s="26">
+        <v>1</v>
+      </c>
+      <c r="C31" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="G31" s="38" t="b">
+      <c r="G31" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="39">
-        <v>1</v>
-      </c>
-      <c r="I31" s="27">
+      <c r="H31" s="38">
+        <v>1</v>
+      </c>
+      <c r="I31" s="26">
         <v>1004</v>
       </c>
-      <c r="J31" s="27"/>
+      <c r="J31" s="26"/>
       <c r="K31" s="2">
         <v>600</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="32">
         <f>D31^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>1600</v>
       </c>
@@ -3911,11 +3908,11 @@
         <f>_xlfn.XLOOKUP($D31,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M31+Q31</f>
         <v>2153</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="34">
         <f t="shared" si="0"/>
         <v>0.0176756481618311</v>
       </c>
@@ -3923,56 +3920,56 @@
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R31" s="36">
+      <c r="R31" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S31" s="36"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="37" t="s">
+      <c r="S31" s="35"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="V31" s="37" t="s">
+      <c r="V31" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W31" s="37"/>
+      <c r="W31" s="36"/>
     </row>
     <row r="32" ht="16.5" spans="1:23">
       <c r="A32" s="2">
         <v>5004</v>
       </c>
-      <c r="B32" s="27">
-        <v>1</v>
-      </c>
-      <c r="C32" s="27" t="b">
+      <c r="B32" s="26">
+        <v>1</v>
+      </c>
+      <c r="C32" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D32" s="2">
         <v>5</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="G32" s="38" t="b">
+      <c r="G32" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H32" s="39">
-        <v>1</v>
-      </c>
-      <c r="I32" s="27">
+      <c r="H32" s="38">
+        <v>1</v>
+      </c>
+      <c r="I32" s="26">
         <v>1005</v>
       </c>
-      <c r="J32" s="27"/>
+      <c r="J32" s="26"/>
       <c r="K32" s="2">
         <v>600</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M32" s="33">
+      <c r="M32" s="32">
         <f>D32^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -3980,11 +3977,11 @@
         <f>_xlfn.XLOOKUP($D32,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O32" s="34">
+      <c r="O32" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M32+Q32</f>
         <v>2638</v>
       </c>
-      <c r="P32" s="35">
+      <c r="P32" s="34">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -3992,56 +3989,56 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R32" s="36">
+      <c r="R32" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S32" s="36"/>
-      <c r="T32" s="37"/>
-      <c r="U32" s="37" t="s">
+      <c r="S32" s="35"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="V32" s="37" t="s">
+      <c r="V32" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W32" s="37"/>
+      <c r="W32" s="36"/>
     </row>
     <row r="33" ht="16.5" spans="1:23">
       <c r="A33" s="2">
         <v>5005</v>
       </c>
-      <c r="B33" s="27">
-        <v>1</v>
-      </c>
-      <c r="C33" s="27" t="b">
+      <c r="B33" s="26">
+        <v>1</v>
+      </c>
+      <c r="C33" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D33" s="2">
         <v>5</v>
       </c>
-      <c r="E33" s="27" t="s">
+      <c r="E33" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="G33" s="38" t="b">
+      <c r="G33" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H33" s="39">
-        <v>1</v>
-      </c>
-      <c r="I33" s="27">
+      <c r="H33" s="38">
+        <v>1</v>
+      </c>
+      <c r="I33" s="26">
         <v>1004</v>
       </c>
-      <c r="J33" s="27"/>
+      <c r="J33" s="26"/>
       <c r="K33" s="2">
         <v>600</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="32">
         <f>D33^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -4049,11 +4046,11 @@
         <f>_xlfn.XLOOKUP($D33,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M33+Q33</f>
         <v>2638</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="34">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -4061,19 +4058,19 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R33" s="36">
+      <c r="R33" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S33" s="36"/>
-      <c r="T33" s="37"/>
-      <c r="U33" s="37" t="s">
+      <c r="S33" s="35"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="V33" s="37" t="s">
+      <c r="V33" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W33" s="37"/>
+      <c r="W33" s="36"/>
     </row>
     <row r="34" ht="16.5" spans="1:23">
       <c r="A34" s="1">
@@ -4082,35 +4079,35 @@
       <c r="B34" s="1">
         <v>1</v>
       </c>
-      <c r="C34" s="30" t="b">
+      <c r="C34" s="29" t="b">
         <v>1</v>
       </c>
       <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="31" t="s">
+      <c r="E34" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="F34" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="G34" s="30" t="b">
+      <c r="G34" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="32">
-        <v>1</v>
-      </c>
-      <c r="I34" s="31">
+      <c r="H34" s="31">
+        <v>1</v>
+      </c>
+      <c r="I34" s="30">
         <v>5006</v>
       </c>
-      <c r="J34" s="27"/>
+      <c r="J34" s="26"/>
       <c r="K34" s="2">
         <v>600</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M34" s="33">
+      <c r="M34" s="32">
         <f>D34^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>2500</v>
       </c>
@@ -4118,11 +4115,11 @@
         <f>_xlfn.XLOOKUP($D34,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O34" s="34">
+      <c r="O34" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M34+Q34</f>
         <v>2638</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="34">
         <f t="shared" si="0"/>
         <v>0.021657389619559</v>
       </c>
@@ -4130,126 +4127,126 @@
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R34" s="36">
+      <c r="R34" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S34" s="36"/>
-      <c r="T34" s="37"/>
-      <c r="U34" s="37" t="s">
+      <c r="S34" s="35"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="V34" s="37" t="s">
+      <c r="V34" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="W34" s="37"/>
+      <c r="W34" s="36"/>
     </row>
     <row r="35" spans="1:23">
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="R35" s="42"/>
-      <c r="S35" s="42"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
     </row>
     <row r="36" spans="1:23">
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="R36" s="42"/>
-      <c r="S36" s="42"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
     </row>
     <row r="37" spans="1:23">
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="R37" s="42"/>
-      <c r="S37" s="42"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="41"/>
     </row>
     <row r="38" spans="1:23">
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="R38" s="42"/>
-      <c r="S38" s="42"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
     </row>
     <row r="39" spans="1:23">
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="R39" s="42"/>
-      <c r="S39" s="42"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="R39" s="41"/>
+      <c r="S39" s="41"/>
     </row>
     <row r="40" spans="1:23">
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
     </row>
     <row r="41" ht="15" spans="1:23">
       <c r="K41" s="14"/>
-      <c r="L41" s="40"/>
+      <c r="L41" s="39"/>
     </row>
     <row r="42" spans="1:23">
-      <c r="K42" s="40"/>
-      <c r="L42" s="40"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
     </row>
     <row r="43" spans="1:23">
-      <c r="K43" s="40"/>
-      <c r="L43" s="40"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
     </row>
     <row r="44" spans="1:23">
-      <c r="K44" s="40"/>
-      <c r="L44" s="40"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="39"/>
     </row>
     <row r="45" spans="1:23">
-      <c r="K45" s="40"/>
-      <c r="L45" s="40"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="39"/>
     </row>
     <row r="46" spans="1:23">
-      <c r="K46" s="40"/>
-      <c r="L46" s="40"/>
+      <c r="K46" s="39"/>
+      <c r="L46" s="39"/>
     </row>
     <row r="47" spans="1:23">
-      <c r="K47" s="40"/>
-      <c r="L47" s="40"/>
+      <c r="K47" s="39"/>
+      <c r="L47" s="39"/>
     </row>
     <row r="48" ht="14.25" spans="1:23">
-      <c r="E48" s="43"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="40"/>
+      <c r="E48" s="42"/>
+      <c r="K48" s="39"/>
+      <c r="L48" s="39"/>
     </row>
     <row r="49" spans="11:12">
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
+      <c r="K49" s="39"/>
+      <c r="L49" s="39"/>
     </row>
     <row r="50" spans="11:12">
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
+      <c r="K50" s="39"/>
+      <c r="L50" s="39"/>
     </row>
     <row r="51" spans="11:12">
-      <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
+      <c r="K51" s="39"/>
+      <c r="L51" s="39"/>
     </row>
     <row r="52" spans="11:12">
-      <c r="K52" s="40"/>
-      <c r="L52" s="40"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39"/>
     </row>
     <row r="53" spans="11:12">
-      <c r="K53" s="40"/>
-      <c r="L53" s="40"/>
+      <c r="K53" s="39"/>
+      <c r="L53" s="39"/>
     </row>
     <row r="54" spans="11:12">
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
+      <c r="K54" s="39"/>
+      <c r="L54" s="39"/>
     </row>
     <row r="55" spans="11:12">
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
+      <c r="K55" s="39"/>
+      <c r="L55" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="W2:W4 W1 D1 D4 U1 U4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 W35:W58 W6 W8:W19" formula="1"/>
+    <ignoredError sqref="W8:W19 W6 W35:W58 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 U4 U1 D4 D1 W1:W4" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -2101,13 +2101,12 @@
       </c>
       <c r="J5" s="26"/>
       <c r="K5" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M5" s="32">
-        <f>D5^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
       <c r="N5" s="2">
@@ -2120,7 +2119,7 @@
       </c>
       <c r="P5" s="34">
         <f>O5/SUM($O$5:$O$34)</f>
-        <v>0.0689621200926063</v>
+        <v>0.064217237741388</v>
       </c>
       <c r="Q5" s="2">
         <f>N5</f>
@@ -2170,13 +2169,12 @@
       </c>
       <c r="J6" s="26"/>
       <c r="K6" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M6" s="32">
-        <f>D6^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
       <c r="N6" s="2">
@@ -2189,7 +2187,7 @@
       </c>
       <c r="P6" s="34">
         <f t="shared" ref="P6:P39" si="0">O6/SUM($O$5:$O$34)</f>
-        <v>0.0689621200926063</v>
+        <v>0.064217237741388</v>
       </c>
       <c r="Q6" s="2">
         <f t="shared" ref="Q6:Q34" si="1">N6</f>
@@ -2239,13 +2237,12 @@
       </c>
       <c r="J7" s="26"/>
       <c r="K7" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M7" s="32">
-        <f>D7^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
       <c r="N7" s="2">
@@ -2258,7 +2255,7 @@
       </c>
       <c r="P7" s="34">
         <f t="shared" si="0"/>
-        <v>0.0689621200926063</v>
+        <v>0.064217237741388</v>
       </c>
       <c r="Q7" s="2">
         <f t="shared" si="1"/>
@@ -2308,14 +2305,13 @@
       </c>
       <c r="J8" s="26"/>
       <c r="K8" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M8" s="32">
-        <f>D8^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N8" s="2">
         <f>_xlfn.XLOOKUP($D8,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2323,11 +2319,11 @@
       </c>
       <c r="O8" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M8+Q8</f>
-        <v>4550</v>
+        <v>4650</v>
       </c>
       <c r="P8" s="34">
         <f t="shared" si="0"/>
-        <v>0.0373544817168284</v>
+        <v>0.0355488280354112</v>
       </c>
       <c r="Q8" s="2">
         <f t="shared" si="1"/>
@@ -2377,14 +2373,13 @@
       </c>
       <c r="J9" s="26"/>
       <c r="K9" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M9" s="32">
-        <f>D9^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N9" s="2">
         <f>_xlfn.XLOOKUP($D9,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2392,11 +2387,11 @@
       </c>
       <c r="O9" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M9+Q9</f>
-        <v>4550</v>
+        <v>4650</v>
       </c>
       <c r="P9" s="34">
         <f t="shared" si="0"/>
-        <v>0.0373544817168284</v>
+        <v>0.0355488280354112</v>
       </c>
       <c r="Q9" s="2">
         <f t="shared" si="1"/>
@@ -2446,14 +2441,13 @@
       </c>
       <c r="J10" s="26"/>
       <c r="K10" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M10" s="32">
-        <f>D10^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N10" s="2">
         <f>_xlfn.XLOOKUP($D10,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2461,11 +2455,11 @@
       </c>
       <c r="O10" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M10+Q10</f>
-        <v>4550</v>
+        <v>4650</v>
       </c>
       <c r="P10" s="34">
         <f t="shared" si="0"/>
-        <v>0.0373544817168284</v>
+        <v>0.0355488280354112</v>
       </c>
       <c r="Q10" s="2">
         <f t="shared" si="1"/>
@@ -2515,14 +2509,13 @@
       </c>
       <c r="J11" s="26"/>
       <c r="K11" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M11" s="32">
-        <f>D11^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="N11" s="2">
         <f>_xlfn.XLOOKUP($D11,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2530,11 +2523,11 @@
       </c>
       <c r="O11" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M11+Q11</f>
-        <v>2560</v>
+        <v>3060</v>
       </c>
       <c r="P11" s="34">
         <f t="shared" si="0"/>
-        <v>0.0210170270758419</v>
+        <v>0.0233934223200771</v>
       </c>
       <c r="Q11" s="2">
         <f t="shared" si="1"/>
@@ -2584,14 +2577,13 @@
       </c>
       <c r="J12" s="26"/>
       <c r="K12" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M12" s="32">
-        <f>D12^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="N12" s="2">
         <f>_xlfn.XLOOKUP($D12,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2599,11 +2591,11 @@
       </c>
       <c r="O12" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M12+Q12</f>
-        <v>2560</v>
+        <v>3060</v>
       </c>
       <c r="P12" s="34">
         <f t="shared" si="0"/>
-        <v>0.0210170270758419</v>
+        <v>0.0233934223200771</v>
       </c>
       <c r="Q12" s="2">
         <f t="shared" si="1"/>
@@ -2653,14 +2645,13 @@
       </c>
       <c r="J13" s="26"/>
       <c r="K13" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M13" s="32">
-        <f>D13^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="N13" s="2">
         <f>_xlfn.XLOOKUP($D13,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2668,11 +2659,11 @@
       </c>
       <c r="O13" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M13+Q13</f>
-        <v>2560</v>
+        <v>3060</v>
       </c>
       <c r="P13" s="34">
         <f t="shared" si="0"/>
-        <v>0.0210170270758419</v>
+        <v>0.0233934223200771</v>
       </c>
       <c r="Q13" s="2">
         <f t="shared" si="1"/>
@@ -2722,14 +2713,13 @@
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="2">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M14" s="32">
-        <f>D14^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N14" s="2">
         <f>_xlfn.XLOOKUP($D14,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2737,11 +2727,11 @@
       </c>
       <c r="O14" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M14+Q14</f>
-        <v>2153</v>
+        <v>2553</v>
       </c>
       <c r="P14" s="34">
         <f t="shared" si="0"/>
-        <v>0.0176756481618311</v>
+        <v>0.019517453327829</v>
       </c>
       <c r="Q14" s="2">
         <f t="shared" si="1"/>
@@ -2791,14 +2781,13 @@
       </c>
       <c r="J15" s="26"/>
       <c r="K15" s="2">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M15" s="32">
-        <f>D15^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N15" s="2">
         <f>_xlfn.XLOOKUP($D15,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2806,11 +2795,11 @@
       </c>
       <c r="O15" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M15+Q15</f>
-        <v>2153</v>
+        <v>2553</v>
       </c>
       <c r="P15" s="34">
         <f t="shared" si="0"/>
-        <v>0.0176756481618311</v>
+        <v>0.019517453327829</v>
       </c>
       <c r="Q15" s="2">
         <f t="shared" si="1"/>
@@ -2860,14 +2849,13 @@
       </c>
       <c r="J16" s="26"/>
       <c r="K16" s="2">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M16" s="32">
-        <f>D16^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N16" s="2">
         <f>_xlfn.XLOOKUP($D16,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2875,11 +2863,11 @@
       </c>
       <c r="O16" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M16+Q16</f>
-        <v>2153</v>
+        <v>2553</v>
       </c>
       <c r="P16" s="34">
         <f t="shared" si="0"/>
-        <v>0.0176756481618311</v>
+        <v>0.019517453327829</v>
       </c>
       <c r="Q16" s="2">
         <f t="shared" si="1"/>
@@ -2929,14 +2917,13 @@
       </c>
       <c r="J17" s="26"/>
       <c r="K17" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M17" s="32">
-        <f>D17^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N17" s="2">
         <f>_xlfn.XLOOKUP($D17,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -2944,11 +2931,11 @@
       </c>
       <c r="O17" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M17+Q17</f>
-        <v>2638</v>
+        <v>3138</v>
       </c>
       <c r="P17" s="34">
         <f t="shared" si="0"/>
-        <v>0.021657389619559</v>
+        <v>0.0239897252419614</v>
       </c>
       <c r="Q17" s="2">
         <f t="shared" si="1"/>
@@ -2998,14 +2985,13 @@
       </c>
       <c r="J18" s="26"/>
       <c r="K18" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M18" s="32">
-        <f>D18^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N18" s="2">
         <f>_xlfn.XLOOKUP($D18,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3013,11 +2999,11 @@
       </c>
       <c r="O18" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M18+Q18</f>
-        <v>2638</v>
+        <v>3138</v>
       </c>
       <c r="P18" s="34">
         <f t="shared" si="0"/>
-        <v>0.021657389619559</v>
+        <v>0.0239897252419614</v>
       </c>
       <c r="Q18" s="2">
         <f t="shared" si="1"/>
@@ -3067,14 +3053,13 @@
       </c>
       <c r="J19" s="26"/>
       <c r="K19" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M19" s="32">
-        <f>D19^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N19" s="2">
         <f>_xlfn.XLOOKUP($D19,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3082,11 +3067,11 @@
       </c>
       <c r="O19" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M19+Q19</f>
-        <v>2638</v>
+        <v>3138</v>
       </c>
       <c r="P19" s="34">
         <f t="shared" si="0"/>
-        <v>0.021657389619559</v>
+        <v>0.0239897252419614</v>
       </c>
       <c r="Q19" s="2">
         <f t="shared" si="1"/>
@@ -3136,13 +3121,12 @@
       </c>
       <c r="J20" s="26"/>
       <c r="K20" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M20" s="32">
-        <f>D20^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
       <c r="N20" s="2">
@@ -3155,7 +3139,7 @@
       </c>
       <c r="P20" s="34">
         <f t="shared" si="0"/>
-        <v>0.0689621200926063</v>
+        <v>0.064217237741388</v>
       </c>
       <c r="Q20" s="2">
         <f t="shared" si="1"/>
@@ -3205,13 +3189,12 @@
       </c>
       <c r="J21" s="26"/>
       <c r="K21" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M21" s="32">
-        <f>D21^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
       <c r="N21" s="2">
@@ -3224,7 +3207,7 @@
       </c>
       <c r="P21" s="34">
         <f t="shared" si="0"/>
-        <v>0.0689621200926063</v>
+        <v>0.064217237741388</v>
       </c>
       <c r="Q21" s="2">
         <f t="shared" si="1"/>
@@ -3274,13 +3257,12 @@
       </c>
       <c r="J22" s="26"/>
       <c r="K22" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M22" s="32">
-        <f>D22^Sheet1!$C$11*Sheet1!$A$11</f>
         <v>100</v>
       </c>
       <c r="N22" s="2">
@@ -3293,7 +3275,7 @@
       </c>
       <c r="P22" s="34">
         <f t="shared" si="0"/>
-        <v>0.0689621200926063</v>
+        <v>0.064217237741388</v>
       </c>
       <c r="Q22" s="2">
         <f t="shared" si="1"/>
@@ -3343,14 +3325,13 @@
       </c>
       <c r="J23" s="26"/>
       <c r="K23" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M23" s="32">
-        <f>D23^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N23" s="2">
         <f>_xlfn.XLOOKUP($D23,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3358,11 +3339,11 @@
       </c>
       <c r="O23" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M23+Q23</f>
-        <v>4550</v>
+        <v>4650</v>
       </c>
       <c r="P23" s="34">
         <f t="shared" si="0"/>
-        <v>0.0373544817168284</v>
+        <v>0.0355488280354112</v>
       </c>
       <c r="Q23" s="2">
         <f t="shared" si="1"/>
@@ -3412,14 +3393,13 @@
       </c>
       <c r="J24" s="26"/>
       <c r="K24" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M24" s="32">
-        <f>D24^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N24" s="2">
         <f>_xlfn.XLOOKUP($D24,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3427,11 +3407,11 @@
       </c>
       <c r="O24" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M24+Q24</f>
-        <v>4550</v>
+        <v>4650</v>
       </c>
       <c r="P24" s="34">
         <f t="shared" si="0"/>
-        <v>0.0373544817168284</v>
+        <v>0.0355488280354112</v>
       </c>
       <c r="Q24" s="2">
         <f t="shared" si="1"/>
@@ -3481,14 +3461,13 @@
       </c>
       <c r="J25" s="26"/>
       <c r="K25" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M25" s="32">
-        <f>D25^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N25" s="2">
         <f>_xlfn.XLOOKUP($D25,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3496,11 +3475,11 @@
       </c>
       <c r="O25" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M25+Q25</f>
-        <v>4550</v>
+        <v>4650</v>
       </c>
       <c r="P25" s="34">
         <f t="shared" si="0"/>
-        <v>0.0373544817168284</v>
+        <v>0.0355488280354112</v>
       </c>
       <c r="Q25" s="2">
         <f t="shared" si="1"/>
@@ -3550,14 +3529,13 @@
       </c>
       <c r="J26" s="26"/>
       <c r="K26" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M26" s="32">
-        <f>D26^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="N26" s="2">
         <f>_xlfn.XLOOKUP($D26,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3565,11 +3543,11 @@
       </c>
       <c r="O26" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M26+Q26</f>
-        <v>2560</v>
+        <v>3060</v>
       </c>
       <c r="P26" s="34">
         <f t="shared" si="0"/>
-        <v>0.0210170270758419</v>
+        <v>0.0233934223200771</v>
       </c>
       <c r="Q26" s="2">
         <f t="shared" si="1"/>
@@ -3619,14 +3597,13 @@
       </c>
       <c r="J27" s="26"/>
       <c r="K27" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M27" s="32">
-        <f>D27^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="N27" s="2">
         <f>_xlfn.XLOOKUP($D27,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3634,11 +3611,11 @@
       </c>
       <c r="O27" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M27+Q27</f>
-        <v>2560</v>
+        <v>3060</v>
       </c>
       <c r="P27" s="34">
         <f t="shared" si="0"/>
-        <v>0.0210170270758419</v>
+        <v>0.0233934223200771</v>
       </c>
       <c r="Q27" s="2">
         <f t="shared" si="1"/>
@@ -3688,14 +3665,13 @@
       </c>
       <c r="J28" s="26"/>
       <c r="K28" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M28" s="32">
-        <f>D28^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="N28" s="2">
         <f>_xlfn.XLOOKUP($D28,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3703,11 +3679,11 @@
       </c>
       <c r="O28" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M28+Q28</f>
-        <v>2560</v>
+        <v>3060</v>
       </c>
       <c r="P28" s="34">
         <f t="shared" si="0"/>
-        <v>0.0210170270758419</v>
+        <v>0.0233934223200771</v>
       </c>
       <c r="Q28" s="2">
         <f t="shared" si="1"/>
@@ -3757,14 +3733,13 @@
       </c>
       <c r="J29" s="26"/>
       <c r="K29" s="2">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M29" s="32">
-        <f>D29^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N29" s="2">
         <f>_xlfn.XLOOKUP($D29,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3772,11 +3747,11 @@
       </c>
       <c r="O29" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M29+Q29</f>
-        <v>2153</v>
+        <v>2553</v>
       </c>
       <c r="P29" s="34">
         <f t="shared" si="0"/>
-        <v>0.0176756481618311</v>
+        <v>0.019517453327829</v>
       </c>
       <c r="Q29" s="2">
         <f t="shared" si="1"/>
@@ -3826,14 +3801,13 @@
       </c>
       <c r="J30" s="26"/>
       <c r="K30" s="2">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M30" s="32">
-        <f>D30^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N30" s="2">
         <f>_xlfn.XLOOKUP($D30,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3841,11 +3815,11 @@
       </c>
       <c r="O30" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M30+Q30</f>
-        <v>2153</v>
+        <v>2553</v>
       </c>
       <c r="P30" s="34">
         <f t="shared" si="0"/>
-        <v>0.0176756481618311</v>
+        <v>0.019517453327829</v>
       </c>
       <c r="Q30" s="2">
         <f t="shared" si="1"/>
@@ -3895,14 +3869,13 @@
       </c>
       <c r="J31" s="26"/>
       <c r="K31" s="2">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M31" s="32">
-        <f>D31^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N31" s="2">
         <f>_xlfn.XLOOKUP($D31,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3910,11 +3883,11 @@
       </c>
       <c r="O31" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M31+Q31</f>
-        <v>2153</v>
+        <v>2553</v>
       </c>
       <c r="P31" s="34">
         <f t="shared" si="0"/>
-        <v>0.0176756481618311</v>
+        <v>0.019517453327829</v>
       </c>
       <c r="Q31" s="2">
         <f t="shared" si="1"/>
@@ -3964,14 +3937,13 @@
       </c>
       <c r="J32" s="26"/>
       <c r="K32" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M32" s="32">
-        <f>D32^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N32" s="2">
         <f>_xlfn.XLOOKUP($D32,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -3979,11 +3951,11 @@
       </c>
       <c r="O32" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M32+Q32</f>
-        <v>2638</v>
+        <v>3138</v>
       </c>
       <c r="P32" s="34">
         <f t="shared" si="0"/>
-        <v>0.021657389619559</v>
+        <v>0.0239897252419614</v>
       </c>
       <c r="Q32" s="2">
         <f t="shared" si="1"/>
@@ -4033,14 +4005,13 @@
       </c>
       <c r="J33" s="26"/>
       <c r="K33" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M33" s="32">
-        <f>D33^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N33" s="2">
         <f>_xlfn.XLOOKUP($D33,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -4048,11 +4019,11 @@
       </c>
       <c r="O33" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M33+Q33</f>
-        <v>2638</v>
+        <v>3138</v>
       </c>
       <c r="P33" s="34">
         <f t="shared" si="0"/>
-        <v>0.021657389619559</v>
+        <v>0.0239897252419614</v>
       </c>
       <c r="Q33" s="2">
         <f t="shared" si="1"/>
@@ -4102,14 +4073,13 @@
       </c>
       <c r="J34" s="26"/>
       <c r="K34" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M34" s="32">
-        <f>D34^Sheet1!$C$11*Sheet1!$A$11</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N34" s="2">
         <f>_xlfn.XLOOKUP($D34,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
@@ -4117,11 +4087,11 @@
       </c>
       <c r="O34" s="33">
         <f>Sheet1!$A$9/Sheet1!$C$9*M34+Q34</f>
-        <v>2638</v>
+        <v>3138</v>
       </c>
       <c r="P34" s="34">
         <f t="shared" si="0"/>
-        <v>0.021657389619559</v>
+        <v>0.0239897252419614</v>
       </c>
       <c r="Q34" s="2">
         <f t="shared" si="1"/>
@@ -4246,7 +4216,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="W8:W19 W6 W35:W58 A1 L1 A4 L4:L9 L11:L12 L14:L15 L17:L18 U4 U1 D4 D1 W1:W4" formula="1"/>
+    <ignoredError sqref="W1:W4 D1 D4 U1 U4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 W35:W58 W6 W8:W19" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/hall/resources/sample/VisitorQuest.xlsx
+++ b/hall/resources/sample/VisitorQuest.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorQuest" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -105,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -197,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0">
+    <comment ref="U1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -220,7 +220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0">
+    <comment ref="V1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -244,7 +244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0">
+    <comment ref="W1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -291,6 +291,9 @@
     <t>名称备注</t>
   </si>
   <si>
+    <t>游客描述多语言</t>
+  </si>
+  <si>
     <t>是否默认解锁</t>
   </si>
   <si>
@@ -364,6 +367,9 @@
   </si>
   <si>
     <t>DuplicatetoShard</t>
+  </si>
+  <si>
+    <t>language</t>
   </si>
   <si>
     <t>IsDefaultUnlocked</t>
@@ -1826,37 +1832,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB55"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
     <col min="2" max="4" width="8.375" customWidth="1"/>
     <col min="5" max="5" width="22.125" customWidth="1"/>
     <col min="6" max="6" width="8.375" customWidth="1"/>
-    <col min="7" max="7" width="18.8166666666667" customWidth="1"/>
-    <col min="8" max="8" width="14.7" customWidth="1"/>
-    <col min="9" max="9" width="16.9083333333333" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="12" max="12" width="8.375" customWidth="1"/>
-    <col min="13" max="13" width="13.3916666666667" customWidth="1"/>
-    <col min="14" max="14" width="12.875" customWidth="1"/>
-    <col min="15" max="15" width="8.93333333333333" style="9" customWidth="1"/>
-    <col min="16" max="16" width="6.375" style="9" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="19" width="6.375" customWidth="1"/>
-    <col min="20" max="20" width="37.7833333333333" customWidth="1"/>
-    <col min="21" max="21" width="66.0333333333333" customWidth="1"/>
-    <col min="22" max="22" width="17.675" customWidth="1"/>
-    <col min="23" max="23" width="16.775" customWidth="1"/>
-    <col min="24" max="24" width="12.875"/>
-    <col min="25" max="25" width="13.125" customWidth="1"/>
-    <col min="26" max="26" width="17.25" customWidth="1"/>
-    <col min="27" max="27" width="17.625" customWidth="1"/>
-    <col min="28" max="28" width="15.375" customWidth="1"/>
+    <col min="7" max="8" width="18.8166666666667" customWidth="1"/>
+    <col min="9" max="9" width="14.7" customWidth="1"/>
+    <col min="10" max="10" width="16.9083333333333" customWidth="1"/>
+    <col min="11" max="11" width="21.5" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="8.375" customWidth="1"/>
+    <col min="14" max="14" width="13.3916666666667" customWidth="1"/>
+    <col min="15" max="15" width="12.875" customWidth="1"/>
+    <col min="16" max="16" width="8.93333333333333" style="9" customWidth="1"/>
+    <col min="17" max="17" width="6.375" style="9" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="20" width="6.375" customWidth="1"/>
+    <col min="21" max="21" width="37.7833333333333" customWidth="1"/>
+    <col min="22" max="22" width="66.0333333333333" customWidth="1"/>
+    <col min="23" max="23" width="17.675" customWidth="1"/>
+    <col min="24" max="24" width="16.775" customWidth="1"/>
+    <col min="25" max="25" width="12.875"/>
+    <col min="26" max="26" width="13.125" customWidth="1"/>
+    <col min="27" max="27" width="17.25" customWidth="1"/>
+    <col min="28" max="28" width="17.625" customWidth="1"/>
+    <col min="29" max="29" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="15.75" spans="1:28">
+    <row r="1" s="3" customFormat="1" ht="15.75" spans="1:29">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1878,175 +1884,184 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="15" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="14"/>
-      <c r="T1" s="11" t="s">
+      <c r="S1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="T1" s="14"/>
+      <c r="U1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="17" t="s">
+      <c r="V1" s="16" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="X1"/>
+      <c r="X1" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="Y1"/>
       <c r="Z1"/>
-      <c r="AA1" s="18"/>
+      <c r="AA1"/>
       <c r="AB1" s="18"/>
-    </row>
-    <row r="2" s="4" customFormat="1" ht="21" customHeight="1" spans="1:28">
+      <c r="AC1" s="18"/>
+    </row>
+    <row r="2" s="4" customFormat="1" ht="21" customHeight="1" spans="1:29">
       <c r="A2" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>22</v>
+      <c r="H2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21" t="s">
-        <v>22</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="21"/>
       <c r="N2" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="22"/>
+        <v>23</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="P2" s="22"/>
-      <c r="Q2" s="21"/>
+      <c r="Q2" s="22"/>
       <c r="R2" s="21"/>
       <c r="S2" s="21"/>
-      <c r="T2" s="21" t="s">
-        <v>25</v>
-      </c>
+      <c r="T2" s="21"/>
       <c r="U2" s="21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="23"/>
-      <c r="X2"/>
+      <c r="W2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="23"/>
       <c r="Y2"/>
       <c r="Z2"/>
-    </row>
-    <row r="3" s="4" customFormat="1" ht="15.75" spans="1:28">
+      <c r="AA2"/>
+    </row>
+    <row r="3" s="4" customFormat="1" ht="15.75" spans="1:29">
       <c r="A3" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="20"/>
       <c r="G3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="H3" s="11" t="s">
         <v>33</v>
       </c>
+      <c r="I3" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="J3" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21" t="s">
+      <c r="K3" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="L3" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="24"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>39</v>
+      </c>
       <c r="P3" s="24"/>
-      <c r="Q3" s="19"/>
+      <c r="Q3" s="24"/>
       <c r="R3" s="19"/>
       <c r="S3" s="19"/>
-      <c r="T3" s="21" t="s">
-        <v>38</v>
-      </c>
+      <c r="T3" s="19"/>
       <c r="U3" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="W3" s="23"/>
-      <c r="X3"/>
+      <c r="V3" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="23"/>
       <c r="Y3"/>
       <c r="Z3"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:28">
+      <c r="AA3"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:29">
       <c r="A4" s="2"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -2057,21 +2072,22 @@
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
       <c r="J4" s="26"/>
-      <c r="K4" s="25"/>
+      <c r="K4" s="26"/>
       <c r="L4" s="25"/>
       <c r="M4" s="25"/>
       <c r="N4" s="25"/>
-      <c r="O4" s="27"/>
+      <c r="O4" s="25"/>
       <c r="P4" s="27"/>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="27"/>
       <c r="R4" s="25"/>
       <c r="S4" s="25"/>
       <c r="T4" s="25"/>
       <c r="U4" s="25"/>
-      <c r="V4" s="28"/>
+      <c r="V4" s="25"/>
       <c r="W4" s="28"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:28">
+      <c r="X4" s="28"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:29">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -2085,61 +2101,64 @@
         <v>1</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="31">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30">
+        <v>44</v>
+      </c>
+      <c r="G5" s="26">
+        <v>2025101</v>
+      </c>
+      <c r="H5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="31">
+        <v>1</v>
+      </c>
+      <c r="J5" s="30">
         <v>1001</v>
       </c>
-      <c r="J5" s="26"/>
-      <c r="K5" s="2">
+      <c r="K5" s="26"/>
+      <c r="L5" s="2">
         <v>400</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" s="32">
+      <c r="M5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="32">
         <v>100</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <f>_xlfn.XLOOKUP($D5,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O5" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M5+Q5</f>
+      <c r="P5" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N5+R5</f>
         <v>8400</v>
       </c>
-      <c r="P5" s="34">
-        <f>O5/SUM($O$5:$O$34)</f>
+      <c r="Q5" s="34">
+        <f>P5/SUM($P$5:$P$34)</f>
         <v>0.064217237741388</v>
       </c>
-      <c r="Q5" s="2">
-        <f>N5</f>
+      <c r="R5" s="2">
+        <f>O5</f>
         <v>8300</v>
       </c>
-      <c r="R5" s="35">
-        <f>Q5/SUM($Q$5:$Q$34)</f>
+      <c r="S5" s="35">
+        <f>R5/SUM($R$5:$R$34)</f>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S5" s="35"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36" t="s">
-        <v>44</v>
-      </c>
+      <c r="T5" s="35"/>
+      <c r="U5" s="36"/>
       <c r="V5" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" s="36"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:28">
+        <v>46</v>
+      </c>
+      <c r="W5" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X5" s="36"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:29">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -2153,61 +2172,64 @@
         <v>1</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="31">
-        <v>1</v>
-      </c>
-      <c r="I6" s="30">
+        <v>49</v>
+      </c>
+      <c r="G6" s="26">
+        <v>2025102</v>
+      </c>
+      <c r="H6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="31">
+        <v>1</v>
+      </c>
+      <c r="J6" s="30">
         <v>1002</v>
       </c>
-      <c r="J6" s="26"/>
-      <c r="K6" s="2">
+      <c r="K6" s="26"/>
+      <c r="L6" s="2">
         <v>400</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="32">
+      <c r="M6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="32">
         <v>100</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2">
         <f>_xlfn.XLOOKUP($D6,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O6" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M6+Q6</f>
+      <c r="P6" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N6+R6</f>
         <v>8400</v>
       </c>
-      <c r="P6" s="34">
-        <f t="shared" ref="P6:P39" si="0">O6/SUM($O$5:$O$34)</f>
+      <c r="Q6" s="34">
+        <f t="shared" ref="Q6:Q39" si="0">P6/SUM($P$5:$P$34)</f>
         <v>0.064217237741388</v>
       </c>
-      <c r="Q6" s="2">
-        <f t="shared" ref="Q6:Q34" si="1">N6</f>
+      <c r="R6" s="2">
+        <f t="shared" ref="R6:R34" si="1">O6</f>
         <v>8300</v>
       </c>
-      <c r="R6" s="35">
-        <f t="shared" ref="R6:R39" si="2">Q6/SUM($Q$5:$Q$34)</f>
+      <c r="S6" s="35">
+        <f t="shared" ref="S6:S39" si="2">R6/SUM($R$5:$R$34)</f>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S6" s="35"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36" t="s">
-        <v>48</v>
-      </c>
+      <c r="T6" s="35"/>
+      <c r="U6" s="36"/>
       <c r="V6" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" s="36"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:28">
+        <v>50</v>
+      </c>
+      <c r="W6" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X6" s="36"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:29">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
@@ -2221,61 +2243,64 @@
         <v>1</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="29" t="b">
+        <v>52</v>
+      </c>
+      <c r="G7" s="26">
+        <v>2025103</v>
+      </c>
+      <c r="H7" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="31">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
+        <v>1</v>
+      </c>
+      <c r="J7" s="30">
         <v>1003</v>
       </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="2">
+      <c r="K7" s="26"/>
+      <c r="L7" s="2">
         <v>400</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="32">
+      <c r="M7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="32">
         <v>100</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <f>_xlfn.XLOOKUP($D7,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O7" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M7+Q7</f>
+      <c r="P7" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N7+R7</f>
         <v>8400</v>
       </c>
-      <c r="P7" s="34">
+      <c r="Q7" s="34">
         <f t="shared" si="0"/>
         <v>0.064217237741388</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R7" s="35">
+      <c r="S7" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S7" s="35"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="T7" s="35"/>
+      <c r="U7" s="36"/>
       <c r="V7" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" s="36"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:28">
+        <v>54</v>
+      </c>
+      <c r="W7" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X7" s="36"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:29">
       <c r="A8" s="2">
         <v>2001</v>
       </c>
@@ -2289,61 +2314,64 @@
         <v>2</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="37" t="b">
+        <v>56</v>
+      </c>
+      <c r="G8" s="26">
+        <v>2025201</v>
+      </c>
+      <c r="H8" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="38">
-        <v>1</v>
-      </c>
-      <c r="I8" s="26">
+      <c r="I8" s="38">
+        <v>1</v>
+      </c>
+      <c r="J8" s="26">
         <v>1003</v>
       </c>
-      <c r="J8" s="26"/>
-      <c r="K8" s="2">
+      <c r="K8" s="26"/>
+      <c r="L8" s="2">
         <v>800</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="32">
+      <c r="M8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="32">
         <v>500</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <f>_xlfn.XLOOKUP($D8,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O8" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M8+Q8</f>
+      <c r="P8" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N8+R8</f>
         <v>4650</v>
       </c>
-      <c r="P8" s="34">
+      <c r="Q8" s="34">
         <f t="shared" si="0"/>
         <v>0.0355488280354112</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R8" s="35">
+      <c r="S8" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S8" s="35"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36" t="s">
-        <v>55</v>
-      </c>
+      <c r="T8" s="35"/>
+      <c r="U8" s="36"/>
       <c r="V8" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W8" s="36"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:28">
+        <v>57</v>
+      </c>
+      <c r="W8" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X8" s="36"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:29">
       <c r="A9" s="2">
         <v>2002</v>
       </c>
@@ -2357,61 +2385,64 @@
         <v>2</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="37" t="b">
+        <v>59</v>
+      </c>
+      <c r="G9" s="26">
+        <v>2025202</v>
+      </c>
+      <c r="H9" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="38">
-        <v>1</v>
-      </c>
-      <c r="I9" s="26">
+      <c r="I9" s="38">
+        <v>1</v>
+      </c>
+      <c r="J9" s="26">
         <v>1001</v>
       </c>
-      <c r="J9" s="26"/>
-      <c r="K9" s="2">
+      <c r="K9" s="26"/>
+      <c r="L9" s="2">
         <v>800</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9" s="32">
+      <c r="M9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" s="32">
         <v>500</v>
       </c>
-      <c r="N9" s="2">
+      <c r="O9" s="2">
         <f>_xlfn.XLOOKUP($D9,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O9" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M9+Q9</f>
+      <c r="P9" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N9+R9</f>
         <v>4650</v>
       </c>
-      <c r="P9" s="34">
+      <c r="Q9" s="34">
         <f t="shared" si="0"/>
         <v>0.0355488280354112</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R9" s="35">
+      <c r="S9" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S9" s="35"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36" t="s">
-        <v>58</v>
-      </c>
+      <c r="T9" s="35"/>
+      <c r="U9" s="36"/>
       <c r="V9" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W9" s="36"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:28">
+        <v>60</v>
+      </c>
+      <c r="W9" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X9" s="36"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:29">
       <c r="A10" s="2">
         <v>2003</v>
       </c>
@@ -2425,61 +2456,64 @@
         <v>2</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="37" t="b">
+        <v>62</v>
+      </c>
+      <c r="G10" s="26">
+        <v>2025203</v>
+      </c>
+      <c r="H10" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="38">
-        <v>1</v>
-      </c>
-      <c r="I10" s="26">
+      <c r="I10" s="38">
+        <v>1</v>
+      </c>
+      <c r="J10" s="26">
         <v>5001</v>
       </c>
-      <c r="J10" s="26"/>
-      <c r="K10" s="2">
+      <c r="K10" s="26"/>
+      <c r="L10" s="2">
         <v>800</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="32">
+      <c r="M10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="32">
         <v>500</v>
       </c>
-      <c r="N10" s="2">
+      <c r="O10" s="2">
         <f>_xlfn.XLOOKUP($D10,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O10" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M10+Q10</f>
+      <c r="P10" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N10+R10</f>
         <v>4650</v>
       </c>
-      <c r="P10" s="34">
+      <c r="Q10" s="34">
         <f t="shared" si="0"/>
         <v>0.0355488280354112</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10" s="2">
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R10" s="35">
+      <c r="S10" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S10" s="35"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36" t="s">
-        <v>48</v>
-      </c>
+      <c r="T10" s="35"/>
+      <c r="U10" s="36"/>
       <c r="V10" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W10" s="36"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:28">
+        <v>50</v>
+      </c>
+      <c r="W10" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X10" s="36"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:29">
       <c r="A11" s="2">
         <v>3001</v>
       </c>
@@ -2493,61 +2527,64 @@
         <v>3</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="37" t="b">
+        <v>64</v>
+      </c>
+      <c r="G11" s="26">
+        <v>2025301</v>
+      </c>
+      <c r="H11" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="38">
-        <v>1</v>
-      </c>
-      <c r="I11" s="26">
+      <c r="I11" s="38">
+        <v>1</v>
+      </c>
+      <c r="J11" s="26">
         <v>1001</v>
       </c>
-      <c r="J11" s="26"/>
-      <c r="K11" s="2">
+      <c r="K11" s="26"/>
+      <c r="L11" s="2">
         <v>1000</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="32">
+      <c r="M11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" s="32">
         <v>1400</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <f>_xlfn.XLOOKUP($D11,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O11" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M11+Q11</f>
+      <c r="P11" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N11+R11</f>
         <v>3060</v>
       </c>
-      <c r="P11" s="34">
+      <c r="Q11" s="34">
         <f t="shared" si="0"/>
         <v>0.0233934223200771</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R11" s="35">
+      <c r="S11" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S11" s="35"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36" t="s">
-        <v>44</v>
-      </c>
+      <c r="T11" s="35"/>
+      <c r="U11" s="36"/>
       <c r="V11" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W11" s="36"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:28">
+        <v>46</v>
+      </c>
+      <c r="W11" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X11" s="36"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:29">
       <c r="A12" s="2">
         <v>3002</v>
       </c>
@@ -2561,61 +2598,64 @@
         <v>3</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="37" t="b">
+        <v>66</v>
+      </c>
+      <c r="G12" s="26">
+        <v>2025302</v>
+      </c>
+      <c r="H12" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="38">
-        <v>1</v>
-      </c>
-      <c r="I12" s="26">
+      <c r="I12" s="38">
+        <v>1</v>
+      </c>
+      <c r="J12" s="26">
         <v>1002</v>
       </c>
-      <c r="J12" s="26"/>
-      <c r="K12" s="2">
+      <c r="K12" s="26"/>
+      <c r="L12" s="2">
         <v>1000</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="32">
+      <c r="M12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="32">
         <v>1400</v>
       </c>
-      <c r="N12" s="2">
+      <c r="O12" s="2">
         <f>_xlfn.XLOOKUP($D12,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O12" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M12+Q12</f>
+      <c r="P12" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N12+R12</f>
         <v>3060</v>
       </c>
-      <c r="P12" s="34">
+      <c r="Q12" s="34">
         <f t="shared" si="0"/>
         <v>0.0233934223200771</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12" s="2">
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R12" s="35">
+      <c r="S12" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S12" s="35"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36" t="s">
-        <v>58</v>
-      </c>
+      <c r="T12" s="35"/>
+      <c r="U12" s="36"/>
       <c r="V12" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W12" s="36"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:28">
+        <v>60</v>
+      </c>
+      <c r="W12" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X12" s="36"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:29">
       <c r="A13" s="2">
         <v>3003</v>
       </c>
@@ -2629,61 +2669,64 @@
         <v>3</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="37" t="b">
+        <v>68</v>
+      </c>
+      <c r="G13" s="26">
+        <v>2025303</v>
+      </c>
+      <c r="H13" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="38">
-        <v>1</v>
-      </c>
-      <c r="I13" s="26">
+      <c r="I13" s="38">
+        <v>1</v>
+      </c>
+      <c r="J13" s="26">
         <v>5001</v>
       </c>
-      <c r="J13" s="26"/>
-      <c r="K13" s="2">
+      <c r="K13" s="26"/>
+      <c r="L13" s="2">
         <v>1000</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="32">
+      <c r="M13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="32">
         <v>1400</v>
       </c>
-      <c r="N13" s="2">
+      <c r="O13" s="2">
         <f>_xlfn.XLOOKUP($D13,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O13" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M13+Q13</f>
+      <c r="P13" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N13+R13</f>
         <v>3060</v>
       </c>
-      <c r="P13" s="34">
+      <c r="Q13" s="34">
         <f t="shared" si="0"/>
         <v>0.0233934223200771</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="R13" s="2">
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R13" s="35">
+      <c r="S13" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S13" s="35"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36" t="s">
-        <v>48</v>
-      </c>
+      <c r="T13" s="35"/>
+      <c r="U13" s="36"/>
       <c r="V13" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W13" s="36"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:28">
+        <v>50</v>
+      </c>
+      <c r="W13" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X13" s="36"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:29">
       <c r="A14" s="2">
         <v>4001</v>
       </c>
@@ -2697,61 +2740,64 @@
         <v>4</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="37" t="b">
+        <v>70</v>
+      </c>
+      <c r="G14" s="26">
+        <v>2025401</v>
+      </c>
+      <c r="H14" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="38">
-        <v>1</v>
-      </c>
-      <c r="I14" s="26">
+      <c r="I14" s="38">
+        <v>1</v>
+      </c>
+      <c r="J14" s="26">
         <v>5001</v>
       </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="2">
+      <c r="K14" s="26"/>
+      <c r="L14" s="2">
         <v>1400</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" s="32">
+      <c r="M14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N14" s="32">
         <v>2000</v>
       </c>
-      <c r="N14" s="2">
+      <c r="O14" s="2">
         <f>_xlfn.XLOOKUP($D14,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O14" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M14+Q14</f>
+      <c r="P14" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N14+R14</f>
         <v>2553</v>
       </c>
-      <c r="P14" s="34">
+      <c r="Q14" s="34">
         <f t="shared" si="0"/>
         <v>0.019517453327829</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="R14" s="2">
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R14" s="35">
+      <c r="S14" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S14" s="35"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36" t="s">
-        <v>55</v>
-      </c>
+      <c r="T14" s="35"/>
+      <c r="U14" s="36"/>
       <c r="V14" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W14" s="36"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:28">
+        <v>57</v>
+      </c>
+      <c r="W14" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X14" s="36"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:29">
       <c r="A15" s="2">
         <v>4002</v>
       </c>
@@ -2765,61 +2811,64 @@
         <v>4</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" s="37" t="b">
+        <v>72</v>
+      </c>
+      <c r="G15" s="26">
+        <v>2025402</v>
+      </c>
+      <c r="H15" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H15" s="38">
-        <v>1</v>
-      </c>
-      <c r="I15" s="26">
+      <c r="I15" s="38">
+        <v>1</v>
+      </c>
+      <c r="J15" s="26">
         <v>1001</v>
       </c>
-      <c r="J15" s="26"/>
-      <c r="K15" s="2">
+      <c r="K15" s="26"/>
+      <c r="L15" s="2">
         <v>1400</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M15" s="32">
+      <c r="M15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N15" s="32">
         <v>2000</v>
       </c>
-      <c r="N15" s="2">
+      <c r="O15" s="2">
         <f>_xlfn.XLOOKUP($D15,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O15" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M15+Q15</f>
+      <c r="P15" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N15+R15</f>
         <v>2553</v>
       </c>
-      <c r="P15" s="34">
+      <c r="Q15" s="34">
         <f t="shared" si="0"/>
         <v>0.019517453327829</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="R15" s="2">
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R15" s="35">
+      <c r="S15" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S15" s="35"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="T15" s="35"/>
+      <c r="U15" s="36"/>
       <c r="V15" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W15" s="36"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:28">
+        <v>54</v>
+      </c>
+      <c r="W15" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X15" s="36"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:29">
       <c r="A16" s="2">
         <v>4003</v>
       </c>
@@ -2833,61 +2882,64 @@
         <v>4</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="37" t="b">
+        <v>74</v>
+      </c>
+      <c r="G16" s="26">
+        <v>2025403</v>
+      </c>
+      <c r="H16" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="38">
-        <v>1</v>
-      </c>
-      <c r="I16" s="26">
+      <c r="I16" s="38">
+        <v>1</v>
+      </c>
+      <c r="J16" s="26">
         <v>1002</v>
       </c>
-      <c r="J16" s="26"/>
-      <c r="K16" s="2">
+      <c r="K16" s="26"/>
+      <c r="L16" s="2">
         <v>1400</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" s="32">
+      <c r="M16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="32">
         <v>2000</v>
       </c>
-      <c r="N16" s="2">
+      <c r="O16" s="2">
         <f>_xlfn.XLOOKUP($D16,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O16" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M16+Q16</f>
+      <c r="P16" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N16+R16</f>
         <v>2553</v>
       </c>
-      <c r="P16" s="34">
+      <c r="Q16" s="34">
         <f t="shared" si="0"/>
         <v>0.019517453327829</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="R16" s="2">
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R16" s="35">
+      <c r="S16" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S16" s="35"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36" t="s">
-        <v>44</v>
-      </c>
+      <c r="T16" s="35"/>
+      <c r="U16" s="36"/>
       <c r="V16" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W16" s="36"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:23">
+        <v>46</v>
+      </c>
+      <c r="W16" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X16" s="36"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:24">
       <c r="A17" s="1">
         <v>5001</v>
       </c>
@@ -2901,61 +2953,64 @@
         <v>5</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="29" t="b">
+        <v>76</v>
+      </c>
+      <c r="G17" s="26">
+        <v>2025501</v>
+      </c>
+      <c r="H17" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="31">
-        <v>1</v>
-      </c>
-      <c r="I17" s="30">
+      <c r="I17" s="31">
+        <v>1</v>
+      </c>
+      <c r="J17" s="30">
         <v>5001</v>
       </c>
-      <c r="J17" s="26"/>
-      <c r="K17" s="2">
+      <c r="K17" s="26"/>
+      <c r="L17" s="2">
         <v>2000</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M17" s="32">
+      <c r="M17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17" s="32">
         <v>3000</v>
       </c>
-      <c r="N17" s="2">
+      <c r="O17" s="2">
         <f>_xlfn.XLOOKUP($D17,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O17" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M17+Q17</f>
+      <c r="P17" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N17+R17</f>
         <v>3138</v>
       </c>
-      <c r="P17" s="34">
+      <c r="Q17" s="34">
         <f t="shared" si="0"/>
         <v>0.0239897252419614</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="R17" s="2">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R17" s="35">
+      <c r="S17" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S17" s="35"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36" t="s">
-        <v>55</v>
-      </c>
+      <c r="T17" s="35"/>
+      <c r="U17" s="36"/>
       <c r="V17" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W17" s="36"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:23">
+        <v>57</v>
+      </c>
+      <c r="W17" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X17" s="36"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:24">
       <c r="A18" s="2">
         <v>5002</v>
       </c>
@@ -2969,61 +3024,64 @@
         <v>5</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="37" t="b">
+        <v>78</v>
+      </c>
+      <c r="G18" s="26">
+        <v>2025502</v>
+      </c>
+      <c r="H18" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="38">
-        <v>1</v>
-      </c>
-      <c r="I18" s="26">
+      <c r="I18" s="38">
+        <v>1</v>
+      </c>
+      <c r="J18" s="26">
         <v>1002</v>
       </c>
-      <c r="J18" s="26"/>
-      <c r="K18" s="2">
+      <c r="K18" s="26"/>
+      <c r="L18" s="2">
         <v>2000</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M18" s="32">
+      <c r="M18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N18" s="32">
         <v>3000</v>
       </c>
-      <c r="N18" s="2">
+      <c r="O18" s="2">
         <f>_xlfn.XLOOKUP($D18,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O18" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M18+Q18</f>
+      <c r="P18" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N18+R18</f>
         <v>3138</v>
       </c>
-      <c r="P18" s="34">
+      <c r="Q18" s="34">
         <f t="shared" si="0"/>
         <v>0.0239897252419614</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R18" s="35">
+      <c r="S18" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S18" s="35"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="T18" s="35"/>
+      <c r="U18" s="36"/>
       <c r="V18" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W18" s="36"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:23">
+        <v>54</v>
+      </c>
+      <c r="W18" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X18" s="36"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:24">
       <c r="A19" s="2">
         <v>5003</v>
       </c>
@@ -3037,61 +3095,64 @@
         <v>5</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="37" t="b">
+        <v>80</v>
+      </c>
+      <c r="G19" s="26">
+        <v>2025503</v>
+      </c>
+      <c r="H19" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="38">
-        <v>1</v>
-      </c>
-      <c r="I19" s="26">
+      <c r="I19" s="38">
+        <v>1</v>
+      </c>
+      <c r="J19" s="26">
         <v>1001</v>
       </c>
-      <c r="J19" s="26"/>
-      <c r="K19" s="2">
+      <c r="K19" s="26"/>
+      <c r="L19" s="2">
         <v>2000</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M19" s="32">
+      <c r="M19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="32">
         <v>3000</v>
       </c>
-      <c r="N19" s="2">
+      <c r="O19" s="2">
         <f>_xlfn.XLOOKUP($D19,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O19" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M19+Q19</f>
+      <c r="P19" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N19+R19</f>
         <v>3138</v>
       </c>
-      <c r="P19" s="34">
+      <c r="Q19" s="34">
         <f t="shared" si="0"/>
         <v>0.0239897252419614</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="R19" s="2">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R19" s="35">
+      <c r="S19" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S19" s="35"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36" t="s">
-        <v>48</v>
-      </c>
+      <c r="T19" s="35"/>
+      <c r="U19" s="36"/>
       <c r="V19" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W19" s="36"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:23">
+        <v>50</v>
+      </c>
+      <c r="W19" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X19" s="36"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:24">
       <c r="A20" s="1">
         <v>1004</v>
       </c>
@@ -3105,61 +3166,64 @@
         <v>1</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="29" t="b">
+        <v>82</v>
+      </c>
+      <c r="G20" s="26">
+        <v>2025104</v>
+      </c>
+      <c r="H20" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="31">
-        <v>1</v>
-      </c>
-      <c r="I20" s="30">
+      <c r="I20" s="31">
+        <v>1</v>
+      </c>
+      <c r="J20" s="30">
         <v>1004</v>
       </c>
-      <c r="J20" s="26"/>
-      <c r="K20" s="2">
+      <c r="K20" s="26"/>
+      <c r="L20" s="2">
         <v>400</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M20" s="32">
+      <c r="M20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N20" s="32">
         <v>100</v>
       </c>
-      <c r="N20" s="2">
+      <c r="O20" s="2">
         <f>_xlfn.XLOOKUP($D20,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O20" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M20+Q20</f>
+      <c r="P20" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N20+R20</f>
         <v>8400</v>
       </c>
-      <c r="P20" s="34">
+      <c r="Q20" s="34">
         <f t="shared" si="0"/>
         <v>0.064217237741388</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="R20" s="2">
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R20" s="35">
+      <c r="S20" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S20" s="35"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36" t="s">
-        <v>55</v>
-      </c>
+      <c r="T20" s="35"/>
+      <c r="U20" s="36"/>
       <c r="V20" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W20" s="36"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:23">
+        <v>57</v>
+      </c>
+      <c r="W20" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X20" s="36"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:24">
       <c r="A21" s="1">
         <v>1005</v>
       </c>
@@ -3173,61 +3237,64 @@
         <v>1</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="29" t="b">
+        <v>84</v>
+      </c>
+      <c r="G21" s="26">
+        <v>2025105</v>
+      </c>
+      <c r="H21" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="31">
-        <v>1</v>
-      </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
+        <v>1</v>
+      </c>
+      <c r="J21" s="30">
         <v>1005</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="2">
+      <c r="K21" s="26"/>
+      <c r="L21" s="2">
         <v>400</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M21" s="32">
+      <c r="M21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N21" s="32">
         <v>100</v>
       </c>
-      <c r="N21" s="2">
+      <c r="O21" s="2">
         <f>_xlfn.XLOOKUP($D21,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O21" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M21+Q21</f>
+      <c r="P21" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N21+R21</f>
         <v>8400</v>
       </c>
-      <c r="P21" s="34">
+      <c r="Q21" s="34">
         <f t="shared" si="0"/>
         <v>0.064217237741388</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21" s="2">
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R21" s="35">
+      <c r="S21" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S21" s="35"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="T21" s="35"/>
+      <c r="U21" s="36"/>
       <c r="V21" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W21" s="36"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:23">
+        <v>54</v>
+      </c>
+      <c r="W21" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X21" s="36"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:24">
       <c r="A22" s="2">
         <v>1006</v>
       </c>
@@ -3241,61 +3308,64 @@
         <v>1</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="37" t="b">
+        <v>86</v>
+      </c>
+      <c r="G22" s="26">
+        <v>2025106</v>
+      </c>
+      <c r="H22" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H22" s="38">
-        <v>1</v>
-      </c>
-      <c r="I22" s="26">
+      <c r="I22" s="38">
+        <v>1</v>
+      </c>
+      <c r="J22" s="26">
         <v>1002</v>
       </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="2">
+      <c r="K22" s="26"/>
+      <c r="L22" s="2">
         <v>400</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M22" s="32">
+      <c r="M22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" s="32">
         <v>100</v>
       </c>
-      <c r="N22" s="2">
+      <c r="O22" s="2">
         <f>_xlfn.XLOOKUP($D22,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>8300</v>
       </c>
-      <c r="O22" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M22+Q22</f>
+      <c r="P22" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N22+R22</f>
         <v>8400</v>
       </c>
-      <c r="P22" s="34">
+      <c r="Q22" s="34">
         <f t="shared" si="0"/>
         <v>0.064217237741388</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="R22" s="2">
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
-      <c r="R22" s="35">
+      <c r="S22" s="35">
         <f t="shared" si="2"/>
         <v>0.0934621534580997</v>
       </c>
-      <c r="S22" s="35"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="36" t="s">
-        <v>85</v>
-      </c>
+      <c r="T22" s="35"/>
+      <c r="U22" s="36"/>
       <c r="V22" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W22" s="36"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:23">
+        <v>87</v>
+      </c>
+      <c r="W22" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X22" s="36"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:24">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -3309,61 +3379,64 @@
         <v>2</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="37" t="b">
+        <v>89</v>
+      </c>
+      <c r="G23" s="26">
+        <v>2025204</v>
+      </c>
+      <c r="H23" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H23" s="38">
-        <v>1</v>
-      </c>
-      <c r="I23" s="26">
+      <c r="I23" s="38">
+        <v>1</v>
+      </c>
+      <c r="J23" s="26">
         <v>5006</v>
       </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="2">
+      <c r="K23" s="26"/>
+      <c r="L23" s="2">
         <v>800</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M23" s="32">
+      <c r="M23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N23" s="32">
         <v>500</v>
       </c>
-      <c r="N23" s="2">
+      <c r="O23" s="2">
         <f>_xlfn.XLOOKUP($D23,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O23" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M23+Q23</f>
+      <c r="P23" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N23+R23</f>
         <v>4650</v>
       </c>
-      <c r="P23" s="34">
+      <c r="Q23" s="34">
         <f t="shared" si="0"/>
         <v>0.0355488280354112</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="R23" s="2">
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R23" s="35">
+      <c r="S23" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S23" s="35"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="36" t="s">
-        <v>58</v>
-      </c>
+      <c r="T23" s="35"/>
+      <c r="U23" s="36"/>
       <c r="V23" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W23" s="36"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:23">
+        <v>60</v>
+      </c>
+      <c r="W23" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X23" s="36"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:24">
       <c r="A24" s="2">
         <v>2005</v>
       </c>
@@ -3377,61 +3450,64 @@
         <v>2</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="37" t="b">
+        <v>91</v>
+      </c>
+      <c r="G24" s="26">
+        <v>2025205</v>
+      </c>
+      <c r="H24" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="38">
-        <v>1</v>
-      </c>
-      <c r="I24" s="26">
+      <c r="I24" s="38">
+        <v>1</v>
+      </c>
+      <c r="J24" s="26">
         <v>1004</v>
       </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="2">
+      <c r="K24" s="26"/>
+      <c r="L24" s="2">
         <v>800</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M24" s="32">
+      <c r="M24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N24" s="32">
         <v>500</v>
       </c>
-      <c r="N24" s="2">
+      <c r="O24" s="2">
         <f>_xlfn.XLOOKUP($D24,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O24" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M24+Q24</f>
+      <c r="P24" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N24+R24</f>
         <v>4650</v>
       </c>
-      <c r="P24" s="34">
+      <c r="Q24" s="34">
         <f t="shared" si="0"/>
         <v>0.0355488280354112</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="R24" s="2">
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R24" s="35">
+      <c r="S24" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S24" s="35"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="36" t="s">
-        <v>58</v>
-      </c>
+      <c r="T24" s="35"/>
+      <c r="U24" s="36"/>
       <c r="V24" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W24" s="36"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:23">
+        <v>60</v>
+      </c>
+      <c r="W24" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X24" s="36"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:24">
       <c r="A25" s="2">
         <v>2006</v>
       </c>
@@ -3445,61 +3521,64 @@
         <v>2</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25" s="37" t="b">
+        <v>93</v>
+      </c>
+      <c r="G25" s="26">
+        <v>2025206</v>
+      </c>
+      <c r="H25" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H25" s="38">
-        <v>1</v>
-      </c>
-      <c r="I25" s="26">
+      <c r="I25" s="38">
+        <v>1</v>
+      </c>
+      <c r="J25" s="26">
         <v>1005</v>
       </c>
-      <c r="J25" s="26"/>
-      <c r="K25" s="2">
+      <c r="K25" s="26"/>
+      <c r="L25" s="2">
         <v>800</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M25" s="32">
+      <c r="M25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="32">
         <v>500</v>
       </c>
-      <c r="N25" s="2">
+      <c r="O25" s="2">
         <f>_xlfn.XLOOKUP($D25,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>4150</v>
       </c>
-      <c r="O25" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M25+Q25</f>
+      <c r="P25" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N25+R25</f>
         <v>4650</v>
       </c>
-      <c r="P25" s="34">
+      <c r="Q25" s="34">
         <f t="shared" si="0"/>
         <v>0.0355488280354112</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="R25" s="2">
         <f t="shared" si="1"/>
         <v>4150</v>
       </c>
-      <c r="R25" s="35">
+      <c r="S25" s="35">
         <f t="shared" si="2"/>
         <v>0.0467310767290498</v>
       </c>
-      <c r="S25" s="35"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36" t="s">
-        <v>44</v>
-      </c>
+      <c r="T25" s="35"/>
+      <c r="U25" s="36"/>
       <c r="V25" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W25" s="36"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:23">
+        <v>46</v>
+      </c>
+      <c r="W25" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X25" s="36"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:24">
       <c r="A26" s="2">
         <v>3004</v>
       </c>
@@ -3513,61 +3592,64 @@
         <v>3</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="37" t="b">
+        <v>95</v>
+      </c>
+      <c r="G26" s="26">
+        <v>2025304</v>
+      </c>
+      <c r="H26" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="38">
-        <v>1</v>
-      </c>
-      <c r="I26" s="26">
+      <c r="I26" s="38">
+        <v>1</v>
+      </c>
+      <c r="J26" s="26">
         <v>1004</v>
       </c>
-      <c r="J26" s="26"/>
-      <c r="K26" s="2">
+      <c r="K26" s="26"/>
+      <c r="L26" s="2">
         <v>1000</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M26" s="32">
+      <c r="M26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N26" s="32">
         <v>1400</v>
       </c>
-      <c r="N26" s="2">
+      <c r="O26" s="2">
         <f>_xlfn.XLOOKUP($D26,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O26" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M26+Q26</f>
+      <c r="P26" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N26+R26</f>
         <v>3060</v>
       </c>
-      <c r="P26" s="34">
+      <c r="Q26" s="34">
         <f t="shared" si="0"/>
         <v>0.0233934223200771</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="R26" s="2">
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R26" s="35">
+      <c r="S26" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S26" s="35"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="T26" s="35"/>
+      <c r="U26" s="36"/>
       <c r="V26" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W26" s="36"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:23">
+        <v>54</v>
+      </c>
+      <c r="W26" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X26" s="36"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:24">
       <c r="A27" s="2">
         <v>3005</v>
       </c>
@@ -3581,61 +3663,64 @@
         <v>3</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="37" t="b">
+        <v>97</v>
+      </c>
+      <c r="G27" s="26">
+        <v>2025305</v>
+      </c>
+      <c r="H27" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H27" s="38">
-        <v>1</v>
-      </c>
-      <c r="I27" s="26">
+      <c r="I27" s="38">
+        <v>1</v>
+      </c>
+      <c r="J27" s="26">
         <v>1005</v>
       </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="2">
+      <c r="K27" s="26"/>
+      <c r="L27" s="2">
         <v>1000</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M27" s="32">
+      <c r="M27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N27" s="32">
         <v>1400</v>
       </c>
-      <c r="N27" s="2">
+      <c r="O27" s="2">
         <f>_xlfn.XLOOKUP($D27,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O27" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M27+Q27</f>
+      <c r="P27" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N27+R27</f>
         <v>3060</v>
       </c>
-      <c r="P27" s="34">
+      <c r="Q27" s="34">
         <f t="shared" si="0"/>
         <v>0.0233934223200771</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="R27" s="2">
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R27" s="35">
+      <c r="S27" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S27" s="35"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36" t="s">
-        <v>55</v>
-      </c>
+      <c r="T27" s="35"/>
+      <c r="U27" s="36"/>
       <c r="V27" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W27" s="36"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:23">
+        <v>57</v>
+      </c>
+      <c r="W27" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X27" s="36"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:24">
       <c r="A28" s="2">
         <v>3006</v>
       </c>
@@ -3649,61 +3734,64 @@
         <v>3</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="37" t="b">
+        <v>99</v>
+      </c>
+      <c r="G28" s="26">
+        <v>2025306</v>
+      </c>
+      <c r="H28" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H28" s="38">
-        <v>1</v>
-      </c>
-      <c r="I28" s="26">
+      <c r="I28" s="38">
+        <v>1</v>
+      </c>
+      <c r="J28" s="26">
         <v>5006</v>
       </c>
-      <c r="J28" s="26"/>
-      <c r="K28" s="2">
+      <c r="K28" s="26"/>
+      <c r="L28" s="2">
         <v>1000</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M28" s="32">
+      <c r="M28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N28" s="32">
         <v>1400</v>
       </c>
-      <c r="N28" s="2">
+      <c r="O28" s="2">
         <f>_xlfn.XLOOKUP($D28,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>1660</v>
       </c>
-      <c r="O28" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M28+Q28</f>
+      <c r="P28" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N28+R28</f>
         <v>3060</v>
       </c>
-      <c r="P28" s="34">
+      <c r="Q28" s="34">
         <f t="shared" si="0"/>
         <v>0.0233934223200771</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="R28" s="2">
         <f t="shared" si="1"/>
         <v>1660</v>
       </c>
-      <c r="R28" s="35">
+      <c r="S28" s="35">
         <f t="shared" si="2"/>
         <v>0.0186924306916199</v>
       </c>
-      <c r="S28" s="35"/>
-      <c r="T28" s="36"/>
-      <c r="U28" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="T28" s="35"/>
+      <c r="U28" s="36"/>
       <c r="V28" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W28" s="36"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:23">
+        <v>54</v>
+      </c>
+      <c r="W28" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X28" s="36"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:24">
       <c r="A29" s="2">
         <v>4004</v>
       </c>
@@ -3717,61 +3805,64 @@
         <v>4</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" s="37" t="b">
+        <v>101</v>
+      </c>
+      <c r="G29" s="26">
+        <v>2025404</v>
+      </c>
+      <c r="H29" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H29" s="38">
-        <v>1</v>
-      </c>
-      <c r="I29" s="26">
+      <c r="I29" s="38">
+        <v>1</v>
+      </c>
+      <c r="J29" s="26">
         <v>5006</v>
       </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="2">
+      <c r="K29" s="26"/>
+      <c r="L29" s="2">
         <v>1400</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M29" s="32">
+      <c r="M29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N29" s="32">
         <v>2000</v>
       </c>
-      <c r="N29" s="2">
+      <c r="O29" s="2">
         <f>_xlfn.XLOOKUP($D29,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O29" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M29+Q29</f>
+      <c r="P29" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N29+R29</f>
         <v>2553</v>
       </c>
-      <c r="P29" s="34">
+      <c r="Q29" s="34">
         <f t="shared" si="0"/>
         <v>0.019517453327829</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="R29" s="2">
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R29" s="35">
+      <c r="S29" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S29" s="35"/>
-      <c r="T29" s="36"/>
-      <c r="U29" s="36" t="s">
-        <v>58</v>
-      </c>
+      <c r="T29" s="35"/>
+      <c r="U29" s="36"/>
       <c r="V29" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W29" s="36"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:23">
+        <v>60</v>
+      </c>
+      <c r="W29" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X29" s="36"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:24">
       <c r="A30" s="2">
         <v>4005</v>
       </c>
@@ -3785,61 +3876,64 @@
         <v>4</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G30" s="37" t="b">
+        <v>103</v>
+      </c>
+      <c r="G30" s="26">
+        <v>2025405</v>
+      </c>
+      <c r="H30" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="38">
-        <v>1</v>
-      </c>
-      <c r="I30" s="26">
+      <c r="I30" s="38">
+        <v>1</v>
+      </c>
+      <c r="J30" s="26">
         <v>1005</v>
       </c>
-      <c r="J30" s="26"/>
-      <c r="K30" s="2">
+      <c r="K30" s="26"/>
+      <c r="L30" s="2">
         <v>1400</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M30" s="32">
+      <c r="M30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N30" s="32">
         <v>2000</v>
       </c>
-      <c r="N30" s="2">
+      <c r="O30" s="2">
         <f>_xlfn.XLOOKUP($D30,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O30" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M30+Q30</f>
+      <c r="P30" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N30+R30</f>
         <v>2553</v>
       </c>
-      <c r="P30" s="34">
+      <c r="Q30" s="34">
         <f t="shared" si="0"/>
         <v>0.019517453327829</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="R30" s="2">
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R30" s="35">
+      <c r="S30" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S30" s="35"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="36" t="s">
-        <v>102</v>
-      </c>
+      <c r="T30" s="35"/>
+      <c r="U30" s="36"/>
       <c r="V30" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W30" s="36"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:23">
+        <v>104</v>
+      </c>
+      <c r="W30" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X30" s="36"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:24">
       <c r="A31" s="2">
         <v>4006</v>
       </c>
@@ -3853,61 +3947,64 @@
         <v>4</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G31" s="37" t="b">
+        <v>106</v>
+      </c>
+      <c r="G31" s="26">
+        <v>2025406</v>
+      </c>
+      <c r="H31" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="38">
-        <v>1</v>
-      </c>
-      <c r="I31" s="26">
+      <c r="I31" s="38">
+        <v>1</v>
+      </c>
+      <c r="J31" s="26">
         <v>1004</v>
       </c>
-      <c r="J31" s="26"/>
-      <c r="K31" s="2">
+      <c r="K31" s="26"/>
+      <c r="L31" s="2">
         <v>1400</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M31" s="32">
+      <c r="M31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="32">
         <v>2000</v>
       </c>
-      <c r="N31" s="2">
+      <c r="O31" s="2">
         <f>_xlfn.XLOOKUP($D31,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>553</v>
       </c>
-      <c r="O31" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M31+Q31</f>
+      <c r="P31" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N31+R31</f>
         <v>2553</v>
       </c>
-      <c r="P31" s="34">
+      <c r="Q31" s="34">
         <f t="shared" si="0"/>
         <v>0.019517453327829</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="R31" s="2">
         <f t="shared" si="1"/>
         <v>553</v>
       </c>
-      <c r="R31" s="35">
+      <c r="S31" s="35">
         <f t="shared" si="2"/>
         <v>0.0062270567304011</v>
       </c>
-      <c r="S31" s="35"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="36" t="s">
-        <v>102</v>
-      </c>
+      <c r="T31" s="35"/>
+      <c r="U31" s="36"/>
       <c r="V31" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W31" s="36"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:23">
+        <v>104</v>
+      </c>
+      <c r="W31" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X31" s="36"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:24">
       <c r="A32" s="2">
         <v>5004</v>
       </c>
@@ -3921,61 +4018,64 @@
         <v>5</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="G32" s="37" t="b">
+        <v>108</v>
+      </c>
+      <c r="G32" s="26">
+        <v>2025504</v>
+      </c>
+      <c r="H32" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H32" s="38">
-        <v>1</v>
-      </c>
-      <c r="I32" s="26">
+      <c r="I32" s="38">
+        <v>1</v>
+      </c>
+      <c r="J32" s="26">
         <v>1005</v>
       </c>
-      <c r="J32" s="26"/>
-      <c r="K32" s="2">
+      <c r="K32" s="26"/>
+      <c r="L32" s="2">
         <v>2000</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M32" s="32">
+      <c r="M32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N32" s="32">
         <v>3000</v>
       </c>
-      <c r="N32" s="2">
+      <c r="O32" s="2">
         <f>_xlfn.XLOOKUP($D32,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O32" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M32+Q32</f>
+      <c r="P32" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N32+R32</f>
         <v>3138</v>
       </c>
-      <c r="P32" s="34">
+      <c r="Q32" s="34">
         <f t="shared" si="0"/>
         <v>0.0239897252419614</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="R32" s="2">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R32" s="35">
+      <c r="S32" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S32" s="35"/>
-      <c r="T32" s="36"/>
-      <c r="U32" s="36" t="s">
-        <v>55</v>
-      </c>
+      <c r="T32" s="35"/>
+      <c r="U32" s="36"/>
       <c r="V32" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W32" s="36"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:23">
+        <v>57</v>
+      </c>
+      <c r="W32" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X32" s="36"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:24">
       <c r="A33" s="2">
         <v>5005</v>
       </c>
@@ -3989,61 +4089,64 @@
         <v>5</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="G33" s="37" t="b">
+        <v>110</v>
+      </c>
+      <c r="G33" s="26">
+        <v>2025505</v>
+      </c>
+      <c r="H33" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="H33" s="38">
-        <v>1</v>
-      </c>
-      <c r="I33" s="26">
+      <c r="I33" s="38">
+        <v>1</v>
+      </c>
+      <c r="J33" s="26">
         <v>1004</v>
       </c>
-      <c r="J33" s="26"/>
-      <c r="K33" s="2">
+      <c r="K33" s="26"/>
+      <c r="L33" s="2">
         <v>2000</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M33" s="32">
+      <c r="M33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N33" s="32">
         <v>3000</v>
       </c>
-      <c r="N33" s="2">
+      <c r="O33" s="2">
         <f>_xlfn.XLOOKUP($D33,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O33" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M33+Q33</f>
+      <c r="P33" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N33+R33</f>
         <v>3138</v>
       </c>
-      <c r="P33" s="34">
+      <c r="Q33" s="34">
         <f t="shared" si="0"/>
         <v>0.0239897252419614</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33" s="2">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R33" s="35">
+      <c r="S33" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S33" s="35"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="T33" s="35"/>
+      <c r="U33" s="36"/>
       <c r="V33" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W33" s="36"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:23">
+        <v>54</v>
+      </c>
+      <c r="W33" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X33" s="36"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:24">
       <c r="A34" s="1">
         <v>5006</v>
       </c>
@@ -4057,166 +4160,145 @@
         <v>5</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="G34" s="29" t="b">
+        <v>112</v>
+      </c>
+      <c r="G34" s="26">
+        <v>2025506</v>
+      </c>
+      <c r="H34" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="H34" s="31">
-        <v>1</v>
-      </c>
-      <c r="I34" s="30">
+      <c r="I34" s="31">
+        <v>1</v>
+      </c>
+      <c r="J34" s="30">
         <v>5006</v>
       </c>
-      <c r="J34" s="26"/>
-      <c r="K34" s="2">
+      <c r="K34" s="26"/>
+      <c r="L34" s="2">
         <v>2000</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M34" s="32">
+      <c r="M34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N34" s="32">
         <v>3000</v>
       </c>
-      <c r="N34" s="2">
+      <c r="O34" s="2">
         <f>_xlfn.XLOOKUP($D34,Sheet1!$A$2:$A$6,Sheet1!$C$2:$C$6,,0)</f>
         <v>138</v>
       </c>
-      <c r="O34" s="33">
-        <f>Sheet1!$A$9/Sheet1!$C$9*M34+Q34</f>
+      <c r="P34" s="33">
+        <f>Sheet1!$A$9/Sheet1!$C$9*N34+R34</f>
         <v>3138</v>
       </c>
-      <c r="P34" s="34">
+      <c r="Q34" s="34">
         <f t="shared" si="0"/>
         <v>0.0239897252419614</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="R34" s="2">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="R34" s="35">
+      <c r="S34" s="35">
         <f t="shared" si="2"/>
         <v>0.00155394905749612</v>
       </c>
-      <c r="S34" s="35"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36" t="s">
-        <v>102</v>
-      </c>
+      <c r="T34" s="35"/>
+      <c r="U34" s="36"/>
       <c r="V34" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="W34" s="36"/>
-    </row>
-    <row r="35" spans="1:23">
-      <c r="K35" s="39"/>
+        <v>104</v>
+      </c>
+      <c r="W34" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="X34" s="36"/>
+    </row>
+    <row r="35" spans="1:24">
       <c r="L35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="M35" s="39"/>
+      <c r="Q35" s="40"/>
       <c r="S35" s="41"/>
-    </row>
-    <row r="36" spans="1:23">
-      <c r="K36" s="39"/>
+      <c r="T35" s="41"/>
+    </row>
+    <row r="36" spans="1:24">
       <c r="L36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="M36" s="39"/>
+      <c r="Q36" s="40"/>
       <c r="S36" s="41"/>
-    </row>
-    <row r="37" spans="1:23">
-      <c r="K37" s="39"/>
+      <c r="T36" s="41"/>
+    </row>
+    <row r="37" spans="1:24">
       <c r="L37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="M37" s="39"/>
+      <c r="Q37" s="40"/>
       <c r="S37" s="41"/>
-    </row>
-    <row r="38" spans="1:23">
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="T37" s="41"/>
+    </row>
+    <row r="38" spans="1:24">
+      <c r="Q38" s="40"/>
       <c r="S38" s="41"/>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="T38" s="41"/>
+    </row>
+    <row r="39" spans="1:24">
+      <c r="Q39" s="40"/>
       <c r="S39" s="41"/>
-    </row>
-    <row r="40" spans="1:23">
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-    </row>
-    <row r="41" ht="15" spans="1:23">
-      <c r="K41" s="14"/>
-      <c r="L41" s="39"/>
-    </row>
-    <row r="42" spans="1:23">
-      <c r="K42" s="39"/>
-      <c r="L42" s="39"/>
-    </row>
-    <row r="43" spans="1:23">
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-    </row>
-    <row r="44" spans="1:23">
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="K45" s="39"/>
+      <c r="T39" s="41"/>
+    </row>
+    <row r="45" spans="1:24">
       <c r="L45" s="39"/>
-    </row>
-    <row r="46" spans="1:23">
-      <c r="K46" s="39"/>
+      <c r="M45" s="39"/>
+    </row>
+    <row r="46" spans="1:24">
       <c r="L46" s="39"/>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="K47" s="39"/>
+      <c r="M46" s="39"/>
+    </row>
+    <row r="47" spans="1:24">
       <c r="L47" s="39"/>
-    </row>
-    <row r="48" ht="14.25" spans="1:23">
+      <c r="M47" s="39"/>
+    </row>
+    <row r="48" ht="14.25" spans="1:24">
       <c r="E48" s="42"/>
-      <c r="K48" s="39"/>
       <c r="L48" s="39"/>
-    </row>
-    <row r="49" spans="11:12">
-      <c r="K49" s="39"/>
+      <c r="M48" s="39"/>
+    </row>
+    <row r="49" spans="12:13">
       <c r="L49" s="39"/>
-    </row>
-    <row r="50" spans="11:12">
-      <c r="K50" s="39"/>
+      <c r="M49" s="39"/>
+    </row>
+    <row r="50" spans="12:13">
       <c r="L50" s="39"/>
-    </row>
-    <row r="51" spans="11:12">
-      <c r="K51" s="39"/>
+      <c r="M50" s="39"/>
+    </row>
+    <row r="51" spans="12:13">
       <c r="L51" s="39"/>
-    </row>
-    <row r="52" spans="11:12">
-      <c r="K52" s="39"/>
+      <c r="M51" s="39"/>
+    </row>
+    <row r="52" spans="12:13">
       <c r="L52" s="39"/>
-    </row>
-    <row r="53" spans="11:12">
-      <c r="K53" s="39"/>
+      <c r="M52" s="39"/>
+    </row>
+    <row r="53" spans="12:13">
       <c r="L53" s="39"/>
-    </row>
-    <row r="54" spans="11:12">
-      <c r="K54" s="39"/>
+      <c r="M53" s="39"/>
+    </row>
+    <row r="54" spans="12:13">
       <c r="L54" s="39"/>
-    </row>
-    <row r="55" spans="11:12">
-      <c r="K55" s="39"/>
+      <c r="M54" s="39"/>
+    </row>
+    <row r="55" spans="12:13">
       <c r="L55" s="39"/>
+      <c r="M55" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="W1:W4 D1 D4 U1 U4 L17:L18 L14:L15 L11:L12 L4:L9 A4 L1 A1 W35:W58 W6 W8:W19" formula="1"/>
+    <ignoredError sqref="X8:X19 X6 X35:X58 A1 M1 A4 M4:M9 M11:M12 M14:M15 M17:M18 V4 V1 D4 D1 X1:X4" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -4230,13 +4312,13 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4287,7 +4369,7 @@
         <v>553</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4308,11 +4390,11 @@
     </row>
     <row r="8" ht="15" spans="1:10">
       <c r="A8" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F8">
         <v>1101</v>
@@ -4346,11 +4428,11 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F10">
         <v>1103</v>
@@ -4547,13 +4629,13 @@
         <v>1111</v>
       </c>
       <c r="F27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -4594,13 +4676,13 @@
         <v>1025101_1125101_2</v>
       </c>
       <c r="R30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U30" s="7">
         <v>1025101</v>
       </c>
       <c r="V30" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="2:22">
@@ -4631,13 +4713,13 @@
         <v>1025102_1125102_2</v>
       </c>
       <c r="R31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U31" s="7">
         <v>1025102</v>
       </c>
       <c r="V31" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="2:22">
@@ -4668,13 +4750,13 @@
         <v>1025103_1125103_2</v>
       </c>
       <c r="R32" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U32" s="7">
         <v>1025103</v>
       </c>
       <c r="V32" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="6:22">
@@ -4705,13 +4787,13 @@
         <v>1025201_1125201_4</v>
       </c>
       <c r="R33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U33" s="7">
         <v>1025104</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="6:22">
@@ -4742,13 +4824,13 @@
         <v>1025202_1125202_4</v>
       </c>
       <c r="R34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U34" s="7">
         <v>1025105</v>
       </c>
       <c r="V34" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="6:22">
@@ -4779,13 +4861,13 @@
         <v>1025203_1125203_4</v>
       </c>
       <c r="R35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U35" s="7">
         <v>1025106</v>
       </c>
       <c r="V35" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="6:22">
@@ -4816,13 +4898,13 @@
         <v>1025301_1125301_6</v>
       </c>
       <c r="R36" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U36" s="8">
         <v>1025201</v>
       </c>
       <c r="V36" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="6:22">
@@ -4853,13 +4935,13 @@
         <v>1025302_1125302_6</v>
       </c>
       <c r="R37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U37" s="8">
         <v>1025202</v>
       </c>
       <c r="V37" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="6:22">
@@ -4890,13 +4972,13 @@
         <v>1025303_1125303_6</v>
       </c>
       <c r="R38" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="U38" s="8">
         <v>1025203</v>
       </c>
       <c r="V38" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="6:22">
@@ -4927,13 +5009,13 @@
         <v>1025401_1125401_8</v>
       </c>
       <c r="R39" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U39" s="8">
         <v>1025204</v>
       </c>
       <c r="V39" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="6:22">
@@ -4964,13 +5046,13 @@
         <v>1025402_1125402_8</v>
       </c>
       <c r="R40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U40" s="8">
         <v>1025205</v>
       </c>
       <c r="V40" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="6:22">
@@ -5001,13 +5083,13 @@
         <v>1025403_1125403_8</v>
       </c>
       <c r="R41" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U41" s="8">
         <v>1025206</v>
       </c>
       <c r="V41" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="6:22">
@@ -5038,13 +5120,13 @@
         <v>1025501_1125501_10</v>
       </c>
       <c r="R42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U42" s="7">
         <v>1025301</v>
       </c>
       <c r="V42" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="6:22">
@@ -5075,13 +5157,13 @@
         <v>1025502_1125502_10</v>
       </c>
       <c r="R43" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="U43" s="7">
         <v>1025302</v>
       </c>
       <c r="V43" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="6:22">
@@ -5112,13 +5194,13 @@
         <v>1025503_1125503_10</v>
       </c>
       <c r="R44" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U44" s="7">
         <v>1025303</v>
       </c>
       <c r="V44" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="6:22">
@@ -5149,13 +5231,13 @@
         <v>1025104_1125104_2</v>
       </c>
       <c r="R45" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U45" s="7">
         <v>1025304</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="6:22">
@@ -5186,13 +5268,13 @@
         <v>1025105_1125105_2</v>
       </c>
       <c r="R46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U46" s="7">
         <v>1025305</v>
       </c>
       <c r="V46" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="6:22">
@@ -5223,13 +5305,13 @@
         <v>1025106_1125106_2</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U47" s="7">
         <v>1025306</v>
       </c>
       <c r="V47" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="6:22">
@@ -5260,13 +5342,13 @@
         <v>1025204_1125204_4</v>
       </c>
       <c r="R48" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="U48" s="8">
         <v>1025401</v>
       </c>
       <c r="V48" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="6:22">
@@ -5297,13 +5379,13 @@
         <v>1025205_1125205_4</v>
       </c>
       <c r="R49" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U49" s="8">
         <v>1025402</v>
       </c>
       <c r="V49" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="6:22">
@@ -5334,13 +5416,13 @@
         <v>1025206_1125206_4</v>
       </c>
       <c r="R50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U50" s="8">
         <v>1025403</v>
       </c>
       <c r="V50" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="6:22">
@@ -5371,13 +5453,13 @@
         <v>1025304_1125304_6</v>
       </c>
       <c r="R51" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U51" s="8">
         <v>1025404</v>
       </c>
       <c r="V51" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="6:22">
@@ -5408,13 +5490,13 @@
         <v>1025305_1125305_6</v>
       </c>
       <c r="R52" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U52" s="8">
         <v>1025405</v>
       </c>
       <c r="V52" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="6:22">
@@ -5445,13 +5527,13 @@
         <v>1025306_1125306_6</v>
       </c>
       <c r="R53" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="U53" s="8">
         <v>1025406</v>
       </c>
       <c r="V53" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="6:22">
@@ -5482,13 +5564,13 @@
         <v>1025404_1125404_8</v>
       </c>
       <c r="R54" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="U54" s="7">
         <v>1025501</v>
       </c>
       <c r="V54" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="6:22">
@@ -5519,13 +5601,13 @@
         <v>1025405_1125405_8</v>
       </c>
       <c r="R55" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="U55" s="7">
         <v>1025502</v>
       </c>
       <c r="V55" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="6:22">
@@ -5556,13 +5638,13 @@
         <v>1025406_1125406_8</v>
       </c>
       <c r="R56" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U56" s="7">
         <v>1025503</v>
       </c>
       <c r="V56" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="6:22">
@@ -5593,13 +5675,13 @@
         <v>1025504_1125504_10</v>
       </c>
       <c r="R57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U57" s="7">
         <v>1025504</v>
       </c>
       <c r="V57" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="6:22">
@@ -5630,13 +5712,13 @@
         <v>1025505_1125505_10</v>
       </c>
       <c r="R58" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="U58" s="7">
         <v>1025505</v>
       </c>
       <c r="V58" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="6:22">
@@ -5667,13 +5749,13 @@
         <v>1025506_1125506_10</v>
       </c>
       <c r="R59" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="U59" s="7">
         <v>1025506</v>
       </c>
       <c r="V59" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
